--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javiv\Desktop\APP RAIDIO\raidio-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913F715E-BE57-456A-B007-6C7AC215986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6320A5-6606-43DB-95E2-547968E5166F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="548">
   <si>
     <t>COMUNIDAD AUTÓNOMA</t>
   </si>
@@ -1386,21 +1386,9 @@
     <t>Sigüenza (casco medieval)</t>
   </si>
   <si>
-    <t>"historia", "pueblo", "arquitectura", "cultura", "datosCuriosos"</t>
-  </si>
-  <si>
     <t>"medieval", "catedral", "castillo_parador", "paseo"</t>
   </si>
   <si>
-    <t>es_gua_catedral_siguenca</t>
-  </si>
-  <si>
-    <t>Catedral de Sigüenza</t>
-  </si>
-  <si>
-    <t>"románico", "gótico", "arte_sacro", "doncel"</t>
-  </si>
-  <si>
     <t>es_gua_salinas_imon</t>
   </si>
   <si>
@@ -1675,6 +1663,9 @@
   </si>
   <si>
     <t>"cister","Don Pablo Muntadas Campeny", "cascadas", "jardines", "paseo", "fotografia"</t>
+  </si>
+  <si>
+    <t>"historia","catedral" "pueblo", "arquitectura", "cultura", "datosCuriosos"</t>
   </si>
 </sst>
 </file>
@@ -1789,8 +1780,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{15205B12-B210-4B64-BC1F-9CEC40C7E40E}" name="Tabla1" displayName="Tabla1" ref="A1:P102" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:P102" xr:uid="{15205B12-B210-4B64-BC1F-9CEC40C7E40E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{15205B12-B210-4B64-BC1F-9CEC40C7E40E}" name="Tabla1" displayName="Tabla1" ref="A1:P101" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:P101" xr:uid="{15205B12-B210-4B64-BC1F-9CEC40C7E40E}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{7C559441-5F94-4417-9B95-BABA681BB1C2}" name="COMUNIDAD AUTÓNOMA"/>
     <tableColumn id="2" xr3:uid="{BA71C8BF-EA88-4B52-BDBB-40F9D6E3A906}" name="PROVINCIA"/>
@@ -2076,7 +2067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" customWidth="1"/>
@@ -4849,10 +4840,10 @@
         <v>432</v>
       </c>
       <c r="E63">
-        <v>40.631619999999998</v>
+        <v>40.6314256</v>
       </c>
       <c r="F63">
-        <v>-3.1659600000000001</v>
+        <v>-3.1650391</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -4893,10 +4884,10 @@
         <v>436</v>
       </c>
       <c r="E64">
-        <v>40.632199999999997</v>
+        <v>40.634571200000003</v>
       </c>
       <c r="F64">
-        <v>-3.1623999999999999</v>
+        <v>-3.1652752999999998</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -4937,10 +4928,10 @@
         <v>441</v>
       </c>
       <c r="E65">
-        <v>40.743400000000001</v>
+        <v>40.7431409</v>
       </c>
       <c r="F65">
-        <v>-3.0341999999999998</v>
+        <v>-3.0341528000000002</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -4952,7 +4943,7 @@
         <v>52</v>
       </c>
       <c r="J65">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="K65" t="s">
         <v>53</v>
@@ -4996,7 +4987,7 @@
         <v>107</v>
       </c>
       <c r="J66">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="K66" t="s">
         <v>108</v>
@@ -5069,22 +5060,22 @@
         <v>453</v>
       </c>
       <c r="E68">
-        <v>41.069400000000002</v>
+        <v>41.066618900000002</v>
       </c>
       <c r="F68">
-        <v>-2.6423000000000001</v>
+        <v>-2.6524928000000001</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>454</v>
+        <v>547</v>
       </c>
       <c r="I68" t="s">
         <v>87</v>
       </c>
       <c r="J68">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="K68" t="s">
         <v>82</v>
@@ -5096,7 +5087,7 @@
         <v>150</v>
       </c>
       <c r="N68" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
@@ -5107,40 +5098,40 @@
         <v>427</v>
       </c>
       <c r="C69" t="s">
+        <v>455</v>
+      </c>
+      <c r="D69" t="s">
         <v>456</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69">
+        <v>41.160087500000003</v>
+      </c>
+      <c r="F69">
+        <v>-2.7391866999999999</v>
+      </c>
+      <c r="G69">
+        <v>3</v>
+      </c>
+      <c r="H69" t="s">
         <v>457</v>
       </c>
-      <c r="E69">
-        <v>41.069899999999997</v>
-      </c>
-      <c r="F69">
-        <v>-2.6433</v>
-      </c>
-      <c r="G69">
-        <v>1</v>
-      </c>
-      <c r="H69" t="s">
-        <v>437</v>
-      </c>
       <c r="I69" t="s">
-        <v>391</v>
+        <v>458</v>
       </c>
       <c r="J69">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="K69" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="L69">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="M69">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="N69" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
@@ -5151,37 +5142,37 @@
         <v>427</v>
       </c>
       <c r="C70" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D70" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E70">
-        <v>41.073500000000003</v>
+        <v>41.020507199999997</v>
       </c>
       <c r="F70">
-        <v>-2.5038999999999998</v>
+        <v>-2.5917397000000002</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I70" t="s">
-        <v>462</v>
+        <v>263</v>
       </c>
       <c r="J70">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="K70" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="L70">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="M70">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N70" t="s">
         <v>463</v>
@@ -5201,34 +5192,34 @@
         <v>465</v>
       </c>
       <c r="E71">
-        <v>41.0169</v>
+        <v>41.014848100000002</v>
       </c>
       <c r="F71">
-        <v>-2.6408</v>
+        <v>-2.6333063000000001</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" t="s">
         <v>466</v>
       </c>
       <c r="I71" t="s">
-        <v>263</v>
+        <v>467</v>
       </c>
       <c r="J71">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="K71" t="s">
         <v>27</v>
       </c>
       <c r="L71">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="M71">
         <v>90</v>
       </c>
       <c r="N71" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
@@ -5239,34 +5230,34 @@
         <v>427</v>
       </c>
       <c r="C72" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D72" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E72">
-        <v>41.014899999999997</v>
+        <v>41.035499999999999</v>
       </c>
       <c r="F72">
-        <v>-2.633</v>
+        <v>-2.4670000000000001</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I72" t="s">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="J72">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="K72" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="L72">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="M72">
         <v>90</v>
@@ -5277,46 +5268,46 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="B73" t="s">
-        <v>427</v>
+        <v>301</v>
       </c>
       <c r="C73" t="s">
-        <v>473</v>
+        <v>302</v>
       </c>
       <c r="D73" t="s">
-        <v>474</v>
-      </c>
-      <c r="E73">
-        <v>41.035499999999999</v>
-      </c>
-      <c r="F73">
-        <v>-2.4670000000000001</v>
+        <v>303</v>
+      </c>
+      <c r="E73" s="4">
+        <v>37.779600000000002</v>
+      </c>
+      <c r="F73" s="3">
+        <v>-3.7848999999999999</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>475</v>
+        <v>304</v>
       </c>
       <c r="I73" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="J73">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="K73" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="L73">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="M73">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="N73" t="s">
-        <v>476</v>
+        <v>305</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -5327,40 +5318,40 @@
         <v>301</v>
       </c>
       <c r="C74" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D74" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E74" s="4">
-        <v>37.779600000000002</v>
+        <v>38.399000000000001</v>
       </c>
       <c r="F74" s="3">
-        <v>-3.7848999999999999</v>
+        <v>-3.49</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I74" t="s">
-        <v>20</v>
+        <v>263</v>
       </c>
       <c r="J74">
         <v>9000</v>
       </c>
       <c r="K74" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="L74">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="M74">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="N74" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
@@ -5371,40 +5362,40 @@
         <v>301</v>
       </c>
       <c r="C75" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D75" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E75" s="4">
-        <v>38.399000000000001</v>
+        <v>38.096200000000003</v>
       </c>
       <c r="F75" s="3">
-        <v>-3.49</v>
+        <v>-3.7749999999999999</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>308</v>
+        <v>98</v>
       </c>
       <c r="I75" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="J75">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="K75" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="L75">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="M75">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N75" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
@@ -5415,25 +5406,25 @@
         <v>301</v>
       </c>
       <c r="C76" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D76" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E76" s="4">
-        <v>38.096200000000003</v>
+        <v>38.094999999999999</v>
       </c>
       <c r="F76" s="3">
-        <v>-3.7749999999999999</v>
+        <v>-3.6360000000000001</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" t="s">
-        <v>98</v>
+        <v>316</v>
       </c>
       <c r="I76" t="s">
-        <v>312</v>
+        <v>253</v>
       </c>
       <c r="J76">
         <v>7000</v>
@@ -5442,13 +5433,13 @@
         <v>53</v>
       </c>
       <c r="L76">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M76">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N76" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
@@ -5459,40 +5450,40 @@
         <v>301</v>
       </c>
       <c r="C77" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D77" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E77" s="4">
-        <v>38.094999999999999</v>
+        <v>37.7654</v>
       </c>
       <c r="F77" s="3">
-        <v>-3.6360000000000001</v>
+        <v>-3.7921999999999998</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I77" t="s">
-        <v>253</v>
+        <v>52</v>
       </c>
       <c r="J77">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="K77" t="s">
         <v>53</v>
       </c>
       <c r="L77">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="M77">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N77" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
@@ -5503,40 +5494,40 @@
         <v>301</v>
       </c>
       <c r="C78" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D78" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E78" s="4">
-        <v>37.7654</v>
+        <v>38.011000000000003</v>
       </c>
       <c r="F78" s="3">
-        <v>-3.7921999999999998</v>
+        <v>-3.371</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I78" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="J78">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="K78" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="L78">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="M78">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N78" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
@@ -5547,16 +5538,16 @@
         <v>301</v>
       </c>
       <c r="C79" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D79" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E79" s="4">
-        <v>38.011000000000003</v>
+        <v>37.993000000000002</v>
       </c>
       <c r="F79" s="3">
-        <v>-3.371</v>
+        <v>-3.4689000000000001</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -5580,7 +5571,7 @@
         <v>120</v>
       </c>
       <c r="N79" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
@@ -5591,40 +5582,40 @@
         <v>301</v>
       </c>
       <c r="C80" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D80" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E80" s="4">
-        <v>37.993000000000002</v>
+        <v>38.305300000000003</v>
       </c>
       <c r="F80" s="3">
-        <v>-3.4689000000000001</v>
+        <v>-3.3437000000000001</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="I80" t="s">
-        <v>143</v>
+        <v>331</v>
       </c>
       <c r="J80">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="K80" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="L80">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="M80">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="N80" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
@@ -5635,40 +5626,40 @@
         <v>301</v>
       </c>
       <c r="C81" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D81" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E81" s="4">
-        <v>38.305300000000003</v>
+        <v>38.173499999999997</v>
       </c>
       <c r="F81" s="3">
-        <v>-3.3437000000000001</v>
+        <v>-3.7746</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" t="s">
-        <v>332</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
-        <v>331</v>
+        <v>52</v>
       </c>
       <c r="J81">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="K81" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L81">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="M81">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="N81" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
@@ -5679,40 +5670,40 @@
         <v>301</v>
       </c>
       <c r="C82" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D82" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E82" s="4">
-        <v>38.173499999999997</v>
+        <v>38.275199999999998</v>
       </c>
       <c r="F82" s="3">
-        <v>-3.7746</v>
+        <v>-3.6177999999999999</v>
       </c>
       <c r="G82">
         <v>2</v>
       </c>
       <c r="H82" t="s">
-        <v>63</v>
+        <v>339</v>
       </c>
       <c r="I82" t="s">
-        <v>52</v>
+        <v>248</v>
       </c>
       <c r="J82">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="K82" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="L82">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M82">
         <v>90</v>
       </c>
       <c r="N82" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
@@ -5723,40 +5714,40 @@
         <v>301</v>
       </c>
       <c r="C83" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D83" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E83" s="4">
-        <v>38.275199999999998</v>
+        <v>38.039000000000001</v>
       </c>
       <c r="F83" s="3">
-        <v>-3.6177999999999999</v>
+        <v>-4.0540000000000003</v>
       </c>
       <c r="G83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H83" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I83" t="s">
-        <v>248</v>
+        <v>343</v>
       </c>
       <c r="J83">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="K83" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L83">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="M83">
         <v>90</v>
       </c>
       <c r="N83" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
@@ -5767,40 +5758,40 @@
         <v>301</v>
       </c>
       <c r="C84" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E84" s="4">
-        <v>38.039000000000001</v>
+        <v>37.909999999999997</v>
       </c>
       <c r="F84" s="3">
-        <v>-4.0540000000000003</v>
+        <v>-2.93</v>
       </c>
       <c r="G84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I84" t="s">
-        <v>343</v>
+        <v>263</v>
       </c>
       <c r="J84">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="K84" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="L84">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="M84">
         <v>90</v>
       </c>
       <c r="N84" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
@@ -5811,40 +5802,40 @@
         <v>301</v>
       </c>
       <c r="C85" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E85" s="4">
-        <v>37.909999999999997</v>
+        <v>37.935499999999998</v>
       </c>
       <c r="F85" s="3">
-        <v>-2.93</v>
+        <v>-4.0552000000000001</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I85" t="s">
-        <v>263</v>
+        <v>143</v>
       </c>
       <c r="J85">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="K85" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="L85">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="M85">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="N85" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
@@ -5855,40 +5846,40 @@
         <v>301</v>
       </c>
       <c r="C86" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D86" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E86" s="4">
-        <v>37.935499999999998</v>
+        <v>37.720999999999997</v>
       </c>
       <c r="F86" s="3">
-        <v>-4.0552000000000001</v>
+        <v>-3.9670000000000001</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="I86" t="s">
-        <v>143</v>
+        <v>356</v>
       </c>
       <c r="J86">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="K86" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L86">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M86">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N86" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
@@ -5899,40 +5890,40 @@
         <v>301</v>
       </c>
       <c r="C87" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E87" s="4">
-        <v>37.720999999999997</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3">
-        <v>-3.9670000000000001</v>
+        <v>-3.8</v>
       </c>
       <c r="G87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H87" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="I87" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="J87">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="K87" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="L87">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="M87">
         <v>90</v>
       </c>
       <c r="N87" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
@@ -5940,43 +5931,43 @@
         <v>300</v>
       </c>
       <c r="B88" t="s">
-        <v>301</v>
+        <v>364</v>
       </c>
       <c r="C88" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D88" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E88" s="4">
-        <v>38</v>
+        <v>37.177300000000002</v>
       </c>
       <c r="F88" s="3">
-        <v>-3.8</v>
+        <v>-3.5985999999999998</v>
       </c>
       <c r="G88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>362</v>
+        <v>231</v>
       </c>
       <c r="I88" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="J88">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="K88" t="s">
         <v>82</v>
       </c>
       <c r="L88">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="M88">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="N88" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
@@ -5987,40 +5978,40 @@
         <v>364</v>
       </c>
       <c r="C89" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D89" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E89" s="4">
-        <v>37.177300000000002</v>
+        <v>37.176099999999998</v>
       </c>
       <c r="F89" s="3">
-        <v>-3.5985999999999998</v>
+        <v>-3.5880999999999998</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>231</v>
+        <v>371</v>
       </c>
       <c r="I89" t="s">
-        <v>20</v>
+        <v>370</v>
       </c>
       <c r="J89">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="K89" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="L89">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="M89">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="N89" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
@@ -6031,40 +6022,40 @@
         <v>364</v>
       </c>
       <c r="C90" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D90" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E90" s="4">
-        <v>37.176099999999998</v>
+        <v>37.180599999999998</v>
       </c>
       <c r="F90" s="3">
-        <v>-3.5880999999999998</v>
+        <v>-3.5939999999999999</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="I90" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J90">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="K90" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L90">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="M90">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="N90" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
@@ -6075,40 +6066,40 @@
         <v>364</v>
       </c>
       <c r="C91" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D91" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E91" s="4">
-        <v>37.180599999999998</v>
+        <v>37.094999999999999</v>
       </c>
       <c r="F91" s="3">
-        <v>-3.5939999999999999</v>
+        <v>-3.3940000000000001</v>
       </c>
       <c r="G91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I91" t="s">
-        <v>375</v>
+        <v>263</v>
       </c>
       <c r="J91">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="K91" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="L91">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="M91">
         <v>90</v>
       </c>
       <c r="N91" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
@@ -6119,40 +6110,40 @@
         <v>364</v>
       </c>
       <c r="C92" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D92" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E92" s="4">
-        <v>37.094999999999999</v>
+        <v>37.167999999999999</v>
       </c>
       <c r="F92" s="3">
-        <v>-3.3940000000000001</v>
+        <v>-4.1509999999999998</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="I92" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="J92">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="K92" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="L92">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="M92">
         <v>90</v>
       </c>
       <c r="N92" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
@@ -6163,40 +6154,40 @@
         <v>364</v>
       </c>
       <c r="C93" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D93" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E93" s="4">
-        <v>37.167999999999999</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="F93" s="3">
-        <v>-4.1509999999999998</v>
+        <v>-3.1339999999999999</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H93" t="s">
-        <v>384</v>
+        <v>123</v>
       </c>
       <c r="I93" t="s">
-        <v>248</v>
+        <v>143</v>
       </c>
       <c r="J93">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="K93" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L93">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="M93">
         <v>90</v>
       </c>
       <c r="N93" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
@@ -6207,40 +6198,40 @@
         <v>364</v>
       </c>
       <c r="C94" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D94" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E94" s="4">
-        <v>37.299999999999997</v>
+        <v>37.176400000000001</v>
       </c>
       <c r="F94" s="3">
-        <v>-3.1339999999999999</v>
+        <v>-3.5994999999999999</v>
       </c>
       <c r="G94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>123</v>
+        <v>392</v>
       </c>
       <c r="I94" t="s">
-        <v>143</v>
+        <v>391</v>
       </c>
       <c r="J94">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="K94" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="L94">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="M94">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="N94" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
@@ -6251,40 +6242,40 @@
         <v>364</v>
       </c>
       <c r="C95" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D95" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E95" s="4">
-        <v>37.176400000000001</v>
+        <v>37.183500000000002</v>
       </c>
       <c r="F95" s="3">
-        <v>-3.5994999999999999</v>
+        <v>-3.5857999999999999</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="I95" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J95">
         <v>6000</v>
       </c>
       <c r="K95" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="L95">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="M95">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="N95" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
@@ -6295,40 +6286,40 @@
         <v>364</v>
       </c>
       <c r="C96" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D96" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E96" s="4">
-        <v>37.183500000000002</v>
+        <v>36.833799999999997</v>
       </c>
       <c r="F96" s="3">
-        <v>-3.5857999999999999</v>
+        <v>-3.5169000000000001</v>
       </c>
       <c r="G96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H96" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="I96" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="J96">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="K96" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="L96">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="M96">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N96" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
@@ -6339,40 +6330,40 @@
         <v>364</v>
       </c>
       <c r="C97" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D97" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E97" s="4">
-        <v>36.833799999999997</v>
+        <v>37.342300000000002</v>
       </c>
       <c r="F97" s="3">
-        <v>-3.5169000000000001</v>
+        <v>-3.7860999999999998</v>
       </c>
       <c r="G97">
         <v>3</v>
       </c>
       <c r="H97" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="I97" t="s">
-        <v>401</v>
+        <v>52</v>
       </c>
       <c r="J97">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="K97" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="L97">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="M97">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N97" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
@@ -6383,40 +6374,40 @@
         <v>364</v>
       </c>
       <c r="C98" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D98" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E98" s="4">
-        <v>37.342300000000002</v>
+        <v>36.919400000000003</v>
       </c>
       <c r="F98" s="3">
-        <v>-3.7860999999999998</v>
+        <v>-3.4802</v>
       </c>
       <c r="G98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H98" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I98" t="s">
-        <v>52</v>
+        <v>410</v>
       </c>
       <c r="J98">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="K98" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L98">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="M98">
         <v>90</v>
       </c>
       <c r="N98" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
@@ -6427,40 +6418,40 @@
         <v>364</v>
       </c>
       <c r="C99" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D99" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E99" s="4">
-        <v>36.919400000000003</v>
+        <v>37.219900000000003</v>
       </c>
       <c r="F99" s="3">
-        <v>-3.4802</v>
+        <v>-3.7856000000000001</v>
       </c>
       <c r="G99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H99" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I99" t="s">
-        <v>410</v>
+        <v>107</v>
       </c>
       <c r="J99">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="K99" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="L99">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="M99">
         <v>90</v>
       </c>
       <c r="N99" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
@@ -6471,40 +6462,40 @@
         <v>364</v>
       </c>
       <c r="C100" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D100" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E100" s="4">
-        <v>37.219900000000003</v>
+        <v>37.015099999999997</v>
       </c>
       <c r="F100" s="3">
-        <v>-3.7856000000000001</v>
+        <v>-3.6004999999999998</v>
       </c>
       <c r="G100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H100" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="I100" t="s">
-        <v>107</v>
+        <v>419</v>
       </c>
       <c r="J100">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="K100" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="L100">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="M100">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="N100" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -6515,169 +6506,169 @@
         <v>364</v>
       </c>
       <c r="C101" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D101" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E101" s="4">
-        <v>37.015099999999997</v>
+        <v>37.177300000000002</v>
       </c>
       <c r="F101" s="3">
-        <v>-3.6004999999999998</v>
+        <v>-3.5985999999999998</v>
       </c>
       <c r="G101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H101" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="I101" t="s">
-        <v>419</v>
+        <v>297</v>
       </c>
       <c r="J101">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="K101" t="s">
         <v>53</v>
       </c>
       <c r="L101">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="M101">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="N101" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>300</v>
+        <v>473</v>
       </c>
       <c r="B102" t="s">
-        <v>364</v>
+        <v>474</v>
       </c>
       <c r="C102" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="D102" t="s">
-        <v>423</v>
-      </c>
-      <c r="E102" s="4">
-        <v>37.177300000000002</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-3.5985999999999998</v>
+        <v>476</v>
+      </c>
+      <c r="E102">
+        <v>41.172081499999997</v>
+      </c>
+      <c r="F102">
+        <v>-2.4360339</v>
       </c>
       <c r="G102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>424</v>
+        <v>477</v>
       </c>
       <c r="I102" t="s">
-        <v>297</v>
+        <v>478</v>
       </c>
       <c r="J102">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="K102" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="L102">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="M102">
         <v>180</v>
       </c>
       <c r="N102" t="s">
-        <v>425</v>
+        <v>479</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B103" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C103" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D103" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E103">
-        <v>41.172499999999999</v>
+        <v>41.170754199999998</v>
       </c>
       <c r="F103">
-        <v>-2.4337</v>
+        <v>-2.4350252999999999</v>
       </c>
       <c r="G103">
         <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I103" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J103">
-        <v>9000</v>
+        <v>1500</v>
       </c>
       <c r="K103" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="L103">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="M103">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="N103" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B104" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C104" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D104" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E104">
-        <v>41.172400000000003</v>
+        <v>41.261531099999999</v>
       </c>
       <c r="F104">
-        <v>-2.4331999999999998</v>
+        <v>-2.1794544999999999</v>
       </c>
       <c r="G104">
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I104" t="s">
-        <v>487</v>
+        <v>76</v>
       </c>
       <c r="J104">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="K104" t="s">
         <v>53</v>
       </c>
       <c r="L104">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M104">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="N104" t="s">
         <v>488</v>
@@ -6685,10 +6676,10 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B105" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C105" t="s">
         <v>489</v>
@@ -6697,31 +6688,31 @@
         <v>490</v>
       </c>
       <c r="E105">
-        <v>41.262500000000003</v>
+        <v>41.2149</v>
       </c>
       <c r="F105">
-        <v>-2.1739999999999999</v>
+        <v>-2.2717000000000001</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H105" t="s">
         <v>491</v>
       </c>
       <c r="I105" t="s">
-        <v>76</v>
-      </c>
-      <c r="J105">
-        <v>6000</v>
+        <v>107</v>
+      </c>
+      <c r="J105" s="5">
+        <v>1000</v>
       </c>
       <c r="K105" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L105">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="M105">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="N105" t="s">
         <v>492</v>
@@ -6729,10 +6720,10 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B106" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C106" t="s">
         <v>493</v>
@@ -6741,28 +6732,28 @@
         <v>494</v>
       </c>
       <c r="E106">
-        <v>41.2149</v>
+        <v>41.365000000000002</v>
       </c>
       <c r="F106">
-        <v>-2.2717000000000001</v>
+        <v>-2.17</v>
       </c>
       <c r="G106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H106" t="s">
         <v>495</v>
       </c>
       <c r="I106" t="s">
-        <v>107</v>
-      </c>
-      <c r="J106" s="5">
-        <v>1000</v>
+        <v>127</v>
+      </c>
+      <c r="J106">
+        <v>11000</v>
       </c>
       <c r="K106" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="L106">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="M106">
         <v>90</v>
@@ -6773,175 +6764,175 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="B107" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="C107" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D107" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E107">
-        <v>41.365000000000002</v>
+        <v>41.296700000000001</v>
       </c>
       <c r="F107">
-        <v>-2.17</v>
+        <v>-1.8942000000000001</v>
       </c>
       <c r="G107">
         <v>2</v>
       </c>
       <c r="H107" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="I107" t="s">
-        <v>127</v>
+        <v>502</v>
       </c>
       <c r="J107">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="K107" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="L107">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M107">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="N107" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B108" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C108" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D108" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E108">
-        <v>41.296700000000001</v>
+        <v>41.294850500000003</v>
       </c>
       <c r="F108">
-        <v>-1.8942000000000001</v>
+        <v>-1.9000086</v>
       </c>
       <c r="G108">
         <v>2</v>
       </c>
       <c r="H108" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I108" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J108">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="K108" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="L108">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="M108">
         <v>120</v>
       </c>
       <c r="N108" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B109" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C109" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D109" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E109">
-        <v>41.296100000000003</v>
+        <v>41.329318299999997</v>
       </c>
       <c r="F109">
-        <v>-1.893</v>
+        <v>-1.7997732</v>
       </c>
       <c r="G109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" t="s">
-        <v>510</v>
+        <v>276</v>
       </c>
       <c r="I109" t="s">
+        <v>107</v>
+      </c>
+      <c r="J109">
+        <v>7000</v>
+      </c>
+      <c r="K109" t="s">
+        <v>108</v>
+      </c>
+      <c r="L109">
+        <v>80</v>
+      </c>
+      <c r="M109">
+        <v>90</v>
+      </c>
+      <c r="N109" t="s">
         <v>511</v>
-      </c>
-      <c r="J109">
-        <v>10000</v>
-      </c>
-      <c r="K109" t="s">
-        <v>27</v>
-      </c>
-      <c r="L109">
-        <v>95</v>
-      </c>
-      <c r="M109">
-        <v>120</v>
-      </c>
-      <c r="N109" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B110" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C110" t="s">
+        <v>512</v>
+      </c>
+      <c r="D110" t="s">
         <v>513</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110">
+        <v>41.353999999999999</v>
+      </c>
+      <c r="F110">
+        <v>-1.6426000000000001</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110" t="s">
         <v>514</v>
       </c>
-      <c r="E110">
-        <v>41.331400000000002</v>
-      </c>
-      <c r="F110">
-        <v>-1.7934000000000001</v>
-      </c>
-      <c r="G110">
-        <v>3</v>
-      </c>
-      <c r="H110" t="s">
-        <v>276</v>
-      </c>
       <c r="I110" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="J110">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="K110" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="L110">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="M110">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="N110" t="s">
         <v>515</v>
@@ -6949,10 +6940,10 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B111" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C111" t="s">
         <v>516</v>
@@ -6961,10 +6952,10 @@
         <v>517</v>
       </c>
       <c r="E111">
-        <v>41.353999999999999</v>
+        <v>41.3538</v>
       </c>
       <c r="F111">
-        <v>-1.6426000000000001</v>
+        <v>-1.6465000000000001</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -6973,107 +6964,107 @@
         <v>518</v>
       </c>
       <c r="I111" t="s">
-        <v>143</v>
+        <v>519</v>
       </c>
       <c r="J111">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="K111" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="L111">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="M111">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="N111" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B112" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C112" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D112" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E112">
-        <v>41.3538</v>
+        <v>41.351999999999997</v>
       </c>
       <c r="F112">
-        <v>-1.6465000000000001</v>
+        <v>-1.64</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H112" t="s">
-        <v>522</v>
+        <v>320</v>
       </c>
       <c r="I112" t="s">
-        <v>523</v>
+        <v>52</v>
       </c>
       <c r="J112">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="K112" t="s">
         <v>53</v>
       </c>
       <c r="L112">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="M112">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="N112" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B113" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C113" t="s">
+        <v>524</v>
+      </c>
+      <c r="D113" t="s">
         <v>525</v>
       </c>
-      <c r="D113" t="s">
-        <v>526</v>
-      </c>
       <c r="E113">
-        <v>41.351999999999997</v>
+        <v>41.236635999999997</v>
       </c>
       <c r="F113">
-        <v>-1.64</v>
+        <v>-1.8383977</v>
       </c>
       <c r="G113">
         <v>2</v>
       </c>
       <c r="H113" t="s">
-        <v>320</v>
+        <v>526</v>
       </c>
       <c r="I113" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="J113">
         <v>7000</v>
       </c>
       <c r="K113" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="L113">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M113">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="N113" t="s">
         <v>527</v>
@@ -7081,10 +7072,10 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B114" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C114" t="s">
         <v>528</v>
@@ -7093,28 +7084,28 @@
         <v>529</v>
       </c>
       <c r="E114">
-        <v>41.238</v>
+        <v>41.212000000000003</v>
       </c>
       <c r="F114">
-        <v>-1.8169999999999999</v>
+        <v>-1.7889999999999999</v>
       </c>
       <c r="G114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H114" t="s">
         <v>530</v>
       </c>
       <c r="I114" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="J114">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="K114" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="L114">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="M114">
         <v>90</v>
@@ -7125,10 +7116,10 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B115" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C115" t="s">
         <v>532</v>
@@ -7137,42 +7128,42 @@
         <v>533</v>
       </c>
       <c r="E115">
-        <v>41.212000000000003</v>
+        <v>41.193239599999998</v>
       </c>
       <c r="F115">
-        <v>-1.7889999999999999</v>
+        <v>-1.7851055</v>
       </c>
       <c r="G115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H115" t="s">
         <v>534</v>
       </c>
       <c r="I115" t="s">
-        <v>107</v>
+        <v>535</v>
       </c>
       <c r="J115">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="K115" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="L115">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="M115">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="N115" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B116" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C116" t="s">
         <v>536</v>
@@ -7181,13 +7172,13 @@
         <v>537</v>
       </c>
       <c r="E116">
-        <v>41.212600000000002</v>
+        <v>41.190435700000002</v>
       </c>
       <c r="F116">
-        <v>-1.7895000000000001</v>
+        <v>-1.8872258</v>
       </c>
       <c r="G116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" t="s">
         <v>538</v>
@@ -7196,107 +7187,63 @@
         <v>539</v>
       </c>
       <c r="J116">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="K116" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="L116">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="M116">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="N116" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B117" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C117" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D117" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E117">
-        <v>41.190899999999999</v>
+        <v>41.115099999999998</v>
       </c>
       <c r="F117">
-        <v>-1.8335999999999999</v>
+        <v>-1.4146000000000001</v>
       </c>
       <c r="G117">
         <v>2</v>
       </c>
       <c r="H117" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I117" t="s">
-        <v>543</v>
-      </c>
-      <c r="J117">
-        <v>15000</v>
+        <v>544</v>
+      </c>
+      <c r="J117" s="5">
+        <v>1000</v>
       </c>
       <c r="K117" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="L117">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="M117">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="N117" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>501</v>
-      </c>
-      <c r="B118" t="s">
-        <v>502</v>
-      </c>
-      <c r="C118" t="s">
         <v>545</v>
-      </c>
-      <c r="D118" t="s">
-        <v>546</v>
-      </c>
-      <c r="E118">
-        <v>41.115099999999998</v>
-      </c>
-      <c r="F118">
-        <v>-1.4146000000000001</v>
-      </c>
-      <c r="G118">
-        <v>2</v>
-      </c>
-      <c r="H118" t="s">
-        <v>547</v>
-      </c>
-      <c r="I118" t="s">
-        <v>548</v>
-      </c>
-      <c r="J118" s="5">
-        <v>1000</v>
-      </c>
-      <c r="K118" t="s">
-        <v>82</v>
-      </c>
-      <c r="L118">
-        <v>120</v>
-      </c>
-      <c r="M118">
-        <v>150</v>
-      </c>
-      <c r="N118" t="s">
-        <v>549</v>
       </c>
     </row>
   </sheetData>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javiv\Desktop\APP RAIDIO\raidio-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6320A5-6606-43DB-95E2-547968E5166F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334D1EEA-E4A2-4F9B-8220-FB0B18EB6753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1662,10 +1662,10 @@
     <t>"murallas", "medieval", "paseo", "patrimonio"</t>
   </si>
   <si>
-    <t>"cister","Don Pablo Muntadas Campeny", "cascadas", "jardines", "paseo", "fotografia"</t>
-  </si>
-  <si>
     <t>"historia","catedral" "pueblo", "arquitectura", "cultura", "datosCuriosos"</t>
+  </si>
+  <si>
+    <t>"cister","Desamortizción de Mendizábal","Don Pablo Muntadas Campeny", "cascadas", "jardines", "paseo", "fotografia"</t>
   </si>
 </sst>
 </file>
@@ -5069,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I68" t="s">
         <v>87</v>
@@ -7155,7 +7155,7 @@
         <v>240</v>
       </c>
       <c r="N115" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javiv\Desktop\APP RAIDIO\raidio-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334D1EEA-E4A2-4F9B-8220-FB0B18EB6753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF47CA12-3294-4011-9FE2-7D8ECDC6886E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>"capitalidad", "historia_urbana", "monarquia", "cultura", "museos", "siglo_xvi_xvii"</t>
   </si>
   <si>
-    <t>sponsorId, sponsorNombre, mensaje, url?</t>
-  </si>
-  <si>
     <t>id, titulo, descripcion, startDate, endDate, importancia</t>
   </si>
   <si>
@@ -1666,6 +1663,9 @@
   </si>
   <si>
     <t>"cister","Desamortizción de Mendizábal","Don Pablo Muntadas Campeny", "cascadas", "jardines", "paseo", "fotografia"</t>
+  </si>
+  <si>
+    <t>"…", "Bar Manolo", "un restaurante muy conocido por sus raciones", "https://www.google.com/maps/place/Bernab%C3%A9u/@40.4544295,-3.6877974,17z/data=!3m1!5s0xd4228e2361e11b7:0x67f5c76cf9a0be21!4m6!3m5!1s0xd4228e23705d39f:0xa8fff6d26e2b1988!8m2!3d40.4530196!4d-3.6883748!16zL20vMDFneGx0?entry=ttu&amp;g_ep=EgoyMDI2MDMyMi4wIKXMDSoASAFQAw%3D%3D"</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +2082,7 @@
     <col min="12" max="12" width="10.88671875" customWidth="1"/>
     <col min="13" max="13" width="23.33203125" customWidth="1"/>
     <col min="14" max="14" width="78.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="60.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="48.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2168,7 +2168,7 @@
         <v>12000</v>
       </c>
       <c r="K2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L2">
         <v>130</v>
@@ -2180,10 +2180,10 @@
         <v>21</v>
       </c>
       <c r="O2" t="s">
+        <v>547</v>
+      </c>
+      <c r="P2" t="s">
         <v>22</v>
-      </c>
-      <c r="P2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -2194,10 +2194,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
       </c>
       <c r="E3" s="4">
         <v>40.7849</v>
@@ -2209,16 +2209,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J3">
         <v>12000</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3">
         <v>115</v>
@@ -2227,7 +2227,7 @@
         <v>45</v>
       </c>
       <c r="N3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -2238,10 +2238,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
       </c>
       <c r="E4" s="4">
         <v>40.847999999999999</v>
@@ -2253,16 +2253,16 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J4">
         <v>7500</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4">
         <v>120</v>
@@ -2271,7 +2271,7 @@
         <v>50</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -2282,10 +2282,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
       </c>
       <c r="E5" s="4">
         <v>40.731299999999997</v>
@@ -2297,16 +2297,16 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J5">
         <v>8000</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L5">
         <v>105</v>
@@ -2315,7 +2315,7 @@
         <v>40</v>
       </c>
       <c r="N5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -2326,10 +2326,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
       </c>
       <c r="E6" s="4">
         <v>40.8566</v>
@@ -2341,16 +2341,16 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J6">
         <v>6000</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6">
         <v>95</v>
@@ -2359,7 +2359,7 @@
         <v>45</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -2370,10 +2370,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
         <v>45</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
       </c>
       <c r="E7" s="4">
         <v>41.103323000000003</v>
@@ -2385,16 +2385,16 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J7">
         <v>4000</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L7">
         <v>120</v>
@@ -2403,7 +2403,7 @@
         <v>60</v>
       </c>
       <c r="N7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -2414,10 +2414,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
         <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
       </c>
       <c r="E8" s="4">
         <v>40.727221999999998</v>
@@ -2429,16 +2429,16 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J8">
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L8">
         <v>120</v>
@@ -2447,7 +2447,7 @@
         <v>45</v>
       </c>
       <c r="N8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -2458,10 +2458,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
         <v>56</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
       </c>
       <c r="E9" s="4">
         <v>40.731900000000003</v>
@@ -2473,16 +2473,16 @@
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J9">
         <v>1500</v>
       </c>
       <c r="K9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L9">
         <v>80</v>
@@ -2491,7 +2491,7 @@
         <v>30</v>
       </c>
       <c r="N9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
@@ -2502,10 +2502,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
         <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
       </c>
       <c r="E10" s="4">
         <v>40.363700000000001</v>
@@ -2517,16 +2517,16 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J10">
         <v>3500</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L10">
         <v>105</v>
@@ -2535,7 +2535,7 @@
         <v>40</v>
       </c>
       <c r="N10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -2546,10 +2546,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
         <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>66</v>
       </c>
       <c r="E11" s="4">
         <v>40.993699999999997</v>
@@ -2561,16 +2561,16 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J11">
         <v>2500</v>
       </c>
       <c r="K11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L11">
         <v>110</v>
@@ -2579,7 +2579,7 @@
         <v>40</v>
       </c>
       <c r="N11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -2590,10 +2590,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
         <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>71</v>
       </c>
       <c r="E12" s="4">
         <v>40.641910299999999</v>
@@ -2605,16 +2605,16 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J12">
         <v>8000</v>
       </c>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L12">
         <v>125</v>
@@ -2623,7 +2623,7 @@
         <v>90</v>
       </c>
       <c r="N12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
@@ -2634,10 +2634,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
         <v>74</v>
-      </c>
-      <c r="D13" t="s">
-        <v>75</v>
       </c>
       <c r="E13" s="4">
         <v>40.590105000000001</v>
@@ -2649,16 +2649,16 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J13">
         <v>5000</v>
       </c>
       <c r="K13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L13">
         <v>130</v>
@@ -2667,7 +2667,7 @@
         <v>90</v>
       </c>
       <c r="N13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -2678,10 +2678,10 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
         <v>79</v>
-      </c>
-      <c r="D14" t="s">
-        <v>80</v>
       </c>
       <c r="E14" s="4">
         <v>40.031010000000002</v>
@@ -2693,16 +2693,16 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J14">
         <v>7000</v>
       </c>
       <c r="K14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L14">
         <v>120</v>
@@ -2711,7 +2711,7 @@
         <v>60</v>
       </c>
       <c r="N14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -2722,10 +2722,10 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
         <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
       </c>
       <c r="E15" s="4">
         <v>40.481979000000003</v>
@@ -2737,16 +2737,16 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J15">
         <v>6000</v>
       </c>
       <c r="K15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L15">
         <v>125</v>
@@ -2755,7 +2755,7 @@
         <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
@@ -2766,10 +2766,10 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
         <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>91</v>
       </c>
       <c r="E16" s="4">
         <v>40.482930000000003</v>
@@ -2781,16 +2781,16 @@
         <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J16">
         <v>3500</v>
       </c>
       <c r="K16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L16">
         <v>105</v>
@@ -2799,7 +2799,7 @@
         <v>45</v>
       </c>
       <c r="N16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2810,10 +2810,10 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
         <v>95</v>
-      </c>
-      <c r="D17" t="s">
-        <v>96</v>
       </c>
       <c r="E17" s="4">
         <v>41.1325</v>
@@ -2825,16 +2825,16 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J17">
         <v>5000</v>
       </c>
       <c r="K17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L17">
         <v>140</v>
@@ -2843,7 +2843,7 @@
         <v>80</v>
       </c>
       <c r="N17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -2854,10 +2854,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
         <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>101</v>
       </c>
       <c r="E18" s="4">
         <v>40.405900000000003</v>
@@ -2869,16 +2869,16 @@
         <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J18">
         <v>4000</v>
       </c>
       <c r="K18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L18">
         <v>125</v>
@@ -2887,7 +2887,7 @@
         <v>90</v>
       </c>
       <c r="N18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -2898,10 +2898,10 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
         <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>106</v>
       </c>
       <c r="E19" s="4">
         <v>40.140267000000001</v>
@@ -2913,16 +2913,16 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J19">
         <v>8000</v>
       </c>
       <c r="K19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L19">
         <v>95</v>
@@ -2931,7 +2931,7 @@
         <v>40</v>
       </c>
       <c r="N19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -2942,10 +2942,10 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
         <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>112</v>
       </c>
       <c r="E20" s="4">
         <v>40.904400000000003</v>
@@ -2957,16 +2957,16 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J20">
         <v>3000</v>
       </c>
       <c r="K20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L20">
         <v>105</v>
@@ -2975,7 +2975,7 @@
         <v>45</v>
       </c>
       <c r="N20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -2986,10 +2986,10 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" t="s">
         <v>116</v>
-      </c>
-      <c r="D21" t="s">
-        <v>117</v>
       </c>
       <c r="E21" s="4">
         <v>40.857500000000002</v>
@@ -3001,16 +3001,16 @@
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J21">
         <v>1800</v>
       </c>
       <c r="K21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L21">
         <v>80</v>
@@ -3019,7 +3019,7 @@
         <v>35</v>
       </c>
       <c r="N21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -3030,10 +3030,10 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" t="s">
         <v>120</v>
-      </c>
-      <c r="D22" t="s">
-        <v>121</v>
       </c>
       <c r="E22" s="4">
         <v>40.3675</v>
@@ -3045,16 +3045,16 @@
         <v>3</v>
       </c>
       <c r="H22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J22">
         <v>1800</v>
       </c>
       <c r="K22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L22">
         <v>85</v>
@@ -3063,7 +3063,7 @@
         <v>40</v>
       </c>
       <c r="N22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -3074,10 +3074,10 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
         <v>125</v>
-      </c>
-      <c r="D23" t="s">
-        <v>126</v>
       </c>
       <c r="E23" s="4">
         <v>40.7194</v>
@@ -3089,16 +3089,16 @@
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J23">
         <v>6000</v>
       </c>
       <c r="K23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L23">
         <v>80</v>
@@ -3107,7 +3107,7 @@
         <v>35</v>
       </c>
       <c r="N23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -3118,10 +3118,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" t="s">
         <v>130</v>
-      </c>
-      <c r="D24" t="s">
-        <v>131</v>
       </c>
       <c r="E24" s="4">
         <v>40.8797</v>
@@ -3133,16 +3133,16 @@
         <v>3</v>
       </c>
       <c r="H24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J24">
         <v>1500</v>
       </c>
       <c r="K24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L24">
         <v>75</v>
@@ -3151,21 +3151,21 @@
         <v>30</v>
       </c>
       <c r="N24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
         <v>135</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>136</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>137</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
       </c>
       <c r="E25" s="4">
         <v>39.8568</v>
@@ -3177,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I25" t="s">
         <v>20</v>
@@ -3186,7 +3186,7 @@
         <v>10000</v>
       </c>
       <c r="K25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L25">
         <v>135</v>
@@ -3195,21 +3195,21 @@
         <v>120</v>
       </c>
       <c r="N25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
         <v>135</v>
       </c>
-      <c r="B26" t="s">
-        <v>136</v>
-      </c>
       <c r="C26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" t="s">
         <v>141</v>
-      </c>
-      <c r="D26" t="s">
-        <v>142</v>
       </c>
       <c r="E26" s="4">
         <v>39.8568</v>
@@ -3221,16 +3221,16 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J26">
         <v>8000</v>
       </c>
       <c r="K26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L26">
         <v>140</v>
@@ -3239,21 +3239,21 @@
         <v>90</v>
       </c>
       <c r="N26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
         <v>135</v>
       </c>
-      <c r="B27" t="s">
-        <v>136</v>
-      </c>
       <c r="C27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" t="s">
         <v>146</v>
-      </c>
-      <c r="D27" t="s">
-        <v>147</v>
       </c>
       <c r="E27" s="4">
         <v>39.857300000000002</v>
@@ -3265,16 +3265,16 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J27">
         <v>4500</v>
       </c>
       <c r="K27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L27">
         <v>135</v>
@@ -3283,21 +3283,21 @@
         <v>90</v>
       </c>
       <c r="N27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" t="s">
         <v>135</v>
       </c>
-      <c r="B28" t="s">
-        <v>136</v>
-      </c>
       <c r="C28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" t="s">
         <v>151</v>
-      </c>
-      <c r="D28" t="s">
-        <v>152</v>
       </c>
       <c r="E28" s="4">
         <v>39.857959999999999</v>
@@ -3309,16 +3309,16 @@
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J28">
         <v>3000</v>
       </c>
       <c r="K28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L28">
         <v>105</v>
@@ -3327,21 +3327,21 @@
         <v>45</v>
       </c>
       <c r="N28" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" t="s">
         <v>135</v>
       </c>
-      <c r="B29" t="s">
-        <v>136</v>
-      </c>
       <c r="C29" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" t="s">
         <v>156</v>
-      </c>
-      <c r="D29" t="s">
-        <v>157</v>
       </c>
       <c r="E29" s="4">
         <v>39.858899999999998</v>
@@ -3353,16 +3353,16 @@
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J29">
         <v>2500</v>
       </c>
       <c r="K29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -3371,21 +3371,21 @@
         <v>45</v>
       </c>
       <c r="N29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" t="s">
         <v>135</v>
       </c>
-      <c r="B30" t="s">
-        <v>136</v>
-      </c>
       <c r="C30" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" t="s">
         <v>160</v>
-      </c>
-      <c r="D30" t="s">
-        <v>161</v>
       </c>
       <c r="E30" s="4">
         <v>39.457900000000002</v>
@@ -3397,16 +3397,16 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J30">
         <v>10500</v>
       </c>
       <c r="K30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L30">
         <v>125</v>
@@ -3415,21 +3415,21 @@
         <v>70</v>
       </c>
       <c r="N30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" t="s">
         <v>135</v>
       </c>
-      <c r="B31" t="s">
-        <v>136</v>
-      </c>
       <c r="C31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" t="s">
         <v>165</v>
-      </c>
-      <c r="D31" t="s">
-        <v>166</v>
       </c>
       <c r="E31" s="4">
         <v>39.463099999999997</v>
@@ -3441,16 +3441,16 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J31">
         <v>5000</v>
       </c>
       <c r="K31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L31">
         <v>120</v>
@@ -3459,21 +3459,21 @@
         <v>60</v>
       </c>
       <c r="N31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" t="s">
         <v>135</v>
       </c>
-      <c r="B32" t="s">
-        <v>136</v>
-      </c>
       <c r="C32" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" t="s">
         <v>169</v>
-      </c>
-      <c r="D32" t="s">
-        <v>170</v>
       </c>
       <c r="E32" s="4">
         <v>39.647300000000001</v>
@@ -3485,16 +3485,16 @@
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J32">
         <v>5000</v>
       </c>
       <c r="K32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -3503,21 +3503,21 @@
         <v>45</v>
       </c>
       <c r="N32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" t="s">
         <v>135</v>
       </c>
-      <c r="B33" t="s">
-        <v>136</v>
-      </c>
       <c r="C33" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" t="s">
         <v>173</v>
-      </c>
-      <c r="D33" t="s">
-        <v>174</v>
       </c>
       <c r="E33" s="4">
         <v>40.167700000000004</v>
@@ -3529,16 +3529,16 @@
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J33">
         <v>3000</v>
       </c>
       <c r="K33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L33">
         <v>105</v>
@@ -3547,21 +3547,21 @@
         <v>45</v>
       </c>
       <c r="N33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" t="s">
         <v>135</v>
       </c>
-      <c r="B34" t="s">
-        <v>136</v>
-      </c>
       <c r="C34" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" t="s">
         <v>176</v>
-      </c>
-      <c r="D34" t="s">
-        <v>177</v>
       </c>
       <c r="E34" s="4">
         <v>39.894799999999996</v>
@@ -3573,16 +3573,16 @@
         <v>3</v>
       </c>
       <c r="H34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J34">
         <v>2000</v>
       </c>
       <c r="K34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L34">
         <v>80</v>
@@ -3591,21 +3591,21 @@
         <v>35</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" t="s">
         <v>135</v>
       </c>
-      <c r="B35" t="s">
-        <v>136</v>
-      </c>
       <c r="C35" t="s">
+        <v>178</v>
+      </c>
+      <c r="D35" t="s">
         <v>179</v>
-      </c>
-      <c r="D35" t="s">
-        <v>180</v>
       </c>
       <c r="E35" s="4">
         <v>39.966700000000003</v>
@@ -3617,16 +3617,16 @@
         <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J35">
         <v>2000</v>
       </c>
       <c r="K35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L35">
         <v>85</v>
@@ -3635,21 +3635,21 @@
         <v>45</v>
       </c>
       <c r="N35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" t="s">
         <v>135</v>
       </c>
-      <c r="B36" t="s">
-        <v>136</v>
-      </c>
       <c r="C36" t="s">
+        <v>183</v>
+      </c>
+      <c r="D36" t="s">
         <v>184</v>
-      </c>
-      <c r="D36" t="s">
-        <v>185</v>
       </c>
       <c r="E36" s="4">
         <v>39.961399999999998</v>
@@ -3661,16 +3661,16 @@
         <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J36">
         <v>2500</v>
       </c>
       <c r="K36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L36">
         <v>95</v>
@@ -3679,21 +3679,21 @@
         <v>45</v>
       </c>
       <c r="N36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" t="s">
         <v>135</v>
       </c>
-      <c r="B37" t="s">
-        <v>136</v>
-      </c>
       <c r="C37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" t="s">
         <v>188</v>
-      </c>
-      <c r="D37" t="s">
-        <v>189</v>
       </c>
       <c r="E37" s="4">
         <v>39.959000000000003</v>
@@ -3705,16 +3705,16 @@
         <v>3</v>
       </c>
       <c r="H37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J37">
         <v>2000</v>
       </c>
       <c r="K37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L37">
         <v>85</v>
@@ -3723,21 +3723,21 @@
         <v>45</v>
       </c>
       <c r="N37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" t="s">
         <v>135</v>
       </c>
-      <c r="B38" t="s">
-        <v>136</v>
-      </c>
       <c r="C38" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" t="s">
         <v>193</v>
-      </c>
-      <c r="D38" t="s">
-        <v>194</v>
       </c>
       <c r="E38" s="4">
         <v>39.760899999999999</v>
@@ -3749,16 +3749,16 @@
         <v>3</v>
       </c>
       <c r="H38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J38">
         <v>2000</v>
       </c>
       <c r="K38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L38">
         <v>80</v>
@@ -3767,21 +3767,21 @@
         <v>35</v>
       </c>
       <c r="N38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" t="s">
         <v>135</v>
       </c>
-      <c r="B39" t="s">
-        <v>136</v>
-      </c>
       <c r="C39" t="s">
+        <v>195</v>
+      </c>
+      <c r="D39" t="s">
         <v>196</v>
-      </c>
-      <c r="D39" t="s">
-        <v>197</v>
       </c>
       <c r="E39" s="4">
         <v>39.880299999999998</v>
@@ -3793,16 +3793,16 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J39">
         <v>5000</v>
       </c>
       <c r="K39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L39">
         <v>120</v>
@@ -3811,21 +3811,21 @@
         <v>50</v>
       </c>
       <c r="N39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" t="s">
         <v>135</v>
       </c>
-      <c r="B40" t="s">
-        <v>136</v>
-      </c>
       <c r="C40" t="s">
+        <v>200</v>
+      </c>
+      <c r="D40" t="s">
         <v>201</v>
-      </c>
-      <c r="D40" t="s">
-        <v>202</v>
       </c>
       <c r="E40" s="4">
         <v>39.674399999999999</v>
@@ -3837,16 +3837,16 @@
         <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J40">
         <v>2500</v>
       </c>
       <c r="K40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L40">
         <v>110</v>
@@ -3855,21 +3855,21 @@
         <v>60</v>
       </c>
       <c r="N40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" t="s">
         <v>135</v>
       </c>
-      <c r="B41" t="s">
-        <v>136</v>
-      </c>
       <c r="C41" t="s">
+        <v>205</v>
+      </c>
+      <c r="D41" t="s">
         <v>206</v>
-      </c>
-      <c r="D41" t="s">
-        <v>207</v>
       </c>
       <c r="E41" s="4">
         <v>39.970100000000002</v>
@@ -3881,16 +3881,16 @@
         <v>3</v>
       </c>
       <c r="H41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J41">
         <v>2000</v>
       </c>
       <c r="K41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L41">
         <v>80</v>
@@ -3899,21 +3899,21 @@
         <v>45</v>
       </c>
       <c r="N41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" t="s">
         <v>135</v>
       </c>
-      <c r="B42" t="s">
-        <v>136</v>
-      </c>
       <c r="C42" t="s">
+        <v>210</v>
+      </c>
+      <c r="D42" t="s">
         <v>211</v>
-      </c>
-      <c r="D42" t="s">
-        <v>212</v>
       </c>
       <c r="E42" s="4">
         <v>39.511299999999999</v>
@@ -3925,16 +3925,16 @@
         <v>3</v>
       </c>
       <c r="H42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J42">
         <v>1500</v>
       </c>
       <c r="K42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L42">
         <v>75</v>
@@ -3943,21 +3943,21 @@
         <v>45</v>
       </c>
       <c r="N42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" t="s">
         <v>135</v>
       </c>
-      <c r="B43" t="s">
-        <v>136</v>
-      </c>
       <c r="C43" t="s">
+        <v>215</v>
+      </c>
+      <c r="D43" t="s">
         <v>216</v>
-      </c>
-      <c r="D43" t="s">
-        <v>217</v>
       </c>
       <c r="E43" s="4">
         <v>39.598500000000001</v>
@@ -3969,16 +3969,16 @@
         <v>3</v>
       </c>
       <c r="H43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J43">
         <v>2000</v>
       </c>
       <c r="K43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L43">
         <v>80</v>
@@ -3987,21 +3987,21 @@
         <v>35</v>
       </c>
       <c r="N43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" t="s">
         <v>135</v>
       </c>
-      <c r="B44" t="s">
-        <v>136</v>
-      </c>
       <c r="C44" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" t="s">
         <v>218</v>
-      </c>
-      <c r="D44" t="s">
-        <v>219</v>
       </c>
       <c r="E44" s="4">
         <v>39.512700000000002</v>
@@ -4013,16 +4013,16 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J44">
         <v>4500</v>
       </c>
       <c r="K44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L44">
         <v>105</v>
@@ -4031,21 +4031,21 @@
         <v>45</v>
       </c>
       <c r="N44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" t="s">
         <v>135</v>
       </c>
-      <c r="B45" t="s">
-        <v>136</v>
-      </c>
       <c r="C45" t="s">
+        <v>222</v>
+      </c>
+      <c r="D45" t="s">
         <v>223</v>
-      </c>
-      <c r="D45" t="s">
-        <v>224</v>
       </c>
       <c r="E45" s="4">
         <v>39.432600000000001</v>
@@ -4057,16 +4057,16 @@
         <v>3</v>
       </c>
       <c r="H45" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J45">
         <v>1500</v>
       </c>
       <c r="K45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L45">
         <v>75</v>
@@ -4075,21 +4075,21 @@
         <v>45</v>
       </c>
       <c r="N45" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B46" t="s">
+        <v>227</v>
+      </c>
+      <c r="C46" t="s">
         <v>228</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>229</v>
-      </c>
-      <c r="D46" t="s">
-        <v>230</v>
       </c>
       <c r="E46" s="4">
         <v>38.9848</v>
@@ -4101,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
@@ -4110,7 +4110,7 @@
         <v>9000</v>
       </c>
       <c r="K46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L46">
         <v>125</v>
@@ -4119,21 +4119,21 @@
         <v>120</v>
       </c>
       <c r="N46" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" t="s">
         <v>233</v>
-      </c>
-      <c r="D47" t="s">
-        <v>234</v>
       </c>
       <c r="E47" s="4">
         <v>38.889400000000002</v>
@@ -4145,16 +4145,16 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I47" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J47">
         <v>6000</v>
       </c>
       <c r="K47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L47">
         <v>120</v>
@@ -4163,21 +4163,21 @@
         <v>60</v>
       </c>
       <c r="N47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C48" t="s">
+        <v>237</v>
+      </c>
+      <c r="D48" t="s">
         <v>238</v>
-      </c>
-      <c r="D48" t="s">
-        <v>239</v>
       </c>
       <c r="E48" s="4">
         <v>39.145099999999999</v>
@@ -4189,16 +4189,16 @@
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J48">
         <v>8000</v>
       </c>
       <c r="K48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L48">
         <v>125</v>
@@ -4207,21 +4207,21 @@
         <v>60</v>
       </c>
       <c r="N48" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B49" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C49" t="s">
+        <v>241</v>
+      </c>
+      <c r="D49" t="s">
         <v>242</v>
-      </c>
-      <c r="D49" t="s">
-        <v>243</v>
       </c>
       <c r="E49" s="4">
         <v>38.7956</v>
@@ -4233,16 +4233,16 @@
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J49">
         <v>5000</v>
       </c>
       <c r="K49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L49">
         <v>120</v>
@@ -4251,21 +4251,21 @@
         <v>60</v>
       </c>
       <c r="N49" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C50" t="s">
+        <v>245</v>
+      </c>
+      <c r="D50" t="s">
         <v>246</v>
-      </c>
-      <c r="D50" t="s">
-        <v>247</v>
       </c>
       <c r="E50" s="4">
         <v>38.762099999999997</v>
@@ -4277,16 +4277,16 @@
         <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J50">
         <v>7000</v>
       </c>
       <c r="K50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L50">
         <v>105</v>
@@ -4295,21 +4295,21 @@
         <v>50</v>
       </c>
       <c r="N50" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D51" t="s">
         <v>251</v>
-      </c>
-      <c r="D51" t="s">
-        <v>252</v>
       </c>
       <c r="E51" s="4">
         <v>38.687899999999999</v>
@@ -4321,16 +4321,16 @@
         <v>3</v>
       </c>
       <c r="H51" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J51">
         <v>7000</v>
       </c>
       <c r="K51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L51">
         <v>85</v>
@@ -4339,21 +4339,21 @@
         <v>60</v>
       </c>
       <c r="N51" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D52" t="s">
         <v>256</v>
-      </c>
-      <c r="D52" t="s">
-        <v>257</v>
       </c>
       <c r="E52" s="4">
         <v>38.523000000000003</v>
@@ -4365,16 +4365,16 @@
         <v>3</v>
       </c>
       <c r="H52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I52" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J52">
         <v>4000</v>
       </c>
       <c r="K52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L52">
         <v>90</v>
@@ -4383,21 +4383,21 @@
         <v>60</v>
       </c>
       <c r="N52" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C53" t="s">
+        <v>260</v>
+      </c>
+      <c r="D53" t="s">
         <v>261</v>
-      </c>
-      <c r="D53" t="s">
-        <v>262</v>
       </c>
       <c r="E53" s="4">
         <v>38.951000000000001</v>
@@ -4409,16 +4409,16 @@
         <v>2</v>
       </c>
       <c r="H53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J53">
         <v>9000</v>
       </c>
       <c r="K53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L53">
         <v>115</v>
@@ -4427,21 +4427,21 @@
         <v>60</v>
       </c>
       <c r="N53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54" t="s">
         <v>266</v>
-      </c>
-      <c r="D54" t="s">
-        <v>267</v>
       </c>
       <c r="E54" s="4">
         <v>38.999299999999998</v>
@@ -4453,16 +4453,16 @@
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I54" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J54">
         <v>7000</v>
       </c>
       <c r="K54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L54">
         <v>95</v>
@@ -4471,21 +4471,21 @@
         <v>60</v>
       </c>
       <c r="N54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D55" t="s">
         <v>270</v>
-      </c>
-      <c r="D55" t="s">
-        <v>271</v>
       </c>
       <c r="E55" s="4">
         <v>39.324399999999997</v>
@@ -4497,16 +4497,16 @@
         <v>2</v>
       </c>
       <c r="H55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J55">
         <v>6000</v>
       </c>
       <c r="K55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L55">
         <v>110</v>
@@ -4515,21 +4515,21 @@
         <v>60</v>
       </c>
       <c r="N55" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C56" t="s">
+        <v>273</v>
+      </c>
+      <c r="D56" t="s">
         <v>274</v>
-      </c>
-      <c r="D56" t="s">
-        <v>275</v>
       </c>
       <c r="E56" s="4">
         <v>38.737299999999998</v>
@@ -4541,16 +4541,16 @@
         <v>2</v>
       </c>
       <c r="H56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J56">
         <v>6000</v>
       </c>
       <c r="K56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L56">
         <v>100</v>
@@ -4559,21 +4559,21 @@
         <v>60</v>
       </c>
       <c r="N56" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C57" t="s">
+        <v>277</v>
+      </c>
+      <c r="D57" t="s">
         <v>278</v>
-      </c>
-      <c r="D57" t="s">
-        <v>279</v>
       </c>
       <c r="E57" s="4">
         <v>39.033999999999999</v>
@@ -4585,16 +4585,16 @@
         <v>3</v>
       </c>
       <c r="H57" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I57" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J57">
         <v>4000</v>
       </c>
       <c r="K57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L57">
         <v>90</v>
@@ -4603,21 +4603,21 @@
         <v>90</v>
       </c>
       <c r="N57" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B58" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C58" t="s">
+        <v>282</v>
+      </c>
+      <c r="D58" t="s">
         <v>283</v>
-      </c>
-      <c r="D58" t="s">
-        <v>284</v>
       </c>
       <c r="E58" s="4">
         <v>38.906300000000002</v>
@@ -4629,16 +4629,16 @@
         <v>3</v>
       </c>
       <c r="H58" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J58">
         <v>4000</v>
       </c>
       <c r="K58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L58">
         <v>85</v>
@@ -4647,21 +4647,21 @@
         <v>60</v>
       </c>
       <c r="N58" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C59" t="s">
+        <v>285</v>
+      </c>
+      <c r="D59" t="s">
         <v>286</v>
-      </c>
-      <c r="D59" t="s">
-        <v>287</v>
       </c>
       <c r="E59" s="4">
         <v>39.308700000000002</v>
@@ -4673,16 +4673,16 @@
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J59">
         <v>12000</v>
       </c>
       <c r="K59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L59">
         <v>125</v>
@@ -4691,21 +4691,21 @@
         <v>60</v>
       </c>
       <c r="N59" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B60" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C60" t="s">
+        <v>289</v>
+      </c>
+      <c r="D60" t="s">
         <v>290</v>
-      </c>
-      <c r="D60" t="s">
-        <v>291</v>
       </c>
       <c r="E60" s="4">
         <v>38.945999999999998</v>
@@ -4717,16 +4717,16 @@
         <v>2</v>
       </c>
       <c r="H60" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J60">
         <v>9000</v>
       </c>
       <c r="K60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L60">
         <v>120</v>
@@ -4735,21 +4735,21 @@
         <v>60</v>
       </c>
       <c r="N60" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C61" t="s">
+        <v>294</v>
+      </c>
+      <c r="D61" t="s">
         <v>295</v>
-      </c>
-      <c r="D61" t="s">
-        <v>296</v>
       </c>
       <c r="E61" s="4">
         <v>38.889400000000002</v>
@@ -4761,16 +4761,16 @@
         <v>3</v>
       </c>
       <c r="H61" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I61" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J61">
         <v>8000</v>
       </c>
       <c r="K61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L61">
         <v>95</v>
@@ -4779,21 +4779,21 @@
         <v>90</v>
       </c>
       <c r="N61" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
+        <v>426</v>
+      </c>
+      <c r="C62" t="s">
         <v>427</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>428</v>
-      </c>
-      <c r="D62" t="s">
-        <v>429</v>
       </c>
       <c r="E62">
         <v>40.633330000000001</v>
@@ -4805,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
@@ -4814,7 +4814,7 @@
         <v>9000</v>
       </c>
       <c r="K62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L62">
         <v>125</v>
@@ -4823,21 +4823,21 @@
         <v>120</v>
       </c>
       <c r="N62" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B63" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C63" t="s">
+        <v>430</v>
+      </c>
+      <c r="D63" t="s">
         <v>431</v>
-      </c>
-      <c r="D63" t="s">
-        <v>432</v>
       </c>
       <c r="E63">
         <v>40.6314256</v>
@@ -4849,16 +4849,16 @@
         <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J63">
         <v>5000</v>
       </c>
       <c r="K63" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L63">
         <v>130</v>
@@ -4867,21 +4867,21 @@
         <v>120</v>
       </c>
       <c r="N63" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B64" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C64" t="s">
+        <v>434</v>
+      </c>
+      <c r="D64" t="s">
         <v>435</v>
-      </c>
-      <c r="D64" t="s">
-        <v>436</v>
       </c>
       <c r="E64">
         <v>40.634571200000003</v>
@@ -4893,16 +4893,16 @@
         <v>2</v>
       </c>
       <c r="H64" t="s">
+        <v>436</v>
+      </c>
+      <c r="I64" t="s">
         <v>437</v>
-      </c>
-      <c r="I64" t="s">
-        <v>438</v>
       </c>
       <c r="J64">
         <v>4000</v>
       </c>
       <c r="K64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L64">
         <v>95</v>
@@ -4911,21 +4911,21 @@
         <v>90</v>
       </c>
       <c r="N64" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B65" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C65" t="s">
+        <v>439</v>
+      </c>
+      <c r="D65" t="s">
         <v>440</v>
-      </c>
-      <c r="D65" t="s">
-        <v>441</v>
       </c>
       <c r="E65">
         <v>40.7431409</v>
@@ -4937,16 +4937,16 @@
         <v>2</v>
       </c>
       <c r="H65" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J65">
         <v>3000</v>
       </c>
       <c r="K65" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L65">
         <v>110</v>
@@ -4955,21 +4955,21 @@
         <v>90</v>
       </c>
       <c r="N65" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B66" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C66" t="s">
+        <v>443</v>
+      </c>
+      <c r="D66" t="s">
         <v>444</v>
-      </c>
-      <c r="D66" t="s">
-        <v>445</v>
       </c>
       <c r="E66">
         <v>40.759700000000002</v>
@@ -4981,16 +4981,16 @@
         <v>2</v>
       </c>
       <c r="H66" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J66">
         <v>11000</v>
       </c>
       <c r="K66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L66">
         <v>100</v>
@@ -4999,21 +4999,21 @@
         <v>90</v>
       </c>
       <c r="N66" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B67" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C67" t="s">
+        <v>447</v>
+      </c>
+      <c r="D67" t="s">
         <v>448</v>
-      </c>
-      <c r="D67" t="s">
-        <v>449</v>
       </c>
       <c r="E67">
         <v>40.417000000000002</v>
@@ -5025,16 +5025,16 @@
         <v>3</v>
       </c>
       <c r="H67" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I67" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J67">
         <v>12000</v>
       </c>
       <c r="K67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L67">
         <v>85</v>
@@ -5043,21 +5043,21 @@
         <v>120</v>
       </c>
       <c r="N67" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B68" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C68" t="s">
+        <v>451</v>
+      </c>
+      <c r="D68" t="s">
         <v>452</v>
-      </c>
-      <c r="D68" t="s">
-        <v>453</v>
       </c>
       <c r="E68">
         <v>41.066618900000002</v>
@@ -5069,16 +5069,16 @@
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J68">
         <v>11000</v>
       </c>
       <c r="K68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L68">
         <v>140</v>
@@ -5087,21 +5087,21 @@
         <v>150</v>
       </c>
       <c r="N68" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C69" t="s">
+        <v>454</v>
+      </c>
+      <c r="D69" t="s">
         <v>455</v>
-      </c>
-      <c r="D69" t="s">
-        <v>456</v>
       </c>
       <c r="E69">
         <v>41.160087500000003</v>
@@ -5113,16 +5113,16 @@
         <v>3</v>
       </c>
       <c r="H69" t="s">
+        <v>456</v>
+      </c>
+      <c r="I69" t="s">
         <v>457</v>
-      </c>
-      <c r="I69" t="s">
-        <v>458</v>
       </c>
       <c r="J69">
         <v>3000</v>
       </c>
       <c r="K69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L69">
         <v>80</v>
@@ -5131,21 +5131,21 @@
         <v>120</v>
       </c>
       <c r="N69" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C70" t="s">
+        <v>459</v>
+      </c>
+      <c r="D70" t="s">
         <v>460</v>
-      </c>
-      <c r="D70" t="s">
-        <v>461</v>
       </c>
       <c r="E70">
         <v>41.020507199999997</v>
@@ -5157,16 +5157,16 @@
         <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I70" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J70">
         <v>9000</v>
       </c>
       <c r="K70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L70">
         <v>130</v>
@@ -5175,21 +5175,21 @@
         <v>90</v>
       </c>
       <c r="N70" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C71" t="s">
+        <v>463</v>
+      </c>
+      <c r="D71" t="s">
         <v>464</v>
-      </c>
-      <c r="D71" t="s">
-        <v>465</v>
       </c>
       <c r="E71">
         <v>41.014848100000002</v>
@@ -5201,16 +5201,16 @@
         <v>2</v>
       </c>
       <c r="H71" t="s">
+        <v>465</v>
+      </c>
+      <c r="I71" t="s">
         <v>466</v>
-      </c>
-      <c r="I71" t="s">
-        <v>467</v>
       </c>
       <c r="J71">
         <v>6000</v>
       </c>
       <c r="K71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L71">
         <v>110</v>
@@ -5219,21 +5219,21 @@
         <v>90</v>
       </c>
       <c r="N71" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C72" t="s">
+        <v>468</v>
+      </c>
+      <c r="D72" t="s">
         <v>469</v>
-      </c>
-      <c r="D72" t="s">
-        <v>470</v>
       </c>
       <c r="E72">
         <v>41.035499999999999</v>
@@ -5245,16 +5245,16 @@
         <v>3</v>
       </c>
       <c r="H72" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J72">
         <v>5000</v>
       </c>
       <c r="K72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L72">
         <v>75</v>
@@ -5263,21 +5263,21 @@
         <v>90</v>
       </c>
       <c r="N72" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>299</v>
+      </c>
+      <c r="B73" t="s">
         <v>300</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>301</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>302</v>
-      </c>
-      <c r="D73" t="s">
-        <v>303</v>
       </c>
       <c r="E73" s="4">
         <v>37.779600000000002</v>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I73" t="s">
         <v>20</v>
@@ -5298,7 +5298,7 @@
         <v>9000</v>
       </c>
       <c r="K73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L73">
         <v>125</v>
@@ -5307,21 +5307,21 @@
         <v>120</v>
       </c>
       <c r="N73" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>299</v>
+      </c>
+      <c r="B74" t="s">
         <v>300</v>
       </c>
-      <c r="B74" t="s">
-        <v>301</v>
-      </c>
       <c r="C74" t="s">
+        <v>305</v>
+      </c>
+      <c r="D74" t="s">
         <v>306</v>
-      </c>
-      <c r="D74" t="s">
-        <v>307</v>
       </c>
       <c r="E74" s="4">
         <v>38.399000000000001</v>
@@ -5333,16 +5333,16 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J74">
         <v>9000</v>
       </c>
       <c r="K74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L74">
         <v>130</v>
@@ -5351,21 +5351,21 @@
         <v>60</v>
       </c>
       <c r="N74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>299</v>
+      </c>
+      <c r="B75" t="s">
         <v>300</v>
       </c>
-      <c r="B75" t="s">
-        <v>301</v>
-      </c>
       <c r="C75" t="s">
+        <v>309</v>
+      </c>
+      <c r="D75" t="s">
         <v>310</v>
-      </c>
-      <c r="D75" t="s">
-        <v>311</v>
       </c>
       <c r="E75" s="4">
         <v>38.096200000000003</v>
@@ -5377,16 +5377,16 @@
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I75" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J75">
         <v>7000</v>
       </c>
       <c r="K75" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L75">
         <v>150</v>
@@ -5395,21 +5395,21 @@
         <v>120</v>
       </c>
       <c r="N75" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>299</v>
+      </c>
+      <c r="B76" t="s">
         <v>300</v>
       </c>
-      <c r="B76" t="s">
-        <v>301</v>
-      </c>
       <c r="C76" t="s">
+        <v>313</v>
+      </c>
+      <c r="D76" t="s">
         <v>314</v>
-      </c>
-      <c r="D76" t="s">
-        <v>315</v>
       </c>
       <c r="E76" s="4">
         <v>38.094999999999999</v>
@@ -5421,16 +5421,16 @@
         <v>2</v>
       </c>
       <c r="H76" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I76" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J76">
         <v>7000</v>
       </c>
       <c r="K76" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L76">
         <v>100</v>
@@ -5439,21 +5439,21 @@
         <v>90</v>
       </c>
       <c r="N76" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>299</v>
+      </c>
+      <c r="B77" t="s">
         <v>300</v>
       </c>
-      <c r="B77" t="s">
-        <v>301</v>
-      </c>
       <c r="C77" t="s">
+        <v>317</v>
+      </c>
+      <c r="D77" t="s">
         <v>318</v>
-      </c>
-      <c r="D77" t="s">
-        <v>319</v>
       </c>
       <c r="E77" s="4">
         <v>37.7654</v>
@@ -5465,16 +5465,16 @@
         <v>2</v>
       </c>
       <c r="H77" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I77" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J77">
         <v>5000</v>
       </c>
       <c r="K77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L77">
         <v>115</v>
@@ -5483,21 +5483,21 @@
         <v>60</v>
       </c>
       <c r="N77" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>299</v>
+      </c>
+      <c r="B78" t="s">
         <v>300</v>
       </c>
-      <c r="B78" t="s">
-        <v>301</v>
-      </c>
       <c r="C78" t="s">
+        <v>321</v>
+      </c>
+      <c r="D78" t="s">
         <v>322</v>
-      </c>
-      <c r="D78" t="s">
-        <v>323</v>
       </c>
       <c r="E78" s="4">
         <v>38.011000000000003</v>
@@ -5509,16 +5509,16 @@
         <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J78">
         <v>9000</v>
       </c>
       <c r="K78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L78">
         <v>140</v>
@@ -5527,21 +5527,21 @@
         <v>120</v>
       </c>
       <c r="N78" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>299</v>
+      </c>
+      <c r="B79" t="s">
         <v>300</v>
       </c>
-      <c r="B79" t="s">
-        <v>301</v>
-      </c>
       <c r="C79" t="s">
+        <v>325</v>
+      </c>
+      <c r="D79" t="s">
         <v>326</v>
-      </c>
-      <c r="D79" t="s">
-        <v>327</v>
       </c>
       <c r="E79" s="4">
         <v>37.993000000000002</v>
@@ -5553,16 +5553,16 @@
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I79" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J79">
         <v>9000</v>
       </c>
       <c r="K79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L79">
         <v>140</v>
@@ -5571,21 +5571,21 @@
         <v>120</v>
       </c>
       <c r="N79" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>299</v>
+      </c>
+      <c r="B80" t="s">
         <v>300</v>
       </c>
-      <c r="B80" t="s">
-        <v>301</v>
-      </c>
       <c r="C80" t="s">
+        <v>328</v>
+      </c>
+      <c r="D80" t="s">
         <v>329</v>
-      </c>
-      <c r="D80" t="s">
-        <v>330</v>
       </c>
       <c r="E80" s="4">
         <v>38.305300000000003</v>
@@ -5597,16 +5597,16 @@
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J80">
         <v>8000</v>
       </c>
       <c r="K80" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L80">
         <v>160</v>
@@ -5615,21 +5615,21 @@
         <v>180</v>
       </c>
       <c r="N80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>299</v>
+      </c>
+      <c r="B81" t="s">
         <v>300</v>
       </c>
-      <c r="B81" t="s">
-        <v>301</v>
-      </c>
       <c r="C81" t="s">
+        <v>333</v>
+      </c>
+      <c r="D81" t="s">
         <v>334</v>
-      </c>
-      <c r="D81" t="s">
-        <v>335</v>
       </c>
       <c r="E81" s="4">
         <v>38.173499999999997</v>
@@ -5641,16 +5641,16 @@
         <v>2</v>
       </c>
       <c r="H81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I81" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J81">
         <v>6000</v>
       </c>
       <c r="K81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L81">
         <v>120</v>
@@ -5659,21 +5659,21 @@
         <v>90</v>
       </c>
       <c r="N81" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>299</v>
+      </c>
+      <c r="B82" t="s">
         <v>300</v>
       </c>
-      <c r="B82" t="s">
-        <v>301</v>
-      </c>
       <c r="C82" t="s">
+        <v>336</v>
+      </c>
+      <c r="D82" t="s">
         <v>337</v>
-      </c>
-      <c r="D82" t="s">
-        <v>338</v>
       </c>
       <c r="E82" s="4">
         <v>38.275199999999998</v>
@@ -5685,16 +5685,16 @@
         <v>2</v>
       </c>
       <c r="H82" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I82" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J82">
         <v>7000</v>
       </c>
       <c r="K82" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L82">
         <v>110</v>
@@ -5703,21 +5703,21 @@
         <v>90</v>
       </c>
       <c r="N82" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>299</v>
+      </c>
+      <c r="B83" t="s">
         <v>300</v>
       </c>
-      <c r="B83" t="s">
-        <v>301</v>
-      </c>
       <c r="C83" t="s">
+        <v>340</v>
+      </c>
+      <c r="D83" t="s">
         <v>341</v>
-      </c>
-      <c r="D83" t="s">
-        <v>342</v>
       </c>
       <c r="E83" s="4">
         <v>38.039000000000001</v>
@@ -5729,16 +5729,16 @@
         <v>3</v>
       </c>
       <c r="H83" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I83" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J83">
         <v>8000</v>
       </c>
       <c r="K83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L83">
         <v>95</v>
@@ -5747,21 +5747,21 @@
         <v>90</v>
       </c>
       <c r="N83" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>299</v>
+      </c>
+      <c r="B84" t="s">
         <v>300</v>
       </c>
-      <c r="B84" t="s">
-        <v>301</v>
-      </c>
       <c r="C84" t="s">
+        <v>345</v>
+      </c>
+      <c r="D84" t="s">
         <v>346</v>
-      </c>
-      <c r="D84" t="s">
-        <v>347</v>
       </c>
       <c r="E84" s="4">
         <v>37.909999999999997</v>
@@ -5773,16 +5773,16 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I84" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J84">
         <v>15000</v>
       </c>
       <c r="K84" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L84">
         <v>130</v>
@@ -5791,21 +5791,21 @@
         <v>90</v>
       </c>
       <c r="N84" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>299</v>
+      </c>
+      <c r="B85" t="s">
         <v>300</v>
       </c>
-      <c r="B85" t="s">
-        <v>301</v>
-      </c>
       <c r="C85" t="s">
+        <v>349</v>
+      </c>
+      <c r="D85" t="s">
         <v>350</v>
-      </c>
-      <c r="D85" t="s">
-        <v>351</v>
       </c>
       <c r="E85" s="4">
         <v>37.935499999999998</v>
@@ -5817,16 +5817,16 @@
         <v>3</v>
       </c>
       <c r="H85" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I85" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J85">
         <v>6000</v>
       </c>
       <c r="K85" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L85">
         <v>95</v>
@@ -5835,21 +5835,21 @@
         <v>120</v>
       </c>
       <c r="N85" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>299</v>
+      </c>
+      <c r="B86" t="s">
         <v>300</v>
       </c>
-      <c r="B86" t="s">
-        <v>301</v>
-      </c>
       <c r="C86" t="s">
+        <v>353</v>
+      </c>
+      <c r="D86" t="s">
         <v>354</v>
-      </c>
-      <c r="D86" t="s">
-        <v>355</v>
       </c>
       <c r="E86" s="4">
         <v>37.720999999999997</v>
@@ -5861,16 +5861,16 @@
         <v>2</v>
       </c>
       <c r="H86" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I86" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J86">
         <v>7000</v>
       </c>
       <c r="K86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L86">
         <v>110</v>
@@ -5879,21 +5879,21 @@
         <v>90</v>
       </c>
       <c r="N86" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>299</v>
+      </c>
+      <c r="B87" t="s">
         <v>300</v>
       </c>
-      <c r="B87" t="s">
-        <v>301</v>
-      </c>
       <c r="C87" t="s">
+        <v>358</v>
+      </c>
+      <c r="D87" t="s">
         <v>359</v>
-      </c>
-      <c r="D87" t="s">
-        <v>360</v>
       </c>
       <c r="E87" s="4">
         <v>38</v>
@@ -5905,16 +5905,16 @@
         <v>3</v>
       </c>
       <c r="H87" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I87" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J87">
         <v>12000</v>
       </c>
       <c r="K87" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L87">
         <v>85</v>
@@ -5923,21 +5923,21 @@
         <v>90</v>
       </c>
       <c r="N87" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B88" t="s">
+        <v>363</v>
+      </c>
+      <c r="C88" t="s">
         <v>364</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>365</v>
-      </c>
-      <c r="D88" t="s">
-        <v>366</v>
       </c>
       <c r="E88" s="4">
         <v>37.177300000000002</v>
@@ -5949,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I88" t="s">
         <v>20</v>
@@ -5958,7 +5958,7 @@
         <v>11000</v>
       </c>
       <c r="K88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L88">
         <v>130</v>
@@ -5967,21 +5967,21 @@
         <v>120</v>
       </c>
       <c r="N88" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B89" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C89" t="s">
+        <v>367</v>
+      </c>
+      <c r="D89" t="s">
         <v>368</v>
-      </c>
-      <c r="D89" t="s">
-        <v>369</v>
       </c>
       <c r="E89" s="4">
         <v>37.176099999999998</v>
@@ -5993,16 +5993,16 @@
         <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I89" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J89">
         <v>7000</v>
       </c>
       <c r="K89" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L89">
         <v>170</v>
@@ -6011,21 +6011,21 @@
         <v>180</v>
       </c>
       <c r="N89" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B90" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C90" t="s">
+        <v>372</v>
+      </c>
+      <c r="D90" t="s">
         <v>373</v>
-      </c>
-      <c r="D90" t="s">
-        <v>374</v>
       </c>
       <c r="E90" s="4">
         <v>37.180599999999998</v>
@@ -6037,16 +6037,16 @@
         <v>2</v>
       </c>
       <c r="H90" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I90" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J90">
         <v>5000</v>
       </c>
       <c r="K90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L90">
         <v>130</v>
@@ -6055,21 +6055,21 @@
         <v>90</v>
       </c>
       <c r="N90" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B91" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C91" t="s">
+        <v>377</v>
+      </c>
+      <c r="D91" t="s">
         <v>378</v>
-      </c>
-      <c r="D91" t="s">
-        <v>379</v>
       </c>
       <c r="E91" s="4">
         <v>37.094999999999999</v>
@@ -6081,16 +6081,16 @@
         <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I91" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J91">
         <v>12000</v>
       </c>
       <c r="K91" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L91">
         <v>140</v>
@@ -6099,21 +6099,21 @@
         <v>90</v>
       </c>
       <c r="N91" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B92" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C92" t="s">
+        <v>381</v>
+      </c>
+      <c r="D92" t="s">
         <v>382</v>
-      </c>
-      <c r="D92" t="s">
-        <v>383</v>
       </c>
       <c r="E92" s="4">
         <v>37.167999999999999</v>
@@ -6125,16 +6125,16 @@
         <v>3</v>
       </c>
       <c r="H92" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I92" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J92">
         <v>6000</v>
       </c>
       <c r="K92" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L92">
         <v>90</v>
@@ -6143,21 +6143,21 @@
         <v>90</v>
       </c>
       <c r="N92" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B93" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C93" t="s">
+        <v>385</v>
+      </c>
+      <c r="D93" t="s">
         <v>386</v>
-      </c>
-      <c r="D93" t="s">
-        <v>387</v>
       </c>
       <c r="E93" s="4">
         <v>37.299999999999997</v>
@@ -6169,16 +6169,16 @@
         <v>2</v>
       </c>
       <c r="H93" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J93">
         <v>8000</v>
       </c>
       <c r="K93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L93">
         <v>110</v>
@@ -6187,21 +6187,21 @@
         <v>90</v>
       </c>
       <c r="N93" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B94" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C94" t="s">
+        <v>388</v>
+      </c>
+      <c r="D94" t="s">
         <v>389</v>
-      </c>
-      <c r="D94" t="s">
-        <v>390</v>
       </c>
       <c r="E94" s="4">
         <v>37.176400000000001</v>
@@ -6213,16 +6213,16 @@
         <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I94" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J94">
         <v>6000</v>
       </c>
       <c r="K94" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L94">
         <v>160</v>
@@ -6231,21 +6231,21 @@
         <v>180</v>
       </c>
       <c r="N94" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B95" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C95" t="s">
+        <v>393</v>
+      </c>
+      <c r="D95" t="s">
         <v>394</v>
-      </c>
-      <c r="D95" t="s">
-        <v>395</v>
       </c>
       <c r="E95" s="4">
         <v>37.183500000000002</v>
@@ -6257,16 +6257,16 @@
         <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I95" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J95">
         <v>6000</v>
       </c>
       <c r="K95" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L95">
         <v>110</v>
@@ -6275,21 +6275,21 @@
         <v>90</v>
       </c>
       <c r="N95" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B96" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C96" t="s">
+        <v>398</v>
+      </c>
+      <c r="D96" t="s">
         <v>399</v>
-      </c>
-      <c r="D96" t="s">
-        <v>400</v>
       </c>
       <c r="E96" s="4">
         <v>36.833799999999997</v>
@@ -6301,16 +6301,16 @@
         <v>3</v>
       </c>
       <c r="H96" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I96" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J96">
         <v>7000</v>
       </c>
       <c r="K96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L96">
         <v>85</v>
@@ -6319,21 +6319,21 @@
         <v>60</v>
       </c>
       <c r="N96" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B97" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C97" t="s">
+        <v>403</v>
+      </c>
+      <c r="D97" t="s">
         <v>404</v>
-      </c>
-      <c r="D97" t="s">
-        <v>405</v>
       </c>
       <c r="E97" s="4">
         <v>37.342300000000002</v>
@@ -6345,16 +6345,16 @@
         <v>3</v>
       </c>
       <c r="H97" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J97">
         <v>5000</v>
       </c>
       <c r="K97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L97">
         <v>95</v>
@@ -6363,21 +6363,21 @@
         <v>90</v>
       </c>
       <c r="N97" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C98" t="s">
+        <v>407</v>
+      </c>
+      <c r="D98" t="s">
         <v>408</v>
-      </c>
-      <c r="D98" t="s">
-        <v>409</v>
       </c>
       <c r="E98" s="4">
         <v>36.919400000000003</v>
@@ -6389,16 +6389,16 @@
         <v>2</v>
       </c>
       <c r="H98" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I98" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J98">
         <v>12000</v>
       </c>
       <c r="K98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L98">
         <v>120</v>
@@ -6407,21 +6407,21 @@
         <v>90</v>
       </c>
       <c r="N98" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B99" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C99" t="s">
+        <v>412</v>
+      </c>
+      <c r="D99" t="s">
         <v>413</v>
-      </c>
-      <c r="D99" t="s">
-        <v>414</v>
       </c>
       <c r="E99" s="4">
         <v>37.219900000000003</v>
@@ -6433,16 +6433,16 @@
         <v>3</v>
       </c>
       <c r="H99" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J99">
         <v>6000</v>
       </c>
       <c r="K99" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L99">
         <v>90</v>
@@ -6451,21 +6451,21 @@
         <v>90</v>
       </c>
       <c r="N99" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B100" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C100" t="s">
+        <v>416</v>
+      </c>
+      <c r="D100" t="s">
         <v>417</v>
-      </c>
-      <c r="D100" t="s">
-        <v>418</v>
       </c>
       <c r="E100" s="4">
         <v>37.015099999999997</v>
@@ -6477,16 +6477,16 @@
         <v>2</v>
       </c>
       <c r="H100" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I100" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J100">
         <v>9000</v>
       </c>
       <c r="K100" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L100">
         <v>135</v>
@@ -6495,21 +6495,21 @@
         <v>120</v>
       </c>
       <c r="N100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C101" t="s">
+        <v>421</v>
+      </c>
+      <c r="D101" t="s">
         <v>422</v>
-      </c>
-      <c r="D101" t="s">
-        <v>423</v>
       </c>
       <c r="E101" s="4">
         <v>37.177300000000002</v>
@@ -6521,16 +6521,16 @@
         <v>3</v>
       </c>
       <c r="H101" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I101" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J101">
         <v>10000</v>
       </c>
       <c r="K101" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L101">
         <v>95</v>
@@ -6539,21 +6539,21 @@
         <v>180</v>
       </c>
       <c r="N101" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>472</v>
+      </c>
+      <c r="B102" t="s">
         <v>473</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>474</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>475</v>
-      </c>
-      <c r="D102" t="s">
-        <v>476</v>
       </c>
       <c r="E102">
         <v>41.172081499999997</v>
@@ -6565,16 +6565,16 @@
         <v>1</v>
       </c>
       <c r="H102" t="s">
+        <v>476</v>
+      </c>
+      <c r="I102" t="s">
         <v>477</v>
-      </c>
-      <c r="I102" t="s">
-        <v>478</v>
       </c>
       <c r="J102">
         <v>3000</v>
       </c>
       <c r="K102" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L102">
         <v>145</v>
@@ -6583,21 +6583,21 @@
         <v>180</v>
       </c>
       <c r="N102" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>472</v>
+      </c>
+      <c r="B103" t="s">
         <v>473</v>
       </c>
-      <c r="B103" t="s">
-        <v>474</v>
-      </c>
       <c r="C103" t="s">
+        <v>479</v>
+      </c>
+      <c r="D103" t="s">
         <v>480</v>
-      </c>
-      <c r="D103" t="s">
-        <v>481</v>
       </c>
       <c r="E103">
         <v>41.170754199999998</v>
@@ -6609,16 +6609,16 @@
         <v>1</v>
       </c>
       <c r="H103" t="s">
+        <v>481</v>
+      </c>
+      <c r="I103" t="s">
         <v>482</v>
-      </c>
-      <c r="I103" t="s">
-        <v>483</v>
       </c>
       <c r="J103">
         <v>1500</v>
       </c>
       <c r="K103" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L103">
         <v>155</v>
@@ -6627,21 +6627,21 @@
         <v>240</v>
       </c>
       <c r="N103" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>472</v>
+      </c>
+      <c r="B104" t="s">
         <v>473</v>
       </c>
-      <c r="B104" t="s">
-        <v>474</v>
-      </c>
       <c r="C104" t="s">
+        <v>484</v>
+      </c>
+      <c r="D104" t="s">
         <v>485</v>
-      </c>
-      <c r="D104" t="s">
-        <v>486</v>
       </c>
       <c r="E104">
         <v>41.261531099999999</v>
@@ -6653,16 +6653,16 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I104" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J104">
         <v>4000</v>
       </c>
       <c r="K104" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L104">
         <v>150</v>
@@ -6671,21 +6671,21 @@
         <v>180</v>
       </c>
       <c r="N104" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>472</v>
+      </c>
+      <c r="B105" t="s">
         <v>473</v>
       </c>
-      <c r="B105" t="s">
-        <v>474</v>
-      </c>
       <c r="C105" t="s">
+        <v>488</v>
+      </c>
+      <c r="D105" t="s">
         <v>489</v>
-      </c>
-      <c r="D105" t="s">
-        <v>490</v>
       </c>
       <c r="E105">
         <v>41.2149</v>
@@ -6697,16 +6697,16 @@
         <v>3</v>
       </c>
       <c r="H105" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I105" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J105" s="5">
         <v>1000</v>
       </c>
       <c r="K105" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L105">
         <v>80</v>
@@ -6715,21 +6715,21 @@
         <v>90</v>
       </c>
       <c r="N105" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>472</v>
+      </c>
+      <c r="B106" t="s">
         <v>473</v>
       </c>
-      <c r="B106" t="s">
-        <v>474</v>
-      </c>
       <c r="C106" t="s">
+        <v>492</v>
+      </c>
+      <c r="D106" t="s">
         <v>493</v>
-      </c>
-      <c r="D106" t="s">
-        <v>494</v>
       </c>
       <c r="E106">
         <v>41.365000000000002</v>
@@ -6741,16 +6741,16 @@
         <v>2</v>
       </c>
       <c r="H106" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I106" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J106">
         <v>11000</v>
       </c>
       <c r="K106" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L106">
         <v>105</v>
@@ -6759,21 +6759,21 @@
         <v>90</v>
       </c>
       <c r="N106" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>496</v>
+      </c>
+      <c r="B107" t="s">
         <v>497</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>498</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>499</v>
-      </c>
-      <c r="D107" t="s">
-        <v>500</v>
       </c>
       <c r="E107">
         <v>41.296700000000001</v>
@@ -6785,16 +6785,16 @@
         <v>2</v>
       </c>
       <c r="H107" t="s">
+        <v>500</v>
+      </c>
+      <c r="I107" t="s">
         <v>501</v>
-      </c>
-      <c r="I107" t="s">
-        <v>502</v>
       </c>
       <c r="J107">
         <v>2000</v>
       </c>
       <c r="K107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L107">
         <v>110</v>
@@ -6803,21 +6803,21 @@
         <v>120</v>
       </c>
       <c r="N107" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>496</v>
+      </c>
+      <c r="B108" t="s">
         <v>497</v>
       </c>
-      <c r="B108" t="s">
-        <v>498</v>
-      </c>
       <c r="C108" t="s">
+        <v>503</v>
+      </c>
+      <c r="D108" t="s">
         <v>504</v>
-      </c>
-      <c r="D108" t="s">
-        <v>505</v>
       </c>
       <c r="E108">
         <v>41.294850500000003</v>
@@ -6829,16 +6829,16 @@
         <v>2</v>
       </c>
       <c r="H108" t="s">
+        <v>505</v>
+      </c>
+      <c r="I108" t="s">
         <v>506</v>
-      </c>
-      <c r="I108" t="s">
-        <v>507</v>
       </c>
       <c r="J108">
         <v>2000</v>
       </c>
       <c r="K108" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L108">
         <v>95</v>
@@ -6847,21 +6847,21 @@
         <v>120</v>
       </c>
       <c r="N108" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>496</v>
+      </c>
+      <c r="B109" t="s">
         <v>497</v>
       </c>
-      <c r="B109" t="s">
-        <v>498</v>
-      </c>
       <c r="C109" t="s">
+        <v>508</v>
+      </c>
+      <c r="D109" t="s">
         <v>509</v>
-      </c>
-      <c r="D109" t="s">
-        <v>510</v>
       </c>
       <c r="E109">
         <v>41.329318299999997</v>
@@ -6873,16 +6873,16 @@
         <v>3</v>
       </c>
       <c r="H109" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J109">
         <v>7000</v>
       </c>
       <c r="K109" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L109">
         <v>80</v>
@@ -6891,21 +6891,21 @@
         <v>90</v>
       </c>
       <c r="N109" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>496</v>
+      </c>
+      <c r="B110" t="s">
         <v>497</v>
       </c>
-      <c r="B110" t="s">
-        <v>498</v>
-      </c>
       <c r="C110" t="s">
+        <v>511</v>
+      </c>
+      <c r="D110" t="s">
         <v>512</v>
-      </c>
-      <c r="D110" t="s">
-        <v>513</v>
       </c>
       <c r="E110">
         <v>41.353999999999999</v>
@@ -6917,16 +6917,16 @@
         <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I110" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J110">
         <v>9000</v>
       </c>
       <c r="K110" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L110">
         <v>145</v>
@@ -6935,21 +6935,21 @@
         <v>150</v>
       </c>
       <c r="N110" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>496</v>
+      </c>
+      <c r="B111" t="s">
         <v>497</v>
       </c>
-      <c r="B111" t="s">
-        <v>498</v>
-      </c>
       <c r="C111" t="s">
+        <v>515</v>
+      </c>
+      <c r="D111" t="s">
         <v>516</v>
-      </c>
-      <c r="D111" t="s">
-        <v>517</v>
       </c>
       <c r="E111">
         <v>41.3538</v>
@@ -6961,16 +6961,16 @@
         <v>1</v>
       </c>
       <c r="H111" t="s">
+        <v>517</v>
+      </c>
+      <c r="I111" t="s">
         <v>518</v>
-      </c>
-      <c r="I111" t="s">
-        <v>519</v>
       </c>
       <c r="J111">
         <v>6000</v>
       </c>
       <c r="K111" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L111">
         <v>155</v>
@@ -6979,21 +6979,21 @@
         <v>180</v>
       </c>
       <c r="N111" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>496</v>
+      </c>
+      <c r="B112" t="s">
         <v>497</v>
       </c>
-      <c r="B112" t="s">
-        <v>498</v>
-      </c>
       <c r="C112" t="s">
+        <v>520</v>
+      </c>
+      <c r="D112" t="s">
         <v>521</v>
-      </c>
-      <c r="D112" t="s">
-        <v>522</v>
       </c>
       <c r="E112">
         <v>41.351999999999997</v>
@@ -7005,16 +7005,16 @@
         <v>2</v>
       </c>
       <c r="H112" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I112" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J112">
         <v>7000</v>
       </c>
       <c r="K112" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L112">
         <v>130</v>
@@ -7023,21 +7023,21 @@
         <v>150</v>
       </c>
       <c r="N112" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>496</v>
+      </c>
+      <c r="B113" t="s">
         <v>497</v>
       </c>
-      <c r="B113" t="s">
-        <v>498</v>
-      </c>
       <c r="C113" t="s">
+        <v>523</v>
+      </c>
+      <c r="D113" t="s">
         <v>524</v>
-      </c>
-      <c r="D113" t="s">
-        <v>525</v>
       </c>
       <c r="E113">
         <v>41.236635999999997</v>
@@ -7049,16 +7049,16 @@
         <v>2</v>
       </c>
       <c r="H113" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I113" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J113">
         <v>7000</v>
       </c>
       <c r="K113" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L113">
         <v>120</v>
@@ -7067,21 +7067,21 @@
         <v>90</v>
       </c>
       <c r="N113" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>496</v>
+      </c>
+      <c r="B114" t="s">
         <v>497</v>
       </c>
-      <c r="B114" t="s">
-        <v>498</v>
-      </c>
       <c r="C114" t="s">
+        <v>527</v>
+      </c>
+      <c r="D114" t="s">
         <v>528</v>
-      </c>
-      <c r="D114" t="s">
-        <v>529</v>
       </c>
       <c r="E114">
         <v>41.212000000000003</v>
@@ -7093,16 +7093,16 @@
         <v>3</v>
       </c>
       <c r="H114" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J114">
         <v>5000</v>
       </c>
       <c r="K114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L114">
         <v>95</v>
@@ -7111,21 +7111,21 @@
         <v>90</v>
       </c>
       <c r="N114" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>496</v>
+      </c>
+      <c r="B115" t="s">
         <v>497</v>
       </c>
-      <c r="B115" t="s">
-        <v>498</v>
-      </c>
       <c r="C115" t="s">
+        <v>531</v>
+      </c>
+      <c r="D115" t="s">
         <v>532</v>
-      </c>
-      <c r="D115" t="s">
-        <v>533</v>
       </c>
       <c r="E115">
         <v>41.193239599999998</v>
@@ -7137,16 +7137,16 @@
         <v>1</v>
       </c>
       <c r="H115" t="s">
+        <v>533</v>
+      </c>
+      <c r="I115" t="s">
         <v>534</v>
-      </c>
-      <c r="I115" t="s">
-        <v>535</v>
       </c>
       <c r="J115">
         <v>3000</v>
       </c>
       <c r="K115" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L115">
         <v>170</v>
@@ -7155,21 +7155,21 @@
         <v>240</v>
       </c>
       <c r="N115" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>496</v>
+      </c>
+      <c r="B116" t="s">
         <v>497</v>
       </c>
-      <c r="B116" t="s">
-        <v>498</v>
-      </c>
       <c r="C116" t="s">
+        <v>535</v>
+      </c>
+      <c r="D116" t="s">
         <v>536</v>
-      </c>
-      <c r="D116" t="s">
-        <v>537</v>
       </c>
       <c r="E116">
         <v>41.190435700000002</v>
@@ -7181,16 +7181,16 @@
         <v>2</v>
       </c>
       <c r="H116" t="s">
+        <v>537</v>
+      </c>
+      <c r="I116" t="s">
         <v>538</v>
-      </c>
-      <c r="I116" t="s">
-        <v>539</v>
       </c>
       <c r="J116">
         <v>3000</v>
       </c>
       <c r="K116" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L116">
         <v>125</v>
@@ -7199,21 +7199,21 @@
         <v>120</v>
       </c>
       <c r="N116" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>496</v>
+      </c>
+      <c r="B117" t="s">
         <v>497</v>
       </c>
-      <c r="B117" t="s">
-        <v>498</v>
-      </c>
       <c r="C117" t="s">
+        <v>540</v>
+      </c>
+      <c r="D117" t="s">
         <v>541</v>
-      </c>
-      <c r="D117" t="s">
-        <v>542</v>
       </c>
       <c r="E117">
         <v>41.115099999999998</v>
@@ -7225,16 +7225,16 @@
         <v>2</v>
       </c>
       <c r="H117" t="s">
+        <v>542</v>
+      </c>
+      <c r="I117" t="s">
         <v>543</v>
-      </c>
-      <c r="I117" t="s">
-        <v>544</v>
       </c>
       <c r="J117" s="5">
         <v>1000</v>
       </c>
       <c r="K117" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L117">
         <v>120</v>
@@ -7243,7 +7243,7 @@
         <v>150</v>
       </c>
       <c r="N117" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javiv\Desktop\APP RAIDIO\raidio-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF47CA12-3294-4011-9FE2-7D8ECDC6886E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C36218-72D9-4365-883E-FEAD8AD7E9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1665,7 +1665,7 @@
     <t>"cister","Desamortizción de Mendizábal","Don Pablo Muntadas Campeny", "cascadas", "jardines", "paseo", "fotografia"</t>
   </si>
   <si>
-    <t>"…", "Bar Manolo", "un restaurante muy conocido por sus raciones", "https://www.google.com/maps/place/Bernab%C3%A9u/@40.4544295,-3.6877974,17z/data=!3m1!5s0xd4228e2361e11b7:0x67f5c76cf9a0be21!4m6!3m5!1s0xd4228e23705d39f:0xa8fff6d26e2b1988!8m2!3d40.4530196!4d-3.6883748!16zL20vMDFneGx0?entry=ttu&amp;g_ep=EgoyMDI2MDMyMi4wIKXMDSoASAFQAw%3D%3D"</t>
+    <t>{"sponsorId":"bar_001","sponsorNombre":"Bar Manolo","mensaje":"Bocadillos y terraza y cocks","url":"https://www.google.com/maps/place/Bernab%C3%A9u/@40.4544295,-3.6877974,17z/data=!3m1!5s0xd4228e2361e11b7:0x67f5c76cf9a0be21!4m6!3m5!1s0xd4228e23705d39f:0xa8fff6d26e2b1988!8m2!3d40.4530196!4d-3.6883748!16zL20vMDFneGx0?entry=ttu&amp;g_ep=EgoyMDI2MDMyMi4wIKXMDSoASAFQAw%3D%3D"}</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +2082,7 @@
     <col min="12" max="12" width="10.88671875" customWidth="1"/>
     <col min="13" max="13" width="23.33203125" customWidth="1"/>
     <col min="14" max="14" width="78.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="60.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="94.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="48.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos_POI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapaPOI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMULARIO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="datos_POI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MapaPOI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="FORMULARIO" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R777"/>
+  <dimension ref="A1:R781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>🏰</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>"historia", "pueblo", "cultura", "ruta"</t>
+          <t>"historia", "batallas", "pueblo", "cultura", "ruta"</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2126,14 +2126,14 @@
         </is>
       </c>
       <c r="M23" s="4" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>80</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>"a381", "a390", "romanos", "medieval", "dulces", "mirador"</t>
+          <t>"guadalete", "reconquista", "invasion_arabe", "711"</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr"/>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>🏛️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>"historia", "provincia", "capital", "cultura", "ruta"</t>
+          <t>"historia", "batallas", "guerra_civil", "provincia", "capital", "cultura", "ruta"</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>capital_provincia</t>
+          <t>ciudad_batalla</t>
         </is>
       </c>
       <c r="K123" s="4" t="n">
@@ -8982,18 +8982,18 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="M123" s="4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N123" s="4" t="n">
         <v>120</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>"a23", "mudejar", "amantes", "capitalidad"</t>
+          <t>"guerra_civil", "batalla_teruel", "frente", "invierno"</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr"/>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>🕍</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F157" s="4" t="n">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>"historia", "santuario", "montaña"</t>
+          <t>"historia", "batallas", "reconquista", "santuario", "montaña"</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>santuario</t>
+          <t>campo_batalla</t>
         </is>
       </c>
       <c r="K157" s="4" t="n">
@@ -11334,14 +11334,14 @@
         </is>
       </c>
       <c r="M157" s="4" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="N157" s="4" t="n">
         <v>60</v>
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>"reconquista", "santuario", "picos_de_europa"</t>
+          <t>"reconquista", "batalla", "origen_espana", "don_pelayo"</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>🏰</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F263" s="4" t="n">
@@ -18625,12 +18625,12 @@
       </c>
       <c r="I263" s="4" t="inlineStr">
         <is>
-          <t>"historia", "pueblo", "arquitectura", "cultura", "datosCuriosos"</t>
+          <t>"historia", "batallas", "pueblo", "arquitectura", "cultura", "datosCuriosos"</t>
         </is>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
-          <t>villa_historica</t>
+          <t>ciudad_batalla</t>
         </is>
       </c>
       <c r="K263" s="4" t="n">
@@ -18638,18 +18638,18 @@
       </c>
       <c r="L263" s="4" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="M263" s="4" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N263" s="4" t="n">
         <v>90</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
-          <t>"patrimonio", "casco_historico", "paseo", "arquitectura", "historia_local", "a62", "frontera", "fortificaciones"</t>
+          <t>"guerra_independencia", "asedio", "wellington", "napoleon"</t>
         </is>
       </c>
       <c r="P263" s="4" t="inlineStr"/>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>🏰</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F299" s="7" t="n">
@@ -21113,12 +21113,12 @@
       </c>
       <c r="I299" s="7" t="inlineStr">
         <is>
-          <t>"historia", "pueblo", "arquitectura", "cultura", "datosCuriosos"</t>
+          <t>"historia", "batallas", "pueblo", "arquitectura", "datosCuriosos"</t>
         </is>
       </c>
       <c r="J299" s="7" t="inlineStr">
         <is>
-          <t>villa_historica</t>
+          <t>pueblo_batalla</t>
         </is>
       </c>
       <c r="K299" s="7" t="n">
@@ -21126,18 +21126,18 @@
       </c>
       <c r="L299" s="7" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="M299" s="7" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N299" s="7" t="n">
         <v>90</v>
       </c>
       <c r="O299" s="7" t="inlineStr">
         <is>
-          <t>"patrimonio", "casco_historico", "paseo", "arquitectura", "historia_local", "medieval", "sabinares"</t>
+          <t>"almanzor", "batalla", "reconquista", "leyenda"</t>
         </is>
       </c>
       <c r="P299" s="7" t="inlineStr"/>
@@ -24407,7 +24407,7 @@
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>🏰</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F347" s="4" t="n">
@@ -24421,12 +24421,12 @@
       </c>
       <c r="I347" s="4" t="inlineStr">
         <is>
-          <t>"historia", "castillo", "ciudad", "ruta"</t>
+          <t>"historia", "batallas", "castillo", "ciudad", "ruta"</t>
         </is>
       </c>
       <c r="J347" s="4" t="inlineStr">
         <is>
-          <t>ciudad_historica</t>
+          <t>ciudad_batalla</t>
         </is>
       </c>
       <c r="K347" s="4" t="n">
@@ -24434,18 +24434,18 @@
       </c>
       <c r="L347" s="4" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="M347" s="4" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="N347" s="4" t="n">
         <v>100</v>
       </c>
       <c r="O347" s="4" t="inlineStr">
         <is>
-          <t>"a31", "a35", "batalla_de_almansa", "castillo", "frontera"</t>
+          <t>"guerra_sucesion", "batalla", "borbones", "austria"</t>
         </is>
       </c>
       <c r="P347" s="4" t="inlineStr"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="E521" s="5" t="inlineStr">
         <is>
-          <t>🏰</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F521" s="4" t="n">
@@ -36409,12 +36409,12 @@
       </c>
       <c r="I521" s="4" t="inlineStr">
         <is>
-          <t>"historia", "ciudad", "ruta"</t>
+          <t>"historia", "batallas", "ciudad", "ruta"</t>
         </is>
       </c>
       <c r="J521" s="4" t="inlineStr">
         <is>
-          <t>ciudad_historica</t>
+          <t>ciudad_batalla</t>
         </is>
       </c>
       <c r="K521" s="4" t="n">
@@ -36426,14 +36426,14 @@
         </is>
       </c>
       <c r="M521" s="4" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="N521" s="4" t="n">
         <v>75</v>
       </c>
       <c r="O521" s="4" t="inlineStr">
         <is>
-          <t>"ap7", "a7", "romano", "castillo"</t>
+          <t>"anibal", "asedio", "roma", "cartago", "segunda_guerra_punica"</t>
         </is>
       </c>
       <c r="P521" s="4" t="inlineStr"/>
@@ -37295,7 +37295,7 @@
       </c>
       <c r="E534" s="5" t="inlineStr">
         <is>
-          <t>🏛️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F534" s="4" t="n">
@@ -37309,12 +37309,12 @@
       </c>
       <c r="I534" s="4" t="inlineStr">
         <is>
-          <t>"historia", "provincia", "capital", "frontera", "cultura"</t>
+          <t>"historia", "batallas", "provincia", "capital", "frontera", "cultura"</t>
         </is>
       </c>
       <c r="J534" s="4" t="inlineStr">
         <is>
-          <t>capital_provincia</t>
+          <t>ciudad_batalla</t>
         </is>
       </c>
       <c r="K534" s="4" t="n">
@@ -37322,18 +37322,18 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="M534" s="4" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="N534" s="4" t="n">
         <v>120</v>
       </c>
       <c r="O534" s="4" t="inlineStr">
         <is>
-          <t>"frontera", "portugal", "alcazaba", "guadiana", "ciudad_amurallada"</t>
+          <t>"guerra_independencia", "asedio", "reconquista", "frontera"</t>
         </is>
       </c>
       <c r="P534" s="4" t="inlineStr"/>
@@ -45127,7 +45127,7 @@
       </c>
       <c r="E647" s="5" t="inlineStr">
         <is>
-          <t>🥾</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F647" s="4" t="n">
@@ -45141,12 +45141,12 @@
       </c>
       <c r="I647" s="4" t="inlineStr">
         <is>
-          <t>"montaña", "camino", "historia"</t>
+          <t>"historia", "batallas", "montaña", "camino"</t>
         </is>
       </c>
       <c r="J647" s="4" t="inlineStr">
         <is>
-          <t>puerto_historico</t>
+          <t>puerto_batalla</t>
         </is>
       </c>
       <c r="K647" s="4" t="n">
@@ -45158,14 +45158,14 @@
         </is>
       </c>
       <c r="M647" s="4" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N647" s="4" t="n">
         <v>75</v>
       </c>
       <c r="O647" s="4" t="inlineStr">
         <is>
-          <t>"pirineo", "camino_de_santiago", "a21"</t>
+          <t>"batalla", "carlomagno", "vascos", "camino_de_santiago"</t>
         </is>
       </c>
       <c r="P647" s="4" t="inlineStr"/>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="E683" s="5" t="inlineStr">
         <is>
-          <t>🏛️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="F683" s="4" t="n">
@@ -47621,12 +47621,12 @@
       </c>
       <c r="I683" s="4" t="inlineStr">
         <is>
-          <t>"capital", "historia", "ruta", "cultura"</t>
+          <t>"historia", "batallas", "capital", "ruta", "cultura"</t>
         </is>
       </c>
       <c r="J683" s="4" t="inlineStr">
         <is>
-          <t>capital_provincia</t>
+          <t>ciudad_batalla</t>
         </is>
       </c>
       <c r="K683" s="4" t="n">
@@ -47634,18 +47634,18 @@
       </c>
       <c r="L683" s="4" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>historia</t>
         </is>
       </c>
       <c r="M683" s="4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N683" s="4" t="n">
         <v>80</v>
       </c>
       <c r="O683" s="4" t="inlineStr">
         <is>
-          <t>"a1", "ap68", "llanada_alavesa", "capital_verde", "casco_historico"</t>
+          <t>"guerra_independencia", "batalla", "napoleon", "wellington"</t>
         </is>
       </c>
       <c r="P683" s="4" t="inlineStr"/>
@@ -54071,6 +54071,266 @@
       <c r="P777" s="9" t="inlineStr"/>
       <c r="Q777" s="9" t="inlineStr"/>
       <c r="R777" s="6" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Soria</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>es_so_numancia_asedio</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Numancia (el asedio romano)</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="F778" t="n">
+        <v>41.8056</v>
+      </c>
+      <c r="G778" t="n">
+        <v>-2.4297</v>
+      </c>
+      <c r="H778" t="n">
+        <v>1</v>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>"historia", "batallas", "asedio", "romano", "datosCuriosos"</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>campo_batalla</t>
+        </is>
+      </c>
+      <c r="K778" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>historia</t>
+        </is>
+      </c>
+      <c r="M778" t="n">
+        <v>165</v>
+      </c>
+      <c r="N778" t="n">
+        <v>180</v>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>"asedio", "numancia", "roma", "celtiberos", "resistencia"</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Ciudad Real</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>es_cr_alarcos_batalla</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Campo de Alarcos (batalla de 1195)</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="F779" t="n">
+        <v>38.9425</v>
+      </c>
+      <c r="G779" t="n">
+        <v>-3.9642</v>
+      </c>
+      <c r="H779" t="n">
+        <v>1</v>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>"historia", "batallas", "reconquista", "datosCuriosos"</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>campo_batalla</t>
+        </is>
+      </c>
+      <c r="K779" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>historia</t>
+        </is>
+      </c>
+      <c r="M779" t="n">
+        <v>145</v>
+      </c>
+      <c r="N779" t="n">
+        <v>150</v>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>"reconquista", "almohades", "alfonso_viii", "batalla", "derrota"</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>es_ca_guadalete_batalla</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Río Guadalete (batalla de 711)</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="F780" t="n">
+        <v>36.7167</v>
+      </c>
+      <c r="G780" t="n">
+        <v>-5.9833</v>
+      </c>
+      <c r="H780" t="n">
+        <v>1</v>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>"historia", "batallas", "conquista", "datosCuriosos"</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>campo_batalla</t>
+        </is>
+      </c>
+      <c r="K780" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>historia</t>
+        </is>
+      </c>
+      <c r="M780" t="n">
+        <v>160</v>
+      </c>
+      <c r="N780" t="n">
+        <v>180</v>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>"invasion_arabe", "711", "don_rodrigo", "tariq", "fin_hispania_visigoda"</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>es_mad_jarama_batalla</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Valle del Jarama (batalla de 1937)</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="F781" t="n">
+        <v>40.2564</v>
+      </c>
+      <c r="G781" t="n">
+        <v>-3.4583</v>
+      </c>
+      <c r="H781" t="n">
+        <v>1</v>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>"historia", "batallas", "guerra_civil", "memoria"</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>campo_batalla</t>
+        </is>
+      </c>
+      <c r="K781" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>historia</t>
+        </is>
+      </c>
+      <c r="M781" t="n">
+        <v>140</v>
+      </c>
+      <c r="N781" t="n">
+        <v>150</v>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>"guerra_civil", "brigadas_internacionales", "frente_madrid", "batalla"</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD50D07-F0A9-FE4B-A001-549DBAACB588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617FED7B-1094-3447-A86C-9DEBFCE6617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-1100" yWindow="-18020" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36505,10 +36505,10 @@
         <v>4385</v>
       </c>
       <c r="H415" s="11">
-        <v>39.466700000000003</v>
+        <v>39.795200000000001</v>
       </c>
       <c r="I415" s="11">
-        <v>-3.5333000000000001</v>
+        <v>-3.4992000000000001</v>
       </c>
       <c r="J415" s="5">
         <v>1</v>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617FED7B-1094-3447-A86C-9DEBFCE6617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19620203-E162-0B4D-A350-0776460DAC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-1100" yWindow="-18020" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36505,10 +36505,10 @@
         <v>4385</v>
       </c>
       <c r="H415" s="11">
-        <v>39.795200000000001</v>
+        <v>39.794677700000001</v>
       </c>
       <c r="I415" s="11">
-        <v>-3.4992000000000001</v>
+        <v>-3.4820440000000001</v>
       </c>
       <c r="J415" s="5">
         <v>1</v>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19620203-E162-0B4D-A350-0776460DAC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885C3B13-EC96-D04F-9243-77F9BAC65BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-1100" yWindow="-18020" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17714,7 +17714,7 @@
         <v>421</v>
       </c>
       <c r="M70" s="6">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="N70" s="23" t="s">
         <v>101</v>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885C3B13-EC96-D04F-9243-77F9BAC65BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED65FD4-B70A-9447-999A-3B5BF1FFA140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-1100" yWindow="-18020" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17714,7 +17714,7 @@
         <v>421</v>
       </c>
       <c r="M70" s="6">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="N70" s="23" t="s">
         <v>101</v>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED65FD4-B70A-9447-999A-3B5BF1FFA140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41824E27-0616-B745-A331-446C7F8C6709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1100" yWindow="-18020" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datos_POI" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8459" uniqueCount="4394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8458" uniqueCount="4393">
   <si>
     <t>COMUNIDAD AUTÓNOMA</t>
   </si>
@@ -10151,9 +10151,6 @@
   </si>
   <si>
     <t>"capitalidad", "historia_urbana", "monarquia", "cultura", "museos", "siglo_xvi_xvii"</t>
-  </si>
-  <si>
-    <t>{"sponsorId":"bar_001","sponsorNombre":"Bar Manolo","mensaje":"Bocadillos y terraza y cocks","url":"https://www.google.com/maps/place/Bernab%C3%A9u/@40.4544295,-3.6877974,17z/data=!3m1!5s0xd4228e2361e11b7:0x67f5c76cf9a0be21!4m6!3m5!1s0xd4228e23705d39f:0xa8fff6d26e2b1988!8m2!3d40.4530196!4d-3.6883748!16zL20vMDFneGx0?entry=ttu&amp;g_ep=EgoyMDI2MDMyMi4wIKXMDSoASAFQAw%3D%3D"}</t>
   </si>
   <si>
     <t>id, titulo, descripcion, startDate, endDate, importancia</t>
@@ -13930,7 +13927,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4379</v>
+        <v>4378</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -16604,7 +16601,7 @@
         <v>302</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>4381</v>
+        <v>4380</v>
       </c>
       <c r="H50" s="11">
         <v>37.015099999999997</v>
@@ -17696,7 +17693,7 @@
         <v>419</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>4380</v>
+        <v>4379</v>
       </c>
       <c r="H70" s="4">
         <v>38.305300000000003</v>
@@ -17752,7 +17749,7 @@
         <v>425</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>4380</v>
+        <v>4379</v>
       </c>
       <c r="H71" s="4">
         <v>38.096200000000003</v>
@@ -18284,19 +18281,19 @@
         <v>415</v>
       </c>
       <c r="C81" s="9" t="s">
+        <v>4389</v>
+      </c>
+      <c r="D81" s="9" t="s">
         <v>4390</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>4391</v>
-      </c>
       <c r="E81" s="10" t="s">
+        <v>4383</v>
+      </c>
+      <c r="F81" s="9" t="s">
         <v>4384</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>4385</v>
-      </c>
       <c r="G81" s="9" t="s">
-        <v>4385</v>
+        <v>4384</v>
       </c>
       <c r="H81" s="11">
         <v>38.031067100000001</v>
@@ -18308,10 +18305,10 @@
         <v>1</v>
       </c>
       <c r="K81" s="9" t="s">
+        <v>4385</v>
+      </c>
+      <c r="L81" s="9" t="s">
         <v>4386</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>4387</v>
       </c>
       <c r="M81" s="13">
         <v>2000</v>
@@ -18326,10 +18323,10 @@
         <v>60</v>
       </c>
       <c r="Q81" s="9" t="s">
+        <v>4391</v>
+      </c>
+      <c r="R81" s="9" t="s">
         <v>4392</v>
-      </c>
-      <c r="R81" s="9" t="s">
-        <v>4393</v>
       </c>
       <c r="S81" s="9"/>
       <c r="T81" s="9"/>
@@ -36490,19 +36487,19 @@
         <v>2163</v>
       </c>
       <c r="C415" s="9" t="s">
+        <v>4381</v>
+      </c>
+      <c r="D415" s="9" t="s">
         <v>4382</v>
       </c>
-      <c r="D415" s="9" t="s">
+      <c r="E415" s="10" t="s">
         <v>4383</v>
       </c>
-      <c r="E415" s="10" t="s">
+      <c r="F415" s="9" t="s">
         <v>4384</v>
       </c>
-      <c r="F415" s="9" t="s">
-        <v>4385</v>
-      </c>
       <c r="G415" s="9" t="s">
-        <v>4385</v>
+        <v>4384</v>
       </c>
       <c r="H415" s="11">
         <v>39.794677700000001</v>
@@ -36514,10 +36511,10 @@
         <v>1</v>
       </c>
       <c r="K415" s="9" t="s">
+        <v>4385</v>
+      </c>
+      <c r="L415" s="9" t="s">
         <v>4386</v>
-      </c>
-      <c r="L415" s="9" t="s">
-        <v>4387</v>
       </c>
       <c r="M415" s="13">
         <v>2000</v>
@@ -36532,10 +36529,10 @@
         <v>60</v>
       </c>
       <c r="Q415" s="9" t="s">
+        <v>4387</v>
+      </c>
+      <c r="R415" s="9" t="s">
         <v>4388</v>
-      </c>
-      <c r="R415" s="9" t="s">
-        <v>4389</v>
       </c>
       <c r="S415" s="9"/>
       <c r="T415" s="9"/>
@@ -48270,7 +48267,7 @@
         <v>3368</v>
       </c>
       <c r="G631" s="2" t="s">
-        <v>4380</v>
+        <v>4379</v>
       </c>
       <c r="H631" s="4">
         <v>41.1325</v>
@@ -48356,11 +48353,9 @@
       <c r="Q632" s="2" t="s">
         <v>3374</v>
       </c>
-      <c r="R632" s="2" t="s">
+      <c r="R632" s="2"/>
+      <c r="S632" s="2" t="s">
         <v>3375</v>
-      </c>
-      <c r="S632" s="2" t="s">
-        <v>3376</v>
       </c>
       <c r="T632" s="2"/>
     </row>
@@ -48372,16 +48367,16 @@
         <v>3365</v>
       </c>
       <c r="C633" s="2" t="s">
+        <v>3376</v>
+      </c>
+      <c r="D633" s="2" t="s">
         <v>3377</v>
       </c>
-      <c r="D633" s="2" t="s">
+      <c r="E633" s="3" t="s">
         <v>3378</v>
       </c>
-      <c r="E633" s="3" t="s">
+      <c r="F633" s="2" t="s">
         <v>3379</v>
-      </c>
-      <c r="F633" s="2" t="s">
-        <v>3380</v>
       </c>
       <c r="G633" s="2"/>
       <c r="H633" s="4">
@@ -48394,10 +48389,10 @@
         <v>1</v>
       </c>
       <c r="K633" s="2" t="s">
+        <v>3380</v>
+      </c>
+      <c r="L633" s="2" t="s">
         <v>3381</v>
-      </c>
-      <c r="L633" s="2" t="s">
-        <v>3382</v>
       </c>
       <c r="M633" s="6">
         <v>8000</v>
@@ -48412,12 +48407,12 @@
         <v>90</v>
       </c>
       <c r="Q633" s="2" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="R633" s="2"/>
       <c r="S633" s="2"/>
       <c r="T633" s="2" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="634" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -48428,16 +48423,16 @@
         <v>3365</v>
       </c>
       <c r="C634" s="2" t="s">
+        <v>3384</v>
+      </c>
+      <c r="D634" s="2" t="s">
         <v>3385</v>
-      </c>
-      <c r="D634" s="2" t="s">
-        <v>3386</v>
       </c>
       <c r="E634" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F634" s="2" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="G634" s="2"/>
       <c r="H634" s="4">
@@ -48450,7 +48445,7 @@
         <v>1</v>
       </c>
       <c r="K634" s="2" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="L634" s="2" t="s">
         <v>921</v>
@@ -48468,12 +48463,12 @@
         <v>70</v>
       </c>
       <c r="Q634" s="2" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="R634" s="2"/>
       <c r="S634" s="2"/>
       <c r="T634" s="2" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="635" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -48484,16 +48479,16 @@
         <v>3365</v>
       </c>
       <c r="C635" s="2" t="s">
+        <v>3390</v>
+      </c>
+      <c r="D635" s="2" t="s">
         <v>3391</v>
       </c>
-      <c r="D635" s="2" t="s">
+      <c r="E635" s="3" t="s">
         <v>3392</v>
       </c>
-      <c r="E635" s="3" t="s">
+      <c r="F635" s="2" t="s">
         <v>3393</v>
-      </c>
-      <c r="F635" s="2" t="s">
-        <v>3394</v>
       </c>
       <c r="G635" s="2"/>
       <c r="H635" s="4">
@@ -48506,10 +48501,10 @@
         <v>1</v>
       </c>
       <c r="K635" s="2" t="s">
+        <v>3394</v>
+      </c>
+      <c r="L635" s="2" t="s">
         <v>3395</v>
-      </c>
-      <c r="L635" s="2" t="s">
-        <v>3396</v>
       </c>
       <c r="M635" s="6">
         <v>7000</v>
@@ -48524,7 +48519,7 @@
         <v>60</v>
       </c>
       <c r="Q635" s="2" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="R635" s="2"/>
       <c r="S635" s="2"/>
@@ -48538,16 +48533,16 @@
         <v>3365</v>
       </c>
       <c r="C636" s="2" t="s">
+        <v>3397</v>
+      </c>
+      <c r="D636" s="2" t="s">
         <v>3398</v>
-      </c>
-      <c r="D636" s="2" t="s">
-        <v>3399</v>
       </c>
       <c r="E636" s="3" t="s">
         <v>603</v>
       </c>
       <c r="F636" s="2" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G636" s="2"/>
       <c r="H636" s="4">
@@ -48560,7 +48555,7 @@
         <v>1</v>
       </c>
       <c r="K636" s="2" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="L636" s="2" t="s">
         <v>1200</v>
@@ -48578,7 +48573,7 @@
         <v>60</v>
       </c>
       <c r="Q636" s="2" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="R636" s="2"/>
       <c r="S636" s="2"/>
@@ -48592,16 +48587,16 @@
         <v>3365</v>
       </c>
       <c r="C637" s="2" t="s">
+        <v>3402</v>
+      </c>
+      <c r="D637" s="2" t="s">
         <v>3403</v>
-      </c>
-      <c r="D637" s="2" t="s">
-        <v>3404</v>
       </c>
       <c r="E637" s="3" t="s">
         <v>603</v>
       </c>
       <c r="F637" s="2" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="G637" s="2"/>
       <c r="H637" s="4">
@@ -48614,7 +48609,7 @@
         <v>1</v>
       </c>
       <c r="K637" s="2" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="L637" s="2" t="s">
         <v>606</v>
@@ -48632,12 +48627,12 @@
         <v>45</v>
       </c>
       <c r="Q637" s="2" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="R637" s="2"/>
       <c r="S637" s="2"/>
       <c r="T637" s="2" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
     </row>
     <row r="638" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -48648,16 +48643,16 @@
         <v>3365</v>
       </c>
       <c r="C638" s="9" t="s">
+        <v>3408</v>
+      </c>
+      <c r="D638" s="9" t="s">
         <v>3409</v>
-      </c>
-      <c r="D638" s="9" t="s">
-        <v>3410</v>
       </c>
       <c r="E638" s="10" t="s">
         <v>418</v>
       </c>
       <c r="F638" s="9" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="G638" s="9"/>
       <c r="H638" s="11">
@@ -48670,10 +48665,10 @@
         <v>2</v>
       </c>
       <c r="K638" s="9" t="s">
+        <v>3411</v>
+      </c>
+      <c r="L638" s="9" t="s">
         <v>3412</v>
-      </c>
-      <c r="L638" s="9" t="s">
-        <v>3413</v>
       </c>
       <c r="M638" s="13">
         <v>4000</v>
@@ -48688,7 +48683,7 @@
         <v>90</v>
       </c>
       <c r="Q638" s="9" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="R638" s="9"/>
       <c r="S638" s="9"/>
@@ -48702,16 +48697,16 @@
         <v>3365</v>
       </c>
       <c r="C639" s="9" t="s">
+        <v>3414</v>
+      </c>
+      <c r="D639" s="9" t="s">
         <v>3415</v>
-      </c>
-      <c r="D639" s="9" t="s">
-        <v>3416</v>
       </c>
       <c r="E639" s="10" t="s">
         <v>2207</v>
       </c>
       <c r="F639" s="9" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="G639" s="9"/>
       <c r="H639" s="11">
@@ -48724,10 +48719,10 @@
         <v>2</v>
       </c>
       <c r="K639" s="9" t="s">
+        <v>3417</v>
+      </c>
+      <c r="L639" s="9" t="s">
         <v>3418</v>
-      </c>
-      <c r="L639" s="9" t="s">
-        <v>3419</v>
       </c>
       <c r="M639" s="13">
         <v>2500</v>
@@ -48742,7 +48737,7 @@
         <v>40</v>
       </c>
       <c r="Q639" s="9" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="R639" s="9"/>
       <c r="S639" s="9"/>
@@ -48756,16 +48751,16 @@
         <v>3365</v>
       </c>
       <c r="C640" s="9" t="s">
+        <v>3420</v>
+      </c>
+      <c r="D640" s="9" t="s">
         <v>3421</v>
-      </c>
-      <c r="D640" s="9" t="s">
-        <v>3422</v>
       </c>
       <c r="E640" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F640" s="9" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="G640" s="9"/>
       <c r="H640" s="11">
@@ -48796,7 +48791,7 @@
         <v>40</v>
       </c>
       <c r="Q640" s="9" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="R640" s="9"/>
       <c r="S640" s="9"/>
@@ -48810,16 +48805,16 @@
         <v>3365</v>
       </c>
       <c r="C641" s="9" t="s">
+        <v>3424</v>
+      </c>
+      <c r="D641" s="9" t="s">
         <v>3425</v>
-      </c>
-      <c r="D641" s="9" t="s">
-        <v>3426</v>
       </c>
       <c r="E641" s="10" t="s">
         <v>648</v>
       </c>
       <c r="F641" s="9" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="G641" s="9"/>
       <c r="H641" s="11">
@@ -48832,10 +48827,10 @@
         <v>2</v>
       </c>
       <c r="K641" s="9" t="s">
+        <v>3427</v>
+      </c>
+      <c r="L641" s="9" t="s">
         <v>3428</v>
-      </c>
-      <c r="L641" s="9" t="s">
-        <v>3429</v>
       </c>
       <c r="M641" s="13">
         <v>3000</v>
@@ -48850,12 +48845,12 @@
         <v>45</v>
       </c>
       <c r="Q641" s="9" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="R641" s="9"/>
       <c r="S641" s="9"/>
       <c r="T641" s="9" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="642" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -48866,16 +48861,16 @@
         <v>3365</v>
       </c>
       <c r="C642" s="9" t="s">
+        <v>3431</v>
+      </c>
+      <c r="D642" s="9" t="s">
         <v>3432</v>
-      </c>
-      <c r="D642" s="9" t="s">
-        <v>3433</v>
       </c>
       <c r="E642" s="10" t="s">
         <v>91</v>
       </c>
       <c r="F642" s="9" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="G642" s="9"/>
       <c r="H642" s="11">
@@ -48888,7 +48883,7 @@
         <v>2</v>
       </c>
       <c r="K642" s="9" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="L642" s="9" t="s">
         <v>123</v>
@@ -48906,7 +48901,7 @@
         <v>40</v>
       </c>
       <c r="Q642" s="9" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="R642" s="9"/>
       <c r="S642" s="9"/>
@@ -48920,16 +48915,16 @@
         <v>3365</v>
       </c>
       <c r="C643" s="17" t="s">
+        <v>3436</v>
+      </c>
+      <c r="D643" s="17" t="s">
         <v>3437</v>
-      </c>
-      <c r="D643" s="17" t="s">
-        <v>3438</v>
       </c>
       <c r="E643" s="18" t="s">
         <v>63</v>
       </c>
       <c r="F643" s="17" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="G643" s="17"/>
       <c r="H643" s="19">
@@ -48960,7 +48955,7 @@
         <v>40</v>
       </c>
       <c r="Q643" s="17" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="R643" s="17"/>
       <c r="S643" s="17"/>
@@ -48974,16 +48969,16 @@
         <v>3365</v>
       </c>
       <c r="C644" s="17" t="s">
+        <v>3440</v>
+      </c>
+      <c r="D644" s="17" t="s">
         <v>3441</v>
-      </c>
-      <c r="D644" s="17" t="s">
-        <v>3442</v>
       </c>
       <c r="E644" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F644" s="17" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="G644" s="17"/>
       <c r="H644" s="19">
@@ -48996,7 +48991,7 @@
         <v>3</v>
       </c>
       <c r="K644" s="17" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="L644" s="17" t="s">
         <v>123</v>
@@ -49014,7 +49009,7 @@
         <v>35</v>
       </c>
       <c r="Q644" s="17" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="R644" s="17"/>
       <c r="S644" s="17"/>
@@ -49022,22 +49017,22 @@
     </row>
     <row r="645" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="2" t="s">
+        <v>3445</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>3445</v>
+      </c>
+      <c r="C645" s="2" t="s">
         <v>3446</v>
       </c>
-      <c r="B645" s="2" t="s">
-        <v>3446</v>
-      </c>
-      <c r="C645" s="2" t="s">
+      <c r="D645" s="2" t="s">
         <v>3447</v>
-      </c>
-      <c r="D645" s="2" t="s">
-        <v>3448</v>
       </c>
       <c r="E645" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F645" s="2" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="G645" s="2"/>
       <c r="H645" s="4">
@@ -49050,7 +49045,7 @@
         <v>1</v>
       </c>
       <c r="K645" s="2" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="L645" s="2" t="s">
         <v>26</v>
@@ -49068,32 +49063,32 @@
         <v>80</v>
       </c>
       <c r="Q645" s="2" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="R645" s="2"/>
       <c r="S645" s="2"/>
       <c r="T645" s="2" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="646" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C646" s="2" t="s">
+        <v>3452</v>
+      </c>
+      <c r="D646" s="2" t="s">
         <v>3453</v>
-      </c>
-      <c r="D646" s="2" t="s">
-        <v>3454</v>
       </c>
       <c r="E646" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F646" s="2" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="G646" s="2"/>
       <c r="H646" s="4">
@@ -49106,7 +49101,7 @@
         <v>1</v>
       </c>
       <c r="K646" s="2" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="L646" s="2" t="s">
         <v>35</v>
@@ -49124,7 +49119,7 @@
         <v>85</v>
       </c>
       <c r="Q646" s="2" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="R646" s="2"/>
       <c r="S646" s="2"/>
@@ -49132,22 +49127,22 @@
     </row>
     <row r="647" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C647" s="2" t="s">
+        <v>3457</v>
+      </c>
+      <c r="D647" s="2" t="s">
         <v>3458</v>
-      </c>
-      <c r="D647" s="2" t="s">
-        <v>3459</v>
       </c>
       <c r="E647" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F647" s="2" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="G647" s="2"/>
       <c r="H647" s="4">
@@ -49178,32 +49173,32 @@
         <v>75</v>
       </c>
       <c r="Q647" s="2" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="R647" s="2"/>
       <c r="S647" s="2"/>
       <c r="T647" s="2" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="648" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C648" s="2" t="s">
+        <v>3462</v>
+      </c>
+      <c r="D648" s="2" t="s">
         <v>3463</v>
-      </c>
-      <c r="D648" s="2" t="s">
-        <v>3464</v>
       </c>
       <c r="E648" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F648" s="2" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="G648" s="2"/>
       <c r="H648" s="4">
@@ -49234,7 +49229,7 @@
         <v>75</v>
       </c>
       <c r="Q648" s="2" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="R648" s="2"/>
       <c r="S648" s="2"/>
@@ -49242,22 +49237,22 @@
     </row>
     <row r="649" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C649" s="2" t="s">
+        <v>3466</v>
+      </c>
+      <c r="D649" s="2" t="s">
         <v>3467</v>
-      </c>
-      <c r="D649" s="2" t="s">
-        <v>3468</v>
       </c>
       <c r="E649" s="3" t="s">
         <v>988</v>
       </c>
       <c r="F649" s="2" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="G649" s="2"/>
       <c r="H649" s="4">
@@ -49270,7 +49265,7 @@
         <v>1</v>
       </c>
       <c r="K649" s="2" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="L649" s="2" t="s">
         <v>1040</v>
@@ -49288,7 +49283,7 @@
         <v>75</v>
       </c>
       <c r="Q649" s="2" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="R649" s="2"/>
       <c r="S649" s="2"/>
@@ -49296,22 +49291,22 @@
     </row>
     <row r="650" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C650" s="2" t="s">
+        <v>3471</v>
+      </c>
+      <c r="D650" s="2" t="s">
         <v>3472</v>
-      </c>
-      <c r="D650" s="2" t="s">
-        <v>3473</v>
       </c>
       <c r="E650" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F650" s="2" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="G650" s="2"/>
       <c r="H650" s="4">
@@ -49324,7 +49319,7 @@
         <v>1</v>
       </c>
       <c r="K650" s="2" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="L650" s="2" t="s">
         <v>72</v>
@@ -49342,7 +49337,7 @@
         <v>70</v>
       </c>
       <c r="Q650" s="2" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="R650" s="2"/>
       <c r="S650" s="2"/>
@@ -49350,22 +49345,22 @@
     </row>
     <row r="651" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C651" s="2" t="s">
+        <v>3476</v>
+      </c>
+      <c r="D651" s="2" t="s">
         <v>3477</v>
-      </c>
-      <c r="D651" s="2" t="s">
-        <v>3478</v>
       </c>
       <c r="E651" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F651" s="2" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="G651" s="2"/>
       <c r="H651" s="4">
@@ -49378,7 +49373,7 @@
         <v>1</v>
       </c>
       <c r="K651" s="2" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="L651" s="2" t="s">
         <v>100</v>
@@ -49396,32 +49391,32 @@
         <v>70</v>
       </c>
       <c r="Q651" s="2" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="R651" s="2"/>
       <c r="S651" s="2"/>
       <c r="T651" s="2" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="652" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C652" s="2" t="s">
+        <v>3481</v>
+      </c>
+      <c r="D652" s="2" t="s">
         <v>3482</v>
-      </c>
-      <c r="D652" s="2" t="s">
-        <v>3483</v>
       </c>
       <c r="E652" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F652" s="2" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="G652" s="2"/>
       <c r="H652" s="4">
@@ -49434,7 +49429,7 @@
         <v>1</v>
       </c>
       <c r="K652" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="L652" s="2" t="s">
         <v>233</v>
@@ -49452,7 +49447,7 @@
         <v>65</v>
       </c>
       <c r="Q652" s="2" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="R652" s="2"/>
       <c r="S652" s="2"/>
@@ -49460,22 +49455,22 @@
     </row>
     <row r="653" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C653" s="2" t="s">
+        <v>3486</v>
+      </c>
+      <c r="D653" s="2" t="s">
         <v>3487</v>
-      </c>
-      <c r="D653" s="2" t="s">
-        <v>3488</v>
       </c>
       <c r="E653" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="G653" s="2"/>
       <c r="H653" s="4">
@@ -49488,7 +49483,7 @@
         <v>1</v>
       </c>
       <c r="K653" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="L653" s="2" t="s">
         <v>72</v>
@@ -49506,7 +49501,7 @@
         <v>60</v>
       </c>
       <c r="Q653" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="R653" s="2"/>
       <c r="S653" s="2"/>
@@ -49514,22 +49509,22 @@
     </row>
     <row r="654" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B654" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C654" s="9" t="s">
+        <v>3491</v>
+      </c>
+      <c r="D654" s="9" t="s">
         <v>3492</v>
-      </c>
-      <c r="D654" s="9" t="s">
-        <v>3493</v>
       </c>
       <c r="E654" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F654" s="9" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="G654" s="9"/>
       <c r="H654" s="11">
@@ -49542,7 +49537,7 @@
         <v>2</v>
       </c>
       <c r="K654" s="9" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="L654" s="9" t="s">
         <v>100</v>
@@ -49560,7 +49555,7 @@
         <v>55</v>
       </c>
       <c r="Q654" s="9" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="R654" s="9"/>
       <c r="S654" s="9"/>
@@ -49568,22 +49563,22 @@
     </row>
     <row r="655" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B655" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C655" s="9" t="s">
+        <v>3496</v>
+      </c>
+      <c r="D655" s="9" t="s">
         <v>3497</v>
-      </c>
-      <c r="D655" s="9" t="s">
-        <v>3498</v>
       </c>
       <c r="E655" s="10" t="s">
         <v>1577</v>
       </c>
       <c r="F655" s="9" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="G655" s="9"/>
       <c r="H655" s="11">
@@ -49596,10 +49591,10 @@
         <v>2</v>
       </c>
       <c r="K655" s="9" t="s">
+        <v>3499</v>
+      </c>
+      <c r="L655" s="9" t="s">
         <v>3500</v>
-      </c>
-      <c r="L655" s="9" t="s">
-        <v>3501</v>
       </c>
       <c r="M655" s="13">
         <v>5000</v>
@@ -49614,7 +49609,7 @@
         <v>55</v>
       </c>
       <c r="Q655" s="9" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="R655" s="9"/>
       <c r="S655" s="9"/>
@@ -49622,22 +49617,22 @@
     </row>
     <row r="656" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B656" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C656" s="9" t="s">
+        <v>3502</v>
+      </c>
+      <c r="D656" s="9" t="s">
         <v>3503</v>
-      </c>
-      <c r="D656" s="9" t="s">
-        <v>3504</v>
       </c>
       <c r="E656" s="10" t="s">
         <v>301</v>
       </c>
       <c r="F656" s="9" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="G656" s="9"/>
       <c r="H656" s="11">
@@ -49650,7 +49645,7 @@
         <v>2</v>
       </c>
       <c r="K656" s="9" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="L656" s="9" t="s">
         <v>685</v>
@@ -49668,7 +49663,7 @@
         <v>55</v>
       </c>
       <c r="Q656" s="9" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="R656" s="9"/>
       <c r="S656" s="9"/>
@@ -49676,22 +49671,22 @@
     </row>
     <row r="657" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B657" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C657" s="9" t="s">
+        <v>3507</v>
+      </c>
+      <c r="D657" s="9" t="s">
         <v>3508</v>
-      </c>
-      <c r="D657" s="9" t="s">
-        <v>3509</v>
       </c>
       <c r="E657" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F657" s="9" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="G657" s="9"/>
       <c r="H657" s="11">
@@ -49704,7 +49699,7 @@
         <v>2</v>
       </c>
       <c r="K657" s="9" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="L657" s="9" t="s">
         <v>112</v>
@@ -49722,7 +49717,7 @@
         <v>55</v>
       </c>
       <c r="Q657" s="9" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="R657" s="9"/>
       <c r="S657" s="9"/>
@@ -49730,22 +49725,22 @@
     </row>
     <row r="658" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B658" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C658" s="9" t="s">
+        <v>3512</v>
+      </c>
+      <c r="D658" s="9" t="s">
         <v>3513</v>
-      </c>
-      <c r="D658" s="9" t="s">
-        <v>3514</v>
       </c>
       <c r="E658" s="10" t="s">
         <v>864</v>
       </c>
       <c r="F658" s="9" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G658" s="9"/>
       <c r="H658" s="11">
@@ -49758,7 +49753,7 @@
         <v>2</v>
       </c>
       <c r="K658" s="9" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="L658" s="9" t="s">
         <v>2331</v>
@@ -49776,7 +49771,7 @@
         <v>55</v>
       </c>
       <c r="Q658" s="9" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="R658" s="9"/>
       <c r="S658" s="9"/>
@@ -49784,22 +49779,22 @@
     </row>
     <row r="659" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B659" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C659" s="9" t="s">
+        <v>3517</v>
+      </c>
+      <c r="D659" s="9" t="s">
         <v>3518</v>
-      </c>
-      <c r="D659" s="9" t="s">
-        <v>3519</v>
       </c>
       <c r="E659" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F659" s="9" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="G659" s="9"/>
       <c r="H659" s="11">
@@ -49812,7 +49807,7 @@
         <v>2</v>
       </c>
       <c r="K659" s="9" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="L659" s="9" t="s">
         <v>100</v>
@@ -49830,7 +49825,7 @@
         <v>50</v>
       </c>
       <c r="Q659" s="9" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="R659" s="9"/>
       <c r="S659" s="9"/>
@@ -49838,22 +49833,22 @@
     </row>
     <row r="660" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B660" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C660" s="9" t="s">
+        <v>3522</v>
+      </c>
+      <c r="D660" s="9" t="s">
         <v>3523</v>
-      </c>
-      <c r="D660" s="9" t="s">
-        <v>3524</v>
       </c>
       <c r="E660" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F660" s="9" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G660" s="9"/>
       <c r="H660" s="11">
@@ -49866,7 +49861,7 @@
         <v>2</v>
       </c>
       <c r="K660" s="9" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="L660" s="9" t="s">
         <v>112</v>
@@ -49884,7 +49879,7 @@
         <v>50</v>
       </c>
       <c r="Q660" s="9" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="R660" s="9"/>
       <c r="S660" s="9"/>
@@ -49892,22 +49887,22 @@
     </row>
     <row r="661" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="2" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B661" s="2" t="s">
         <v>3528</v>
       </c>
-      <c r="B661" s="2" t="s">
+      <c r="C661" s="2" t="s">
         <v>3529</v>
       </c>
-      <c r="C661" s="2" t="s">
+      <c r="D661" s="2" t="s">
         <v>3530</v>
-      </c>
-      <c r="D661" s="2" t="s">
-        <v>3531</v>
       </c>
       <c r="E661" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F661" s="2" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="G661" s="2"/>
       <c r="H661" s="4">
@@ -49920,7 +49915,7 @@
         <v>1</v>
       </c>
       <c r="K661" s="2" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="L661" s="2" t="s">
         <v>26</v>
@@ -49938,32 +49933,32 @@
         <v>85</v>
       </c>
       <c r="Q661" s="2" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="R661" s="2"/>
       <c r="S661" s="2"/>
       <c r="T661" s="2" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="662" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B662" s="2" t="s">
         <v>3528</v>
       </c>
-      <c r="B662" s="2" t="s">
-        <v>3529</v>
-      </c>
       <c r="C662" s="2" t="s">
+        <v>3535</v>
+      </c>
+      <c r="D662" s="2" t="s">
         <v>3536</v>
-      </c>
-      <c r="D662" s="2" t="s">
-        <v>3537</v>
       </c>
       <c r="E662" s="3" t="s">
         <v>461</v>
       </c>
       <c r="F662" s="2" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G662" s="2"/>
       <c r="H662" s="4">
@@ -49976,10 +49971,10 @@
         <v>1</v>
       </c>
       <c r="K662" s="2" t="s">
+        <v>3538</v>
+      </c>
+      <c r="L662" s="2" t="s">
         <v>3539</v>
-      </c>
-      <c r="L662" s="2" t="s">
-        <v>3540</v>
       </c>
       <c r="M662" s="6">
         <v>5500</v>
@@ -49994,7 +49989,7 @@
         <v>85</v>
       </c>
       <c r="Q662" s="2" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="R662" s="2"/>
       <c r="S662" s="2"/>
@@ -50002,22 +49997,22 @@
     </row>
     <row r="663" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="2" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B663" s="2" t="s">
         <v>3528</v>
       </c>
-      <c r="B663" s="2" t="s">
-        <v>3529</v>
-      </c>
       <c r="C663" s="2" t="s">
+        <v>3541</v>
+      </c>
+      <c r="D663" s="2" t="s">
         <v>3542</v>
-      </c>
-      <c r="D663" s="2" t="s">
-        <v>3543</v>
       </c>
       <c r="E663" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F663" s="2" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="G663" s="2"/>
       <c r="H663" s="4">
@@ -50030,7 +50025,7 @@
         <v>1</v>
       </c>
       <c r="K663" s="2" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="L663" s="2" t="s">
         <v>72</v>
@@ -50048,32 +50043,32 @@
         <v>80</v>
       </c>
       <c r="Q663" s="2" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="R663" s="2"/>
       <c r="S663" s="2"/>
       <c r="T663" s="2" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="664" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="2" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B664" s="2" t="s">
         <v>3528</v>
       </c>
-      <c r="B664" s="2" t="s">
-        <v>3529</v>
-      </c>
       <c r="C664" s="2" t="s">
+        <v>3547</v>
+      </c>
+      <c r="D664" s="2" t="s">
         <v>3548</v>
-      </c>
-      <c r="D664" s="2" t="s">
-        <v>3549</v>
       </c>
       <c r="E664" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F664" s="2" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="G664" s="2"/>
       <c r="H664" s="4">
@@ -50086,7 +50081,7 @@
         <v>1</v>
       </c>
       <c r="K664" s="2" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="L664" s="2" t="s">
         <v>35</v>
@@ -50104,7 +50099,7 @@
         <v>75</v>
       </c>
       <c r="Q664" s="2" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="R664" s="2"/>
       <c r="S664" s="2"/>
@@ -50112,22 +50107,22 @@
     </row>
     <row r="665" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="2" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B665" s="2" t="s">
         <v>3528</v>
       </c>
-      <c r="B665" s="2" t="s">
-        <v>3529</v>
-      </c>
       <c r="C665" s="2" t="s">
+        <v>3552</v>
+      </c>
+      <c r="D665" s="2" t="s">
         <v>3553</v>
-      </c>
-      <c r="D665" s="2" t="s">
-        <v>3554</v>
       </c>
       <c r="E665" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F665" s="2" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="G665" s="2"/>
       <c r="H665" s="4">
@@ -50140,7 +50135,7 @@
         <v>1</v>
       </c>
       <c r="K665" s="2" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="L665" s="2" t="s">
         <v>72</v>
@@ -50158,7 +50153,7 @@
         <v>60</v>
       </c>
       <c r="Q665" s="2" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="R665" s="2"/>
       <c r="S665" s="2"/>
@@ -50166,22 +50161,22 @@
     </row>
     <row r="666" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="9" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B666" s="9" t="s">
         <v>3528</v>
       </c>
-      <c r="B666" s="9" t="s">
-        <v>3529</v>
-      </c>
       <c r="C666" s="9" t="s">
+        <v>3557</v>
+      </c>
+      <c r="D666" s="9" t="s">
         <v>3558</v>
-      </c>
-      <c r="D666" s="9" t="s">
-        <v>3559</v>
       </c>
       <c r="E666" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F666" s="9" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="G666" s="9"/>
       <c r="H666" s="11">
@@ -50194,7 +50189,7 @@
         <v>2</v>
       </c>
       <c r="K666" s="9" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="L666" s="9" t="s">
         <v>72</v>
@@ -50212,7 +50207,7 @@
         <v>55</v>
       </c>
       <c r="Q666" s="9" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="R666" s="9"/>
       <c r="S666" s="9"/>
@@ -50220,22 +50215,22 @@
     </row>
     <row r="667" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="9" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B667" s="9" t="s">
         <v>3528</v>
       </c>
-      <c r="B667" s="9" t="s">
-        <v>3529</v>
-      </c>
       <c r="C667" s="9" t="s">
+        <v>3561</v>
+      </c>
+      <c r="D667" s="9" t="s">
         <v>3562</v>
-      </c>
-      <c r="D667" s="9" t="s">
-        <v>3563</v>
       </c>
       <c r="E667" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F667" s="9" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="G667" s="9"/>
       <c r="H667" s="11">
@@ -50248,7 +50243,7 @@
         <v>2</v>
       </c>
       <c r="K667" s="9" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="L667" s="9" t="s">
         <v>1018</v>
@@ -50266,32 +50261,32 @@
         <v>55</v>
       </c>
       <c r="Q667" s="9" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="R667" s="9"/>
       <c r="S667" s="9"/>
       <c r="T667" s="9" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="668" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="9" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B668" s="9" t="s">
         <v>3528</v>
       </c>
-      <c r="B668" s="9" t="s">
-        <v>3529</v>
-      </c>
       <c r="C668" s="9" t="s">
+        <v>3567</v>
+      </c>
+      <c r="D668" s="9" t="s">
         <v>3568</v>
-      </c>
-      <c r="D668" s="9" t="s">
-        <v>3569</v>
       </c>
       <c r="E668" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F668" s="9" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="G668" s="9"/>
       <c r="H668" s="11">
@@ -50304,7 +50299,7 @@
         <v>2</v>
       </c>
       <c r="K668" s="9" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="L668" s="9" t="s">
         <v>1018</v>
@@ -50322,7 +50317,7 @@
         <v>55</v>
       </c>
       <c r="Q668" s="9" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="R668" s="9"/>
       <c r="S668" s="9"/>
@@ -50330,22 +50325,22 @@
     </row>
     <row r="669" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="9" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B669" s="9" t="s">
         <v>3528</v>
       </c>
-      <c r="B669" s="9" t="s">
-        <v>3529</v>
-      </c>
       <c r="C669" s="9" t="s">
+        <v>3572</v>
+      </c>
+      <c r="D669" s="9" t="s">
         <v>3573</v>
-      </c>
-      <c r="D669" s="9" t="s">
-        <v>3574</v>
       </c>
       <c r="E669" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F669" s="9" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="G669" s="9"/>
       <c r="H669" s="11">
@@ -50358,7 +50353,7 @@
         <v>2</v>
       </c>
       <c r="K669" s="9" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="L669" s="9" t="s">
         <v>72</v>
@@ -50376,7 +50371,7 @@
         <v>50</v>
       </c>
       <c r="Q669" s="9" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="R669" s="9"/>
       <c r="S669" s="9"/>
@@ -50384,22 +50379,22 @@
     </row>
     <row r="670" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="17" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B670" s="17" t="s">
         <v>3528</v>
       </c>
-      <c r="B670" s="17" t="s">
-        <v>3529</v>
-      </c>
       <c r="C670" s="17" t="s">
+        <v>3577</v>
+      </c>
+      <c r="D670" s="17" t="s">
         <v>3578</v>
-      </c>
-      <c r="D670" s="17" t="s">
-        <v>3579</v>
       </c>
       <c r="E670" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F670" s="17" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="G670" s="17"/>
       <c r="H670" s="19">
@@ -50430,7 +50425,7 @@
         <v>40</v>
       </c>
       <c r="Q670" s="17" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="R670" s="17"/>
       <c r="S670" s="17"/>
@@ -50438,22 +50433,22 @@
     </row>
     <row r="671" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="17" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B671" s="17" t="s">
         <v>3528</v>
       </c>
-      <c r="B671" s="17" t="s">
-        <v>3529</v>
-      </c>
       <c r="C671" s="17" t="s">
+        <v>3581</v>
+      </c>
+      <c r="D671" s="17" t="s">
         <v>3582</v>
-      </c>
-      <c r="D671" s="17" t="s">
-        <v>3583</v>
       </c>
       <c r="E671" s="18" t="s">
         <v>850</v>
       </c>
       <c r="F671" s="17" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="G671" s="17"/>
       <c r="H671" s="19">
@@ -50466,10 +50461,10 @@
         <v>3</v>
       </c>
       <c r="K671" s="17" t="s">
+        <v>3584</v>
+      </c>
+      <c r="L671" s="17" t="s">
         <v>3585</v>
-      </c>
-      <c r="L671" s="17" t="s">
-        <v>3586</v>
       </c>
       <c r="M671" s="21">
         <v>4500</v>
@@ -50484,7 +50479,7 @@
         <v>40</v>
       </c>
       <c r="Q671" s="17" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="R671" s="17"/>
       <c r="S671" s="17"/>
@@ -50492,22 +50487,22 @@
     </row>
     <row r="672" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B672" s="2" t="s">
+        <v>3587</v>
+      </c>
+      <c r="C672" s="2" t="s">
         <v>3588</v>
       </c>
-      <c r="C672" s="2" t="s">
+      <c r="D672" s="2" t="s">
         <v>3589</v>
-      </c>
-      <c r="D672" s="2" t="s">
-        <v>3590</v>
       </c>
       <c r="E672" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F672" s="2" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="G672" s="2"/>
       <c r="H672" s="4">
@@ -50520,7 +50515,7 @@
         <v>1</v>
       </c>
       <c r="K672" s="2" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="L672" s="2" t="s">
         <v>26</v>
@@ -50538,32 +50533,32 @@
         <v>85</v>
       </c>
       <c r="Q672" s="2" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="R672" s="2"/>
       <c r="S672" s="2"/>
       <c r="T672" s="2" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="673" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C673" s="2" t="s">
+        <v>3594</v>
+      </c>
+      <c r="D673" s="2" t="s">
         <v>3595</v>
-      </c>
-      <c r="D673" s="2" t="s">
-        <v>3596</v>
       </c>
       <c r="E673" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F673" s="2" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="G673" s="2"/>
       <c r="H673" s="4">
@@ -50576,10 +50571,10 @@
         <v>1</v>
       </c>
       <c r="K673" s="2" t="s">
+        <v>3597</v>
+      </c>
+      <c r="L673" s="2" t="s">
         <v>3598</v>
-      </c>
-      <c r="L673" s="2" t="s">
-        <v>3599</v>
       </c>
       <c r="M673" s="6">
         <v>5500</v>
@@ -50594,7 +50589,7 @@
         <v>80</v>
       </c>
       <c r="Q673" s="2" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="R673" s="2"/>
       <c r="S673" s="2"/>
@@ -50602,22 +50597,22 @@
     </row>
     <row r="674" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C674" s="2" t="s">
+        <v>3600</v>
+      </c>
+      <c r="D674" s="2" t="s">
         <v>3601</v>
-      </c>
-      <c r="D674" s="2" t="s">
-        <v>3602</v>
       </c>
       <c r="E674" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F674" s="2" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="G674" s="2"/>
       <c r="H674" s="4">
@@ -50630,7 +50625,7 @@
         <v>1</v>
       </c>
       <c r="K674" s="2" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="L674" s="2" t="s">
         <v>1018</v>
@@ -50648,32 +50643,32 @@
         <v>75</v>
       </c>
       <c r="Q674" s="2" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="R674" s="2"/>
       <c r="S674" s="2"/>
       <c r="T674" s="2" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="675" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C675" s="2" t="s">
+        <v>3606</v>
+      </c>
+      <c r="D675" s="2" t="s">
         <v>3607</v>
-      </c>
-      <c r="D675" s="2" t="s">
-        <v>3608</v>
       </c>
       <c r="E675" s="3" t="s">
         <v>479</v>
       </c>
       <c r="F675" s="2" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="G675" s="2"/>
       <c r="H675" s="4">
@@ -50686,7 +50681,7 @@
         <v>1</v>
       </c>
       <c r="K675" s="2" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="L675" s="2" t="s">
         <v>482</v>
@@ -50704,7 +50699,7 @@
         <v>65</v>
       </c>
       <c r="Q675" s="2" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="R675" s="2"/>
       <c r="S675" s="2"/>
@@ -50712,22 +50707,22 @@
     </row>
     <row r="676" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C676" s="2" t="s">
+        <v>3611</v>
+      </c>
+      <c r="D676" s="2" t="s">
         <v>3612</v>
-      </c>
-      <c r="D676" s="2" t="s">
-        <v>3613</v>
       </c>
       <c r="E676" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F676" s="2" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="G676" s="2"/>
       <c r="H676" s="4">
@@ -50740,7 +50735,7 @@
         <v>1</v>
       </c>
       <c r="K676" s="2" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="L676" s="2" t="s">
         <v>1018</v>
@@ -50758,32 +50753,32 @@
         <v>60</v>
       </c>
       <c r="Q676" s="2" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="R676" s="2"/>
       <c r="S676" s="2"/>
       <c r="T676" s="2" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="677" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C677" s="2" t="s">
+        <v>3617</v>
+      </c>
+      <c r="D677" s="2" t="s">
         <v>3618</v>
-      </c>
-      <c r="D677" s="2" t="s">
-        <v>3619</v>
       </c>
       <c r="E677" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F677" s="2" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="G677" s="2"/>
       <c r="H677" s="4">
@@ -50796,7 +50791,7 @@
         <v>1</v>
       </c>
       <c r="K677" s="2" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="L677" s="2" t="s">
         <v>72</v>
@@ -50814,7 +50809,7 @@
         <v>65</v>
       </c>
       <c r="Q677" s="2" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="R677" s="2"/>
       <c r="S677" s="2"/>
@@ -50822,22 +50817,22 @@
     </row>
     <row r="678" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B678" s="9" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C678" s="9" t="s">
+        <v>3622</v>
+      </c>
+      <c r="D678" s="9" t="s">
         <v>3623</v>
-      </c>
-      <c r="D678" s="9" t="s">
-        <v>3624</v>
       </c>
       <c r="E678" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F678" s="9" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="G678" s="9"/>
       <c r="H678" s="11">
@@ -50850,7 +50845,7 @@
         <v>2</v>
       </c>
       <c r="K678" s="9" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="L678" s="9" t="s">
         <v>112</v>
@@ -50868,7 +50863,7 @@
         <v>60</v>
       </c>
       <c r="Q678" s="9" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="R678" s="9"/>
       <c r="S678" s="9"/>
@@ -50876,22 +50871,22 @@
     </row>
     <row r="679" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B679" s="9" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C679" s="9" t="s">
+        <v>3627</v>
+      </c>
+      <c r="D679" s="9" t="s">
         <v>3628</v>
-      </c>
-      <c r="D679" s="9" t="s">
-        <v>3629</v>
       </c>
       <c r="E679" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F679" s="9" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="G679" s="9"/>
       <c r="H679" s="11">
@@ -50904,7 +50899,7 @@
         <v>2</v>
       </c>
       <c r="K679" s="9" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="L679" s="9" t="s">
         <v>112</v>
@@ -50922,7 +50917,7 @@
         <v>50</v>
       </c>
       <c r="Q679" s="9" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="R679" s="9"/>
       <c r="S679" s="9"/>
@@ -50930,22 +50925,22 @@
     </row>
     <row r="680" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B680" s="9" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C680" s="9" t="s">
+        <v>3632</v>
+      </c>
+      <c r="D680" s="9" t="s">
         <v>3633</v>
-      </c>
-      <c r="D680" s="9" t="s">
-        <v>3634</v>
       </c>
       <c r="E680" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F680" s="9" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="G680" s="9"/>
       <c r="H680" s="11">
@@ -50958,7 +50953,7 @@
         <v>2</v>
       </c>
       <c r="K680" s="9" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="L680" s="9" t="s">
         <v>72</v>
@@ -50976,7 +50971,7 @@
         <v>50</v>
       </c>
       <c r="Q680" s="9" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="R680" s="9"/>
       <c r="S680" s="9"/>
@@ -50984,22 +50979,22 @@
     </row>
     <row r="681" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B681" s="9" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C681" s="9" t="s">
+        <v>3637</v>
+      </c>
+      <c r="D681" s="9" t="s">
         <v>3638</v>
-      </c>
-      <c r="D681" s="9" t="s">
-        <v>3639</v>
       </c>
       <c r="E681" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F681" s="9" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="G681" s="9"/>
       <c r="H681" s="11">
@@ -51012,7 +51007,7 @@
         <v>2</v>
       </c>
       <c r="K681" s="9" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="L681" s="9" t="s">
         <v>72</v>
@@ -51030,7 +51025,7 @@
         <v>50</v>
       </c>
       <c r="Q681" s="9" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="R681" s="9"/>
       <c r="S681" s="9"/>
@@ -51038,22 +51033,22 @@
     </row>
     <row r="682" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B682" s="9" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C682" s="9" t="s">
+        <v>3642</v>
+      </c>
+      <c r="D682" s="9" t="s">
         <v>3643</v>
-      </c>
-      <c r="D682" s="9" t="s">
-        <v>3644</v>
       </c>
       <c r="E682" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F682" s="9" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="G682" s="9"/>
       <c r="H682" s="11">
@@ -51066,7 +51061,7 @@
         <v>2</v>
       </c>
       <c r="K682" s="9" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="L682" s="9" t="s">
         <v>1018</v>
@@ -51084,7 +51079,7 @@
         <v>45</v>
       </c>
       <c r="Q682" s="9" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="R682" s="9"/>
       <c r="S682" s="9"/>
@@ -51092,22 +51087,22 @@
     </row>
     <row r="683" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B683" s="9" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C683" s="9" t="s">
+        <v>3646</v>
+      </c>
+      <c r="D683" s="9" t="s">
         <v>3647</v>
-      </c>
-      <c r="D683" s="9" t="s">
-        <v>3648</v>
       </c>
       <c r="E683" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F683" s="9" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="G683" s="9"/>
       <c r="H683" s="11">
@@ -51120,7 +51115,7 @@
         <v>2</v>
       </c>
       <c r="K683" s="9" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="L683" s="9" t="s">
         <v>72</v>
@@ -51138,32 +51133,32 @@
         <v>45</v>
       </c>
       <c r="Q683" s="9" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="R683" s="9"/>
       <c r="S683" s="9"/>
       <c r="T683" s="9" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="684" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="17" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B684" s="17" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C684" s="17" t="s">
+        <v>3652</v>
+      </c>
+      <c r="D684" s="17" t="s">
         <v>3653</v>
-      </c>
-      <c r="D684" s="17" t="s">
-        <v>3654</v>
       </c>
       <c r="E684" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F684" s="17" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="G684" s="17"/>
       <c r="H684" s="19">
@@ -51176,7 +51171,7 @@
         <v>3</v>
       </c>
       <c r="K684" s="17" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="L684" s="17" t="s">
         <v>123</v>
@@ -51194,7 +51189,7 @@
         <v>40</v>
       </c>
       <c r="Q684" s="17" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="R684" s="17"/>
       <c r="S684" s="17"/>
@@ -51202,22 +51197,22 @@
     </row>
     <row r="685" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B685" s="2" t="s">
+        <v>3657</v>
+      </c>
+      <c r="C685" s="2" t="s">
         <v>3658</v>
       </c>
-      <c r="C685" s="2" t="s">
+      <c r="D685" s="2" t="s">
         <v>3659</v>
-      </c>
-      <c r="D685" s="2" t="s">
-        <v>3660</v>
       </c>
       <c r="E685" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F685" s="2" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="G685" s="2"/>
       <c r="H685" s="4">
@@ -51230,7 +51225,7 @@
         <v>1</v>
       </c>
       <c r="K685" s="2" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="L685" s="2" t="s">
         <v>26</v>
@@ -51248,32 +51243,32 @@
         <v>80</v>
       </c>
       <c r="Q685" s="2" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="R685" s="2"/>
       <c r="S685" s="2"/>
       <c r="T685" s="2" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="686" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C686" s="2" t="s">
+        <v>3664</v>
+      </c>
+      <c r="D686" s="2" t="s">
         <v>3665</v>
-      </c>
-      <c r="D686" s="2" t="s">
-        <v>3666</v>
       </c>
       <c r="E686" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F686" s="2" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="G686" s="2"/>
       <c r="H686" s="4">
@@ -51286,7 +51281,7 @@
         <v>1</v>
       </c>
       <c r="K686" s="2" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="L686" s="2" t="s">
         <v>72</v>
@@ -51304,32 +51299,32 @@
         <v>80</v>
       </c>
       <c r="Q686" s="2" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="R686" s="2"/>
       <c r="S686" s="2"/>
       <c r="T686" s="2" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="687" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C687" s="2" t="s">
+        <v>3670</v>
+      </c>
+      <c r="D687" s="2" t="s">
         <v>3671</v>
-      </c>
-      <c r="D687" s="2" t="s">
-        <v>3672</v>
       </c>
       <c r="E687" s="3" t="s">
         <v>2153</v>
       </c>
       <c r="F687" s="2" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="G687" s="2"/>
       <c r="H687" s="4">
@@ -51342,7 +51337,7 @@
         <v>1</v>
       </c>
       <c r="K687" s="2" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="L687" s="2" t="s">
         <v>2156</v>
@@ -51360,32 +51355,32 @@
         <v>70</v>
       </c>
       <c r="Q687" s="2" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="R687" s="2"/>
       <c r="S687" s="2"/>
       <c r="T687" s="2" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="688" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C688" s="2" t="s">
+        <v>3676</v>
+      </c>
+      <c r="D688" s="2" t="s">
         <v>3677</v>
-      </c>
-      <c r="D688" s="2" t="s">
-        <v>3678</v>
       </c>
       <c r="E688" s="3" t="s">
         <v>461</v>
       </c>
       <c r="F688" s="2" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="G688" s="2"/>
       <c r="H688" s="4">
@@ -51398,10 +51393,10 @@
         <v>1</v>
       </c>
       <c r="K688" s="2" t="s">
+        <v>3679</v>
+      </c>
+      <c r="L688" s="2" t="s">
         <v>3680</v>
-      </c>
-      <c r="L688" s="2" t="s">
-        <v>3681</v>
       </c>
       <c r="M688" s="6">
         <v>5000</v>
@@ -51416,32 +51411,32 @@
         <v>75</v>
       </c>
       <c r="Q688" s="2" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="R688" s="2"/>
       <c r="S688" s="2"/>
       <c r="T688" s="2" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="689" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C689" s="2" t="s">
+        <v>3683</v>
+      </c>
+      <c r="D689" s="2" t="s">
         <v>3684</v>
-      </c>
-      <c r="D689" s="2" t="s">
-        <v>3685</v>
       </c>
       <c r="E689" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F689" s="2" t="s">
-        <v>3686</v>
+        <v>3685</v>
       </c>
       <c r="G689" s="2"/>
       <c r="H689" s="4">
@@ -51454,7 +51449,7 @@
         <v>1</v>
       </c>
       <c r="K689" s="2" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="L689" s="2" t="s">
         <v>35</v>
@@ -51472,7 +51467,7 @@
         <v>70</v>
       </c>
       <c r="Q689" s="2" t="s">
-        <v>3687</v>
+        <v>3686</v>
       </c>
       <c r="R689" s="2"/>
       <c r="S689" s="2"/>
@@ -51480,22 +51475,22 @@
     </row>
     <row r="690" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C690" s="2" t="s">
+        <v>3687</v>
+      </c>
+      <c r="D690" s="2" t="s">
         <v>3688</v>
-      </c>
-      <c r="D690" s="2" t="s">
-        <v>3689</v>
       </c>
       <c r="E690" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F690" s="2" t="s">
-        <v>3690</v>
+        <v>3689</v>
       </c>
       <c r="G690" s="2"/>
       <c r="H690" s="4">
@@ -51508,7 +51503,7 @@
         <v>1</v>
       </c>
       <c r="K690" s="2" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
       <c r="L690" s="2" t="s">
         <v>35</v>
@@ -51526,7 +51521,7 @@
         <v>70</v>
       </c>
       <c r="Q690" s="2" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="R690" s="2"/>
       <c r="S690" s="2"/>
@@ -51534,22 +51529,22 @@
     </row>
     <row r="691" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C691" s="2" t="s">
+        <v>3692</v>
+      </c>
+      <c r="D691" s="2" t="s">
         <v>3693</v>
-      </c>
-      <c r="D691" s="2" t="s">
-        <v>3694</v>
       </c>
       <c r="E691" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F691" s="2" t="s">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="G691" s="2"/>
       <c r="H691" s="4">
@@ -51562,7 +51557,7 @@
         <v>1</v>
       </c>
       <c r="K691" s="2" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
       <c r="L691" s="2" t="s">
         <v>1982</v>
@@ -51580,7 +51575,7 @@
         <v>60</v>
       </c>
       <c r="Q691" s="2" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
       <c r="R691" s="2"/>
       <c r="S691" s="2"/>
@@ -51588,22 +51583,22 @@
     </row>
     <row r="692" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B692" s="9" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C692" s="9" t="s">
+        <v>3697</v>
+      </c>
+      <c r="D692" s="9" t="s">
         <v>3698</v>
-      </c>
-      <c r="D692" s="9" t="s">
-        <v>3699</v>
       </c>
       <c r="E692" s="10" t="s">
         <v>301</v>
       </c>
       <c r="F692" s="9" t="s">
-        <v>3700</v>
+        <v>3699</v>
       </c>
       <c r="G692" s="9"/>
       <c r="H692" s="11">
@@ -51616,7 +51611,7 @@
         <v>2</v>
       </c>
       <c r="K692" s="9" t="s">
-        <v>3701</v>
+        <v>3700</v>
       </c>
       <c r="L692" s="9" t="s">
         <v>984</v>
@@ -51634,7 +51629,7 @@
         <v>55</v>
       </c>
       <c r="Q692" s="9" t="s">
-        <v>3702</v>
+        <v>3701</v>
       </c>
       <c r="R692" s="9"/>
       <c r="S692" s="9"/>
@@ -51642,22 +51637,22 @@
     </row>
     <row r="693" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B693" s="9" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C693" s="9" t="s">
+        <v>3702</v>
+      </c>
+      <c r="D693" s="9" t="s">
         <v>3703</v>
-      </c>
-      <c r="D693" s="9" t="s">
-        <v>3704</v>
       </c>
       <c r="E693" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F693" s="9" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="G693" s="9"/>
       <c r="H693" s="11">
@@ -51670,7 +51665,7 @@
         <v>2</v>
       </c>
       <c r="K693" s="9" t="s">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="L693" s="9" t="s">
         <v>72</v>
@@ -51688,7 +51683,7 @@
         <v>50</v>
       </c>
       <c r="Q693" s="9" t="s">
-        <v>3707</v>
+        <v>3706</v>
       </c>
       <c r="R693" s="9"/>
       <c r="S693" s="9"/>
@@ -51696,22 +51691,22 @@
     </row>
     <row r="694" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B694" s="9" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C694" s="9" t="s">
+        <v>3707</v>
+      </c>
+      <c r="D694" s="9" t="s">
         <v>3708</v>
-      </c>
-      <c r="D694" s="9" t="s">
-        <v>3709</v>
       </c>
       <c r="E694" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F694" s="9" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="G694" s="9"/>
       <c r="H694" s="11">
@@ -51724,7 +51719,7 @@
         <v>2</v>
       </c>
       <c r="K694" s="9" t="s">
-        <v>3711</v>
+        <v>3710</v>
       </c>
       <c r="L694" s="9" t="s">
         <v>112</v>
@@ -51742,7 +51737,7 @@
         <v>45</v>
       </c>
       <c r="Q694" s="9" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="R694" s="9"/>
       <c r="S694" s="9"/>
@@ -51750,22 +51745,22 @@
     </row>
     <row r="695" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B695" s="9" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C695" s="9" t="s">
+        <v>3712</v>
+      </c>
+      <c r="D695" s="9" t="s">
         <v>3713</v>
-      </c>
-      <c r="D695" s="9" t="s">
-        <v>3714</v>
       </c>
       <c r="E695" s="10" t="s">
         <v>830</v>
       </c>
       <c r="F695" s="9" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="G695" s="9"/>
       <c r="H695" s="11">
@@ -51778,7 +51773,7 @@
         <v>2</v>
       </c>
       <c r="K695" s="9" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="L695" s="9" t="s">
         <v>833</v>
@@ -51796,7 +51791,7 @@
         <v>50</v>
       </c>
       <c r="Q695" s="9" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="R695" s="9"/>
       <c r="S695" s="9"/>
@@ -51804,22 +51799,22 @@
     </row>
     <row r="696" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B696" s="9" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C696" s="9" t="s">
+        <v>3717</v>
+      </c>
+      <c r="D696" s="9" t="s">
         <v>3718</v>
-      </c>
-      <c r="D696" s="9" t="s">
-        <v>3719</v>
       </c>
       <c r="E696" s="10" t="s">
         <v>91</v>
       </c>
       <c r="F696" s="9" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="G696" s="9"/>
       <c r="H696" s="11">
@@ -51832,7 +51827,7 @@
         <v>2</v>
       </c>
       <c r="K696" s="9" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="L696" s="9" t="s">
         <v>94</v>
@@ -51850,7 +51845,7 @@
         <v>45</v>
       </c>
       <c r="Q696" s="9" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="R696" s="9"/>
       <c r="S696" s="9"/>
@@ -51858,22 +51853,22 @@
     </row>
     <row r="697" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="17" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B697" s="17" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C697" s="17" t="s">
+        <v>3722</v>
+      </c>
+      <c r="D697" s="17" t="s">
         <v>3723</v>
-      </c>
-      <c r="D697" s="17" t="s">
-        <v>3724</v>
       </c>
       <c r="E697" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F697" s="17" t="s">
-        <v>3725</v>
+        <v>3724</v>
       </c>
       <c r="G697" s="17"/>
       <c r="H697" s="19">
@@ -51886,7 +51881,7 @@
         <v>3</v>
       </c>
       <c r="K697" s="17" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="L697" s="17" t="s">
         <v>123</v>
@@ -51904,7 +51899,7 @@
         <v>40</v>
       </c>
       <c r="Q697" s="17" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="R697" s="17"/>
       <c r="S697" s="17"/>
@@ -51912,22 +51907,22 @@
     </row>
     <row r="698" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B698" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B698" s="2" t="s">
+      <c r="C698" s="2" t="s">
         <v>3729</v>
       </c>
-      <c r="C698" s="2" t="s">
+      <c r="D698" s="2" t="s">
         <v>3730</v>
-      </c>
-      <c r="D698" s="2" t="s">
-        <v>3731</v>
       </c>
       <c r="E698" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F698" s="2" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
       <c r="G698" s="2"/>
       <c r="H698" s="4">
@@ -51958,32 +51953,32 @@
         <v>80</v>
       </c>
       <c r="Q698" s="2" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="R698" s="2"/>
       <c r="S698" s="2"/>
       <c r="T698" s="2" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="699" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B699" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B699" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C699" s="2" t="s">
+        <v>3734</v>
+      </c>
+      <c r="D699" s="2" t="s">
         <v>3735</v>
-      </c>
-      <c r="D699" s="2" t="s">
-        <v>3736</v>
       </c>
       <c r="E699" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F699" s="2" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="G699" s="2"/>
       <c r="H699" s="4">
@@ -51996,7 +51991,7 @@
         <v>1</v>
       </c>
       <c r="K699" s="2" t="s">
-        <v>3738</v>
+        <v>3737</v>
       </c>
       <c r="L699" s="2" t="s">
         <v>100</v>
@@ -52014,32 +52009,32 @@
         <v>80</v>
       </c>
       <c r="Q699" s="2" t="s">
-        <v>3739</v>
+        <v>3738</v>
       </c>
       <c r="R699" s="2"/>
       <c r="S699" s="2"/>
       <c r="T699" s="2" t="s">
-        <v>3740</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="700" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B700" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B700" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C700" s="2" t="s">
+        <v>3740</v>
+      </c>
+      <c r="D700" s="2" t="s">
         <v>3741</v>
-      </c>
-      <c r="D700" s="2" t="s">
-        <v>3742</v>
       </c>
       <c r="E700" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F700" s="2" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="G700" s="2"/>
       <c r="H700" s="4">
@@ -52070,32 +52065,32 @@
         <v>75</v>
       </c>
       <c r="Q700" s="2" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
       <c r="R700" s="2"/>
       <c r="S700" s="2"/>
       <c r="T700" s="2" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="701" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B701" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B701" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C701" s="2" t="s">
+        <v>3745</v>
+      </c>
+      <c r="D701" s="2" t="s">
         <v>3746</v>
-      </c>
-      <c r="D701" s="2" t="s">
-        <v>3747</v>
       </c>
       <c r="E701" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F701" s="2" t="s">
-        <v>3748</v>
+        <v>3747</v>
       </c>
       <c r="G701" s="2"/>
       <c r="H701" s="4">
@@ -52108,7 +52103,7 @@
         <v>1</v>
       </c>
       <c r="K701" s="2" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="L701" s="2" t="s">
         <v>100</v>
@@ -52126,7 +52121,7 @@
         <v>65</v>
       </c>
       <c r="Q701" s="2" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="R701" s="2"/>
       <c r="S701" s="2"/>
@@ -52134,22 +52129,22 @@
     </row>
     <row r="702" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B702" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B702" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C702" s="2" t="s">
+        <v>3750</v>
+      </c>
+      <c r="D702" s="2" t="s">
         <v>3751</v>
-      </c>
-      <c r="D702" s="2" t="s">
-        <v>3752</v>
       </c>
       <c r="E702" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F702" s="2" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="G702" s="2"/>
       <c r="H702" s="4">
@@ -52162,10 +52157,10 @@
         <v>1</v>
       </c>
       <c r="K702" s="2" t="s">
+        <v>3753</v>
+      </c>
+      <c r="L702" s="2" t="s">
         <v>3754</v>
-      </c>
-      <c r="L702" s="2" t="s">
-        <v>3755</v>
       </c>
       <c r="M702" s="6">
         <v>8500</v>
@@ -52180,7 +52175,7 @@
         <v>60</v>
       </c>
       <c r="Q702" s="2" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="R702" s="2"/>
       <c r="S702" s="2"/>
@@ -52188,22 +52183,22 @@
     </row>
     <row r="703" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B703" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B703" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C703" s="2" t="s">
+        <v>3756</v>
+      </c>
+      <c r="D703" s="2" t="s">
         <v>3757</v>
-      </c>
-      <c r="D703" s="2" t="s">
-        <v>3758</v>
       </c>
       <c r="E703" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F703" s="2" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="G703" s="2"/>
       <c r="H703" s="4">
@@ -52216,7 +52211,7 @@
         <v>1</v>
       </c>
       <c r="K703" s="2" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="L703" s="2" t="s">
         <v>909</v>
@@ -52234,7 +52229,7 @@
         <v>55</v>
       </c>
       <c r="Q703" s="2" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="R703" s="2"/>
       <c r="S703" s="2"/>
@@ -52242,22 +52237,22 @@
     </row>
     <row r="704" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B704" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B704" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C704" s="2" t="s">
+        <v>3761</v>
+      </c>
+      <c r="D704" s="2" t="s">
         <v>3762</v>
-      </c>
-      <c r="D704" s="2" t="s">
-        <v>3763</v>
       </c>
       <c r="E704" s="3" t="s">
         <v>110</v>
       </c>
       <c r="F704" s="2" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="G704" s="2"/>
       <c r="H704" s="4">
@@ -52288,7 +52283,7 @@
         <v>60</v>
       </c>
       <c r="Q704" s="2" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="R704" s="2"/>
       <c r="S704" s="2"/>
@@ -52296,22 +52291,22 @@
     </row>
     <row r="705" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B705" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B705" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C705" s="2" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D705" s="2" t="s">
         <v>3766</v>
-      </c>
-      <c r="D705" s="2" t="s">
-        <v>3767</v>
       </c>
       <c r="E705" s="3" t="s">
         <v>490</v>
       </c>
       <c r="F705" s="2" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="G705" s="2"/>
       <c r="H705" s="4">
@@ -52342,7 +52337,7 @@
         <v>55</v>
       </c>
       <c r="Q705" s="2" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="R705" s="2"/>
       <c r="S705" s="2"/>
@@ -52350,22 +52345,22 @@
     </row>
     <row r="706" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B706" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B706" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C706" s="2" t="s">
+        <v>3769</v>
+      </c>
+      <c r="D706" s="2" t="s">
         <v>3770</v>
-      </c>
-      <c r="D706" s="2" t="s">
-        <v>3771</v>
       </c>
       <c r="E706" s="3" t="s">
         <v>110</v>
       </c>
       <c r="F706" s="2" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="G706" s="2"/>
       <c r="H706" s="4">
@@ -52396,7 +52391,7 @@
         <v>55</v>
       </c>
       <c r="Q706" s="2" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="R706" s="2"/>
       <c r="S706" s="2"/>
@@ -52404,22 +52399,22 @@
     </row>
     <row r="707" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B707" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B707" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C707" s="2" t="s">
+        <v>3773</v>
+      </c>
+      <c r="D707" s="2" t="s">
         <v>3774</v>
-      </c>
-      <c r="D707" s="2" t="s">
-        <v>3775</v>
       </c>
       <c r="E707" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F707" s="2" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="G707" s="2"/>
       <c r="H707" s="4">
@@ -52432,10 +52427,10 @@
         <v>1</v>
       </c>
       <c r="K707" s="2" t="s">
+        <v>3776</v>
+      </c>
+      <c r="L707" s="2" t="s">
         <v>3777</v>
-      </c>
-      <c r="L707" s="2" t="s">
-        <v>3778</v>
       </c>
       <c r="M707" s="6">
         <v>6500</v>
@@ -52450,7 +52445,7 @@
         <v>55</v>
       </c>
       <c r="Q707" s="2" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="R707" s="2"/>
       <c r="S707" s="2"/>
@@ -52458,22 +52453,22 @@
     </row>
     <row r="708" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B708" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B708" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C708" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="D708" s="2" t="s">
         <v>3780</v>
-      </c>
-      <c r="D708" s="2" t="s">
-        <v>3781</v>
       </c>
       <c r="E708" s="3" t="s">
         <v>110</v>
       </c>
       <c r="F708" s="2" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="G708" s="2"/>
       <c r="H708" s="4">
@@ -52504,7 +52499,7 @@
         <v>50</v>
       </c>
       <c r="Q708" s="2" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="R708" s="2"/>
       <c r="S708" s="2"/>
@@ -52512,22 +52507,22 @@
     </row>
     <row r="709" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B709" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B709" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C709" s="2" t="s">
+        <v>3783</v>
+      </c>
+      <c r="D709" s="2" t="s">
         <v>3784</v>
-      </c>
-      <c r="D709" s="2" t="s">
-        <v>3785</v>
       </c>
       <c r="E709" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F709" s="2" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="G709" s="2"/>
       <c r="H709" s="4">
@@ -52558,7 +52553,7 @@
         <v>50</v>
       </c>
       <c r="Q709" s="2" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="R709" s="2"/>
       <c r="S709" s="2"/>
@@ -52566,22 +52561,22 @@
     </row>
     <row r="710" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B710" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B710" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C710" s="2" t="s">
+        <v>3787</v>
+      </c>
+      <c r="D710" s="2" t="s">
         <v>3788</v>
-      </c>
-      <c r="D710" s="2" t="s">
-        <v>3789</v>
       </c>
       <c r="E710" s="3" t="s">
         <v>864</v>
       </c>
       <c r="F710" s="2" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="G710" s="2"/>
       <c r="H710" s="4">
@@ -52594,7 +52589,7 @@
         <v>1</v>
       </c>
       <c r="K710" s="2" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="L710" s="2" t="s">
         <v>867</v>
@@ -52612,7 +52607,7 @@
         <v>50</v>
       </c>
       <c r="Q710" s="2" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="R710" s="2"/>
       <c r="S710" s="2"/>
@@ -52620,22 +52615,22 @@
     </row>
     <row r="711" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B711" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B711" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C711" s="2" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D711" s="2" t="s">
         <v>3793</v>
-      </c>
-      <c r="D711" s="2" t="s">
-        <v>3794</v>
       </c>
       <c r="E711" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F711" s="2" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="G711" s="2"/>
       <c r="H711" s="4">
@@ -52648,7 +52643,7 @@
         <v>1</v>
       </c>
       <c r="K711" s="2" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="L711" s="2" t="s">
         <v>2743</v>
@@ -52666,7 +52661,7 @@
         <v>50</v>
       </c>
       <c r="Q711" s="2" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="R711" s="2"/>
       <c r="S711" s="2"/>
@@ -52674,22 +52669,22 @@
     </row>
     <row r="712" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B712" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B712" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C712" s="2" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D712" s="2" t="s">
         <v>3798</v>
-      </c>
-      <c r="D712" s="2" t="s">
-        <v>3799</v>
       </c>
       <c r="E712" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F712" s="2" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="G712" s="2"/>
       <c r="H712" s="4">
@@ -52720,7 +52715,7 @@
         <v>45</v>
       </c>
       <c r="Q712" s="2" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="R712" s="2"/>
       <c r="S712" s="2"/>
@@ -52728,22 +52723,22 @@
     </row>
     <row r="713" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="2" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B713" s="2" t="s">
         <v>3728</v>
       </c>
-      <c r="B713" s="2" t="s">
-        <v>3729</v>
-      </c>
       <c r="C713" s="2" t="s">
+        <v>3801</v>
+      </c>
+      <c r="D713" s="2" t="s">
         <v>3802</v>
-      </c>
-      <c r="D713" s="2" t="s">
-        <v>3803</v>
       </c>
       <c r="E713" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F713" s="2" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="G713" s="2"/>
       <c r="H713" s="4">
@@ -52756,7 +52751,7 @@
         <v>1</v>
       </c>
       <c r="K713" s="2" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="L713" s="2" t="s">
         <v>123</v>
@@ -52774,7 +52769,7 @@
         <v>45</v>
       </c>
       <c r="Q713" s="2" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="R713" s="2"/>
       <c r="S713" s="2"/>
@@ -52788,16 +52783,16 @@
         <v>2899</v>
       </c>
       <c r="C714" s="2" t="s">
+        <v>3806</v>
+      </c>
+      <c r="D714" s="2" t="s">
         <v>3807</v>
-      </c>
-      <c r="D714" s="2" t="s">
-        <v>3808</v>
       </c>
       <c r="E714" s="3" t="s">
         <v>857</v>
       </c>
       <c r="F714" s="2" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="G714" s="2"/>
       <c r="H714" s="4">
@@ -52810,16 +52805,16 @@
         <v>1</v>
       </c>
       <c r="K714" s="2" t="s">
+        <v>3809</v>
+      </c>
+      <c r="L714" s="2" t="s">
         <v>3810</v>
-      </c>
-      <c r="L714" s="2" t="s">
-        <v>3811</v>
       </c>
       <c r="M714" s="6">
         <v>4000</v>
       </c>
       <c r="N714" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O714" s="6">
         <v>95</v>
@@ -52828,7 +52823,7 @@
         <v>60</v>
       </c>
       <c r="Q714" s="2" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="R714" s="2"/>
       <c r="S714" s="2"/>
@@ -52842,16 +52837,16 @@
         <v>1447</v>
       </c>
       <c r="C715" s="2" t="s">
+        <v>3813</v>
+      </c>
+      <c r="D715" s="2" t="s">
         <v>3814</v>
-      </c>
-      <c r="D715" s="2" t="s">
-        <v>3815</v>
       </c>
       <c r="E715" s="3" t="s">
         <v>857</v>
       </c>
       <c r="F715" s="2" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="G715" s="2"/>
       <c r="H715" s="4">
@@ -52864,16 +52859,16 @@
         <v>1</v>
       </c>
       <c r="K715" s="2" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="L715" s="2" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M715" s="6">
         <v>3500</v>
       </c>
       <c r="N715" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O715" s="6">
         <v>95</v>
@@ -52882,7 +52877,7 @@
         <v>60</v>
       </c>
       <c r="Q715" s="2" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="R715" s="2"/>
       <c r="S715" s="2"/>
@@ -52896,16 +52891,16 @@
         <v>2838</v>
       </c>
       <c r="C716" s="2" t="s">
+        <v>3818</v>
+      </c>
+      <c r="D716" s="2" t="s">
         <v>3819</v>
-      </c>
-      <c r="D716" s="2" t="s">
-        <v>3820</v>
       </c>
       <c r="E716" s="3" t="s">
         <v>857</v>
       </c>
       <c r="F716" s="2" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="G716" s="2"/>
       <c r="H716" s="4">
@@ -52918,16 +52913,16 @@
         <v>1</v>
       </c>
       <c r="K716" s="2" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="L716" s="2" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M716" s="6">
         <v>4000</v>
       </c>
       <c r="N716" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O716" s="6">
         <v>95</v>
@@ -52936,7 +52931,7 @@
         <v>60</v>
       </c>
       <c r="Q716" s="2" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="R716" s="2"/>
       <c r="S716" s="2"/>
@@ -52950,16 +52945,16 @@
         <v>1447</v>
       </c>
       <c r="C717" s="9" t="s">
+        <v>3823</v>
+      </c>
+      <c r="D717" s="9" t="s">
         <v>3824</v>
-      </c>
-      <c r="D717" s="9" t="s">
-        <v>3825</v>
       </c>
       <c r="E717" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F717" s="9" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="G717" s="9"/>
       <c r="H717" s="11">
@@ -52972,16 +52967,16 @@
         <v>2</v>
       </c>
       <c r="K717" s="9" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="L717" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M717" s="13">
         <v>3000</v>
       </c>
       <c r="N717" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O717" s="13">
         <v>80</v>
@@ -52990,7 +52985,7 @@
         <v>55</v>
       </c>
       <c r="Q717" s="9" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="R717" s="9"/>
       <c r="S717" s="9"/>
@@ -53004,16 +52999,16 @@
         <v>600</v>
       </c>
       <c r="C718" s="9" t="s">
+        <v>3828</v>
+      </c>
+      <c r="D718" s="9" t="s">
         <v>3829</v>
-      </c>
-      <c r="D718" s="9" t="s">
-        <v>3830</v>
       </c>
       <c r="E718" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F718" s="9" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="G718" s="9"/>
       <c r="H718" s="11">
@@ -53026,16 +53021,16 @@
         <v>2</v>
       </c>
       <c r="K718" s="9" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="L718" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M718" s="13">
         <v>3500</v>
       </c>
       <c r="N718" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O718" s="13">
         <v>80</v>
@@ -53044,7 +53039,7 @@
         <v>55</v>
       </c>
       <c r="Q718" s="9" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="R718" s="9"/>
       <c r="S718" s="9"/>
@@ -53058,16 +53053,16 @@
         <v>782</v>
       </c>
       <c r="C719" s="9" t="s">
+        <v>3833</v>
+      </c>
+      <c r="D719" s="9" t="s">
         <v>3834</v>
-      </c>
-      <c r="D719" s="9" t="s">
-        <v>3835</v>
       </c>
       <c r="E719" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F719" s="9" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="G719" s="9"/>
       <c r="H719" s="11">
@@ -53080,16 +53075,16 @@
         <v>2</v>
       </c>
       <c r="K719" s="9" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="L719" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M719" s="13">
         <v>3500</v>
       </c>
       <c r="N719" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O719" s="13">
         <v>78</v>
@@ -53098,7 +53093,7 @@
         <v>55</v>
       </c>
       <c r="Q719" s="9" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="R719" s="9"/>
       <c r="S719" s="9"/>
@@ -53112,16 +53107,16 @@
         <v>600</v>
       </c>
       <c r="C720" s="9" t="s">
+        <v>3838</v>
+      </c>
+      <c r="D720" s="9" t="s">
         <v>3839</v>
-      </c>
-      <c r="D720" s="9" t="s">
-        <v>3840</v>
       </c>
       <c r="E720" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F720" s="9" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="G720" s="9"/>
       <c r="H720" s="11">
@@ -53134,16 +53129,16 @@
         <v>2</v>
       </c>
       <c r="K720" s="9" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="L720" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M720" s="13">
         <v>3000</v>
       </c>
       <c r="N720" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O720" s="13">
         <v>75</v>
@@ -53152,7 +53147,7 @@
         <v>50</v>
       </c>
       <c r="Q720" s="9" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="R720" s="9"/>
       <c r="S720" s="9"/>
@@ -53166,16 +53161,16 @@
         <v>2069</v>
       </c>
       <c r="C721" s="9" t="s">
+        <v>3843</v>
+      </c>
+      <c r="D721" s="9" t="s">
         <v>3844</v>
-      </c>
-      <c r="D721" s="9" t="s">
-        <v>3845</v>
       </c>
       <c r="E721" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F721" s="9" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="G721" s="9"/>
       <c r="H721" s="11">
@@ -53188,16 +53183,16 @@
         <v>2</v>
       </c>
       <c r="K721" s="9" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="L721" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M721" s="13">
         <v>3000</v>
       </c>
       <c r="N721" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O721" s="13">
         <v>75</v>
@@ -53206,7 +53201,7 @@
         <v>55</v>
       </c>
       <c r="Q721" s="9" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="R721" s="9"/>
       <c r="S721" s="9"/>
@@ -53220,16 +53215,16 @@
         <v>3131</v>
       </c>
       <c r="C722" s="9" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D722" s="9" t="s">
         <v>3849</v>
-      </c>
-      <c r="D722" s="9" t="s">
-        <v>3850</v>
       </c>
       <c r="E722" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F722" s="9" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="G722" s="9"/>
       <c r="H722" s="11">
@@ -53242,16 +53237,16 @@
         <v>2</v>
       </c>
       <c r="K722" s="9" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="L722" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M722" s="13">
         <v>3000</v>
       </c>
       <c r="N722" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O722" s="13">
         <v>72</v>
@@ -53260,7 +53255,7 @@
         <v>50</v>
       </c>
       <c r="Q722" s="9" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="R722" s="9"/>
       <c r="S722" s="9"/>
@@ -53274,16 +53269,16 @@
         <v>2899</v>
       </c>
       <c r="C723" s="2" t="s">
+        <v>3852</v>
+      </c>
+      <c r="D723" s="2" t="s">
         <v>3853</v>
-      </c>
-      <c r="D723" s="2" t="s">
-        <v>3854</v>
       </c>
       <c r="E723" s="3" t="s">
         <v>964</v>
       </c>
       <c r="F723" s="2" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="G723" s="2"/>
       <c r="H723" s="4">
@@ -53296,7 +53291,7 @@
         <v>1</v>
       </c>
       <c r="K723" s="2" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="L723" s="2" t="s">
         <v>967</v>
@@ -53305,7 +53300,7 @@
         <v>2000</v>
       </c>
       <c r="N723" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O723" s="6">
         <v>95</v>
@@ -53314,7 +53309,7 @@
         <v>60</v>
       </c>
       <c r="Q723" s="2" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="R723" s="2"/>
       <c r="S723" s="2"/>
@@ -53328,16 +53323,16 @@
         <v>2838</v>
       </c>
       <c r="C724" s="9" t="s">
+        <v>3857</v>
+      </c>
+      <c r="D724" s="9" t="s">
         <v>3858</v>
-      </c>
-      <c r="D724" s="9" t="s">
-        <v>3859</v>
       </c>
       <c r="E724" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F724" s="9" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="G724" s="9"/>
       <c r="H724" s="11">
@@ -53350,16 +53345,16 @@
         <v>2</v>
       </c>
       <c r="K724" s="9" t="s">
+        <v>3860</v>
+      </c>
+      <c r="L724" s="9" t="s">
         <v>3861</v>
-      </c>
-      <c r="L724" s="9" t="s">
-        <v>3862</v>
       </c>
       <c r="M724" s="13">
         <v>2000</v>
       </c>
       <c r="N724" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O724" s="13">
         <v>82</v>
@@ -53368,7 +53363,7 @@
         <v>55</v>
       </c>
       <c r="Q724" s="9" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="R724" s="9"/>
       <c r="S724" s="9"/>
@@ -53376,22 +53371,22 @@
     </row>
     <row r="725" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="2" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B725" s="2" t="s">
         <v>3528</v>
       </c>
-      <c r="B725" s="2" t="s">
-        <v>3529</v>
-      </c>
       <c r="C725" s="2" t="s">
+        <v>3863</v>
+      </c>
+      <c r="D725" s="2" t="s">
         <v>3864</v>
       </c>
-      <c r="D725" s="2" t="s">
+      <c r="E725" s="3" t="s">
         <v>3865</v>
       </c>
-      <c r="E725" s="3" t="s">
+      <c r="F725" s="2" t="s">
         <v>3866</v>
-      </c>
-      <c r="F725" s="2" t="s">
-        <v>3867</v>
       </c>
       <c r="G725" s="2"/>
       <c r="H725" s="4">
@@ -53404,16 +53399,16 @@
         <v>1</v>
       </c>
       <c r="K725" s="2" t="s">
+        <v>3867</v>
+      </c>
+      <c r="L725" s="2" t="s">
         <v>3868</v>
-      </c>
-      <c r="L725" s="2" t="s">
-        <v>3869</v>
       </c>
       <c r="M725" s="6">
         <v>2000</v>
       </c>
       <c r="N725" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O725" s="6">
         <v>95</v>
@@ -53422,7 +53417,7 @@
         <v>60</v>
       </c>
       <c r="Q725" s="2" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="R725" s="2"/>
       <c r="S725" s="2"/>
@@ -53436,16 +53431,16 @@
         <v>495</v>
       </c>
       <c r="C726" s="2" t="s">
+        <v>3870</v>
+      </c>
+      <c r="D726" s="2" t="s">
         <v>3871</v>
-      </c>
-      <c r="D726" s="2" t="s">
-        <v>3872</v>
       </c>
       <c r="E726" s="3" t="s">
         <v>964</v>
       </c>
       <c r="F726" s="2" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="G726" s="2"/>
       <c r="H726" s="4">
@@ -53458,7 +53453,7 @@
         <v>1</v>
       </c>
       <c r="K726" s="2" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="L726" s="2" t="s">
         <v>967</v>
@@ -53467,7 +53462,7 @@
         <v>2000</v>
       </c>
       <c r="N726" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O726" s="6">
         <v>90</v>
@@ -53476,7 +53471,7 @@
         <v>55</v>
       </c>
       <c r="Q726" s="2" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="R726" s="2"/>
       <c r="S726" s="2"/>
@@ -53490,16 +53485,16 @@
         <v>1837</v>
       </c>
       <c r="C727" s="9" t="s">
+        <v>3875</v>
+      </c>
+      <c r="D727" s="9" t="s">
         <v>3876</v>
-      </c>
-      <c r="D727" s="9" t="s">
-        <v>3877</v>
       </c>
       <c r="E727" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F727" s="9" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="G727" s="9"/>
       <c r="H727" s="11">
@@ -53512,16 +53507,16 @@
         <v>2</v>
       </c>
       <c r="K727" s="9" t="s">
+        <v>3878</v>
+      </c>
+      <c r="L727" s="9" t="s">
         <v>3879</v>
-      </c>
-      <c r="L727" s="9" t="s">
-        <v>3880</v>
       </c>
       <c r="M727" s="13">
         <v>2500</v>
       </c>
       <c r="N727" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O727" s="13">
         <v>72</v>
@@ -53530,7 +53525,7 @@
         <v>50</v>
       </c>
       <c r="Q727" s="9" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="R727" s="9"/>
       <c r="S727" s="9"/>
@@ -53544,16 +53539,16 @@
         <v>2343</v>
       </c>
       <c r="C728" s="9" t="s">
+        <v>3881</v>
+      </c>
+      <c r="D728" s="9" t="s">
         <v>3882</v>
-      </c>
-      <c r="D728" s="9" t="s">
-        <v>3883</v>
       </c>
       <c r="E728" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F728" s="9" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="G728" s="9"/>
       <c r="H728" s="11">
@@ -53566,7 +53561,7 @@
         <v>2</v>
       </c>
       <c r="K728" s="9" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="L728" s="9" t="s">
         <v>967</v>
@@ -53575,7 +53570,7 @@
         <v>1500</v>
       </c>
       <c r="N728" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O728" s="13">
         <v>78</v>
@@ -53584,7 +53579,7 @@
         <v>50</v>
       </c>
       <c r="Q728" s="9" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="R728" s="9"/>
       <c r="S728" s="9"/>
@@ -53598,16 +53593,16 @@
         <v>1702</v>
       </c>
       <c r="C729" s="9" t="s">
+        <v>3886</v>
+      </c>
+      <c r="D729" s="9" t="s">
         <v>3887</v>
-      </c>
-      <c r="D729" s="9" t="s">
-        <v>3888</v>
       </c>
       <c r="E729" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F729" s="9" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="G729" s="9"/>
       <c r="H729" s="11">
@@ -53620,16 +53615,16 @@
         <v>2</v>
       </c>
       <c r="K729" s="9" t="s">
+        <v>3889</v>
+      </c>
+      <c r="L729" s="9" t="s">
         <v>3890</v>
-      </c>
-      <c r="L729" s="9" t="s">
-        <v>3891</v>
       </c>
       <c r="M729" s="13">
         <v>3000</v>
       </c>
       <c r="N729" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O729" s="13">
         <v>78</v>
@@ -53638,7 +53633,7 @@
         <v>50</v>
       </c>
       <c r="Q729" s="9" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="R729" s="9"/>
       <c r="S729" s="9"/>
@@ -53652,16 +53647,16 @@
         <v>2528</v>
       </c>
       <c r="C730" s="9" t="s">
+        <v>3892</v>
+      </c>
+      <c r="D730" s="9" t="s">
         <v>3893</v>
-      </c>
-      <c r="D730" s="9" t="s">
-        <v>3894</v>
       </c>
       <c r="E730" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F730" s="9" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="G730" s="9"/>
       <c r="H730" s="11">
@@ -53674,16 +53669,16 @@
         <v>2</v>
       </c>
       <c r="K730" s="9" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="L730" s="9" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="M730" s="13">
         <v>2500</v>
       </c>
       <c r="N730" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O730" s="13">
         <v>72</v>
@@ -53692,7 +53687,7 @@
         <v>50</v>
       </c>
       <c r="Q730" s="9" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="R730" s="9"/>
       <c r="S730" s="9"/>
@@ -53706,16 +53701,16 @@
         <v>570</v>
       </c>
       <c r="C731" s="9" t="s">
+        <v>3897</v>
+      </c>
+      <c r="D731" s="9" t="s">
         <v>3898</v>
-      </c>
-      <c r="D731" s="9" t="s">
-        <v>3899</v>
       </c>
       <c r="E731" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F731" s="9" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="G731" s="9"/>
       <c r="H731" s="11">
@@ -53728,16 +53723,16 @@
         <v>2</v>
       </c>
       <c r="K731" s="9" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="L731" s="9" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="M731" s="13">
         <v>2000</v>
       </c>
       <c r="N731" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O731" s="13">
         <v>82</v>
@@ -53746,7 +53741,7 @@
         <v>55</v>
       </c>
       <c r="Q731" s="9" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="R731" s="9"/>
       <c r="S731" s="9"/>
@@ -53760,16 +53755,16 @@
         <v>2899</v>
       </c>
       <c r="C732" s="9" t="s">
+        <v>3902</v>
+      </c>
+      <c r="D732" s="9" t="s">
         <v>3903</v>
       </c>
-      <c r="D732" s="9" t="s">
+      <c r="E732" s="10" t="s">
         <v>3904</v>
       </c>
-      <c r="E732" s="10" t="s">
+      <c r="F732" s="9" t="s">
         <v>3905</v>
-      </c>
-      <c r="F732" s="9" t="s">
-        <v>3906</v>
       </c>
       <c r="G732" s="9"/>
       <c r="H732" s="11">
@@ -53782,16 +53777,16 @@
         <v>2</v>
       </c>
       <c r="K732" s="9" t="s">
+        <v>3906</v>
+      </c>
+      <c r="L732" s="9" t="s">
         <v>3907</v>
-      </c>
-      <c r="L732" s="9" t="s">
-        <v>3908</v>
       </c>
       <c r="M732" s="13">
         <v>5000</v>
       </c>
       <c r="N732" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O732" s="13">
         <v>88</v>
@@ -53800,7 +53795,7 @@
         <v>65</v>
       </c>
       <c r="Q732" s="9" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="R732" s="9"/>
       <c r="S732" s="9"/>
@@ -53814,16 +53809,16 @@
         <v>2069</v>
       </c>
       <c r="C733" s="9" t="s">
+        <v>3909</v>
+      </c>
+      <c r="D733" s="9" t="s">
         <v>3910</v>
       </c>
-      <c r="D733" s="9" t="s">
+      <c r="E733" s="10" t="s">
+        <v>3904</v>
+      </c>
+      <c r="F733" s="9" t="s">
         <v>3911</v>
-      </c>
-      <c r="E733" s="10" t="s">
-        <v>3905</v>
-      </c>
-      <c r="F733" s="9" t="s">
-        <v>3912</v>
       </c>
       <c r="G733" s="9"/>
       <c r="H733" s="11">
@@ -53836,16 +53831,16 @@
         <v>2</v>
       </c>
       <c r="K733" s="9" t="s">
+        <v>3906</v>
+      </c>
+      <c r="L733" s="9" t="s">
         <v>3907</v>
-      </c>
-      <c r="L733" s="9" t="s">
-        <v>3908</v>
       </c>
       <c r="M733" s="13">
         <v>4000</v>
       </c>
       <c r="N733" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O733" s="13">
         <v>82</v>
@@ -53854,7 +53849,7 @@
         <v>60</v>
       </c>
       <c r="Q733" s="9" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="R733" s="9"/>
       <c r="S733" s="9"/>
@@ -53868,16 +53863,16 @@
         <v>1242</v>
       </c>
       <c r="C734" s="9" t="s">
+        <v>3913</v>
+      </c>
+      <c r="D734" s="9" t="s">
         <v>3914</v>
       </c>
-      <c r="D734" s="9" t="s">
+      <c r="E734" s="10" t="s">
+        <v>3904</v>
+      </c>
+      <c r="F734" s="9" t="s">
         <v>3915</v>
-      </c>
-      <c r="E734" s="10" t="s">
-        <v>3905</v>
-      </c>
-      <c r="F734" s="9" t="s">
-        <v>3916</v>
       </c>
       <c r="G734" s="9"/>
       <c r="H734" s="11">
@@ -53890,16 +53885,16 @@
         <v>2</v>
       </c>
       <c r="K734" s="9" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="L734" s="9" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="M734" s="13">
         <v>4000</v>
       </c>
       <c r="N734" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O734" s="13">
         <v>72</v>
@@ -53908,7 +53903,7 @@
         <v>55</v>
       </c>
       <c r="Q734" s="9" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
       <c r="R734" s="9"/>
       <c r="S734" s="9"/>
@@ -53922,16 +53917,16 @@
         <v>2528</v>
       </c>
       <c r="C735" s="9" t="s">
+        <v>3918</v>
+      </c>
+      <c r="D735" s="9" t="s">
         <v>3919</v>
       </c>
-      <c r="D735" s="9" t="s">
+      <c r="E735" s="10" t="s">
+        <v>3904</v>
+      </c>
+      <c r="F735" s="9" t="s">
         <v>3920</v>
-      </c>
-      <c r="E735" s="10" t="s">
-        <v>3905</v>
-      </c>
-      <c r="F735" s="9" t="s">
-        <v>3921</v>
       </c>
       <c r="G735" s="9"/>
       <c r="H735" s="11">
@@ -53944,16 +53939,16 @@
         <v>2</v>
       </c>
       <c r="K735" s="9" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="L735" s="9" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="M735" s="13">
         <v>5000</v>
       </c>
       <c r="N735" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O735" s="13">
         <v>85</v>
@@ -53962,7 +53957,7 @@
         <v>60</v>
       </c>
       <c r="Q735" s="9" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="R735" s="9"/>
       <c r="S735" s="9"/>
@@ -53970,22 +53965,22 @@
     </row>
     <row r="736" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="9" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="B736" s="9" t="s">
         <v>2764</v>
       </c>
       <c r="C736" s="9" t="s">
+        <v>3924</v>
+      </c>
+      <c r="D736" s="9" t="s">
         <v>3925</v>
       </c>
-      <c r="D736" s="9" t="s">
+      <c r="E736" s="10" t="s">
+        <v>3904</v>
+      </c>
+      <c r="F736" s="9" t="s">
         <v>3926</v>
-      </c>
-      <c r="E736" s="10" t="s">
-        <v>3905</v>
-      </c>
-      <c r="F736" s="9" t="s">
-        <v>3927</v>
       </c>
       <c r="G736" s="9"/>
       <c r="H736" s="11">
@@ -53998,16 +53993,16 @@
         <v>2</v>
       </c>
       <c r="K736" s="9" t="s">
+        <v>3906</v>
+      </c>
+      <c r="L736" s="9" t="s">
         <v>3907</v>
-      </c>
-      <c r="L736" s="9" t="s">
-        <v>3908</v>
       </c>
       <c r="M736" s="13">
         <v>4000</v>
       </c>
       <c r="N736" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O736" s="13">
         <v>80</v>
@@ -54016,7 +54011,7 @@
         <v>60</v>
       </c>
       <c r="Q736" s="9" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="R736" s="9"/>
       <c r="S736" s="9"/>
@@ -54030,16 +54025,16 @@
         <v>335</v>
       </c>
       <c r="C737" s="2" t="s">
+        <v>3928</v>
+      </c>
+      <c r="D737" s="2" t="s">
         <v>3929</v>
-      </c>
-      <c r="D737" s="2" t="s">
-        <v>3930</v>
       </c>
       <c r="E737" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F737" s="2" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="G737" s="2"/>
       <c r="H737" s="4">
@@ -54052,16 +54047,16 @@
         <v>1</v>
       </c>
       <c r="K737" s="2" t="s">
+        <v>3931</v>
+      </c>
+      <c r="L737" s="2" t="s">
         <v>3932</v>
-      </c>
-      <c r="L737" s="2" t="s">
-        <v>3933</v>
       </c>
       <c r="M737" s="6">
         <v>4000</v>
       </c>
       <c r="N737" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O737" s="6">
         <v>95</v>
@@ -54070,7 +54065,7 @@
         <v>65</v>
       </c>
       <c r="Q737" s="2" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="R737" s="2"/>
       <c r="S737" s="2"/>
@@ -54084,16 +54079,16 @@
         <v>1927</v>
       </c>
       <c r="C738" s="2" t="s">
+        <v>3934</v>
+      </c>
+      <c r="D738" s="2" t="s">
         <v>3935</v>
-      </c>
-      <c r="D738" s="2" t="s">
-        <v>3936</v>
       </c>
       <c r="E738" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F738" s="2" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="G738" s="2"/>
       <c r="H738" s="4">
@@ -54106,16 +54101,16 @@
         <v>1</v>
       </c>
       <c r="K738" s="2" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="L738" s="2" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="M738" s="6">
         <v>3500</v>
       </c>
       <c r="N738" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O738" s="6">
         <v>92</v>
@@ -54124,7 +54119,7 @@
         <v>65</v>
       </c>
       <c r="Q738" s="2" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="R738" s="2"/>
       <c r="S738" s="2"/>
@@ -54138,16 +54133,16 @@
         <v>894</v>
       </c>
       <c r="C739" s="9" t="s">
+        <v>3939</v>
+      </c>
+      <c r="D739" s="9" t="s">
         <v>3940</v>
-      </c>
-      <c r="D739" s="9" t="s">
-        <v>3941</v>
       </c>
       <c r="E739" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F739" s="9" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="G739" s="9"/>
       <c r="H739" s="11">
@@ -54160,16 +54155,16 @@
         <v>2</v>
       </c>
       <c r="K739" s="9" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="L739" s="9" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="M739" s="13">
         <v>5000</v>
       </c>
       <c r="N739" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O739" s="13">
         <v>82</v>
@@ -54178,7 +54173,7 @@
         <v>60</v>
       </c>
       <c r="Q739" s="9" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="R739" s="9"/>
       <c r="S739" s="9"/>
@@ -54192,16 +54187,16 @@
         <v>1317</v>
       </c>
       <c r="C740" s="9" t="s">
+        <v>3944</v>
+      </c>
+      <c r="D740" s="9" t="s">
         <v>3945</v>
-      </c>
-      <c r="D740" s="9" t="s">
-        <v>3946</v>
       </c>
       <c r="E740" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F740" s="9" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="G740" s="9"/>
       <c r="H740" s="11">
@@ -54214,16 +54209,16 @@
         <v>2</v>
       </c>
       <c r="K740" s="9" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="L740" s="9" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="M740" s="13">
         <v>4000</v>
       </c>
       <c r="N740" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O740" s="13">
         <v>75</v>
@@ -54232,7 +54227,7 @@
         <v>55</v>
       </c>
       <c r="Q740" s="9" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="R740" s="9"/>
       <c r="S740" s="9"/>
@@ -54246,16 +54241,16 @@
         <v>3131</v>
       </c>
       <c r="C741" s="9" t="s">
+        <v>3949</v>
+      </c>
+      <c r="D741" s="9" t="s">
         <v>3950</v>
-      </c>
-      <c r="D741" s="9" t="s">
-        <v>3951</v>
       </c>
       <c r="E741" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F741" s="9" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="G741" s="9"/>
       <c r="H741" s="11">
@@ -54268,16 +54263,16 @@
         <v>2</v>
       </c>
       <c r="K741" s="9" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="L741" s="9" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="M741" s="13">
         <v>3000</v>
       </c>
       <c r="N741" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O741" s="13">
         <v>72</v>
@@ -54286,7 +54281,7 @@
         <v>50</v>
       </c>
       <c r="Q741" s="9" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="R741" s="9"/>
       <c r="S741" s="9"/>
@@ -54300,16 +54295,16 @@
         <v>335</v>
       </c>
       <c r="C742" s="9" t="s">
+        <v>3954</v>
+      </c>
+      <c r="D742" s="9" t="s">
         <v>3955</v>
-      </c>
-      <c r="D742" s="9" t="s">
-        <v>3956</v>
       </c>
       <c r="E742" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F742" s="9" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="G742" s="9"/>
       <c r="H742" s="11">
@@ -54322,16 +54317,16 @@
         <v>2</v>
       </c>
       <c r="K742" s="9" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="L742" s="9" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="M742" s="13">
         <v>3000</v>
       </c>
       <c r="N742" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O742" s="13">
         <v>72</v>
@@ -54340,7 +54335,7 @@
         <v>50</v>
       </c>
       <c r="Q742" s="9" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="R742" s="9"/>
       <c r="S742" s="9"/>
@@ -54354,16 +54349,16 @@
         <v>2245</v>
       </c>
       <c r="C743" s="9" t="s">
+        <v>3959</v>
+      </c>
+      <c r="D743" s="9" t="s">
         <v>3960</v>
-      </c>
-      <c r="D743" s="9" t="s">
-        <v>3961</v>
       </c>
       <c r="E743" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F743" s="9" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="G743" s="9"/>
       <c r="H743" s="11">
@@ -54376,16 +54371,16 @@
         <v>2</v>
       </c>
       <c r="K743" s="9" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="L743" s="9" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="M743" s="13">
         <v>3000</v>
       </c>
       <c r="N743" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O743" s="13">
         <v>70</v>
@@ -54394,7 +54389,7 @@
         <v>50</v>
       </c>
       <c r="Q743" s="9" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="R743" s="9"/>
       <c r="S743" s="9"/>
@@ -54408,16 +54403,16 @@
         <v>570</v>
       </c>
       <c r="C744" s="9" t="s">
+        <v>3964</v>
+      </c>
+      <c r="D744" s="9" t="s">
         <v>3965</v>
       </c>
-      <c r="D744" s="9" t="s">
+      <c r="E744" s="10" t="s">
         <v>3966</v>
       </c>
-      <c r="E744" s="10" t="s">
+      <c r="F744" s="9" t="s">
         <v>3967</v>
-      </c>
-      <c r="F744" s="9" t="s">
-        <v>3968</v>
       </c>
       <c r="G744" s="9"/>
       <c r="H744" s="11">
@@ -54430,16 +54425,16 @@
         <v>2</v>
       </c>
       <c r="K744" s="9" t="s">
+        <v>3968</v>
+      </c>
+      <c r="L744" s="9" t="s">
         <v>3969</v>
-      </c>
-      <c r="L744" s="9" t="s">
-        <v>3970</v>
       </c>
       <c r="M744" s="13">
         <v>2000</v>
       </c>
       <c r="N744" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O744" s="13">
         <v>72</v>
@@ -54448,7 +54443,7 @@
         <v>50</v>
       </c>
       <c r="Q744" s="9" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="R744" s="9"/>
       <c r="S744" s="9"/>
@@ -54462,16 +54457,16 @@
         <v>702</v>
       </c>
       <c r="C745" s="9" t="s">
+        <v>3971</v>
+      </c>
+      <c r="D745" s="9" t="s">
         <v>3972</v>
-      </c>
-      <c r="D745" s="9" t="s">
-        <v>3973</v>
       </c>
       <c r="E745" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F745" s="9" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="G745" s="9"/>
       <c r="H745" s="11">
@@ -54484,16 +54479,16 @@
         <v>2</v>
       </c>
       <c r="K745" s="9" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="L745" s="9" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="M745" s="13">
         <v>2000</v>
       </c>
       <c r="N745" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O745" s="13">
         <v>70</v>
@@ -54502,7 +54497,7 @@
         <v>50</v>
       </c>
       <c r="Q745" s="9" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="R745" s="9"/>
       <c r="S745" s="9"/>
@@ -54516,16 +54511,16 @@
         <v>1521</v>
       </c>
       <c r="C746" s="2" t="s">
+        <v>3976</v>
+      </c>
+      <c r="D746" s="2" t="s">
         <v>3977</v>
-      </c>
-      <c r="D746" s="2" t="s">
-        <v>3978</v>
       </c>
       <c r="E746" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F746" s="2" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="G746" s="2"/>
       <c r="H746" s="4">
@@ -54538,16 +54533,16 @@
         <v>1</v>
       </c>
       <c r="K746" s="2" t="s">
+        <v>3979</v>
+      </c>
+      <c r="L746" s="2" t="s">
         <v>3980</v>
-      </c>
-      <c r="L746" s="2" t="s">
-        <v>3981</v>
       </c>
       <c r="M746" s="6">
         <v>2000</v>
       </c>
       <c r="N746" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O746" s="6">
         <v>95</v>
@@ -54556,7 +54551,7 @@
         <v>60</v>
       </c>
       <c r="Q746" s="2" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="R746" s="2"/>
       <c r="S746" s="2"/>
@@ -54570,16 +54565,16 @@
         <v>2434</v>
       </c>
       <c r="C747" s="9" t="s">
+        <v>3982</v>
+      </c>
+      <c r="D747" s="9" t="s">
         <v>3983</v>
       </c>
-      <c r="D747" s="9" t="s">
+      <c r="E747" s="10" t="s">
         <v>3984</v>
       </c>
-      <c r="E747" s="10" t="s">
+      <c r="F747" s="9" t="s">
         <v>3985</v>
-      </c>
-      <c r="F747" s="9" t="s">
-        <v>3986</v>
       </c>
       <c r="G747" s="9"/>
       <c r="H747" s="11">
@@ -54592,16 +54587,16 @@
         <v>2</v>
       </c>
       <c r="K747" s="9" t="s">
+        <v>3986</v>
+      </c>
+      <c r="L747" s="9" t="s">
         <v>3987</v>
-      </c>
-      <c r="L747" s="9" t="s">
-        <v>3988</v>
       </c>
       <c r="M747" s="13">
         <v>3000</v>
       </c>
       <c r="N747" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O747" s="13">
         <v>72</v>
@@ -54610,7 +54605,7 @@
         <v>50</v>
       </c>
       <c r="Q747" s="9" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="R747" s="9"/>
       <c r="S747" s="9"/>
@@ -54624,16 +54619,16 @@
         <v>415</v>
       </c>
       <c r="C748" s="9" t="s">
+        <v>3989</v>
+      </c>
+      <c r="D748" s="9" t="s">
         <v>3990</v>
       </c>
-      <c r="D748" s="9" t="s">
+      <c r="E748" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F748" s="9" t="s">
         <v>3991</v>
-      </c>
-      <c r="E748" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F748" s="9" t="s">
-        <v>3992</v>
       </c>
       <c r="G748" s="9"/>
       <c r="H748" s="11">
@@ -54646,16 +54641,16 @@
         <v>2</v>
       </c>
       <c r="K748" s="9" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="L748" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M748" s="13">
         <v>3000</v>
       </c>
       <c r="N748" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O748" s="13">
         <v>70</v>
@@ -54664,7 +54659,7 @@
         <v>50</v>
       </c>
       <c r="Q748" s="9" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="R748" s="9"/>
       <c r="S748" s="9"/>
@@ -54672,22 +54667,22 @@
     </row>
     <row r="749" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="9" t="s">
-        <v>3729</v>
+        <v>3728</v>
       </c>
       <c r="B749" s="9" t="s">
-        <v>3729</v>
+        <v>3728</v>
       </c>
       <c r="C749" s="9" t="s">
+        <v>3994</v>
+      </c>
+      <c r="D749" s="9" t="s">
         <v>3995</v>
-      </c>
-      <c r="D749" s="9" t="s">
-        <v>3996</v>
       </c>
       <c r="E749" s="10" t="s">
         <v>830</v>
       </c>
       <c r="F749" s="9" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="G749" s="9"/>
       <c r="H749" s="11">
@@ -54700,16 +54695,16 @@
         <v>2</v>
       </c>
       <c r="K749" s="9" t="s">
+        <v>3997</v>
+      </c>
+      <c r="L749" s="9" t="s">
         <v>3998</v>
-      </c>
-      <c r="L749" s="9" t="s">
-        <v>3999</v>
       </c>
       <c r="M749" s="13">
         <v>4000</v>
       </c>
       <c r="N749" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O749" s="13">
         <v>80</v>
@@ -54718,7 +54713,7 @@
         <v>60</v>
       </c>
       <c r="Q749" s="9" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="R749" s="9"/>
       <c r="S749" s="9"/>
@@ -54732,16 +54727,16 @@
         <v>20</v>
       </c>
       <c r="C750" s="9" t="s">
+        <v>4000</v>
+      </c>
+      <c r="D750" s="9" t="s">
         <v>4001</v>
       </c>
-      <c r="D750" s="9" t="s">
+      <c r="E750" s="10" t="s">
         <v>4002</v>
       </c>
-      <c r="E750" s="10" t="s">
+      <c r="F750" s="9" t="s">
         <v>4003</v>
-      </c>
-      <c r="F750" s="9" t="s">
-        <v>4004</v>
       </c>
       <c r="G750" s="9"/>
       <c r="H750" s="11">
@@ -54754,16 +54749,16 @@
         <v>2</v>
       </c>
       <c r="K750" s="9" t="s">
+        <v>4004</v>
+      </c>
+      <c r="L750" s="9" t="s">
         <v>4005</v>
-      </c>
-      <c r="L750" s="9" t="s">
-        <v>4006</v>
       </c>
       <c r="M750" s="13">
         <v>4000</v>
       </c>
       <c r="N750" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O750" s="13">
         <v>80</v>
@@ -54772,7 +54767,7 @@
         <v>55</v>
       </c>
       <c r="Q750" s="9" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="R750" s="9"/>
       <c r="S750" s="9"/>
@@ -54780,22 +54775,22 @@
     </row>
     <row r="751" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B751" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C751" s="9" t="s">
+        <v>4007</v>
+      </c>
+      <c r="D751" s="9" t="s">
         <v>4008</v>
-      </c>
-      <c r="D751" s="9" t="s">
-        <v>4009</v>
       </c>
       <c r="E751" s="10" t="s">
         <v>2172</v>
       </c>
       <c r="F751" s="9" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="G751" s="9"/>
       <c r="H751" s="11">
@@ -54808,16 +54803,16 @@
         <v>2</v>
       </c>
       <c r="K751" s="9" t="s">
+        <v>4010</v>
+      </c>
+      <c r="L751" s="9" t="s">
         <v>4011</v>
-      </c>
-      <c r="L751" s="9" t="s">
-        <v>4012</v>
       </c>
       <c r="M751" s="13">
         <v>5000</v>
       </c>
       <c r="N751" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O751" s="13">
         <v>75</v>
@@ -54826,7 +54821,7 @@
         <v>55</v>
       </c>
       <c r="Q751" s="9" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="R751" s="9"/>
       <c r="S751" s="9"/>
@@ -54840,16 +54835,16 @@
         <v>207</v>
       </c>
       <c r="C752" s="9" t="s">
+        <v>4013</v>
+      </c>
+      <c r="D752" s="9" t="s">
         <v>4014</v>
-      </c>
-      <c r="D752" s="9" t="s">
-        <v>4015</v>
       </c>
       <c r="E752" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F752" s="9" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="G752" s="9"/>
       <c r="H752" s="11">
@@ -54862,16 +54857,16 @@
         <v>2</v>
       </c>
       <c r="K752" s="9" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="L752" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M752" s="13">
         <v>4000</v>
       </c>
       <c r="N752" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O752" s="13">
         <v>72</v>
@@ -54880,7 +54875,7 @@
         <v>55</v>
       </c>
       <c r="Q752" s="9" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="R752" s="9"/>
       <c r="S752" s="9"/>
@@ -54894,16 +54889,16 @@
         <v>894</v>
       </c>
       <c r="C753" s="9" t="s">
+        <v>4018</v>
+      </c>
+      <c r="D753" s="9" t="s">
         <v>4019</v>
-      </c>
-      <c r="D753" s="9" t="s">
-        <v>4020</v>
       </c>
       <c r="E753" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F753" s="9" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="G753" s="9"/>
       <c r="H753" s="11">
@@ -54916,16 +54911,16 @@
         <v>2</v>
       </c>
       <c r="K753" s="9" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="L753" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M753" s="13">
         <v>3000</v>
       </c>
       <c r="N753" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O753" s="13">
         <v>75</v>
@@ -54934,7 +54929,7 @@
         <v>55</v>
       </c>
       <c r="Q753" s="9" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="R753" s="9"/>
       <c r="S753" s="9"/>
@@ -54942,22 +54937,22 @@
     </row>
     <row r="754" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B754" s="9" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C754" s="9" t="s">
+        <v>4023</v>
+      </c>
+      <c r="D754" s="9" t="s">
         <v>4024</v>
       </c>
-      <c r="D754" s="9" t="s">
+      <c r="E754" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F754" s="9" t="s">
         <v>4025</v>
-      </c>
-      <c r="E754" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F754" s="9" t="s">
-        <v>4026</v>
       </c>
       <c r="G754" s="9"/>
       <c r="H754" s="11">
@@ -54970,16 +54965,16 @@
         <v>2</v>
       </c>
       <c r="K754" s="9" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="L754" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M754" s="13">
         <v>2000</v>
       </c>
       <c r="N754" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O754" s="13">
         <v>70</v>
@@ -54988,7 +54983,7 @@
         <v>50</v>
       </c>
       <c r="Q754" s="9" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="R754" s="9"/>
       <c r="S754" s="9"/>
@@ -55002,16 +54997,16 @@
         <v>1070</v>
       </c>
       <c r="C755" s="9" t="s">
+        <v>4028</v>
+      </c>
+      <c r="D755" s="9" t="s">
         <v>4029</v>
-      </c>
-      <c r="D755" s="9" t="s">
-        <v>4030</v>
       </c>
       <c r="E755" s="10" t="s">
         <v>1120</v>
       </c>
       <c r="F755" s="9" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="G755" s="9"/>
       <c r="H755" s="11">
@@ -55024,7 +55019,7 @@
         <v>2</v>
       </c>
       <c r="K755" s="9" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="L755" s="9" t="s">
         <v>1122</v>
@@ -55033,7 +55028,7 @@
         <v>2000</v>
       </c>
       <c r="N755" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O755" s="13">
         <v>68</v>
@@ -55042,7 +55037,7 @@
         <v>50</v>
       </c>
       <c r="Q755" s="9" t="s">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="R755" s="9"/>
       <c r="S755" s="9"/>
@@ -55056,16 +55051,16 @@
         <v>2958</v>
       </c>
       <c r="C756" s="2" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D756" s="2" t="s">
         <v>4034</v>
-      </c>
-      <c r="D756" s="2" t="s">
-        <v>4035</v>
       </c>
       <c r="E756" s="3" t="s">
         <v>1120</v>
       </c>
       <c r="F756" s="2" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="G756" s="2"/>
       <c r="H756" s="4">
@@ -55078,7 +55073,7 @@
         <v>1</v>
       </c>
       <c r="K756" s="2" t="s">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="L756" s="2" t="s">
         <v>1122</v>
@@ -55087,7 +55082,7 @@
         <v>2500</v>
       </c>
       <c r="N756" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O756" s="6">
         <v>95</v>
@@ -55096,7 +55091,7 @@
         <v>60</v>
       </c>
       <c r="Q756" s="2" t="s">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="R756" s="2"/>
       <c r="S756" s="2"/>
@@ -55110,16 +55105,16 @@
         <v>782</v>
       </c>
       <c r="C757" s="9" t="s">
+        <v>4038</v>
+      </c>
+      <c r="D757" s="9" t="s">
         <v>4039</v>
-      </c>
-      <c r="D757" s="9" t="s">
-        <v>4040</v>
       </c>
       <c r="E757" s="10" t="s">
         <v>1100</v>
       </c>
       <c r="F757" s="9" t="s">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="G757" s="9"/>
       <c r="H757" s="11">
@@ -55132,16 +55127,16 @@
         <v>2</v>
       </c>
       <c r="K757" s="9" t="s">
+        <v>4041</v>
+      </c>
+      <c r="L757" s="9" t="s">
         <v>4042</v>
-      </c>
-      <c r="L757" s="9" t="s">
-        <v>4043</v>
       </c>
       <c r="M757" s="13">
         <v>3000</v>
       </c>
       <c r="N757" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O757" s="13">
         <v>78</v>
@@ -55150,7 +55145,7 @@
         <v>55</v>
       </c>
       <c r="Q757" s="9" t="s">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="R757" s="9"/>
       <c r="S757" s="9"/>
@@ -55164,16 +55159,16 @@
         <v>3296</v>
       </c>
       <c r="C758" s="9" t="s">
+        <v>4044</v>
+      </c>
+      <c r="D758" s="9" t="s">
         <v>4045</v>
-      </c>
-      <c r="D758" s="9" t="s">
-        <v>4046</v>
       </c>
       <c r="E758" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F758" s="9" t="s">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="G758" s="9"/>
       <c r="H758" s="11">
@@ -55186,16 +55181,16 @@
         <v>2</v>
       </c>
       <c r="K758" s="9" t="s">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="L758" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M758" s="13">
         <v>2500</v>
       </c>
       <c r="N758" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O758" s="13">
         <v>65</v>
@@ -55204,7 +55199,7 @@
         <v>50</v>
       </c>
       <c r="Q758" s="9" t="s">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="R758" s="9"/>
       <c r="S758" s="9"/>
@@ -55212,22 +55207,22 @@
     </row>
     <row r="759" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="9" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="B759" s="9" t="s">
         <v>2764</v>
       </c>
       <c r="C759" s="9" t="s">
+        <v>4049</v>
+      </c>
+      <c r="D759" s="9" t="s">
         <v>4050</v>
-      </c>
-      <c r="D759" s="9" t="s">
-        <v>4051</v>
       </c>
       <c r="E759" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F759" s="9" t="s">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="G759" s="9"/>
       <c r="H759" s="11">
@@ -55240,16 +55235,16 @@
         <v>2</v>
       </c>
       <c r="K759" s="9" t="s">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="L759" s="9" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M759" s="13">
         <v>3000</v>
       </c>
       <c r="N759" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O759" s="13">
         <v>68</v>
@@ -55258,7 +55253,7 @@
         <v>50</v>
       </c>
       <c r="Q759" s="9" t="s">
-        <v>4054</v>
+        <v>4053</v>
       </c>
       <c r="R759" s="9"/>
       <c r="S759" s="9"/>
@@ -55272,16 +55267,16 @@
         <v>3365</v>
       </c>
       <c r="C760" s="2" t="s">
+        <v>4054</v>
+      </c>
+      <c r="D760" s="2" t="s">
         <v>4055</v>
       </c>
-      <c r="D760" s="2" t="s">
+      <c r="E760" s="3" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F760" s="2" t="s">
         <v>4056</v>
-      </c>
-      <c r="E760" s="3" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F760" s="2" t="s">
-        <v>4057</v>
       </c>
       <c r="G760" s="2"/>
       <c r="H760" s="4">
@@ -55294,16 +55289,16 @@
         <v>1</v>
       </c>
       <c r="K760" s="2" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="L760" s="2" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M760" s="6">
         <v>8000</v>
       </c>
       <c r="N760" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O760" s="6">
         <v>98</v>
@@ -55312,7 +55307,7 @@
         <v>65</v>
       </c>
       <c r="Q760" s="2" t="s">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="R760" s="2"/>
       <c r="S760" s="2"/>
@@ -55326,16 +55321,16 @@
         <v>894</v>
       </c>
       <c r="C761" s="2" t="s">
+        <v>4059</v>
+      </c>
+      <c r="D761" s="2" t="s">
         <v>4060</v>
       </c>
-      <c r="D761" s="2" t="s">
+      <c r="E761" s="3" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F761" s="2" t="s">
         <v>4061</v>
-      </c>
-      <c r="E761" s="3" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F761" s="2" t="s">
-        <v>4062</v>
       </c>
       <c r="G761" s="2"/>
       <c r="H761" s="4">
@@ -55348,16 +55343,16 @@
         <v>1</v>
       </c>
       <c r="K761" s="2" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="L761" s="2" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M761" s="6">
         <v>8000</v>
       </c>
       <c r="N761" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O761" s="6">
         <v>97</v>
@@ -55366,7 +55361,7 @@
         <v>65</v>
       </c>
       <c r="Q761" s="2" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="R761" s="2"/>
       <c r="S761" s="2"/>
@@ -55380,16 +55375,16 @@
         <v>2343</v>
       </c>
       <c r="C762" s="9" t="s">
+        <v>4063</v>
+      </c>
+      <c r="D762" s="9" t="s">
         <v>4064</v>
       </c>
-      <c r="D762" s="9" t="s">
+      <c r="E762" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F762" s="9" t="s">
         <v>4065</v>
-      </c>
-      <c r="E762" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F762" s="9" t="s">
-        <v>4066</v>
       </c>
       <c r="G762" s="9"/>
       <c r="H762" s="11">
@@ -55402,16 +55397,16 @@
         <v>2</v>
       </c>
       <c r="K762" s="9" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="L762" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M762" s="13">
         <v>6000</v>
       </c>
       <c r="N762" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O762" s="13">
         <v>88</v>
@@ -55420,7 +55415,7 @@
         <v>60</v>
       </c>
       <c r="Q762" s="9" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="R762" s="9"/>
       <c r="S762" s="9"/>
@@ -55434,16 +55429,16 @@
         <v>415</v>
       </c>
       <c r="C763" s="9" t="s">
+        <v>4068</v>
+      </c>
+      <c r="D763" s="9" t="s">
         <v>4069</v>
       </c>
-      <c r="D763" s="9" t="s">
+      <c r="E763" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F763" s="9" t="s">
         <v>4070</v>
-      </c>
-      <c r="E763" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F763" s="9" t="s">
-        <v>4071</v>
       </c>
       <c r="G763" s="9"/>
       <c r="H763" s="11">
@@ -55456,16 +55451,16 @@
         <v>2</v>
       </c>
       <c r="K763" s="9" t="s">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="L763" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M763" s="13">
         <v>5000</v>
       </c>
       <c r="N763" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O763" s="13">
         <v>80</v>
@@ -55474,7 +55469,7 @@
         <v>55</v>
       </c>
       <c r="Q763" s="9" t="s">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="R763" s="9"/>
       <c r="S763" s="9"/>
@@ -55482,22 +55477,22 @@
     </row>
     <row r="764" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B764" s="9" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C764" s="9" t="s">
+        <v>4073</v>
+      </c>
+      <c r="D764" s="9" t="s">
         <v>4074</v>
       </c>
-      <c r="D764" s="9" t="s">
+      <c r="E764" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F764" s="9" t="s">
         <v>4075</v>
-      </c>
-      <c r="E764" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F764" s="9" t="s">
-        <v>4076</v>
       </c>
       <c r="G764" s="9"/>
       <c r="H764" s="11">
@@ -55510,16 +55505,16 @@
         <v>2</v>
       </c>
       <c r="K764" s="9" t="s">
-        <v>4077</v>
+        <v>4076</v>
       </c>
       <c r="L764" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M764" s="13">
         <v>4000</v>
       </c>
       <c r="N764" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O764" s="13">
         <v>75</v>
@@ -55528,7 +55523,7 @@
         <v>55</v>
       </c>
       <c r="Q764" s="9" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="R764" s="9"/>
       <c r="S764" s="9"/>
@@ -55542,16 +55537,16 @@
         <v>600</v>
       </c>
       <c r="C765" s="2" t="s">
+        <v>4078</v>
+      </c>
+      <c r="D765" s="2" t="s">
         <v>4079</v>
       </c>
-      <c r="D765" s="2" t="s">
+      <c r="E765" s="3" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F765" s="2" t="s">
         <v>4080</v>
-      </c>
-      <c r="E765" s="3" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F765" s="2" t="s">
-        <v>4081</v>
       </c>
       <c r="G765" s="2"/>
       <c r="H765" s="4">
@@ -55564,16 +55559,16 @@
         <v>1</v>
       </c>
       <c r="K765" s="2" t="s">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="L765" s="2" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M765" s="6">
         <v>4000</v>
       </c>
       <c r="N765" s="34" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O765" s="6">
         <v>92</v>
@@ -55582,7 +55577,7 @@
         <v>60</v>
       </c>
       <c r="Q765" s="2" t="s">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="R765" s="2"/>
       <c r="S765" s="2"/>
@@ -55596,16 +55591,16 @@
         <v>3365</v>
       </c>
       <c r="C766" s="9" t="s">
+        <v>4083</v>
+      </c>
+      <c r="D766" s="9" t="s">
         <v>4084</v>
       </c>
-      <c r="D766" s="9" t="s">
+      <c r="E766" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F766" s="9" t="s">
         <v>4085</v>
-      </c>
-      <c r="E766" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F766" s="9" t="s">
-        <v>4086</v>
       </c>
       <c r="G766" s="9"/>
       <c r="H766" s="11">
@@ -55618,16 +55613,16 @@
         <v>2</v>
       </c>
       <c r="K766" s="9" t="s">
-        <v>4087</v>
+        <v>4086</v>
       </c>
       <c r="L766" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M766" s="13">
         <v>4000</v>
       </c>
       <c r="N766" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O766" s="13">
         <v>85</v>
@@ -55636,7 +55631,7 @@
         <v>58</v>
       </c>
       <c r="Q766" s="9" t="s">
-        <v>4088</v>
+        <v>4087</v>
       </c>
       <c r="R766" s="9"/>
       <c r="S766" s="9"/>
@@ -55650,16 +55645,16 @@
         <v>2434</v>
       </c>
       <c r="C767" s="9" t="s">
+        <v>4088</v>
+      </c>
+      <c r="D767" s="9" t="s">
         <v>4089</v>
       </c>
-      <c r="D767" s="9" t="s">
+      <c r="E767" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F767" s="9" t="s">
         <v>4090</v>
-      </c>
-      <c r="E767" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F767" s="9" t="s">
-        <v>4091</v>
       </c>
       <c r="G767" s="9"/>
       <c r="H767" s="11">
@@ -55672,16 +55667,16 @@
         <v>2</v>
       </c>
       <c r="K767" s="9" t="s">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="L767" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M767" s="13">
         <v>3000</v>
       </c>
       <c r="N767" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O767" s="13">
         <v>78</v>
@@ -55690,7 +55685,7 @@
         <v>55</v>
       </c>
       <c r="Q767" s="9" t="s">
-        <v>4093</v>
+        <v>4092</v>
       </c>
       <c r="R767" s="9"/>
       <c r="S767" s="9"/>
@@ -55704,16 +55699,16 @@
         <v>894</v>
       </c>
       <c r="C768" s="9" t="s">
+        <v>4093</v>
+      </c>
+      <c r="D768" s="9" t="s">
         <v>4094</v>
       </c>
-      <c r="D768" s="9" t="s">
+      <c r="E768" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F768" s="9" t="s">
         <v>4095</v>
-      </c>
-      <c r="E768" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F768" s="9" t="s">
-        <v>4096</v>
       </c>
       <c r="G768" s="9"/>
       <c r="H768" s="11">
@@ -55726,16 +55721,16 @@
         <v>2</v>
       </c>
       <c r="K768" s="9" t="s">
-        <v>4097</v>
+        <v>4096</v>
       </c>
       <c r="L768" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M768" s="13">
         <v>3000</v>
       </c>
       <c r="N768" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O768" s="13">
         <v>72</v>
@@ -55744,7 +55739,7 @@
         <v>50</v>
       </c>
       <c r="Q768" s="9" t="s">
-        <v>4098</v>
+        <v>4097</v>
       </c>
       <c r="R768" s="9"/>
       <c r="S768" s="9"/>
@@ -55758,16 +55753,16 @@
         <v>2343</v>
       </c>
       <c r="C769" s="9" t="s">
+        <v>4098</v>
+      </c>
+      <c r="D769" s="9" t="s">
         <v>4099</v>
       </c>
-      <c r="D769" s="9" t="s">
+      <c r="E769" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F769" s="9" t="s">
         <v>4100</v>
-      </c>
-      <c r="E769" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F769" s="9" t="s">
-        <v>4101</v>
       </c>
       <c r="G769" s="9"/>
       <c r="H769" s="11">
@@ -55780,16 +55775,16 @@
         <v>2</v>
       </c>
       <c r="K769" s="9" t="s">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="L769" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M769" s="13">
         <v>2500</v>
       </c>
       <c r="N769" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O769" s="13">
         <v>68</v>
@@ -55798,7 +55793,7 @@
         <v>50</v>
       </c>
       <c r="Q769" s="9" t="s">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="R769" s="9"/>
       <c r="S769" s="9"/>
@@ -55812,16 +55807,16 @@
         <v>1317</v>
       </c>
       <c r="C770" s="9" t="s">
+        <v>4103</v>
+      </c>
+      <c r="D770" s="9" t="s">
         <v>4104</v>
       </c>
-      <c r="D770" s="9" t="s">
+      <c r="E770" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F770" s="9" t="s">
         <v>4105</v>
-      </c>
-      <c r="E770" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F770" s="9" t="s">
-        <v>4106</v>
       </c>
       <c r="G770" s="9"/>
       <c r="H770" s="11">
@@ -55834,16 +55829,16 @@
         <v>2</v>
       </c>
       <c r="K770" s="9" t="s">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="L770" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M770" s="13">
         <v>3500</v>
       </c>
       <c r="N770" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O770" s="13">
         <v>72</v>
@@ -55852,7 +55847,7 @@
         <v>52</v>
       </c>
       <c r="Q770" s="9" t="s">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="R770" s="9"/>
       <c r="S770" s="9"/>
@@ -55860,22 +55855,22 @@
     </row>
     <row r="771" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="9" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B771" s="9" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C771" s="9" t="s">
+        <v>4108</v>
+      </c>
+      <c r="D771" s="9" t="s">
         <v>4109</v>
       </c>
-      <c r="D771" s="9" t="s">
+      <c r="E771" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F771" s="9" t="s">
         <v>4110</v>
-      </c>
-      <c r="E771" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F771" s="9" t="s">
-        <v>4111</v>
       </c>
       <c r="G771" s="9"/>
       <c r="H771" s="11">
@@ -55888,16 +55883,16 @@
         <v>2</v>
       </c>
       <c r="K771" s="9" t="s">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="L771" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M771" s="13">
         <v>3000</v>
       </c>
       <c r="N771" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O771" s="13">
         <v>68</v>
@@ -55906,7 +55901,7 @@
         <v>50</v>
       </c>
       <c r="Q771" s="9" t="s">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="R771" s="9"/>
       <c r="S771" s="9"/>
@@ -55920,16 +55915,16 @@
         <v>1521</v>
       </c>
       <c r="C772" s="9" t="s">
+        <v>4113</v>
+      </c>
+      <c r="D772" s="9" t="s">
         <v>4114</v>
       </c>
-      <c r="D772" s="9" t="s">
+      <c r="E772" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F772" s="9" t="s">
         <v>4115</v>
-      </c>
-      <c r="E772" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F772" s="9" t="s">
-        <v>4116</v>
       </c>
       <c r="G772" s="9"/>
       <c r="H772" s="11">
@@ -55942,16 +55937,16 @@
         <v>2</v>
       </c>
       <c r="K772" s="9" t="s">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="L772" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M772" s="13">
         <v>3000</v>
       </c>
       <c r="N772" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O772" s="13">
         <v>70</v>
@@ -55960,7 +55955,7 @@
         <v>50</v>
       </c>
       <c r="Q772" s="9" t="s">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="R772" s="9"/>
       <c r="S772" s="9"/>
@@ -55974,16 +55969,16 @@
         <v>495</v>
       </c>
       <c r="C773" s="9" t="s">
+        <v>4118</v>
+      </c>
+      <c r="D773" s="9" t="s">
         <v>4119</v>
       </c>
-      <c r="D773" s="9" t="s">
+      <c r="E773" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F773" s="9" t="s">
         <v>4120</v>
-      </c>
-      <c r="E773" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F773" s="9" t="s">
-        <v>4121</v>
       </c>
       <c r="G773" s="9"/>
       <c r="H773" s="11">
@@ -55996,16 +55991,16 @@
         <v>2</v>
       </c>
       <c r="K773" s="9" t="s">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="L773" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M773" s="13">
         <v>2500</v>
       </c>
       <c r="N773" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O773" s="13">
         <v>68</v>
@@ -56014,7 +56009,7 @@
         <v>50</v>
       </c>
       <c r="Q773" s="9" t="s">
-        <v>4123</v>
+        <v>4122</v>
       </c>
       <c r="R773" s="9"/>
       <c r="S773" s="9"/>
@@ -56022,22 +56017,22 @@
     </row>
     <row r="774" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B774" s="9" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C774" s="9" t="s">
+        <v>4123</v>
+      </c>
+      <c r="D774" s="9" t="s">
         <v>4124</v>
       </c>
-      <c r="D774" s="9" t="s">
+      <c r="E774" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F774" s="9" t="s">
         <v>4125</v>
-      </c>
-      <c r="E774" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F774" s="9" t="s">
-        <v>4126</v>
       </c>
       <c r="G774" s="9"/>
       <c r="H774" s="11">
@@ -56050,16 +56045,16 @@
         <v>2</v>
       </c>
       <c r="K774" s="9" t="s">
-        <v>4127</v>
+        <v>4126</v>
       </c>
       <c r="L774" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M774" s="13">
         <v>2500</v>
       </c>
       <c r="N774" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O774" s="13">
         <v>65</v>
@@ -56068,7 +56063,7 @@
         <v>48</v>
       </c>
       <c r="Q774" s="9" t="s">
-        <v>4128</v>
+        <v>4127</v>
       </c>
       <c r="R774" s="9"/>
       <c r="S774" s="9"/>
@@ -56082,16 +56077,16 @@
         <v>3212</v>
       </c>
       <c r="C775" s="9" t="s">
+        <v>4128</v>
+      </c>
+      <c r="D775" s="9" t="s">
         <v>4129</v>
       </c>
-      <c r="D775" s="9" t="s">
+      <c r="E775" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F775" s="9" t="s">
         <v>4130</v>
-      </c>
-      <c r="E775" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F775" s="9" t="s">
-        <v>4131</v>
       </c>
       <c r="G775" s="9"/>
       <c r="H775" s="11">
@@ -56104,16 +56099,16 @@
         <v>2</v>
       </c>
       <c r="K775" s="9" t="s">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="L775" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M775" s="13">
         <v>2500</v>
       </c>
       <c r="N775" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O775" s="13">
         <v>65</v>
@@ -56122,7 +56117,7 @@
         <v>48</v>
       </c>
       <c r="Q775" s="9" t="s">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="R775" s="9"/>
       <c r="S775" s="9"/>
@@ -56136,16 +56131,16 @@
         <v>600</v>
       </c>
       <c r="C776" s="9" t="s">
+        <v>4133</v>
+      </c>
+      <c r="D776" s="9" t="s">
         <v>4134</v>
       </c>
-      <c r="D776" s="9" t="s">
+      <c r="E776" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F776" s="9" t="s">
         <v>4135</v>
-      </c>
-      <c r="E776" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F776" s="9" t="s">
-        <v>4136</v>
       </c>
       <c r="G776" s="9"/>
       <c r="H776" s="11">
@@ -56158,16 +56153,16 @@
         <v>2</v>
       </c>
       <c r="K776" s="9" t="s">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="L776" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M776" s="13">
         <v>3000</v>
       </c>
       <c r="N776" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O776" s="13">
         <v>68</v>
@@ -56176,7 +56171,7 @@
         <v>50</v>
       </c>
       <c r="Q776" s="9" t="s">
-        <v>4137</v>
+        <v>4136</v>
       </c>
       <c r="R776" s="9"/>
       <c r="S776" s="9"/>
@@ -56190,16 +56185,16 @@
         <v>2245</v>
       </c>
       <c r="C777" s="9" t="s">
+        <v>4137</v>
+      </c>
+      <c r="D777" s="9" t="s">
         <v>4138</v>
       </c>
-      <c r="D777" s="9" t="s">
+      <c r="E777" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F777" s="9" t="s">
         <v>4139</v>
-      </c>
-      <c r="E777" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F777" s="9" t="s">
-        <v>4140</v>
       </c>
       <c r="G777" s="9"/>
       <c r="H777" s="11">
@@ -56212,16 +56207,16 @@
         <v>2</v>
       </c>
       <c r="K777" s="9" t="s">
-        <v>4141</v>
+        <v>4140</v>
       </c>
       <c r="L777" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M777" s="13">
         <v>5000</v>
       </c>
       <c r="N777" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O777" s="13">
         <v>75</v>
@@ -56230,7 +56225,7 @@
         <v>52</v>
       </c>
       <c r="Q777" s="9" t="s">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="R777" s="9"/>
       <c r="S777" s="9"/>
@@ -56244,16 +56239,16 @@
         <v>2434</v>
       </c>
       <c r="C778" s="9" t="s">
+        <v>4142</v>
+      </c>
+      <c r="D778" s="9" t="s">
         <v>4143</v>
       </c>
-      <c r="D778" s="9" t="s">
+      <c r="E778" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F778" s="9" t="s">
         <v>4144</v>
-      </c>
-      <c r="E778" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F778" s="9" t="s">
-        <v>4145</v>
       </c>
       <c r="G778" s="9"/>
       <c r="H778" s="11">
@@ -56266,16 +56261,16 @@
         <v>2</v>
       </c>
       <c r="K778" s="9" t="s">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="L778" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M778" s="13">
         <v>3500</v>
       </c>
       <c r="N778" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O778" s="13">
         <v>75</v>
@@ -56284,7 +56279,7 @@
         <v>52</v>
       </c>
       <c r="Q778" s="9" t="s">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="R778" s="9"/>
       <c r="S778" s="9"/>
@@ -56298,16 +56293,16 @@
         <v>125</v>
       </c>
       <c r="C779" s="9" t="s">
+        <v>4147</v>
+      </c>
+      <c r="D779" s="9" t="s">
         <v>4148</v>
       </c>
-      <c r="D779" s="9" t="s">
+      <c r="E779" s="10" t="s">
+        <v>3984</v>
+      </c>
+      <c r="F779" s="9" t="s">
         <v>4149</v>
-      </c>
-      <c r="E779" s="10" t="s">
-        <v>3985</v>
-      </c>
-      <c r="F779" s="9" t="s">
-        <v>4150</v>
       </c>
       <c r="G779" s="9"/>
       <c r="H779" s="11">
@@ -56320,16 +56315,16 @@
         <v>2</v>
       </c>
       <c r="K779" s="9" t="s">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="L779" s="9" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="M779" s="13">
         <v>6000</v>
       </c>
       <c r="N779" s="35" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="O779" s="13">
         <v>72</v>
@@ -56338,7 +56333,7 @@
         <v>55</v>
       </c>
       <c r="Q779" s="9" t="s">
-        <v>4152</v>
+        <v>4151</v>
       </c>
       <c r="R779" s="9"/>
       <c r="S779" s="9"/>
@@ -56352,10 +56347,10 @@
         <v>287</v>
       </c>
       <c r="C780" s="2" t="s">
+        <v>4152</v>
+      </c>
+      <c r="D780" s="2" t="s">
         <v>4153</v>
-      </c>
-      <c r="D780" s="2" t="s">
-        <v>4154</v>
       </c>
       <c r="E780" s="3" t="s">
         <v>56</v>
@@ -56390,12 +56385,12 @@
         <v>85</v>
       </c>
       <c r="Q780" s="2" t="s">
-        <v>4155</v>
+        <v>4154</v>
       </c>
       <c r="R780" s="2"/>
       <c r="S780" s="2"/>
       <c r="T780" s="2" t="s">
-        <v>4156</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="781" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -56406,10 +56401,10 @@
         <v>287</v>
       </c>
       <c r="C781" s="9" t="s">
+        <v>4156</v>
+      </c>
+      <c r="D781" s="9" t="s">
         <v>4157</v>
-      </c>
-      <c r="D781" s="9" t="s">
-        <v>4158</v>
       </c>
       <c r="E781" s="10" t="s">
         <v>648</v>
@@ -56426,7 +56421,7 @@
         <v>2</v>
       </c>
       <c r="K781" s="9" t="s">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="L781" s="9" t="s">
         <v>66</v>
@@ -56444,7 +56439,7 @@
         <v>75</v>
       </c>
       <c r="Q781" s="9" t="s">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="R781" s="9"/>
       <c r="S781" s="9"/>
@@ -56458,10 +56453,10 @@
         <v>287</v>
       </c>
       <c r="C782" s="9" t="s">
+        <v>4160</v>
+      </c>
+      <c r="D782" s="9" t="s">
         <v>4161</v>
-      </c>
-      <c r="D782" s="9" t="s">
-        <v>4162</v>
       </c>
       <c r="E782" s="10" t="s">
         <v>1160</v>
@@ -56496,7 +56491,7 @@
         <v>80</v>
       </c>
       <c r="Q782" s="9" t="s">
-        <v>4163</v>
+        <v>4162</v>
       </c>
       <c r="R782" s="9"/>
       <c r="S782" s="9"/>
@@ -56510,13 +56505,13 @@
         <v>287</v>
       </c>
       <c r="C783" s="9" t="s">
+        <v>4163</v>
+      </c>
+      <c r="D783" s="9" t="s">
         <v>4164</v>
       </c>
-      <c r="D783" s="9" t="s">
+      <c r="E783" s="10" t="s">
         <v>4165</v>
-      </c>
-      <c r="E783" s="10" t="s">
-        <v>4166</v>
       </c>
       <c r="F783" s="9"/>
       <c r="G783" s="9"/>
@@ -56548,7 +56543,7 @@
         <v>75</v>
       </c>
       <c r="Q783" s="9" t="s">
-        <v>4167</v>
+        <v>4166</v>
       </c>
       <c r="R783" s="9"/>
       <c r="S783" s="9"/>
@@ -56562,10 +56557,10 @@
         <v>287</v>
       </c>
       <c r="C784" s="9" t="s">
+        <v>4167</v>
+      </c>
+      <c r="D784" s="9" t="s">
         <v>4168</v>
-      </c>
-      <c r="D784" s="9" t="s">
-        <v>4169</v>
       </c>
       <c r="E784" s="10" t="s">
         <v>864</v>
@@ -56600,7 +56595,7 @@
         <v>75</v>
       </c>
       <c r="Q784" s="9" t="s">
-        <v>4170</v>
+        <v>4169</v>
       </c>
       <c r="R784" s="9"/>
       <c r="S784" s="9"/>
@@ -56614,10 +56609,10 @@
         <v>287</v>
       </c>
       <c r="C785" s="9" t="s">
+        <v>4170</v>
+      </c>
+      <c r="D785" s="9" t="s">
         <v>4171</v>
-      </c>
-      <c r="D785" s="9" t="s">
-        <v>4172</v>
       </c>
       <c r="E785" s="10" t="s">
         <v>40</v>
@@ -56634,10 +56629,10 @@
         <v>2</v>
       </c>
       <c r="K785" s="9" t="s">
+        <v>4172</v>
+      </c>
+      <c r="L785" s="9" t="s">
         <v>4173</v>
-      </c>
-      <c r="L785" s="9" t="s">
-        <v>4174</v>
       </c>
       <c r="M785" s="13">
         <v>8000</v>
@@ -56652,7 +56647,7 @@
         <v>75</v>
       </c>
       <c r="Q785" s="9" t="s">
-        <v>4175</v>
+        <v>4174</v>
       </c>
       <c r="R785" s="9"/>
       <c r="S785" s="9"/>
@@ -56666,10 +56661,10 @@
         <v>287</v>
       </c>
       <c r="C786" s="17" t="s">
+        <v>4175</v>
+      </c>
+      <c r="D786" s="17" t="s">
         <v>4176</v>
-      </c>
-      <c r="D786" s="17" t="s">
-        <v>4177</v>
       </c>
       <c r="E786" s="18" t="s">
         <v>2388</v>
@@ -56686,7 +56681,7 @@
         <v>3</v>
       </c>
       <c r="K786" s="17" t="s">
-        <v>4178</v>
+        <v>4177</v>
       </c>
       <c r="L786" s="17" t="s">
         <v>35</v>
@@ -56704,7 +56699,7 @@
         <v>60</v>
       </c>
       <c r="Q786" s="17" t="s">
-        <v>4179</v>
+        <v>4178</v>
       </c>
       <c r="R786" s="17"/>
       <c r="S786" s="17"/>
@@ -56718,13 +56713,13 @@
         <v>287</v>
       </c>
       <c r="C787" s="17" t="s">
+        <v>4179</v>
+      </c>
+      <c r="D787" s="17" t="s">
         <v>4180</v>
       </c>
-      <c r="D787" s="17" t="s">
+      <c r="E787" s="18" t="s">
         <v>4181</v>
-      </c>
-      <c r="E787" s="18" t="s">
-        <v>4182</v>
       </c>
       <c r="F787" s="17"/>
       <c r="G787" s="17"/>
@@ -56738,7 +56733,7 @@
         <v>3</v>
       </c>
       <c r="K787" s="17" t="s">
-        <v>4183</v>
+        <v>4182</v>
       </c>
       <c r="L787" s="17" t="s">
         <v>112</v>
@@ -56756,7 +56751,7 @@
         <v>60</v>
       </c>
       <c r="Q787" s="17" t="s">
-        <v>4184</v>
+        <v>4183</v>
       </c>
       <c r="R787" s="17"/>
       <c r="S787" s="17"/>
@@ -56770,10 +56765,10 @@
         <v>287</v>
       </c>
       <c r="C788" s="17" t="s">
+        <v>4184</v>
+      </c>
+      <c r="D788" s="17" t="s">
         <v>4185</v>
-      </c>
-      <c r="D788" s="17" t="s">
-        <v>4186</v>
       </c>
       <c r="E788" s="18" t="s">
         <v>301</v>
@@ -56790,7 +56785,7 @@
         <v>3</v>
       </c>
       <c r="K788" s="17" t="s">
-        <v>4187</v>
+        <v>4186</v>
       </c>
       <c r="L788" s="17" t="s">
         <v>3369</v>
@@ -56808,7 +56803,7 @@
         <v>60</v>
       </c>
       <c r="Q788" s="17" t="s">
-        <v>4188</v>
+        <v>4187</v>
       </c>
       <c r="R788" s="17"/>
       <c r="S788" s="17"/>
@@ -56822,10 +56817,10 @@
         <v>570</v>
       </c>
       <c r="C789" s="2" t="s">
+        <v>4188</v>
+      </c>
+      <c r="D789" s="2" t="s">
         <v>4189</v>
-      </c>
-      <c r="D789" s="2" t="s">
-        <v>4190</v>
       </c>
       <c r="E789" s="3" t="s">
         <v>23</v>
@@ -56860,12 +56855,12 @@
         <v>85</v>
       </c>
       <c r="Q789" s="2" t="s">
-        <v>4191</v>
+        <v>4190</v>
       </c>
       <c r="R789" s="2"/>
       <c r="S789" s="2"/>
       <c r="T789" s="2" t="s">
-        <v>4192</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="790" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -56876,10 +56871,10 @@
         <v>570</v>
       </c>
       <c r="C790" s="9" t="s">
+        <v>4192</v>
+      </c>
+      <c r="D790" s="9" t="s">
         <v>4193</v>
-      </c>
-      <c r="D790" s="9" t="s">
-        <v>4194</v>
       </c>
       <c r="E790" s="10" t="s">
         <v>1120</v>
@@ -56896,7 +56891,7 @@
         <v>2</v>
       </c>
       <c r="K790" s="9" t="s">
-        <v>4195</v>
+        <v>4194</v>
       </c>
       <c r="L790" s="9" t="s">
         <v>100</v>
@@ -56914,7 +56909,7 @@
         <v>80</v>
       </c>
       <c r="Q790" s="9" t="s">
-        <v>4196</v>
+        <v>4195</v>
       </c>
       <c r="R790" s="9"/>
       <c r="S790" s="9"/>
@@ -56928,10 +56923,10 @@
         <v>570</v>
       </c>
       <c r="C791" s="9" t="s">
+        <v>4196</v>
+      </c>
+      <c r="D791" s="9" t="s">
         <v>4197</v>
-      </c>
-      <c r="D791" s="9" t="s">
-        <v>4198</v>
       </c>
       <c r="E791" s="10" t="s">
         <v>63</v>
@@ -56966,7 +56961,7 @@
         <v>80</v>
       </c>
       <c r="Q791" s="9" t="s">
-        <v>4199</v>
+        <v>4198</v>
       </c>
       <c r="R791" s="9"/>
       <c r="S791" s="9"/>
@@ -56980,13 +56975,13 @@
         <v>570</v>
       </c>
       <c r="C792" s="9" t="s">
+        <v>4199</v>
+      </c>
+      <c r="D792" s="9" t="s">
         <v>4200</v>
       </c>
-      <c r="D792" s="9" t="s">
+      <c r="E792" s="10" t="s">
         <v>4201</v>
-      </c>
-      <c r="E792" s="10" t="s">
-        <v>4202</v>
       </c>
       <c r="F792" s="9"/>
       <c r="G792" s="9"/>
@@ -57018,7 +57013,7 @@
         <v>75</v>
       </c>
       <c r="Q792" s="9" t="s">
-        <v>4203</v>
+        <v>4202</v>
       </c>
       <c r="R792" s="9"/>
       <c r="S792" s="9"/>
@@ -57032,13 +57027,13 @@
         <v>570</v>
       </c>
       <c r="C793" s="9" t="s">
+        <v>4203</v>
+      </c>
+      <c r="D793" s="9" t="s">
         <v>4204</v>
       </c>
-      <c r="D793" s="9" t="s">
+      <c r="E793" s="10" t="s">
         <v>4205</v>
-      </c>
-      <c r="E793" s="10" t="s">
-        <v>4206</v>
       </c>
       <c r="F793" s="9"/>
       <c r="G793" s="9"/>
@@ -57070,7 +57065,7 @@
         <v>75</v>
       </c>
       <c r="Q793" s="9" t="s">
-        <v>4207</v>
+        <v>4206</v>
       </c>
       <c r="R793" s="9"/>
       <c r="S793" s="9"/>
@@ -57084,13 +57079,13 @@
         <v>570</v>
       </c>
       <c r="C794" s="9" t="s">
+        <v>4207</v>
+      </c>
+      <c r="D794" s="9" t="s">
         <v>4208</v>
       </c>
-      <c r="D794" s="9" t="s">
+      <c r="E794" s="10" t="s">
         <v>4209</v>
-      </c>
-      <c r="E794" s="10" t="s">
-        <v>4210</v>
       </c>
       <c r="F794" s="9"/>
       <c r="G794" s="9"/>
@@ -57107,7 +57102,7 @@
         <v>382</v>
       </c>
       <c r="L794" s="9" t="s">
-        <v>4211</v>
+        <v>4210</v>
       </c>
       <c r="M794" s="13">
         <v>7000</v>
@@ -57122,12 +57117,12 @@
         <v>75</v>
       </c>
       <c r="Q794" s="9" t="s">
-        <v>4212</v>
+        <v>4211</v>
       </c>
       <c r="R794" s="9"/>
       <c r="S794" s="9"/>
       <c r="T794" s="9" t="s">
-        <v>4213</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="795" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -57138,10 +57133,10 @@
         <v>570</v>
       </c>
       <c r="C795" s="9" t="s">
+        <v>4213</v>
+      </c>
+      <c r="D795" s="9" t="s">
         <v>4214</v>
-      </c>
-      <c r="D795" s="9" t="s">
-        <v>4215</v>
       </c>
       <c r="E795" s="10" t="s">
         <v>520</v>
@@ -57161,7 +57156,7 @@
         <v>522</v>
       </c>
       <c r="L795" s="9" t="s">
-        <v>4216</v>
+        <v>4215</v>
       </c>
       <c r="M795" s="13">
         <v>8000</v>
@@ -57176,12 +57171,12 @@
         <v>75</v>
       </c>
       <c r="Q795" s="9" t="s">
-        <v>4217</v>
+        <v>4216</v>
       </c>
       <c r="R795" s="9"/>
       <c r="S795" s="9"/>
       <c r="T795" s="9" t="s">
-        <v>4218</v>
+        <v>4217</v>
       </c>
     </row>
     <row r="796" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -57192,10 +57187,10 @@
         <v>570</v>
       </c>
       <c r="C796" s="17" t="s">
+        <v>4218</v>
+      </c>
+      <c r="D796" s="17" t="s">
         <v>4219</v>
-      </c>
-      <c r="D796" s="17" t="s">
-        <v>4220</v>
       </c>
       <c r="E796" s="18" t="s">
         <v>1986</v>
@@ -57230,7 +57225,7 @@
         <v>60</v>
       </c>
       <c r="Q796" s="17" t="s">
-        <v>4221</v>
+        <v>4220</v>
       </c>
       <c r="R796" s="17"/>
       <c r="S796" s="17"/>
@@ -57244,13 +57239,13 @@
         <v>570</v>
       </c>
       <c r="C797" s="17" t="s">
+        <v>4221</v>
+      </c>
+      <c r="D797" s="17" t="s">
         <v>4222</v>
       </c>
-      <c r="D797" s="17" t="s">
+      <c r="E797" s="18" t="s">
         <v>4223</v>
-      </c>
-      <c r="E797" s="18" t="s">
-        <v>4224</v>
       </c>
       <c r="F797" s="17"/>
       <c r="G797" s="17"/>
@@ -57264,7 +57259,7 @@
         <v>3</v>
       </c>
       <c r="K797" s="17" t="s">
-        <v>4225</v>
+        <v>4224</v>
       </c>
       <c r="L797" s="17" t="s">
         <v>66</v>
@@ -57282,7 +57277,7 @@
         <v>60</v>
       </c>
       <c r="Q797" s="17" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
       <c r="R797" s="17"/>
       <c r="S797" s="17"/>
@@ -57296,10 +57291,10 @@
         <v>570</v>
       </c>
       <c r="C798" s="17" t="s">
+        <v>4226</v>
+      </c>
+      <c r="D798" s="17" t="s">
         <v>4227</v>
-      </c>
-      <c r="D798" s="17" t="s">
-        <v>4228</v>
       </c>
       <c r="E798" s="18" t="s">
         <v>418</v>
@@ -57334,7 +57329,7 @@
         <v>60</v>
       </c>
       <c r="Q798" s="17" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
       <c r="R798" s="17"/>
       <c r="S798" s="17"/>
@@ -57348,13 +57343,13 @@
         <v>1242</v>
       </c>
       <c r="C799" s="17" t="s">
+        <v>4229</v>
+      </c>
+      <c r="D799" s="17" t="s">
         <v>4230</v>
       </c>
-      <c r="D799" s="17" t="s">
+      <c r="E799" s="18" t="s">
         <v>4231</v>
-      </c>
-      <c r="E799" s="18" t="s">
-        <v>4232</v>
       </c>
       <c r="F799" s="17"/>
       <c r="G799" s="17"/>
@@ -57368,10 +57363,10 @@
         <v>3</v>
       </c>
       <c r="K799" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L799" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L799" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M799" s="21">
         <v>3000</v>
@@ -57386,10 +57381,10 @@
         <v>120</v>
       </c>
       <c r="Q799" s="17" t="s">
+        <v>4234</v>
+      </c>
+      <c r="R799" s="17" t="s">
         <v>4235</v>
-      </c>
-      <c r="R799" s="17" t="s">
-        <v>4236</v>
       </c>
       <c r="S799" s="17"/>
       <c r="T799" s="17"/>
@@ -57402,13 +57397,13 @@
         <v>1242</v>
       </c>
       <c r="C800" s="17" t="s">
+        <v>4236</v>
+      </c>
+      <c r="D800" s="17" t="s">
         <v>4237</v>
       </c>
-      <c r="D800" s="17" t="s">
+      <c r="E800" s="18" t="s">
         <v>4238</v>
-      </c>
-      <c r="E800" s="18" t="s">
-        <v>4239</v>
       </c>
       <c r="F800" s="17"/>
       <c r="G800" s="17"/>
@@ -57422,10 +57417,10 @@
         <v>3</v>
       </c>
       <c r="K800" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L800" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L800" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M800" s="21">
         <v>3000</v>
@@ -57440,10 +57435,10 @@
         <v>120</v>
       </c>
       <c r="Q800" s="17" t="s">
+        <v>4239</v>
+      </c>
+      <c r="R800" s="17" t="s">
         <v>4240</v>
-      </c>
-      <c r="R800" s="17" t="s">
-        <v>4241</v>
       </c>
       <c r="S800" s="17"/>
       <c r="T800" s="17"/>
@@ -57456,13 +57451,13 @@
         <v>2069</v>
       </c>
       <c r="C801" s="17" t="s">
+        <v>4241</v>
+      </c>
+      <c r="D801" s="17" t="s">
         <v>4242</v>
       </c>
-      <c r="D801" s="17" t="s">
+      <c r="E801" s="18" t="s">
         <v>4243</v>
-      </c>
-      <c r="E801" s="18" t="s">
-        <v>4244</v>
       </c>
       <c r="F801" s="17"/>
       <c r="G801" s="17"/>
@@ -57476,10 +57471,10 @@
         <v>3</v>
       </c>
       <c r="K801" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L801" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L801" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M801" s="21">
         <v>3000</v>
@@ -57494,10 +57489,10 @@
         <v>120</v>
       </c>
       <c r="Q801" s="17" t="s">
+        <v>4244</v>
+      </c>
+      <c r="R801" s="17" t="s">
         <v>4245</v>
-      </c>
-      <c r="R801" s="17" t="s">
-        <v>4246</v>
       </c>
       <c r="S801" s="17"/>
       <c r="T801" s="17"/>
@@ -57510,13 +57505,13 @@
         <v>782</v>
       </c>
       <c r="C802" s="17" t="s">
+        <v>4246</v>
+      </c>
+      <c r="D802" s="17" t="s">
         <v>4247</v>
       </c>
-      <c r="D802" s="17" t="s">
+      <c r="E802" s="18" t="s">
         <v>4248</v>
-      </c>
-      <c r="E802" s="18" t="s">
-        <v>4249</v>
       </c>
       <c r="F802" s="17"/>
       <c r="G802" s="17"/>
@@ -57530,10 +57525,10 @@
         <v>3</v>
       </c>
       <c r="K802" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L802" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L802" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M802" s="21">
         <v>3000</v>
@@ -57548,10 +57543,10 @@
         <v>120</v>
       </c>
       <c r="Q802" s="17" t="s">
+        <v>4249</v>
+      </c>
+      <c r="R802" s="17" t="s">
         <v>4250</v>
-      </c>
-      <c r="R802" s="17" t="s">
-        <v>4251</v>
       </c>
       <c r="S802" s="17"/>
       <c r="T802" s="17"/>
@@ -57564,13 +57559,13 @@
         <v>1996</v>
       </c>
       <c r="C803" s="17" t="s">
+        <v>4251</v>
+      </c>
+      <c r="D803" s="17" t="s">
         <v>4252</v>
       </c>
-      <c r="D803" s="17" t="s">
+      <c r="E803" s="18" t="s">
         <v>4253</v>
-      </c>
-      <c r="E803" s="18" t="s">
-        <v>4254</v>
       </c>
       <c r="F803" s="17"/>
       <c r="G803" s="17"/>
@@ -57584,10 +57579,10 @@
         <v>3</v>
       </c>
       <c r="K803" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L803" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L803" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M803" s="21">
         <v>3000</v>
@@ -57602,10 +57597,10 @@
         <v>120</v>
       </c>
       <c r="Q803" s="17" t="s">
+        <v>4254</v>
+      </c>
+      <c r="R803" s="17" t="s">
         <v>4255</v>
-      </c>
-      <c r="R803" s="17" t="s">
-        <v>4256</v>
       </c>
       <c r="S803" s="17"/>
       <c r="T803" s="17"/>
@@ -57618,13 +57613,13 @@
         <v>2764</v>
       </c>
       <c r="C804" s="17" t="s">
+        <v>4256</v>
+      </c>
+      <c r="D804" s="17" t="s">
         <v>4257</v>
       </c>
-      <c r="D804" s="17" t="s">
+      <c r="E804" s="18" t="s">
         <v>4258</v>
-      </c>
-      <c r="E804" s="18" t="s">
-        <v>4259</v>
       </c>
       <c r="F804" s="17"/>
       <c r="G804" s="17"/>
@@ -57638,10 +57633,10 @@
         <v>3</v>
       </c>
       <c r="K804" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L804" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L804" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M804" s="21">
         <v>3000</v>
@@ -57656,10 +57651,10 @@
         <v>120</v>
       </c>
       <c r="Q804" s="17" t="s">
+        <v>4259</v>
+      </c>
+      <c r="R804" s="17" t="s">
         <v>4260</v>
-      </c>
-      <c r="R804" s="17" t="s">
-        <v>4261</v>
       </c>
       <c r="S804" s="17"/>
       <c r="T804" s="17"/>
@@ -57672,13 +57667,13 @@
         <v>1927</v>
       </c>
       <c r="C805" s="17" t="s">
+        <v>4261</v>
+      </c>
+      <c r="D805" s="17" t="s">
         <v>4262</v>
       </c>
-      <c r="D805" s="17" t="s">
-        <v>4263</v>
-      </c>
       <c r="E805" s="18" t="s">
-        <v>4182</v>
+        <v>4181</v>
       </c>
       <c r="F805" s="17"/>
       <c r="G805" s="17"/>
@@ -57692,10 +57687,10 @@
         <v>3</v>
       </c>
       <c r="K805" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L805" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L805" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M805" s="21">
         <v>3000</v>
@@ -57710,10 +57705,10 @@
         <v>120</v>
       </c>
       <c r="Q805" s="17" t="s">
+        <v>4263</v>
+      </c>
+      <c r="R805" s="17" t="s">
         <v>4264</v>
-      </c>
-      <c r="R805" s="17" t="s">
-        <v>4265</v>
       </c>
       <c r="S805" s="17"/>
       <c r="T805" s="17"/>
@@ -57726,13 +57721,13 @@
         <v>415</v>
       </c>
       <c r="C806" s="17" t="s">
+        <v>4265</v>
+      </c>
+      <c r="D806" s="17" t="s">
         <v>4266</v>
       </c>
-      <c r="D806" s="17" t="s">
+      <c r="E806" s="18" t="s">
         <v>4267</v>
-      </c>
-      <c r="E806" s="18" t="s">
-        <v>4268</v>
       </c>
       <c r="F806" s="17"/>
       <c r="G806" s="17"/>
@@ -57746,10 +57741,10 @@
         <v>3</v>
       </c>
       <c r="K806" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L806" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L806" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M806" s="21">
         <v>3000</v>
@@ -57764,10 +57759,10 @@
         <v>120</v>
       </c>
       <c r="Q806" s="17" t="s">
+        <v>4268</v>
+      </c>
+      <c r="R806" s="17" t="s">
         <v>4269</v>
-      </c>
-      <c r="R806" s="17" t="s">
-        <v>4270</v>
       </c>
       <c r="S806" s="17"/>
       <c r="T806" s="17"/>
@@ -57780,13 +57775,13 @@
         <v>2899</v>
       </c>
       <c r="C807" s="17" t="s">
+        <v>4270</v>
+      </c>
+      <c r="D807" s="17" t="s">
         <v>4271</v>
       </c>
-      <c r="D807" s="17" t="s">
+      <c r="E807" s="18" t="s">
         <v>4272</v>
-      </c>
-      <c r="E807" s="18" t="s">
-        <v>4273</v>
       </c>
       <c r="F807" s="17"/>
       <c r="G807" s="17"/>
@@ -57800,10 +57795,10 @@
         <v>3</v>
       </c>
       <c r="K807" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L807" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L807" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M807" s="21">
         <v>3000</v>
@@ -57818,10 +57813,10 @@
         <v>120</v>
       </c>
       <c r="Q807" s="17" t="s">
+        <v>4273</v>
+      </c>
+      <c r="R807" s="17" t="s">
         <v>4274</v>
-      </c>
-      <c r="R807" s="17" t="s">
-        <v>4275</v>
       </c>
       <c r="S807" s="17"/>
       <c r="T807" s="17"/>
@@ -57834,13 +57829,13 @@
         <v>2838</v>
       </c>
       <c r="C808" s="17" t="s">
+        <v>4275</v>
+      </c>
+      <c r="D808" s="17" t="s">
         <v>4276</v>
       </c>
-      <c r="D808" s="17" t="s">
-        <v>4277</v>
-      </c>
       <c r="E808" s="18" t="s">
-        <v>4206</v>
+        <v>4205</v>
       </c>
       <c r="F808" s="17"/>
       <c r="G808" s="17"/>
@@ -57854,10 +57849,10 @@
         <v>3</v>
       </c>
       <c r="K808" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L808" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L808" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M808" s="21">
         <v>3000</v>
@@ -57872,10 +57867,10 @@
         <v>120</v>
       </c>
       <c r="Q808" s="17" t="s">
+        <v>4277</v>
+      </c>
+      <c r="R808" s="17" t="s">
         <v>4278</v>
-      </c>
-      <c r="R808" s="17" t="s">
-        <v>4279</v>
       </c>
       <c r="S808" s="17"/>
       <c r="T808" s="17"/>
@@ -57888,13 +57883,13 @@
         <v>1777</v>
       </c>
       <c r="C809" s="17" t="s">
+        <v>4279</v>
+      </c>
+      <c r="D809" s="17" t="s">
         <v>4280</v>
       </c>
-      <c r="D809" s="17" t="s">
+      <c r="E809" s="18" t="s">
         <v>4281</v>
-      </c>
-      <c r="E809" s="18" t="s">
-        <v>4282</v>
       </c>
       <c r="F809" s="17"/>
       <c r="G809" s="17"/>
@@ -57908,10 +57903,10 @@
         <v>3</v>
       </c>
       <c r="K809" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L809" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L809" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M809" s="21">
         <v>3000</v>
@@ -57926,10 +57921,10 @@
         <v>120</v>
       </c>
       <c r="Q809" s="17" t="s">
+        <v>4282</v>
+      </c>
+      <c r="R809" s="17" t="s">
         <v>4283</v>
-      </c>
-      <c r="R809" s="17" t="s">
-        <v>4284</v>
       </c>
       <c r="S809" s="17"/>
       <c r="T809" s="17"/>
@@ -57942,13 +57937,13 @@
         <v>1317</v>
       </c>
       <c r="C810" s="17" t="s">
+        <v>4284</v>
+      </c>
+      <c r="D810" s="17" t="s">
         <v>4285</v>
       </c>
-      <c r="D810" s="17" t="s">
+      <c r="E810" s="18" t="s">
         <v>4286</v>
-      </c>
-      <c r="E810" s="18" t="s">
-        <v>4287</v>
       </c>
       <c r="F810" s="17"/>
       <c r="G810" s="17"/>
@@ -57962,10 +57957,10 @@
         <v>3</v>
       </c>
       <c r="K810" s="17" t="s">
+        <v>4232</v>
+      </c>
+      <c r="L810" s="17" t="s">
         <v>4233</v>
-      </c>
-      <c r="L810" s="17" t="s">
-        <v>4234</v>
       </c>
       <c r="M810" s="21">
         <v>3000</v>
@@ -57980,10 +57975,10 @@
         <v>120</v>
       </c>
       <c r="Q810" s="17" t="s">
+        <v>4287</v>
+      </c>
+      <c r="R810" s="17" t="s">
         <v>4288</v>
-      </c>
-      <c r="R810" s="17" t="s">
-        <v>4289</v>
       </c>
       <c r="S810" s="17"/>
       <c r="T810" s="17"/>
@@ -57996,17 +57991,17 @@
         <v>1581</v>
       </c>
       <c r="C811" s="2" t="s">
+        <v>4289</v>
+      </c>
+      <c r="D811" s="2" t="s">
         <v>4290</v>
-      </c>
-      <c r="D811" s="2" t="s">
-        <v>4291</v>
       </c>
       <c r="E811" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F811" s="2"/>
       <c r="G811" s="2" t="s">
-        <v>4293</v>
+        <v>4292</v>
       </c>
       <c r="H811" s="4">
         <v>41.81</v>
@@ -58018,10 +58013,10 @@
         <v>1</v>
       </c>
       <c r="K811" s="2" t="s">
+        <v>4291</v>
+      </c>
+      <c r="L811" s="2" t="s">
         <v>4292</v>
-      </c>
-      <c r="L811" s="2" t="s">
-        <v>4293</v>
       </c>
       <c r="M811" s="6">
         <v>6000</v>
@@ -58036,7 +58031,7 @@
         <v>90</v>
       </c>
       <c r="Q811" s="2" t="s">
-        <v>4294</v>
+        <v>4293</v>
       </c>
       <c r="R811" s="2"/>
       <c r="S811" s="2"/>
@@ -58050,10 +58045,10 @@
         <v>1642</v>
       </c>
       <c r="C812" s="9" t="s">
+        <v>4294</v>
+      </c>
+      <c r="D812" s="9" t="s">
         <v>4295</v>
-      </c>
-      <c r="D812" s="9" t="s">
-        <v>4296</v>
       </c>
       <c r="E812" s="10" t="s">
         <v>418</v>
@@ -58070,7 +58065,7 @@
         <v>2</v>
       </c>
       <c r="K812" s="9" t="s">
-        <v>4292</v>
+        <v>4291</v>
       </c>
       <c r="L812" s="9" t="s">
         <v>421</v>
@@ -58088,7 +58083,7 @@
         <v>75</v>
       </c>
       <c r="Q812" s="9" t="s">
-        <v>4297</v>
+        <v>4296</v>
       </c>
       <c r="R812" s="9"/>
       <c r="S812" s="9"/>
@@ -58102,13 +58097,13 @@
         <v>1927</v>
       </c>
       <c r="C813" s="9" t="s">
+        <v>4297</v>
+      </c>
+      <c r="D813" s="9" t="s">
         <v>4298</v>
       </c>
-      <c r="D813" s="9" t="s">
+      <c r="E813" s="10" t="s">
         <v>4299</v>
-      </c>
-      <c r="E813" s="10" t="s">
-        <v>4300</v>
       </c>
       <c r="F813" s="9"/>
       <c r="G813" s="9"/>
@@ -58122,7 +58117,7 @@
         <v>2</v>
       </c>
       <c r="K813" s="9" t="s">
-        <v>4292</v>
+        <v>4291</v>
       </c>
       <c r="L813" s="9" t="s">
         <v>421</v>
@@ -58140,7 +58135,7 @@
         <v>75</v>
       </c>
       <c r="Q813" s="9" t="s">
-        <v>4301</v>
+        <v>4300</v>
       </c>
       <c r="R813" s="9"/>
       <c r="S813" s="9"/>
@@ -58154,13 +58149,13 @@
         <v>2528</v>
       </c>
       <c r="C814" s="9" t="s">
+        <v>4301</v>
+      </c>
+      <c r="D814" s="9" t="s">
         <v>4302</v>
       </c>
-      <c r="D814" s="9" t="s">
-        <v>4303</v>
-      </c>
       <c r="E814" s="10" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="F814" s="9"/>
       <c r="G814" s="9"/>
@@ -58174,7 +58169,7 @@
         <v>2</v>
       </c>
       <c r="K814" s="9" t="s">
-        <v>4304</v>
+        <v>4303</v>
       </c>
       <c r="L814" s="9" t="s">
         <v>421</v>
@@ -58192,7 +58187,7 @@
         <v>75</v>
       </c>
       <c r="Q814" s="9" t="s">
-        <v>4305</v>
+        <v>4304</v>
       </c>
       <c r="R814" s="9"/>
       <c r="S814" s="9"/>
@@ -58206,10 +58201,10 @@
         <v>125</v>
       </c>
       <c r="C815" s="9" t="s">
+        <v>4305</v>
+      </c>
+      <c r="D815" s="9" t="s">
         <v>4306</v>
-      </c>
-      <c r="D815" s="9" t="s">
-        <v>4307</v>
       </c>
       <c r="E815" s="10" t="s">
         <v>418</v>
@@ -58226,7 +58221,7 @@
         <v>2</v>
       </c>
       <c r="K815" s="9" t="s">
-        <v>4308</v>
+        <v>4307</v>
       </c>
       <c r="L815" s="9" t="s">
         <v>421</v>
@@ -58244,7 +58239,7 @@
         <v>75</v>
       </c>
       <c r="Q815" s="9" t="s">
-        <v>4309</v>
+        <v>4308</v>
       </c>
       <c r="R815" s="9"/>
       <c r="S815" s="9"/>
@@ -58258,13 +58253,13 @@
         <v>2163</v>
       </c>
       <c r="C816" s="9" t="s">
+        <v>4309</v>
+      </c>
+      <c r="D816" s="9" t="s">
         <v>4310</v>
       </c>
-      <c r="D816" s="9" t="s">
+      <c r="E816" s="10" t="s">
         <v>4311</v>
-      </c>
-      <c r="E816" s="10" t="s">
-        <v>4312</v>
       </c>
       <c r="F816" s="9"/>
       <c r="G816" s="9"/>
@@ -58278,7 +58273,7 @@
         <v>2</v>
       </c>
       <c r="K816" s="9" t="s">
-        <v>4292</v>
+        <v>4291</v>
       </c>
       <c r="L816" s="9" t="s">
         <v>421</v>
@@ -58296,7 +58291,7 @@
         <v>75</v>
       </c>
       <c r="Q816" s="9" t="s">
-        <v>4313</v>
+        <v>4312</v>
       </c>
       <c r="R816" s="9"/>
       <c r="S816" s="9"/>
@@ -58310,10 +58305,10 @@
         <v>2838</v>
       </c>
       <c r="C817" s="9" t="s">
+        <v>4313</v>
+      </c>
+      <c r="D817" s="9" t="s">
         <v>4314</v>
-      </c>
-      <c r="D817" s="9" t="s">
-        <v>4315</v>
       </c>
       <c r="E817" s="10" t="s">
         <v>63</v>
@@ -58330,7 +58325,7 @@
         <v>2</v>
       </c>
       <c r="K817" s="9" t="s">
-        <v>4316</v>
+        <v>4315</v>
       </c>
       <c r="L817" s="9" t="s">
         <v>421</v>
@@ -58348,7 +58343,7 @@
         <v>75</v>
       </c>
       <c r="Q817" s="9" t="s">
-        <v>4317</v>
+        <v>4316</v>
       </c>
       <c r="R817" s="9"/>
       <c r="S817" s="9"/>
@@ -58362,13 +58357,13 @@
         <v>495</v>
       </c>
       <c r="C818" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="D818" s="9" t="s">
         <v>4318</v>
       </c>
-      <c r="D818" s="9" t="s">
+      <c r="E818" s="10" t="s">
         <v>4319</v>
-      </c>
-      <c r="E818" s="10" t="s">
-        <v>4320</v>
       </c>
       <c r="F818" s="9"/>
       <c r="G818" s="9"/>
@@ -58382,10 +58377,10 @@
         <v>2</v>
       </c>
       <c r="K818" s="9" t="s">
+        <v>4320</v>
+      </c>
+      <c r="L818" s="9" t="s">
         <v>4321</v>
-      </c>
-      <c r="L818" s="9" t="s">
-        <v>4322</v>
       </c>
       <c r="M818" s="13">
         <v>4500</v>
@@ -58400,7 +58395,7 @@
         <v>75</v>
       </c>
       <c r="Q818" s="9" t="s">
-        <v>4323</v>
+        <v>4322</v>
       </c>
       <c r="R818" s="9"/>
       <c r="S818" s="9"/>
@@ -58414,13 +58409,13 @@
         <v>600</v>
       </c>
       <c r="C819" s="17" t="s">
+        <v>4323</v>
+      </c>
+      <c r="D819" s="17" t="s">
         <v>4324</v>
       </c>
-      <c r="D819" s="17" t="s">
+      <c r="E819" s="18" t="s">
         <v>4325</v>
-      </c>
-      <c r="E819" s="18" t="s">
-        <v>4326</v>
       </c>
       <c r="F819" s="17"/>
       <c r="G819" s="17"/>
@@ -58434,10 +58429,10 @@
         <v>3</v>
       </c>
       <c r="K819" s="17" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
       <c r="L819" s="17" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
       <c r="M819" s="21">
         <v>4000</v>
@@ -58452,7 +58447,7 @@
         <v>60</v>
       </c>
       <c r="Q819" s="17" t="s">
-        <v>4328</v>
+        <v>4327</v>
       </c>
       <c r="R819" s="17"/>
       <c r="S819" s="17"/>
@@ -58466,13 +58461,13 @@
         <v>1242</v>
       </c>
       <c r="C820" s="17" t="s">
+        <v>4328</v>
+      </c>
+      <c r="D820" s="17" t="s">
         <v>4329</v>
       </c>
-      <c r="D820" s="17" t="s">
+      <c r="E820" s="18" t="s">
         <v>4330</v>
-      </c>
-      <c r="E820" s="18" t="s">
-        <v>4331</v>
       </c>
       <c r="F820" s="17"/>
       <c r="G820" s="17"/>
@@ -58486,10 +58481,10 @@
         <v>3</v>
       </c>
       <c r="K820" s="17" t="s">
-        <v>4332</v>
+        <v>4331</v>
       </c>
       <c r="L820" s="17" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
       <c r="M820" s="21">
         <v>4500</v>
@@ -58504,7 +58499,7 @@
         <v>60</v>
       </c>
       <c r="Q820" s="17" t="s">
-        <v>4333</v>
+        <v>4332</v>
       </c>
       <c r="R820" s="17"/>
       <c r="S820" s="17"/>
@@ -58518,10 +58513,10 @@
         <v>2958</v>
       </c>
       <c r="C821" s="17" t="s">
+        <v>4333</v>
+      </c>
+      <c r="D821" s="17" t="s">
         <v>4334</v>
-      </c>
-      <c r="D821" s="17" t="s">
-        <v>4335</v>
       </c>
       <c r="E821" s="18" t="s">
         <v>301</v>
@@ -58538,10 +58533,10 @@
         <v>3</v>
       </c>
       <c r="K821" s="17" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
       <c r="L821" s="17" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
       <c r="M821" s="21">
         <v>4500</v>
@@ -58556,7 +58551,7 @@
         <v>60</v>
       </c>
       <c r="Q821" s="17" t="s">
-        <v>4336</v>
+        <v>4335</v>
       </c>
       <c r="R821" s="17"/>
       <c r="S821" s="17"/>
@@ -58564,19 +58559,19 @@
     </row>
     <row r="822" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="17" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="B822" s="17" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="C822" s="17" t="s">
+        <v>4336</v>
+      </c>
+      <c r="D822" s="17" t="s">
         <v>4337</v>
       </c>
-      <c r="D822" s="17" t="s">
+      <c r="E822" s="18" t="s">
         <v>4338</v>
-      </c>
-      <c r="E822" s="18" t="s">
-        <v>4339</v>
       </c>
       <c r="F822" s="17"/>
       <c r="G822" s="17"/>
@@ -58590,10 +58585,10 @@
         <v>3</v>
       </c>
       <c r="K822" s="17" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
       <c r="L822" s="17" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
       <c r="M822" s="21">
         <v>5000</v>
@@ -58608,7 +58603,7 @@
         <v>60</v>
       </c>
       <c r="Q822" s="17" t="s">
-        <v>4340</v>
+        <v>4339</v>
       </c>
       <c r="R822" s="17"/>
       <c r="S822" s="17"/>
@@ -58622,10 +58617,10 @@
         <v>2899</v>
       </c>
       <c r="C823" s="17" t="s">
+        <v>4340</v>
+      </c>
+      <c r="D823" s="17" t="s">
         <v>4341</v>
-      </c>
-      <c r="D823" s="17" t="s">
-        <v>4342</v>
       </c>
       <c r="E823" s="18" t="s">
         <v>2388</v>
@@ -58642,10 +58637,10 @@
         <v>3</v>
       </c>
       <c r="K823" s="17" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
       <c r="L823" s="17" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
       <c r="M823" s="21">
         <v>4500</v>
@@ -58660,7 +58655,7 @@
         <v>60</v>
       </c>
       <c r="Q823" s="17" t="s">
-        <v>4343</v>
+        <v>4342</v>
       </c>
       <c r="R823" s="17"/>
       <c r="S823" s="17"/>
@@ -58674,10 +58669,10 @@
         <v>2690</v>
       </c>
       <c r="C824" s="17" t="s">
+        <v>4343</v>
+      </c>
+      <c r="D824" s="17" t="s">
         <v>4344</v>
-      </c>
-      <c r="D824" s="17" t="s">
-        <v>4345</v>
       </c>
       <c r="E824" s="18" t="s">
         <v>830</v>
@@ -58694,10 +58689,10 @@
         <v>3</v>
       </c>
       <c r="K824" s="17" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
       <c r="L824" s="17" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
       <c r="M824" s="21">
         <v>3500</v>
@@ -58712,7 +58707,7 @@
         <v>60</v>
       </c>
       <c r="Q824" s="17" t="s">
-        <v>4346</v>
+        <v>4345</v>
       </c>
       <c r="R824" s="17"/>
       <c r="S824" s="17"/>
@@ -58735,41 +58730,41 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="37" t="s">
-        <v>4347</v>
+        <v>4346</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
-        <v>4348</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
+        <v>4348</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>4349</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>4350</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
+        <v>4350</v>
+      </c>
+      <c r="B5" s="40" t="s">
         <v>4351</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>4352</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="42" t="s">
+        <v>4352</v>
+      </c>
+      <c r="B6" s="40" t="s">
         <v>4353</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>4354</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>4355</v>
+        <v>4354</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -58777,7 +58772,7 @@
         <v>101</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -58785,23 +58780,23 @@
         <v>36</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="45" t="s">
-        <v>4357</v>
+        <v>4356</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="46" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -58809,15 +58804,15 @@
         <v>1884</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="48" t="s">
-        <v>4358</v>
+        <v>4357</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -58825,7 +58820,7 @@
         <v>992</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -58833,12 +58828,12 @@
         <v>2648</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="38" t="s">
-        <v>4359</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -58846,7 +58841,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>4360</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -58854,7 +58849,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>4361</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -58862,15 +58857,15 @@
         <v>4</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>4362</v>
+        <v>4361</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="51" t="s">
+        <v>4362</v>
+      </c>
+      <c r="B22" s="40" t="s">
         <v>4363</v>
-      </c>
-      <c r="B22" s="40" t="s">
-        <v>4364</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -58878,7 +58873,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>4365</v>
+        <v>4364</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -58886,7 +58881,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>4366</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -58894,7 +58889,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>4367</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -58902,7 +58897,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>4368</v>
+        <v>4367</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -58910,7 +58905,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>4369</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -58918,7 +58913,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>4370</v>
+        <v>4369</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -58926,7 +58921,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>4371</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -58934,7 +58929,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>4372</v>
+        <v>4371</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -58942,30 +58937,30 @@
         <v>18</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>4373</v>
+        <v>4372</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
+        <v>4373</v>
+      </c>
+      <c r="B32" s="40" t="s">
         <v>4374</v>
-      </c>
-      <c r="B32" s="40" t="s">
-        <v>4375</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="52" t="s">
-        <v>4376</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.2">
       <c r="B35" s="53" t="s">
-        <v>4377</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B36" s="53" t="s">
-        <v>4378</v>
+        <v>4377</v>
       </c>
     </row>
   </sheetData>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41824E27-0616-B745-A331-446C7F8C6709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66876ABB-6483-3747-83FE-29343D7D7B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48395,7 +48395,7 @@
         <v>3381</v>
       </c>
       <c r="M633" s="6">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="N633" s="23" t="s">
         <v>101</v>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66876ABB-6483-3747-83FE-29343D7D7B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD73F95-4E88-0C4B-A08E-B299DA78A2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48395,7 +48395,7 @@
         <v>3381</v>
       </c>
       <c r="M633" s="6">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="N633" s="23" t="s">
         <v>101</v>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD73F95-4E88-0C4B-A08E-B299DA78A2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9C67EA-028E-4B4E-A881-16FB68FE5AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10168,15 +10168,9 @@
     <t>https://raw.githubusercontent.com/CarlosVelasco1998/raidio-backend/main/poi-images/valle-de-los-caidos.png</t>
   </si>
   <si>
-    <t>"historia", "guerra_civil", "memoria", "arquitectura", "datosCuriosos"</t>
-  </si>
-  <si>
     <t>memorial</t>
   </si>
   <si>
-    <t>"arquitectura", "siglo_xx", "memoria_historica", "contexto_guerra_civil", "construccion"</t>
-  </si>
-  <si>
     <t>[{"id": "es_mad_el_escorial", "nombre": "Monasterio de San Lorenzo de El Escorial (UNESCO)", "tipo": "monasterio", "nivel": 1, "lat": 40.590105, "lng": -4.147921, "radio": 5000}]</t>
   </si>
   <si>
@@ -13205,6 +13199,12 @@
   </si>
   <si>
     <t>{"sponsorId":"spon_a4_Jabalquinto","sponsorNombre":"E.S. Jabalquinto","mensaje":"repostas, descansas y pruebas el primer aceite de oliva de Jaén recién catado, ya en plena tierra del olivo","url":"https://www.google.com/maps/place/Gasolinera+Repsol/@38.0207004,-3.7892213,15.17z/data=!4m10!1m2!2m1!1sgasolinera!3m6!1s0xd6c299f51727a85:0x3c3b246577bad203!8m2!3d38.0234334!4d-3.77986!15sCgpnYXNvbGluZXJhWgwiCmdhc29saW5lcmGSAQtnYXNfc3RhdGlvbpoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VObE5sODNkM0puUlJBQuABAPoBBAgAEDM!16s%2Fg%2F11bx5pm6bw?entry=ttu&amp;g_ep=EgoyMDI2MDcwNi4wIKXMDSoASAFQAw%3D%3D"}</t>
+  </si>
+  <si>
+    <t>"historia", "memoria", "religión cristiana", "arquitectura", "datosCuriosos"</t>
+  </si>
+  <si>
+    <t>"Cruz_mas_grande", "siglo_xx", "contexto_guerra_civil", "construccion", "reconocimiento".</t>
   </si>
 </sst>
 </file>
@@ -13927,7 +13927,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4378</v>
+        <v>4376</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -16601,7 +16601,7 @@
         <v>302</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>4380</v>
+        <v>4378</v>
       </c>
       <c r="H50" s="11">
         <v>37.015099999999997</v>
@@ -17693,7 +17693,7 @@
         <v>419</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>4379</v>
+        <v>4377</v>
       </c>
       <c r="H70" s="4">
         <v>38.305300000000003</v>
@@ -17749,7 +17749,7 @@
         <v>425</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>4379</v>
+        <v>4377</v>
       </c>
       <c r="H71" s="4">
         <v>38.096200000000003</v>
@@ -18281,19 +18281,19 @@
         <v>415</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>4389</v>
+        <v>4387</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>4390</v>
+        <v>4388</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>4383</v>
+        <v>4381</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>4384</v>
+        <v>4382</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>4384</v>
+        <v>4382</v>
       </c>
       <c r="H81" s="11">
         <v>38.031067100000001</v>
@@ -18305,10 +18305,10 @@
         <v>1</v>
       </c>
       <c r="K81" s="9" t="s">
-        <v>4385</v>
+        <v>4383</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>4386</v>
+        <v>4384</v>
       </c>
       <c r="M81" s="13">
         <v>2000</v>
@@ -18323,10 +18323,10 @@
         <v>60</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>4391</v>
+        <v>4389</v>
       </c>
       <c r="R81" s="9" t="s">
-        <v>4392</v>
+        <v>4390</v>
       </c>
       <c r="S81" s="9"/>
       <c r="T81" s="9"/>
@@ -36487,19 +36487,19 @@
         <v>2163</v>
       </c>
       <c r="C415" s="9" t="s">
+        <v>4379</v>
+      </c>
+      <c r="D415" s="9" t="s">
+        <v>4380</v>
+      </c>
+      <c r="E415" s="10" t="s">
         <v>4381</v>
       </c>
-      <c r="D415" s="9" t="s">
+      <c r="F415" s="9" t="s">
         <v>4382</v>
       </c>
-      <c r="E415" s="10" t="s">
-        <v>4383</v>
-      </c>
-      <c r="F415" s="9" t="s">
-        <v>4384</v>
-      </c>
       <c r="G415" s="9" t="s">
-        <v>4384</v>
+        <v>4382</v>
       </c>
       <c r="H415" s="11">
         <v>39.794677700000001</v>
@@ -36511,10 +36511,10 @@
         <v>1</v>
       </c>
       <c r="K415" s="9" t="s">
-        <v>4385</v>
+        <v>4383</v>
       </c>
       <c r="L415" s="9" t="s">
-        <v>4386</v>
+        <v>4384</v>
       </c>
       <c r="M415" s="13">
         <v>2000</v>
@@ -36529,10 +36529,10 @@
         <v>60</v>
       </c>
       <c r="Q415" s="9" t="s">
-        <v>4387</v>
+        <v>4385</v>
       </c>
       <c r="R415" s="9" t="s">
-        <v>4388</v>
+        <v>4386</v>
       </c>
       <c r="S415" s="9"/>
       <c r="T415" s="9"/>
@@ -48267,7 +48267,7 @@
         <v>3368</v>
       </c>
       <c r="G631" s="2" t="s">
-        <v>4379</v>
+        <v>4377</v>
       </c>
       <c r="H631" s="4">
         <v>41.1325</v>
@@ -48389,10 +48389,10 @@
         <v>1</v>
       </c>
       <c r="K633" s="2" t="s">
+        <v>4391</v>
+      </c>
+      <c r="L633" s="2" t="s">
         <v>3380</v>
-      </c>
-      <c r="L633" s="2" t="s">
-        <v>3381</v>
       </c>
       <c r="M633" s="6">
         <v>11000</v>
@@ -48407,12 +48407,12 @@
         <v>90</v>
       </c>
       <c r="Q633" s="2" t="s">
-        <v>3382</v>
+        <v>4392</v>
       </c>
       <c r="R633" s="2"/>
       <c r="S633" s="2"/>
       <c r="T633" s="2" t="s">
-        <v>3383</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="634" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -48423,16 +48423,16 @@
         <v>3365</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>3384</v>
+        <v>3382</v>
       </c>
       <c r="D634" s="2" t="s">
-        <v>3385</v>
+        <v>3383</v>
       </c>
       <c r="E634" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F634" s="2" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
       <c r="G634" s="2"/>
       <c r="H634" s="4">
@@ -48445,7 +48445,7 @@
         <v>1</v>
       </c>
       <c r="K634" s="2" t="s">
-        <v>3387</v>
+        <v>3385</v>
       </c>
       <c r="L634" s="2" t="s">
         <v>921</v>
@@ -48463,12 +48463,12 @@
         <v>70</v>
       </c>
       <c r="Q634" s="2" t="s">
-        <v>3388</v>
+        <v>3386</v>
       </c>
       <c r="R634" s="2"/>
       <c r="S634" s="2"/>
       <c r="T634" s="2" t="s">
-        <v>3389</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="635" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -48479,16 +48479,16 @@
         <v>3365</v>
       </c>
       <c r="C635" s="2" t="s">
+        <v>3388</v>
+      </c>
+      <c r="D635" s="2" t="s">
+        <v>3389</v>
+      </c>
+      <c r="E635" s="3" t="s">
         <v>3390</v>
       </c>
-      <c r="D635" s="2" t="s">
+      <c r="F635" s="2" t="s">
         <v>3391</v>
-      </c>
-      <c r="E635" s="3" t="s">
-        <v>3392</v>
-      </c>
-      <c r="F635" s="2" t="s">
-        <v>3393</v>
       </c>
       <c r="G635" s="2"/>
       <c r="H635" s="4">
@@ -48501,10 +48501,10 @@
         <v>1</v>
       </c>
       <c r="K635" s="2" t="s">
-        <v>3394</v>
+        <v>3392</v>
       </c>
       <c r="L635" s="2" t="s">
-        <v>3395</v>
+        <v>3393</v>
       </c>
       <c r="M635" s="6">
         <v>7000</v>
@@ -48519,7 +48519,7 @@
         <v>60</v>
       </c>
       <c r="Q635" s="2" t="s">
-        <v>3396</v>
+        <v>3394</v>
       </c>
       <c r="R635" s="2"/>
       <c r="S635" s="2"/>
@@ -48533,16 +48533,16 @@
         <v>3365</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>3397</v>
+        <v>3395</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>3398</v>
+        <v>3396</v>
       </c>
       <c r="E636" s="3" t="s">
         <v>603</v>
       </c>
       <c r="F636" s="2" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
       <c r="G636" s="2"/>
       <c r="H636" s="4">
@@ -48555,7 +48555,7 @@
         <v>1</v>
       </c>
       <c r="K636" s="2" t="s">
-        <v>3400</v>
+        <v>3398</v>
       </c>
       <c r="L636" s="2" t="s">
         <v>1200</v>
@@ -48573,7 +48573,7 @@
         <v>60</v>
       </c>
       <c r="Q636" s="2" t="s">
-        <v>3401</v>
+        <v>3399</v>
       </c>
       <c r="R636" s="2"/>
       <c r="S636" s="2"/>
@@ -48587,16 +48587,16 @@
         <v>3365</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>3402</v>
+        <v>3400</v>
       </c>
       <c r="D637" s="2" t="s">
-        <v>3403</v>
+        <v>3401</v>
       </c>
       <c r="E637" s="3" t="s">
         <v>603</v>
       </c>
       <c r="F637" s="2" t="s">
-        <v>3404</v>
+        <v>3402</v>
       </c>
       <c r="G637" s="2"/>
       <c r="H637" s="4">
@@ -48609,7 +48609,7 @@
         <v>1</v>
       </c>
       <c r="K637" s="2" t="s">
-        <v>3405</v>
+        <v>3403</v>
       </c>
       <c r="L637" s="2" t="s">
         <v>606</v>
@@ -48627,12 +48627,12 @@
         <v>45</v>
       </c>
       <c r="Q637" s="2" t="s">
-        <v>3406</v>
+        <v>3404</v>
       </c>
       <c r="R637" s="2"/>
       <c r="S637" s="2"/>
       <c r="T637" s="2" t="s">
-        <v>3407</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="638" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -48643,16 +48643,16 @@
         <v>3365</v>
       </c>
       <c r="C638" s="9" t="s">
-        <v>3408</v>
+        <v>3406</v>
       </c>
       <c r="D638" s="9" t="s">
-        <v>3409</v>
+        <v>3407</v>
       </c>
       <c r="E638" s="10" t="s">
         <v>418</v>
       </c>
       <c r="F638" s="9" t="s">
-        <v>3410</v>
+        <v>3408</v>
       </c>
       <c r="G638" s="9"/>
       <c r="H638" s="11">
@@ -48665,10 +48665,10 @@
         <v>2</v>
       </c>
       <c r="K638" s="9" t="s">
-        <v>3411</v>
+        <v>3409</v>
       </c>
       <c r="L638" s="9" t="s">
-        <v>3412</v>
+        <v>3410</v>
       </c>
       <c r="M638" s="13">
         <v>4000</v>
@@ -48683,7 +48683,7 @@
         <v>90</v>
       </c>
       <c r="Q638" s="9" t="s">
-        <v>3413</v>
+        <v>3411</v>
       </c>
       <c r="R638" s="9"/>
       <c r="S638" s="9"/>
@@ -48697,16 +48697,16 @@
         <v>3365</v>
       </c>
       <c r="C639" s="9" t="s">
-        <v>3414</v>
+        <v>3412</v>
       </c>
       <c r="D639" s="9" t="s">
-        <v>3415</v>
+        <v>3413</v>
       </c>
       <c r="E639" s="10" t="s">
         <v>2207</v>
       </c>
       <c r="F639" s="9" t="s">
-        <v>3416</v>
+        <v>3414</v>
       </c>
       <c r="G639" s="9"/>
       <c r="H639" s="11">
@@ -48719,10 +48719,10 @@
         <v>2</v>
       </c>
       <c r="K639" s="9" t="s">
-        <v>3417</v>
+        <v>3415</v>
       </c>
       <c r="L639" s="9" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="M639" s="13">
         <v>2500</v>
@@ -48737,7 +48737,7 @@
         <v>40</v>
       </c>
       <c r="Q639" s="9" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="R639" s="9"/>
       <c r="S639" s="9"/>
@@ -48751,16 +48751,16 @@
         <v>3365</v>
       </c>
       <c r="C640" s="9" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="D640" s="9" t="s">
-        <v>3421</v>
+        <v>3419</v>
       </c>
       <c r="E640" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F640" s="9" t="s">
-        <v>3422</v>
+        <v>3420</v>
       </c>
       <c r="G640" s="9"/>
       <c r="H640" s="11">
@@ -48791,7 +48791,7 @@
         <v>40</v>
       </c>
       <c r="Q640" s="9" t="s">
-        <v>3423</v>
+        <v>3421</v>
       </c>
       <c r="R640" s="9"/>
       <c r="S640" s="9"/>
@@ -48805,16 +48805,16 @@
         <v>3365</v>
       </c>
       <c r="C641" s="9" t="s">
-        <v>3424</v>
+        <v>3422</v>
       </c>
       <c r="D641" s="9" t="s">
-        <v>3425</v>
+        <v>3423</v>
       </c>
       <c r="E641" s="10" t="s">
         <v>648</v>
       </c>
       <c r="F641" s="9" t="s">
-        <v>3426</v>
+        <v>3424</v>
       </c>
       <c r="G641" s="9"/>
       <c r="H641" s="11">
@@ -48827,10 +48827,10 @@
         <v>2</v>
       </c>
       <c r="K641" s="9" t="s">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="L641" s="9" t="s">
-        <v>3428</v>
+        <v>3426</v>
       </c>
       <c r="M641" s="13">
         <v>3000</v>
@@ -48845,12 +48845,12 @@
         <v>45</v>
       </c>
       <c r="Q641" s="9" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="R641" s="9"/>
       <c r="S641" s="9"/>
       <c r="T641" s="9" t="s">
-        <v>3430</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="642" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -48861,16 +48861,16 @@
         <v>3365</v>
       </c>
       <c r="C642" s="9" t="s">
-        <v>3431</v>
+        <v>3429</v>
       </c>
       <c r="D642" s="9" t="s">
-        <v>3432</v>
+        <v>3430</v>
       </c>
       <c r="E642" s="10" t="s">
         <v>91</v>
       </c>
       <c r="F642" s="9" t="s">
-        <v>3433</v>
+        <v>3431</v>
       </c>
       <c r="G642" s="9"/>
       <c r="H642" s="11">
@@ -48883,7 +48883,7 @@
         <v>2</v>
       </c>
       <c r="K642" s="9" t="s">
-        <v>3434</v>
+        <v>3432</v>
       </c>
       <c r="L642" s="9" t="s">
         <v>123</v>
@@ -48901,7 +48901,7 @@
         <v>40</v>
       </c>
       <c r="Q642" s="9" t="s">
-        <v>3435</v>
+        <v>3433</v>
       </c>
       <c r="R642" s="9"/>
       <c r="S642" s="9"/>
@@ -48915,16 +48915,16 @@
         <v>3365</v>
       </c>
       <c r="C643" s="17" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="D643" s="17" t="s">
-        <v>3437</v>
+        <v>3435</v>
       </c>
       <c r="E643" s="18" t="s">
         <v>63</v>
       </c>
       <c r="F643" s="17" t="s">
-        <v>3438</v>
+        <v>3436</v>
       </c>
       <c r="G643" s="17"/>
       <c r="H643" s="19">
@@ -48955,7 +48955,7 @@
         <v>40</v>
       </c>
       <c r="Q643" s="17" t="s">
-        <v>3439</v>
+        <v>3437</v>
       </c>
       <c r="R643" s="17"/>
       <c r="S643" s="17"/>
@@ -48969,16 +48969,16 @@
         <v>3365</v>
       </c>
       <c r="C644" s="17" t="s">
-        <v>3440</v>
+        <v>3438</v>
       </c>
       <c r="D644" s="17" t="s">
-        <v>3441</v>
+        <v>3439</v>
       </c>
       <c r="E644" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F644" s="17" t="s">
-        <v>3442</v>
+        <v>3440</v>
       </c>
       <c r="G644" s="17"/>
       <c r="H644" s="19">
@@ -48991,7 +48991,7 @@
         <v>3</v>
       </c>
       <c r="K644" s="17" t="s">
-        <v>3443</v>
+        <v>3441</v>
       </c>
       <c r="L644" s="17" t="s">
         <v>123</v>
@@ -49009,7 +49009,7 @@
         <v>35</v>
       </c>
       <c r="Q644" s="17" t="s">
-        <v>3444</v>
+        <v>3442</v>
       </c>
       <c r="R644" s="17"/>
       <c r="S644" s="17"/>
@@ -49017,22 +49017,22 @@
     </row>
     <row r="645" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="2" t="s">
+        <v>3443</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>3443</v>
+      </c>
+      <c r="C645" s="2" t="s">
+        <v>3444</v>
+      </c>
+      <c r="D645" s="2" t="s">
         <v>3445</v>
-      </c>
-      <c r="B645" s="2" t="s">
-        <v>3445</v>
-      </c>
-      <c r="C645" s="2" t="s">
-        <v>3446</v>
-      </c>
-      <c r="D645" s="2" t="s">
-        <v>3447</v>
       </c>
       <c r="E645" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F645" s="2" t="s">
-        <v>3448</v>
+        <v>3446</v>
       </c>
       <c r="G645" s="2"/>
       <c r="H645" s="4">
@@ -49045,7 +49045,7 @@
         <v>1</v>
       </c>
       <c r="K645" s="2" t="s">
-        <v>3449</v>
+        <v>3447</v>
       </c>
       <c r="L645" s="2" t="s">
         <v>26</v>
@@ -49063,32 +49063,32 @@
         <v>80</v>
       </c>
       <c r="Q645" s="2" t="s">
-        <v>3450</v>
+        <v>3448</v>
       </c>
       <c r="R645" s="2"/>
       <c r="S645" s="2"/>
       <c r="T645" s="2" t="s">
-        <v>3451</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="646" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>3452</v>
+        <v>3450</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>3453</v>
+        <v>3451</v>
       </c>
       <c r="E646" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F646" s="2" t="s">
-        <v>3454</v>
+        <v>3452</v>
       </c>
       <c r="G646" s="2"/>
       <c r="H646" s="4">
@@ -49101,7 +49101,7 @@
         <v>1</v>
       </c>
       <c r="K646" s="2" t="s">
-        <v>3455</v>
+        <v>3453</v>
       </c>
       <c r="L646" s="2" t="s">
         <v>35</v>
@@ -49119,7 +49119,7 @@
         <v>85</v>
       </c>
       <c r="Q646" s="2" t="s">
-        <v>3456</v>
+        <v>3454</v>
       </c>
       <c r="R646" s="2"/>
       <c r="S646" s="2"/>
@@ -49127,22 +49127,22 @@
     </row>
     <row r="647" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>3457</v>
+        <v>3455</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>3458</v>
+        <v>3456</v>
       </c>
       <c r="E647" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F647" s="2" t="s">
-        <v>3459</v>
+        <v>3457</v>
       </c>
       <c r="G647" s="2"/>
       <c r="H647" s="4">
@@ -49173,32 +49173,32 @@
         <v>75</v>
       </c>
       <c r="Q647" s="2" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="R647" s="2"/>
       <c r="S647" s="2"/>
       <c r="T647" s="2" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="648" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
       <c r="D648" s="2" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="E648" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F648" s="2" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="G648" s="2"/>
       <c r="H648" s="4">
@@ -49229,7 +49229,7 @@
         <v>75</v>
       </c>
       <c r="Q648" s="2" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="R648" s="2"/>
       <c r="S648" s="2"/>
@@ -49237,22 +49237,22 @@
     </row>
     <row r="649" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="D649" s="2" t="s">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="E649" s="3" t="s">
         <v>988</v>
       </c>
       <c r="F649" s="2" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="G649" s="2"/>
       <c r="H649" s="4">
@@ -49265,7 +49265,7 @@
         <v>1</v>
       </c>
       <c r="K649" s="2" t="s">
-        <v>3469</v>
+        <v>3467</v>
       </c>
       <c r="L649" s="2" t="s">
         <v>1040</v>
@@ -49283,7 +49283,7 @@
         <v>75</v>
       </c>
       <c r="Q649" s="2" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="R649" s="2"/>
       <c r="S649" s="2"/>
@@ -49291,22 +49291,22 @@
     </row>
     <row r="650" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="D650" s="2" t="s">
-        <v>3472</v>
+        <v>3470</v>
       </c>
       <c r="E650" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F650" s="2" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="G650" s="2"/>
       <c r="H650" s="4">
@@ -49319,7 +49319,7 @@
         <v>1</v>
       </c>
       <c r="K650" s="2" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="L650" s="2" t="s">
         <v>72</v>
@@ -49337,7 +49337,7 @@
         <v>70</v>
       </c>
       <c r="Q650" s="2" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="R650" s="2"/>
       <c r="S650" s="2"/>
@@ -49345,22 +49345,22 @@
     </row>
     <row r="651" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>3476</v>
+        <v>3474</v>
       </c>
       <c r="D651" s="2" t="s">
-        <v>3477</v>
+        <v>3475</v>
       </c>
       <c r="E651" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F651" s="2" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="G651" s="2"/>
       <c r="H651" s="4">
@@ -49373,7 +49373,7 @@
         <v>1</v>
       </c>
       <c r="K651" s="2" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="L651" s="2" t="s">
         <v>100</v>
@@ -49391,32 +49391,32 @@
         <v>70</v>
       </c>
       <c r="Q651" s="2" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="R651" s="2"/>
       <c r="S651" s="2"/>
       <c r="T651" s="2" t="s">
-        <v>3480</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="652" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="E652" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F652" s="2" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="G652" s="2"/>
       <c r="H652" s="4">
@@ -49429,7 +49429,7 @@
         <v>1</v>
       </c>
       <c r="K652" s="2" t="s">
-        <v>3484</v>
+        <v>3482</v>
       </c>
       <c r="L652" s="2" t="s">
         <v>233</v>
@@ -49447,7 +49447,7 @@
         <v>65</v>
       </c>
       <c r="Q652" s="2" t="s">
-        <v>3485</v>
+        <v>3483</v>
       </c>
       <c r="R652" s="2"/>
       <c r="S652" s="2"/>
@@ -49455,22 +49455,22 @@
     </row>
     <row r="653" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="E653" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F653" s="2" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="G653" s="2"/>
       <c r="H653" s="4">
@@ -49483,7 +49483,7 @@
         <v>1</v>
       </c>
       <c r="K653" s="2" t="s">
-        <v>3489</v>
+        <v>3487</v>
       </c>
       <c r="L653" s="2" t="s">
         <v>72</v>
@@ -49501,7 +49501,7 @@
         <v>60</v>
       </c>
       <c r="Q653" s="2" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="R653" s="2"/>
       <c r="S653" s="2"/>
@@ -49509,22 +49509,22 @@
     </row>
     <row r="654" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B654" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C654" s="9" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="D654" s="9" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="E654" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F654" s="9" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="G654" s="9"/>
       <c r="H654" s="11">
@@ -49537,7 +49537,7 @@
         <v>2</v>
       </c>
       <c r="K654" s="9" t="s">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="L654" s="9" t="s">
         <v>100</v>
@@ -49555,7 +49555,7 @@
         <v>55</v>
       </c>
       <c r="Q654" s="9" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="R654" s="9"/>
       <c r="S654" s="9"/>
@@ -49563,22 +49563,22 @@
     </row>
     <row r="655" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B655" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C655" s="9" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="D655" s="9" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="E655" s="10" t="s">
         <v>1577</v>
       </c>
       <c r="F655" s="9" t="s">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="G655" s="9"/>
       <c r="H655" s="11">
@@ -49591,10 +49591,10 @@
         <v>2</v>
       </c>
       <c r="K655" s="9" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="L655" s="9" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="M655" s="13">
         <v>5000</v>
@@ -49609,7 +49609,7 @@
         <v>55</v>
       </c>
       <c r="Q655" s="9" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="R655" s="9"/>
       <c r="S655" s="9"/>
@@ -49617,22 +49617,22 @@
     </row>
     <row r="656" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B656" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C656" s="9" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="D656" s="9" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="E656" s="10" t="s">
         <v>301</v>
       </c>
       <c r="F656" s="9" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="G656" s="9"/>
       <c r="H656" s="11">
@@ -49645,7 +49645,7 @@
         <v>2</v>
       </c>
       <c r="K656" s="9" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="L656" s="9" t="s">
         <v>685</v>
@@ -49663,7 +49663,7 @@
         <v>55</v>
       </c>
       <c r="Q656" s="9" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="R656" s="9"/>
       <c r="S656" s="9"/>
@@ -49671,22 +49671,22 @@
     </row>
     <row r="657" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B657" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C657" s="9" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="D657" s="9" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="E657" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F657" s="9" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="G657" s="9"/>
       <c r="H657" s="11">
@@ -49699,7 +49699,7 @@
         <v>2</v>
       </c>
       <c r="K657" s="9" t="s">
-        <v>3510</v>
+        <v>3508</v>
       </c>
       <c r="L657" s="9" t="s">
         <v>112</v>
@@ -49717,7 +49717,7 @@
         <v>55</v>
       </c>
       <c r="Q657" s="9" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="R657" s="9"/>
       <c r="S657" s="9"/>
@@ -49725,22 +49725,22 @@
     </row>
     <row r="658" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B658" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C658" s="9" t="s">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="D658" s="9" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="E658" s="10" t="s">
         <v>864</v>
       </c>
       <c r="F658" s="9" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="G658" s="9"/>
       <c r="H658" s="11">
@@ -49753,7 +49753,7 @@
         <v>2</v>
       </c>
       <c r="K658" s="9" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="L658" s="9" t="s">
         <v>2331</v>
@@ -49771,7 +49771,7 @@
         <v>55</v>
       </c>
       <c r="Q658" s="9" t="s">
-        <v>3516</v>
+        <v>3514</v>
       </c>
       <c r="R658" s="9"/>
       <c r="S658" s="9"/>
@@ -49779,22 +49779,22 @@
     </row>
     <row r="659" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B659" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C659" s="9" t="s">
-        <v>3517</v>
+        <v>3515</v>
       </c>
       <c r="D659" s="9" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
       <c r="E659" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F659" s="9" t="s">
-        <v>3519</v>
+        <v>3517</v>
       </c>
       <c r="G659" s="9"/>
       <c r="H659" s="11">
@@ -49807,7 +49807,7 @@
         <v>2</v>
       </c>
       <c r="K659" s="9" t="s">
-        <v>3520</v>
+        <v>3518</v>
       </c>
       <c r="L659" s="9" t="s">
         <v>100</v>
@@ -49825,7 +49825,7 @@
         <v>50</v>
       </c>
       <c r="Q659" s="9" t="s">
-        <v>3521</v>
+        <v>3519</v>
       </c>
       <c r="R659" s="9"/>
       <c r="S659" s="9"/>
@@ -49833,22 +49833,22 @@
     </row>
     <row r="660" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B660" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C660" s="9" t="s">
-        <v>3522</v>
+        <v>3520</v>
       </c>
       <c r="D660" s="9" t="s">
-        <v>3523</v>
+        <v>3521</v>
       </c>
       <c r="E660" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F660" s="9" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
       <c r="G660" s="9"/>
       <c r="H660" s="11">
@@ -49861,7 +49861,7 @@
         <v>2</v>
       </c>
       <c r="K660" s="9" t="s">
-        <v>3525</v>
+        <v>3523</v>
       </c>
       <c r="L660" s="9" t="s">
         <v>112</v>
@@ -49879,7 +49879,7 @@
         <v>50</v>
       </c>
       <c r="Q660" s="9" t="s">
-        <v>3526</v>
+        <v>3524</v>
       </c>
       <c r="R660" s="9"/>
       <c r="S660" s="9"/>
@@ -49887,22 +49887,22 @@
     </row>
     <row r="661" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="2" t="s">
+        <v>3525</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>3526</v>
+      </c>
+      <c r="C661" s="2" t="s">
         <v>3527</v>
       </c>
-      <c r="B661" s="2" t="s">
+      <c r="D661" s="2" t="s">
         <v>3528</v>
-      </c>
-      <c r="C661" s="2" t="s">
-        <v>3529</v>
-      </c>
-      <c r="D661" s="2" t="s">
-        <v>3530</v>
       </c>
       <c r="E661" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F661" s="2" t="s">
-        <v>3531</v>
+        <v>3529</v>
       </c>
       <c r="G661" s="2"/>
       <c r="H661" s="4">
@@ -49915,7 +49915,7 @@
         <v>1</v>
       </c>
       <c r="K661" s="2" t="s">
-        <v>3532</v>
+        <v>3530</v>
       </c>
       <c r="L661" s="2" t="s">
         <v>26</v>
@@ -49933,32 +49933,32 @@
         <v>85</v>
       </c>
       <c r="Q661" s="2" t="s">
-        <v>3533</v>
+        <v>3531</v>
       </c>
       <c r="R661" s="2"/>
       <c r="S661" s="2"/>
       <c r="T661" s="2" t="s">
-        <v>3534</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="662" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>3536</v>
+        <v>3534</v>
       </c>
       <c r="E662" s="3" t="s">
         <v>461</v>
       </c>
       <c r="F662" s="2" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="G662" s="2"/>
       <c r="H662" s="4">
@@ -49971,10 +49971,10 @@
         <v>1</v>
       </c>
       <c r="K662" s="2" t="s">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="L662" s="2" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="M662" s="6">
         <v>5500</v>
@@ -49989,7 +49989,7 @@
         <v>85</v>
       </c>
       <c r="Q662" s="2" t="s">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="R662" s="2"/>
       <c r="S662" s="2"/>
@@ -49997,22 +49997,22 @@
     </row>
     <row r="663" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="D663" s="2" t="s">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="E663" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F663" s="2" t="s">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="G663" s="2"/>
       <c r="H663" s="4">
@@ -50025,7 +50025,7 @@
         <v>1</v>
       </c>
       <c r="K663" s="2" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="L663" s="2" t="s">
         <v>72</v>
@@ -50043,32 +50043,32 @@
         <v>80</v>
       </c>
       <c r="Q663" s="2" t="s">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="R663" s="2"/>
       <c r="S663" s="2"/>
       <c r="T663" s="2" t="s">
-        <v>3546</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="664" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D664" s="2" t="s">
-        <v>3548</v>
+        <v>3546</v>
       </c>
       <c r="E664" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F664" s="2" t="s">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="G664" s="2"/>
       <c r="H664" s="4">
@@ -50081,7 +50081,7 @@
         <v>1</v>
       </c>
       <c r="K664" s="2" t="s">
-        <v>3550</v>
+        <v>3548</v>
       </c>
       <c r="L664" s="2" t="s">
         <v>35</v>
@@ -50099,7 +50099,7 @@
         <v>75</v>
       </c>
       <c r="Q664" s="2" t="s">
-        <v>3551</v>
+        <v>3549</v>
       </c>
       <c r="R664" s="2"/>
       <c r="S664" s="2"/>
@@ -50107,22 +50107,22 @@
     </row>
     <row r="665" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>3553</v>
+        <v>3551</v>
       </c>
       <c r="E665" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F665" s="2" t="s">
-        <v>3554</v>
+        <v>3552</v>
       </c>
       <c r="G665" s="2"/>
       <c r="H665" s="4">
@@ -50135,7 +50135,7 @@
         <v>1</v>
       </c>
       <c r="K665" s="2" t="s">
-        <v>3555</v>
+        <v>3553</v>
       </c>
       <c r="L665" s="2" t="s">
         <v>72</v>
@@ -50153,7 +50153,7 @@
         <v>60</v>
       </c>
       <c r="Q665" s="2" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="R665" s="2"/>
       <c r="S665" s="2"/>
@@ -50161,22 +50161,22 @@
     </row>
     <row r="666" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B666" s="9" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C666" s="9" t="s">
-        <v>3557</v>
+        <v>3555</v>
       </c>
       <c r="D666" s="9" t="s">
-        <v>3558</v>
+        <v>3556</v>
       </c>
       <c r="E666" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F666" s="9" t="s">
-        <v>3559</v>
+        <v>3557</v>
       </c>
       <c r="G666" s="9"/>
       <c r="H666" s="11">
@@ -50189,7 +50189,7 @@
         <v>2</v>
       </c>
       <c r="K666" s="9" t="s">
-        <v>3555</v>
+        <v>3553</v>
       </c>
       <c r="L666" s="9" t="s">
         <v>72</v>
@@ -50207,7 +50207,7 @@
         <v>55</v>
       </c>
       <c r="Q666" s="9" t="s">
-        <v>3560</v>
+        <v>3558</v>
       </c>
       <c r="R666" s="9"/>
       <c r="S666" s="9"/>
@@ -50215,22 +50215,22 @@
     </row>
     <row r="667" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B667" s="9" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C667" s="9" t="s">
-        <v>3561</v>
+        <v>3559</v>
       </c>
       <c r="D667" s="9" t="s">
-        <v>3562</v>
+        <v>3560</v>
       </c>
       <c r="E667" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F667" s="9" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G667" s="9"/>
       <c r="H667" s="11">
@@ -50243,7 +50243,7 @@
         <v>2</v>
       </c>
       <c r="K667" s="9" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="L667" s="9" t="s">
         <v>1018</v>
@@ -50261,32 +50261,32 @@
         <v>55</v>
       </c>
       <c r="Q667" s="9" t="s">
-        <v>3565</v>
+        <v>3563</v>
       </c>
       <c r="R667" s="9"/>
       <c r="S667" s="9"/>
       <c r="T667" s="9" t="s">
-        <v>3566</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="668" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B668" s="9" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C668" s="9" t="s">
-        <v>3567</v>
+        <v>3565</v>
       </c>
       <c r="D668" s="9" t="s">
-        <v>3568</v>
+        <v>3566</v>
       </c>
       <c r="E668" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F668" s="9" t="s">
-        <v>3569</v>
+        <v>3567</v>
       </c>
       <c r="G668" s="9"/>
       <c r="H668" s="11">
@@ -50299,7 +50299,7 @@
         <v>2</v>
       </c>
       <c r="K668" s="9" t="s">
-        <v>3570</v>
+        <v>3568</v>
       </c>
       <c r="L668" s="9" t="s">
         <v>1018</v>
@@ -50317,7 +50317,7 @@
         <v>55</v>
       </c>
       <c r="Q668" s="9" t="s">
-        <v>3571</v>
+        <v>3569</v>
       </c>
       <c r="R668" s="9"/>
       <c r="S668" s="9"/>
@@ -50325,22 +50325,22 @@
     </row>
     <row r="669" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B669" s="9" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C669" s="9" t="s">
-        <v>3572</v>
+        <v>3570</v>
       </c>
       <c r="D669" s="9" t="s">
-        <v>3573</v>
+        <v>3571</v>
       </c>
       <c r="E669" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F669" s="9" t="s">
-        <v>3574</v>
+        <v>3572</v>
       </c>
       <c r="G669" s="9"/>
       <c r="H669" s="11">
@@ -50353,7 +50353,7 @@
         <v>2</v>
       </c>
       <c r="K669" s="9" t="s">
-        <v>3575</v>
+        <v>3573</v>
       </c>
       <c r="L669" s="9" t="s">
         <v>72</v>
@@ -50371,7 +50371,7 @@
         <v>50</v>
       </c>
       <c r="Q669" s="9" t="s">
-        <v>3576</v>
+        <v>3574</v>
       </c>
       <c r="R669" s="9"/>
       <c r="S669" s="9"/>
@@ -50379,22 +50379,22 @@
     </row>
     <row r="670" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="17" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B670" s="17" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C670" s="17" t="s">
-        <v>3577</v>
+        <v>3575</v>
       </c>
       <c r="D670" s="17" t="s">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="E670" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F670" s="17" t="s">
-        <v>3579</v>
+        <v>3577</v>
       </c>
       <c r="G670" s="17"/>
       <c r="H670" s="19">
@@ -50425,7 +50425,7 @@
         <v>40</v>
       </c>
       <c r="Q670" s="17" t="s">
-        <v>3580</v>
+        <v>3578</v>
       </c>
       <c r="R670" s="17"/>
       <c r="S670" s="17"/>
@@ -50433,22 +50433,22 @@
     </row>
     <row r="671" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="17" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B671" s="17" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C671" s="17" t="s">
-        <v>3581</v>
+        <v>3579</v>
       </c>
       <c r="D671" s="17" t="s">
-        <v>3582</v>
+        <v>3580</v>
       </c>
       <c r="E671" s="18" t="s">
         <v>850</v>
       </c>
       <c r="F671" s="17" t="s">
-        <v>3583</v>
+        <v>3581</v>
       </c>
       <c r="G671" s="17"/>
       <c r="H671" s="19">
@@ -50461,10 +50461,10 @@
         <v>3</v>
       </c>
       <c r="K671" s="17" t="s">
-        <v>3584</v>
+        <v>3582</v>
       </c>
       <c r="L671" s="17" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="M671" s="21">
         <v>4500</v>
@@ -50479,7 +50479,7 @@
         <v>40</v>
       </c>
       <c r="Q671" s="17" t="s">
-        <v>3586</v>
+        <v>3584</v>
       </c>
       <c r="R671" s="17"/>
       <c r="S671" s="17"/>
@@ -50487,22 +50487,22 @@
     </row>
     <row r="672" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B672" s="2" t="s">
+        <v>3585</v>
+      </c>
+      <c r="C672" s="2" t="s">
+        <v>3586</v>
+      </c>
+      <c r="D672" s="2" t="s">
         <v>3587</v>
-      </c>
-      <c r="C672" s="2" t="s">
-        <v>3588</v>
-      </c>
-      <c r="D672" s="2" t="s">
-        <v>3589</v>
       </c>
       <c r="E672" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F672" s="2" t="s">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="G672" s="2"/>
       <c r="H672" s="4">
@@ -50515,7 +50515,7 @@
         <v>1</v>
       </c>
       <c r="K672" s="2" t="s">
-        <v>3591</v>
+        <v>3589</v>
       </c>
       <c r="L672" s="2" t="s">
         <v>26</v>
@@ -50533,32 +50533,32 @@
         <v>85</v>
       </c>
       <c r="Q672" s="2" t="s">
-        <v>3592</v>
+        <v>3590</v>
       </c>
       <c r="R672" s="2"/>
       <c r="S672" s="2"/>
       <c r="T672" s="2" t="s">
-        <v>3593</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="673" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
       <c r="D673" s="2" t="s">
-        <v>3595</v>
+        <v>3593</v>
       </c>
       <c r="E673" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F673" s="2" t="s">
-        <v>3596</v>
+        <v>3594</v>
       </c>
       <c r="G673" s="2"/>
       <c r="H673" s="4">
@@ -50571,10 +50571,10 @@
         <v>1</v>
       </c>
       <c r="K673" s="2" t="s">
-        <v>3597</v>
+        <v>3595</v>
       </c>
       <c r="L673" s="2" t="s">
-        <v>3598</v>
+        <v>3596</v>
       </c>
       <c r="M673" s="6">
         <v>5500</v>
@@ -50589,7 +50589,7 @@
         <v>80</v>
       </c>
       <c r="Q673" s="2" t="s">
-        <v>3599</v>
+        <v>3597</v>
       </c>
       <c r="R673" s="2"/>
       <c r="S673" s="2"/>
@@ -50597,22 +50597,22 @@
     </row>
     <row r="674" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>3600</v>
+        <v>3598</v>
       </c>
       <c r="D674" s="2" t="s">
-        <v>3601</v>
+        <v>3599</v>
       </c>
       <c r="E674" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F674" s="2" t="s">
-        <v>3602</v>
+        <v>3600</v>
       </c>
       <c r="G674" s="2"/>
       <c r="H674" s="4">
@@ -50625,7 +50625,7 @@
         <v>1</v>
       </c>
       <c r="K674" s="2" t="s">
-        <v>3603</v>
+        <v>3601</v>
       </c>
       <c r="L674" s="2" t="s">
         <v>1018</v>
@@ -50643,32 +50643,32 @@
         <v>75</v>
       </c>
       <c r="Q674" s="2" t="s">
-        <v>3604</v>
+        <v>3602</v>
       </c>
       <c r="R674" s="2"/>
       <c r="S674" s="2"/>
       <c r="T674" s="2" t="s">
-        <v>3605</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="675" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>3606</v>
+        <v>3604</v>
       </c>
       <c r="D675" s="2" t="s">
-        <v>3607</v>
+        <v>3605</v>
       </c>
       <c r="E675" s="3" t="s">
         <v>479</v>
       </c>
       <c r="F675" s="2" t="s">
-        <v>3608</v>
+        <v>3606</v>
       </c>
       <c r="G675" s="2"/>
       <c r="H675" s="4">
@@ -50681,7 +50681,7 @@
         <v>1</v>
       </c>
       <c r="K675" s="2" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="L675" s="2" t="s">
         <v>482</v>
@@ -50699,7 +50699,7 @@
         <v>65</v>
       </c>
       <c r="Q675" s="2" t="s">
-        <v>3610</v>
+        <v>3608</v>
       </c>
       <c r="R675" s="2"/>
       <c r="S675" s="2"/>
@@ -50707,22 +50707,22 @@
     </row>
     <row r="676" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>3611</v>
+        <v>3609</v>
       </c>
       <c r="D676" s="2" t="s">
-        <v>3612</v>
+        <v>3610</v>
       </c>
       <c r="E676" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F676" s="2" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="G676" s="2"/>
       <c r="H676" s="4">
@@ -50735,7 +50735,7 @@
         <v>1</v>
       </c>
       <c r="K676" s="2" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="L676" s="2" t="s">
         <v>1018</v>
@@ -50753,32 +50753,32 @@
         <v>60</v>
       </c>
       <c r="Q676" s="2" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="R676" s="2"/>
       <c r="S676" s="2"/>
       <c r="T676" s="2" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="677" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>3617</v>
+        <v>3615</v>
       </c>
       <c r="D677" s="2" t="s">
-        <v>3618</v>
+        <v>3616</v>
       </c>
       <c r="E677" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F677" s="2" t="s">
-        <v>3619</v>
+        <v>3617</v>
       </c>
       <c r="G677" s="2"/>
       <c r="H677" s="4">
@@ -50791,7 +50791,7 @@
         <v>1</v>
       </c>
       <c r="K677" s="2" t="s">
-        <v>3620</v>
+        <v>3618</v>
       </c>
       <c r="L677" s="2" t="s">
         <v>72</v>
@@ -50809,7 +50809,7 @@
         <v>65</v>
       </c>
       <c r="Q677" s="2" t="s">
-        <v>3621</v>
+        <v>3619</v>
       </c>
       <c r="R677" s="2"/>
       <c r="S677" s="2"/>
@@ -50817,22 +50817,22 @@
     </row>
     <row r="678" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B678" s="9" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C678" s="9" t="s">
-        <v>3622</v>
+        <v>3620</v>
       </c>
       <c r="D678" s="9" t="s">
-        <v>3623</v>
+        <v>3621</v>
       </c>
       <c r="E678" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F678" s="9" t="s">
-        <v>3624</v>
+        <v>3622</v>
       </c>
       <c r="G678" s="9"/>
       <c r="H678" s="11">
@@ -50845,7 +50845,7 @@
         <v>2</v>
       </c>
       <c r="K678" s="9" t="s">
-        <v>3625</v>
+        <v>3623</v>
       </c>
       <c r="L678" s="9" t="s">
         <v>112</v>
@@ -50863,7 +50863,7 @@
         <v>60</v>
       </c>
       <c r="Q678" s="9" t="s">
-        <v>3626</v>
+        <v>3624</v>
       </c>
       <c r="R678" s="9"/>
       <c r="S678" s="9"/>
@@ -50871,22 +50871,22 @@
     </row>
     <row r="679" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B679" s="9" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C679" s="9" t="s">
-        <v>3627</v>
+        <v>3625</v>
       </c>
       <c r="D679" s="9" t="s">
-        <v>3628</v>
+        <v>3626</v>
       </c>
       <c r="E679" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F679" s="9" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="G679" s="9"/>
       <c r="H679" s="11">
@@ -50899,7 +50899,7 @@
         <v>2</v>
       </c>
       <c r="K679" s="9" t="s">
-        <v>3630</v>
+        <v>3628</v>
       </c>
       <c r="L679" s="9" t="s">
         <v>112</v>
@@ -50917,7 +50917,7 @@
         <v>50</v>
       </c>
       <c r="Q679" s="9" t="s">
-        <v>3631</v>
+        <v>3629</v>
       </c>
       <c r="R679" s="9"/>
       <c r="S679" s="9"/>
@@ -50925,22 +50925,22 @@
     </row>
     <row r="680" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B680" s="9" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C680" s="9" t="s">
-        <v>3632</v>
+        <v>3630</v>
       </c>
       <c r="D680" s="9" t="s">
-        <v>3633</v>
+        <v>3631</v>
       </c>
       <c r="E680" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F680" s="9" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="G680" s="9"/>
       <c r="H680" s="11">
@@ -50953,7 +50953,7 @@
         <v>2</v>
       </c>
       <c r="K680" s="9" t="s">
-        <v>3635</v>
+        <v>3633</v>
       </c>
       <c r="L680" s="9" t="s">
         <v>72</v>
@@ -50971,7 +50971,7 @@
         <v>50</v>
       </c>
       <c r="Q680" s="9" t="s">
-        <v>3636</v>
+        <v>3634</v>
       </c>
       <c r="R680" s="9"/>
       <c r="S680" s="9"/>
@@ -50979,22 +50979,22 @@
     </row>
     <row r="681" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B681" s="9" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C681" s="9" t="s">
-        <v>3637</v>
+        <v>3635</v>
       </c>
       <c r="D681" s="9" t="s">
-        <v>3638</v>
+        <v>3636</v>
       </c>
       <c r="E681" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F681" s="9" t="s">
-        <v>3639</v>
+        <v>3637</v>
       </c>
       <c r="G681" s="9"/>
       <c r="H681" s="11">
@@ -51007,7 +51007,7 @@
         <v>2</v>
       </c>
       <c r="K681" s="9" t="s">
-        <v>3640</v>
+        <v>3638</v>
       </c>
       <c r="L681" s="9" t="s">
         <v>72</v>
@@ -51025,7 +51025,7 @@
         <v>50</v>
       </c>
       <c r="Q681" s="9" t="s">
-        <v>3641</v>
+        <v>3639</v>
       </c>
       <c r="R681" s="9"/>
       <c r="S681" s="9"/>
@@ -51033,22 +51033,22 @@
     </row>
     <row r="682" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B682" s="9" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C682" s="9" t="s">
-        <v>3642</v>
+        <v>3640</v>
       </c>
       <c r="D682" s="9" t="s">
-        <v>3643</v>
+        <v>3641</v>
       </c>
       <c r="E682" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F682" s="9" t="s">
-        <v>3644</v>
+        <v>3642</v>
       </c>
       <c r="G682" s="9"/>
       <c r="H682" s="11">
@@ -51061,7 +51061,7 @@
         <v>2</v>
       </c>
       <c r="K682" s="9" t="s">
-        <v>3570</v>
+        <v>3568</v>
       </c>
       <c r="L682" s="9" t="s">
         <v>1018</v>
@@ -51079,7 +51079,7 @@
         <v>45</v>
       </c>
       <c r="Q682" s="9" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="R682" s="9"/>
       <c r="S682" s="9"/>
@@ -51087,22 +51087,22 @@
     </row>
     <row r="683" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B683" s="9" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C683" s="9" t="s">
-        <v>3646</v>
+        <v>3644</v>
       </c>
       <c r="D683" s="9" t="s">
-        <v>3647</v>
+        <v>3645</v>
       </c>
       <c r="E683" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F683" s="9" t="s">
-        <v>3648</v>
+        <v>3646</v>
       </c>
       <c r="G683" s="9"/>
       <c r="H683" s="11">
@@ -51115,7 +51115,7 @@
         <v>2</v>
       </c>
       <c r="K683" s="9" t="s">
-        <v>3649</v>
+        <v>3647</v>
       </c>
       <c r="L683" s="9" t="s">
         <v>72</v>
@@ -51133,32 +51133,32 @@
         <v>45</v>
       </c>
       <c r="Q683" s="9" t="s">
-        <v>3650</v>
+        <v>3648</v>
       </c>
       <c r="R683" s="9"/>
       <c r="S683" s="9"/>
       <c r="T683" s="9" t="s">
-        <v>3651</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="684" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="17" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B684" s="17" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C684" s="17" t="s">
-        <v>3652</v>
+        <v>3650</v>
       </c>
       <c r="D684" s="17" t="s">
-        <v>3653</v>
+        <v>3651</v>
       </c>
       <c r="E684" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F684" s="17" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="G684" s="17"/>
       <c r="H684" s="19">
@@ -51171,7 +51171,7 @@
         <v>3</v>
       </c>
       <c r="K684" s="17" t="s">
-        <v>3655</v>
+        <v>3653</v>
       </c>
       <c r="L684" s="17" t="s">
         <v>123</v>
@@ -51189,7 +51189,7 @@
         <v>40</v>
       </c>
       <c r="Q684" s="17" t="s">
-        <v>3656</v>
+        <v>3654</v>
       </c>
       <c r="R684" s="17"/>
       <c r="S684" s="17"/>
@@ -51197,22 +51197,22 @@
     </row>
     <row r="685" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B685" s="2" t="s">
+        <v>3655</v>
+      </c>
+      <c r="C685" s="2" t="s">
+        <v>3656</v>
+      </c>
+      <c r="D685" s="2" t="s">
         <v>3657</v>
-      </c>
-      <c r="C685" s="2" t="s">
-        <v>3658</v>
-      </c>
-      <c r="D685" s="2" t="s">
-        <v>3659</v>
       </c>
       <c r="E685" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F685" s="2" t="s">
-        <v>3660</v>
+        <v>3658</v>
       </c>
       <c r="G685" s="2"/>
       <c r="H685" s="4">
@@ -51225,7 +51225,7 @@
         <v>1</v>
       </c>
       <c r="K685" s="2" t="s">
-        <v>3661</v>
+        <v>3659</v>
       </c>
       <c r="L685" s="2" t="s">
         <v>26</v>
@@ -51243,32 +51243,32 @@
         <v>80</v>
       </c>
       <c r="Q685" s="2" t="s">
-        <v>3662</v>
+        <v>3660</v>
       </c>
       <c r="R685" s="2"/>
       <c r="S685" s="2"/>
       <c r="T685" s="2" t="s">
-        <v>3663</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="686" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>3664</v>
+        <v>3662</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>3665</v>
+        <v>3663</v>
       </c>
       <c r="E686" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F686" s="2" t="s">
-        <v>3666</v>
+        <v>3664</v>
       </c>
       <c r="G686" s="2"/>
       <c r="H686" s="4">
@@ -51281,7 +51281,7 @@
         <v>1</v>
       </c>
       <c r="K686" s="2" t="s">
-        <v>3667</v>
+        <v>3665</v>
       </c>
       <c r="L686" s="2" t="s">
         <v>72</v>
@@ -51299,32 +51299,32 @@
         <v>80</v>
       </c>
       <c r="Q686" s="2" t="s">
-        <v>3668</v>
+        <v>3666</v>
       </c>
       <c r="R686" s="2"/>
       <c r="S686" s="2"/>
       <c r="T686" s="2" t="s">
-        <v>3669</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="687" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>3670</v>
+        <v>3668</v>
       </c>
       <c r="D687" s="2" t="s">
-        <v>3671</v>
+        <v>3669</v>
       </c>
       <c r="E687" s="3" t="s">
         <v>2153</v>
       </c>
       <c r="F687" s="2" t="s">
-        <v>3672</v>
+        <v>3670</v>
       </c>
       <c r="G687" s="2"/>
       <c r="H687" s="4">
@@ -51337,7 +51337,7 @@
         <v>1</v>
       </c>
       <c r="K687" s="2" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
       <c r="L687" s="2" t="s">
         <v>2156</v>
@@ -51355,32 +51355,32 @@
         <v>70</v>
       </c>
       <c r="Q687" s="2" t="s">
-        <v>3674</v>
+        <v>3672</v>
       </c>
       <c r="R687" s="2"/>
       <c r="S687" s="2"/>
       <c r="T687" s="2" t="s">
-        <v>3675</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="688" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>3676</v>
+        <v>3674</v>
       </c>
       <c r="D688" s="2" t="s">
-        <v>3677</v>
+        <v>3675</v>
       </c>
       <c r="E688" s="3" t="s">
         <v>461</v>
       </c>
       <c r="F688" s="2" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
       <c r="G688" s="2"/>
       <c r="H688" s="4">
@@ -51393,10 +51393,10 @@
         <v>1</v>
       </c>
       <c r="K688" s="2" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
       <c r="L688" s="2" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="M688" s="6">
         <v>5000</v>
@@ -51411,32 +51411,32 @@
         <v>75</v>
       </c>
       <c r="Q688" s="2" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="R688" s="2"/>
       <c r="S688" s="2"/>
       <c r="T688" s="2" t="s">
-        <v>3682</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="689" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>3683</v>
+        <v>3681</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="E689" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F689" s="2" t="s">
-        <v>3685</v>
+        <v>3683</v>
       </c>
       <c r="G689" s="2"/>
       <c r="H689" s="4">
@@ -51449,7 +51449,7 @@
         <v>1</v>
       </c>
       <c r="K689" s="2" t="s">
-        <v>3550</v>
+        <v>3548</v>
       </c>
       <c r="L689" s="2" t="s">
         <v>35</v>
@@ -51467,7 +51467,7 @@
         <v>70</v>
       </c>
       <c r="Q689" s="2" t="s">
-        <v>3686</v>
+        <v>3684</v>
       </c>
       <c r="R689" s="2"/>
       <c r="S689" s="2"/>
@@ -51475,22 +51475,22 @@
     </row>
     <row r="690" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>3687</v>
+        <v>3685</v>
       </c>
       <c r="D690" s="2" t="s">
-        <v>3688</v>
+        <v>3686</v>
       </c>
       <c r="E690" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F690" s="2" t="s">
-        <v>3689</v>
+        <v>3687</v>
       </c>
       <c r="G690" s="2"/>
       <c r="H690" s="4">
@@ -51503,7 +51503,7 @@
         <v>1</v>
       </c>
       <c r="K690" s="2" t="s">
-        <v>3690</v>
+        <v>3688</v>
       </c>
       <c r="L690" s="2" t="s">
         <v>35</v>
@@ -51521,7 +51521,7 @@
         <v>70</v>
       </c>
       <c r="Q690" s="2" t="s">
-        <v>3691</v>
+        <v>3689</v>
       </c>
       <c r="R690" s="2"/>
       <c r="S690" s="2"/>
@@ -51529,22 +51529,22 @@
     </row>
     <row r="691" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>3692</v>
+        <v>3690</v>
       </c>
       <c r="D691" s="2" t="s">
-        <v>3693</v>
+        <v>3691</v>
       </c>
       <c r="E691" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F691" s="2" t="s">
-        <v>3694</v>
+        <v>3692</v>
       </c>
       <c r="G691" s="2"/>
       <c r="H691" s="4">
@@ -51557,7 +51557,7 @@
         <v>1</v>
       </c>
       <c r="K691" s="2" t="s">
-        <v>3695</v>
+        <v>3693</v>
       </c>
       <c r="L691" s="2" t="s">
         <v>1982</v>
@@ -51575,7 +51575,7 @@
         <v>60</v>
       </c>
       <c r="Q691" s="2" t="s">
-        <v>3696</v>
+        <v>3694</v>
       </c>
       <c r="R691" s="2"/>
       <c r="S691" s="2"/>
@@ -51583,22 +51583,22 @@
     </row>
     <row r="692" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B692" s="9" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C692" s="9" t="s">
-        <v>3697</v>
+        <v>3695</v>
       </c>
       <c r="D692" s="9" t="s">
-        <v>3698</v>
+        <v>3696</v>
       </c>
       <c r="E692" s="10" t="s">
         <v>301</v>
       </c>
       <c r="F692" s="9" t="s">
-        <v>3699</v>
+        <v>3697</v>
       </c>
       <c r="G692" s="9"/>
       <c r="H692" s="11">
@@ -51611,7 +51611,7 @@
         <v>2</v>
       </c>
       <c r="K692" s="9" t="s">
-        <v>3700</v>
+        <v>3698</v>
       </c>
       <c r="L692" s="9" t="s">
         <v>984</v>
@@ -51629,7 +51629,7 @@
         <v>55</v>
       </c>
       <c r="Q692" s="9" t="s">
-        <v>3701</v>
+        <v>3699</v>
       </c>
       <c r="R692" s="9"/>
       <c r="S692" s="9"/>
@@ -51637,22 +51637,22 @@
     </row>
     <row r="693" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B693" s="9" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C693" s="9" t="s">
-        <v>3702</v>
+        <v>3700</v>
       </c>
       <c r="D693" s="9" t="s">
-        <v>3703</v>
+        <v>3701</v>
       </c>
       <c r="E693" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F693" s="9" t="s">
-        <v>3704</v>
+        <v>3702</v>
       </c>
       <c r="G693" s="9"/>
       <c r="H693" s="11">
@@ -51665,7 +51665,7 @@
         <v>2</v>
       </c>
       <c r="K693" s="9" t="s">
-        <v>3705</v>
+        <v>3703</v>
       </c>
       <c r="L693" s="9" t="s">
         <v>72</v>
@@ -51683,7 +51683,7 @@
         <v>50</v>
       </c>
       <c r="Q693" s="9" t="s">
-        <v>3706</v>
+        <v>3704</v>
       </c>
       <c r="R693" s="9"/>
       <c r="S693" s="9"/>
@@ -51691,22 +51691,22 @@
     </row>
     <row r="694" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B694" s="9" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C694" s="9" t="s">
-        <v>3707</v>
+        <v>3705</v>
       </c>
       <c r="D694" s="9" t="s">
-        <v>3708</v>
+        <v>3706</v>
       </c>
       <c r="E694" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F694" s="9" t="s">
-        <v>3709</v>
+        <v>3707</v>
       </c>
       <c r="G694" s="9"/>
       <c r="H694" s="11">
@@ -51719,7 +51719,7 @@
         <v>2</v>
       </c>
       <c r="K694" s="9" t="s">
-        <v>3710</v>
+        <v>3708</v>
       </c>
       <c r="L694" s="9" t="s">
         <v>112</v>
@@ -51737,7 +51737,7 @@
         <v>45</v>
       </c>
       <c r="Q694" s="9" t="s">
-        <v>3711</v>
+        <v>3709</v>
       </c>
       <c r="R694" s="9"/>
       <c r="S694" s="9"/>
@@ -51745,22 +51745,22 @@
     </row>
     <row r="695" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B695" s="9" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C695" s="9" t="s">
-        <v>3712</v>
+        <v>3710</v>
       </c>
       <c r="D695" s="9" t="s">
-        <v>3713</v>
+        <v>3711</v>
       </c>
       <c r="E695" s="10" t="s">
         <v>830</v>
       </c>
       <c r="F695" s="9" t="s">
-        <v>3714</v>
+        <v>3712</v>
       </c>
       <c r="G695" s="9"/>
       <c r="H695" s="11">
@@ -51773,7 +51773,7 @@
         <v>2</v>
       </c>
       <c r="K695" s="9" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
       <c r="L695" s="9" t="s">
         <v>833</v>
@@ -51791,7 +51791,7 @@
         <v>50</v>
       </c>
       <c r="Q695" s="9" t="s">
-        <v>3716</v>
+        <v>3714</v>
       </c>
       <c r="R695" s="9"/>
       <c r="S695" s="9"/>
@@ -51799,22 +51799,22 @@
     </row>
     <row r="696" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B696" s="9" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C696" s="9" t="s">
-        <v>3717</v>
+        <v>3715</v>
       </c>
       <c r="D696" s="9" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="E696" s="10" t="s">
         <v>91</v>
       </c>
       <c r="F696" s="9" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
       <c r="G696" s="9"/>
       <c r="H696" s="11">
@@ -51827,7 +51827,7 @@
         <v>2</v>
       </c>
       <c r="K696" s="9" t="s">
-        <v>3720</v>
+        <v>3718</v>
       </c>
       <c r="L696" s="9" t="s">
         <v>94</v>
@@ -51845,7 +51845,7 @@
         <v>45</v>
       </c>
       <c r="Q696" s="9" t="s">
-        <v>3721</v>
+        <v>3719</v>
       </c>
       <c r="R696" s="9"/>
       <c r="S696" s="9"/>
@@ -51853,22 +51853,22 @@
     </row>
     <row r="697" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="17" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B697" s="17" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C697" s="17" t="s">
-        <v>3722</v>
+        <v>3720</v>
       </c>
       <c r="D697" s="17" t="s">
-        <v>3723</v>
+        <v>3721</v>
       </c>
       <c r="E697" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F697" s="17" t="s">
-        <v>3724</v>
+        <v>3722</v>
       </c>
       <c r="G697" s="17"/>
       <c r="H697" s="19">
@@ -51881,7 +51881,7 @@
         <v>3</v>
       </c>
       <c r="K697" s="17" t="s">
-        <v>3725</v>
+        <v>3723</v>
       </c>
       <c r="L697" s="17" t="s">
         <v>123</v>
@@ -51899,7 +51899,7 @@
         <v>40</v>
       </c>
       <c r="Q697" s="17" t="s">
-        <v>3726</v>
+        <v>3724</v>
       </c>
       <c r="R697" s="17"/>
       <c r="S697" s="17"/>
@@ -51907,22 +51907,22 @@
     </row>
     <row r="698" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="2" t="s">
+        <v>3725</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>3726</v>
+      </c>
+      <c r="C698" s="2" t="s">
         <v>3727</v>
       </c>
-      <c r="B698" s="2" t="s">
+      <c r="D698" s="2" t="s">
         <v>3728</v>
-      </c>
-      <c r="C698" s="2" t="s">
-        <v>3729</v>
-      </c>
-      <c r="D698" s="2" t="s">
-        <v>3730</v>
       </c>
       <c r="E698" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F698" s="2" t="s">
-        <v>3731</v>
+        <v>3729</v>
       </c>
       <c r="G698" s="2"/>
       <c r="H698" s="4">
@@ -51953,32 +51953,32 @@
         <v>80</v>
       </c>
       <c r="Q698" s="2" t="s">
-        <v>3732</v>
+        <v>3730</v>
       </c>
       <c r="R698" s="2"/>
       <c r="S698" s="2"/>
       <c r="T698" s="2" t="s">
-        <v>3733</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="699" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="D699" s="2" t="s">
-        <v>3735</v>
+        <v>3733</v>
       </c>
       <c r="E699" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F699" s="2" t="s">
-        <v>3736</v>
+        <v>3734</v>
       </c>
       <c r="G699" s="2"/>
       <c r="H699" s="4">
@@ -51991,7 +51991,7 @@
         <v>1</v>
       </c>
       <c r="K699" s="2" t="s">
-        <v>3737</v>
+        <v>3735</v>
       </c>
       <c r="L699" s="2" t="s">
         <v>100</v>
@@ -52009,32 +52009,32 @@
         <v>80</v>
       </c>
       <c r="Q699" s="2" t="s">
-        <v>3738</v>
+        <v>3736</v>
       </c>
       <c r="R699" s="2"/>
       <c r="S699" s="2"/>
       <c r="T699" s="2" t="s">
-        <v>3739</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="700" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>3740</v>
+        <v>3738</v>
       </c>
       <c r="D700" s="2" t="s">
-        <v>3741</v>
+        <v>3739</v>
       </c>
       <c r="E700" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F700" s="2" t="s">
-        <v>3742</v>
+        <v>3740</v>
       </c>
       <c r="G700" s="2"/>
       <c r="H700" s="4">
@@ -52065,32 +52065,32 @@
         <v>75</v>
       </c>
       <c r="Q700" s="2" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="R700" s="2"/>
       <c r="S700" s="2"/>
       <c r="T700" s="2" t="s">
-        <v>3744</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="701" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>3745</v>
+        <v>3743</v>
       </c>
       <c r="D701" s="2" t="s">
-        <v>3746</v>
+        <v>3744</v>
       </c>
       <c r="E701" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F701" s="2" t="s">
-        <v>3747</v>
+        <v>3745</v>
       </c>
       <c r="G701" s="2"/>
       <c r="H701" s="4">
@@ -52103,7 +52103,7 @@
         <v>1</v>
       </c>
       <c r="K701" s="2" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="L701" s="2" t="s">
         <v>100</v>
@@ -52121,7 +52121,7 @@
         <v>65</v>
       </c>
       <c r="Q701" s="2" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="R701" s="2"/>
       <c r="S701" s="2"/>
@@ -52129,22 +52129,22 @@
     </row>
     <row r="702" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>3750</v>
+        <v>3748</v>
       </c>
       <c r="D702" s="2" t="s">
-        <v>3751</v>
+        <v>3749</v>
       </c>
       <c r="E702" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F702" s="2" t="s">
-        <v>3752</v>
+        <v>3750</v>
       </c>
       <c r="G702" s="2"/>
       <c r="H702" s="4">
@@ -52157,10 +52157,10 @@
         <v>1</v>
       </c>
       <c r="K702" s="2" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="L702" s="2" t="s">
-        <v>3754</v>
+        <v>3752</v>
       </c>
       <c r="M702" s="6">
         <v>8500</v>
@@ -52175,7 +52175,7 @@
         <v>60</v>
       </c>
       <c r="Q702" s="2" t="s">
-        <v>3755</v>
+        <v>3753</v>
       </c>
       <c r="R702" s="2"/>
       <c r="S702" s="2"/>
@@ -52183,22 +52183,22 @@
     </row>
     <row r="703" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>3756</v>
+        <v>3754</v>
       </c>
       <c r="D703" s="2" t="s">
-        <v>3757</v>
+        <v>3755</v>
       </c>
       <c r="E703" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F703" s="2" t="s">
-        <v>3758</v>
+        <v>3756</v>
       </c>
       <c r="G703" s="2"/>
       <c r="H703" s="4">
@@ -52211,7 +52211,7 @@
         <v>1</v>
       </c>
       <c r="K703" s="2" t="s">
-        <v>3759</v>
+        <v>3757</v>
       </c>
       <c r="L703" s="2" t="s">
         <v>909</v>
@@ -52229,7 +52229,7 @@
         <v>55</v>
       </c>
       <c r="Q703" s="2" t="s">
-        <v>3760</v>
+        <v>3758</v>
       </c>
       <c r="R703" s="2"/>
       <c r="S703" s="2"/>
@@ -52237,22 +52237,22 @@
     </row>
     <row r="704" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>3761</v>
+        <v>3759</v>
       </c>
       <c r="D704" s="2" t="s">
-        <v>3762</v>
+        <v>3760</v>
       </c>
       <c r="E704" s="3" t="s">
         <v>110</v>
       </c>
       <c r="F704" s="2" t="s">
-        <v>3763</v>
+        <v>3761</v>
       </c>
       <c r="G704" s="2"/>
       <c r="H704" s="4">
@@ -52283,7 +52283,7 @@
         <v>60</v>
       </c>
       <c r="Q704" s="2" t="s">
-        <v>3764</v>
+        <v>3762</v>
       </c>
       <c r="R704" s="2"/>
       <c r="S704" s="2"/>
@@ -52291,22 +52291,22 @@
     </row>
     <row r="705" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>3765</v>
+        <v>3763</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>3766</v>
+        <v>3764</v>
       </c>
       <c r="E705" s="3" t="s">
         <v>490</v>
       </c>
       <c r="F705" s="2" t="s">
-        <v>3767</v>
+        <v>3765</v>
       </c>
       <c r="G705" s="2"/>
       <c r="H705" s="4">
@@ -52337,7 +52337,7 @@
         <v>55</v>
       </c>
       <c r="Q705" s="2" t="s">
-        <v>3768</v>
+        <v>3766</v>
       </c>
       <c r="R705" s="2"/>
       <c r="S705" s="2"/>
@@ -52345,22 +52345,22 @@
     </row>
     <row r="706" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>3769</v>
+        <v>3767</v>
       </c>
       <c r="D706" s="2" t="s">
-        <v>3770</v>
+        <v>3768</v>
       </c>
       <c r="E706" s="3" t="s">
         <v>110</v>
       </c>
       <c r="F706" s="2" t="s">
-        <v>3771</v>
+        <v>3769</v>
       </c>
       <c r="G706" s="2"/>
       <c r="H706" s="4">
@@ -52391,7 +52391,7 @@
         <v>55</v>
       </c>
       <c r="Q706" s="2" t="s">
-        <v>3772</v>
+        <v>3770</v>
       </c>
       <c r="R706" s="2"/>
       <c r="S706" s="2"/>
@@ -52399,22 +52399,22 @@
     </row>
     <row r="707" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>3773</v>
+        <v>3771</v>
       </c>
       <c r="D707" s="2" t="s">
-        <v>3774</v>
+        <v>3772</v>
       </c>
       <c r="E707" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F707" s="2" t="s">
-        <v>3775</v>
+        <v>3773</v>
       </c>
       <c r="G707" s="2"/>
       <c r="H707" s="4">
@@ -52427,10 +52427,10 @@
         <v>1</v>
       </c>
       <c r="K707" s="2" t="s">
-        <v>3776</v>
+        <v>3774</v>
       </c>
       <c r="L707" s="2" t="s">
-        <v>3777</v>
+        <v>3775</v>
       </c>
       <c r="M707" s="6">
         <v>6500</v>
@@ -52445,7 +52445,7 @@
         <v>55</v>
       </c>
       <c r="Q707" s="2" t="s">
-        <v>3778</v>
+        <v>3776</v>
       </c>
       <c r="R707" s="2"/>
       <c r="S707" s="2"/>
@@ -52453,22 +52453,22 @@
     </row>
     <row r="708" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>3779</v>
+        <v>3777</v>
       </c>
       <c r="D708" s="2" t="s">
-        <v>3780</v>
+        <v>3778</v>
       </c>
       <c r="E708" s="3" t="s">
         <v>110</v>
       </c>
       <c r="F708" s="2" t="s">
-        <v>3781</v>
+        <v>3779</v>
       </c>
       <c r="G708" s="2"/>
       <c r="H708" s="4">
@@ -52499,7 +52499,7 @@
         <v>50</v>
       </c>
       <c r="Q708" s="2" t="s">
-        <v>3782</v>
+        <v>3780</v>
       </c>
       <c r="R708" s="2"/>
       <c r="S708" s="2"/>
@@ -52507,22 +52507,22 @@
     </row>
     <row r="709" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>3783</v>
+        <v>3781</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>3784</v>
+        <v>3782</v>
       </c>
       <c r="E709" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F709" s="2" t="s">
-        <v>3785</v>
+        <v>3783</v>
       </c>
       <c r="G709" s="2"/>
       <c r="H709" s="4">
@@ -52553,7 +52553,7 @@
         <v>50</v>
       </c>
       <c r="Q709" s="2" t="s">
-        <v>3786</v>
+        <v>3784</v>
       </c>
       <c r="R709" s="2"/>
       <c r="S709" s="2"/>
@@ -52561,22 +52561,22 @@
     </row>
     <row r="710" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>3787</v>
+        <v>3785</v>
       </c>
       <c r="D710" s="2" t="s">
-        <v>3788</v>
+        <v>3786</v>
       </c>
       <c r="E710" s="3" t="s">
         <v>864</v>
       </c>
       <c r="F710" s="2" t="s">
-        <v>3789</v>
+        <v>3787</v>
       </c>
       <c r="G710" s="2"/>
       <c r="H710" s="4">
@@ -52589,7 +52589,7 @@
         <v>1</v>
       </c>
       <c r="K710" s="2" t="s">
-        <v>3790</v>
+        <v>3788</v>
       </c>
       <c r="L710" s="2" t="s">
         <v>867</v>
@@ -52607,7 +52607,7 @@
         <v>50</v>
       </c>
       <c r="Q710" s="2" t="s">
-        <v>3791</v>
+        <v>3789</v>
       </c>
       <c r="R710" s="2"/>
       <c r="S710" s="2"/>
@@ -52615,22 +52615,22 @@
     </row>
     <row r="711" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>3792</v>
+        <v>3790</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>3793</v>
+        <v>3791</v>
       </c>
       <c r="E711" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F711" s="2" t="s">
-        <v>3794</v>
+        <v>3792</v>
       </c>
       <c r="G711" s="2"/>
       <c r="H711" s="4">
@@ -52643,7 +52643,7 @@
         <v>1</v>
       </c>
       <c r="K711" s="2" t="s">
-        <v>3795</v>
+        <v>3793</v>
       </c>
       <c r="L711" s="2" t="s">
         <v>2743</v>
@@ -52661,7 +52661,7 @@
         <v>50</v>
       </c>
       <c r="Q711" s="2" t="s">
-        <v>3796</v>
+        <v>3794</v>
       </c>
       <c r="R711" s="2"/>
       <c r="S711" s="2"/>
@@ -52669,22 +52669,22 @@
     </row>
     <row r="712" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>3797</v>
+        <v>3795</v>
       </c>
       <c r="D712" s="2" t="s">
-        <v>3798</v>
+        <v>3796</v>
       </c>
       <c r="E712" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F712" s="2" t="s">
-        <v>3799</v>
+        <v>3797</v>
       </c>
       <c r="G712" s="2"/>
       <c r="H712" s="4">
@@ -52715,7 +52715,7 @@
         <v>45</v>
       </c>
       <c r="Q712" s="2" t="s">
-        <v>3800</v>
+        <v>3798</v>
       </c>
       <c r="R712" s="2"/>
       <c r="S712" s="2"/>
@@ -52723,22 +52723,22 @@
     </row>
     <row r="713" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="2" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>3801</v>
+        <v>3799</v>
       </c>
       <c r="D713" s="2" t="s">
-        <v>3802</v>
+        <v>3800</v>
       </c>
       <c r="E713" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F713" s="2" t="s">
-        <v>3803</v>
+        <v>3801</v>
       </c>
       <c r="G713" s="2"/>
       <c r="H713" s="4">
@@ -52751,7 +52751,7 @@
         <v>1</v>
       </c>
       <c r="K713" s="2" t="s">
-        <v>3804</v>
+        <v>3802</v>
       </c>
       <c r="L713" s="2" t="s">
         <v>123</v>
@@ -52769,7 +52769,7 @@
         <v>45</v>
       </c>
       <c r="Q713" s="2" t="s">
-        <v>3805</v>
+        <v>3803</v>
       </c>
       <c r="R713" s="2"/>
       <c r="S713" s="2"/>
@@ -52783,16 +52783,16 @@
         <v>2899</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="D714" s="2" t="s">
-        <v>3807</v>
+        <v>3805</v>
       </c>
       <c r="E714" s="3" t="s">
         <v>857</v>
       </c>
       <c r="F714" s="2" t="s">
-        <v>3808</v>
+        <v>3806</v>
       </c>
       <c r="G714" s="2"/>
       <c r="H714" s="4">
@@ -52805,16 +52805,16 @@
         <v>1</v>
       </c>
       <c r="K714" s="2" t="s">
-        <v>3809</v>
+        <v>3807</v>
       </c>
       <c r="L714" s="2" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M714" s="6">
         <v>4000</v>
       </c>
       <c r="N714" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O714" s="6">
         <v>95</v>
@@ -52823,7 +52823,7 @@
         <v>60</v>
       </c>
       <c r="Q714" s="2" t="s">
-        <v>3812</v>
+        <v>3810</v>
       </c>
       <c r="R714" s="2"/>
       <c r="S714" s="2"/>
@@ -52837,16 +52837,16 @@
         <v>1447</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>3813</v>
+        <v>3811</v>
       </c>
       <c r="D715" s="2" t="s">
-        <v>3814</v>
+        <v>3812</v>
       </c>
       <c r="E715" s="3" t="s">
         <v>857</v>
       </c>
       <c r="F715" s="2" t="s">
-        <v>3815</v>
+        <v>3813</v>
       </c>
       <c r="G715" s="2"/>
       <c r="H715" s="4">
@@ -52859,16 +52859,16 @@
         <v>1</v>
       </c>
       <c r="K715" s="2" t="s">
-        <v>3816</v>
+        <v>3814</v>
       </c>
       <c r="L715" s="2" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M715" s="6">
         <v>3500</v>
       </c>
       <c r="N715" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O715" s="6">
         <v>95</v>
@@ -52877,7 +52877,7 @@
         <v>60</v>
       </c>
       <c r="Q715" s="2" t="s">
-        <v>3817</v>
+        <v>3815</v>
       </c>
       <c r="R715" s="2"/>
       <c r="S715" s="2"/>
@@ -52891,16 +52891,16 @@
         <v>2838</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>3818</v>
+        <v>3816</v>
       </c>
       <c r="D716" s="2" t="s">
-        <v>3819</v>
+        <v>3817</v>
       </c>
       <c r="E716" s="3" t="s">
         <v>857</v>
       </c>
       <c r="F716" s="2" t="s">
-        <v>3820</v>
+        <v>3818</v>
       </c>
       <c r="G716" s="2"/>
       <c r="H716" s="4">
@@ -52913,16 +52913,16 @@
         <v>1</v>
       </c>
       <c r="K716" s="2" t="s">
-        <v>3821</v>
+        <v>3819</v>
       </c>
       <c r="L716" s="2" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M716" s="6">
         <v>4000</v>
       </c>
       <c r="N716" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O716" s="6">
         <v>95</v>
@@ -52931,7 +52931,7 @@
         <v>60</v>
       </c>
       <c r="Q716" s="2" t="s">
-        <v>3822</v>
+        <v>3820</v>
       </c>
       <c r="R716" s="2"/>
       <c r="S716" s="2"/>
@@ -52945,16 +52945,16 @@
         <v>1447</v>
       </c>
       <c r="C717" s="9" t="s">
-        <v>3823</v>
+        <v>3821</v>
       </c>
       <c r="D717" s="9" t="s">
-        <v>3824</v>
+        <v>3822</v>
       </c>
       <c r="E717" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F717" s="9" t="s">
-        <v>3825</v>
+        <v>3823</v>
       </c>
       <c r="G717" s="9"/>
       <c r="H717" s="11">
@@ -52967,16 +52967,16 @@
         <v>2</v>
       </c>
       <c r="K717" s="9" t="s">
-        <v>3826</v>
+        <v>3824</v>
       </c>
       <c r="L717" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M717" s="13">
         <v>3000</v>
       </c>
       <c r="N717" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O717" s="13">
         <v>80</v>
@@ -52985,7 +52985,7 @@
         <v>55</v>
       </c>
       <c r="Q717" s="9" t="s">
-        <v>3827</v>
+        <v>3825</v>
       </c>
       <c r="R717" s="9"/>
       <c r="S717" s="9"/>
@@ -52999,16 +52999,16 @@
         <v>600</v>
       </c>
       <c r="C718" s="9" t="s">
-        <v>3828</v>
+        <v>3826</v>
       </c>
       <c r="D718" s="9" t="s">
-        <v>3829</v>
+        <v>3827</v>
       </c>
       <c r="E718" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F718" s="9" t="s">
-        <v>3830</v>
+        <v>3828</v>
       </c>
       <c r="G718" s="9"/>
       <c r="H718" s="11">
@@ -53021,16 +53021,16 @@
         <v>2</v>
       </c>
       <c r="K718" s="9" t="s">
-        <v>3831</v>
+        <v>3829</v>
       </c>
       <c r="L718" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M718" s="13">
         <v>3500</v>
       </c>
       <c r="N718" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O718" s="13">
         <v>80</v>
@@ -53039,7 +53039,7 @@
         <v>55</v>
       </c>
       <c r="Q718" s="9" t="s">
-        <v>3832</v>
+        <v>3830</v>
       </c>
       <c r="R718" s="9"/>
       <c r="S718" s="9"/>
@@ -53053,16 +53053,16 @@
         <v>782</v>
       </c>
       <c r="C719" s="9" t="s">
-        <v>3833</v>
+        <v>3831</v>
       </c>
       <c r="D719" s="9" t="s">
-        <v>3834</v>
+        <v>3832</v>
       </c>
       <c r="E719" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F719" s="9" t="s">
-        <v>3835</v>
+        <v>3833</v>
       </c>
       <c r="G719" s="9"/>
       <c r="H719" s="11">
@@ -53075,16 +53075,16 @@
         <v>2</v>
       </c>
       <c r="K719" s="9" t="s">
-        <v>3836</v>
+        <v>3834</v>
       </c>
       <c r="L719" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M719" s="13">
         <v>3500</v>
       </c>
       <c r="N719" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O719" s="13">
         <v>78</v>
@@ -53093,7 +53093,7 @@
         <v>55</v>
       </c>
       <c r="Q719" s="9" t="s">
-        <v>3837</v>
+        <v>3835</v>
       </c>
       <c r="R719" s="9"/>
       <c r="S719" s="9"/>
@@ -53107,16 +53107,16 @@
         <v>600</v>
       </c>
       <c r="C720" s="9" t="s">
-        <v>3838</v>
+        <v>3836</v>
       </c>
       <c r="D720" s="9" t="s">
-        <v>3839</v>
+        <v>3837</v>
       </c>
       <c r="E720" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F720" s="9" t="s">
-        <v>3840</v>
+        <v>3838</v>
       </c>
       <c r="G720" s="9"/>
       <c r="H720" s="11">
@@ -53129,16 +53129,16 @@
         <v>2</v>
       </c>
       <c r="K720" s="9" t="s">
-        <v>3841</v>
+        <v>3839</v>
       </c>
       <c r="L720" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M720" s="13">
         <v>3000</v>
       </c>
       <c r="N720" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O720" s="13">
         <v>75</v>
@@ -53147,7 +53147,7 @@
         <v>50</v>
       </c>
       <c r="Q720" s="9" t="s">
-        <v>3842</v>
+        <v>3840</v>
       </c>
       <c r="R720" s="9"/>
       <c r="S720" s="9"/>
@@ -53161,16 +53161,16 @@
         <v>2069</v>
       </c>
       <c r="C721" s="9" t="s">
-        <v>3843</v>
+        <v>3841</v>
       </c>
       <c r="D721" s="9" t="s">
-        <v>3844</v>
+        <v>3842</v>
       </c>
       <c r="E721" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F721" s="9" t="s">
-        <v>3845</v>
+        <v>3843</v>
       </c>
       <c r="G721" s="9"/>
       <c r="H721" s="11">
@@ -53183,16 +53183,16 @@
         <v>2</v>
       </c>
       <c r="K721" s="9" t="s">
-        <v>3846</v>
+        <v>3844</v>
       </c>
       <c r="L721" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M721" s="13">
         <v>3000</v>
       </c>
       <c r="N721" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O721" s="13">
         <v>75</v>
@@ -53201,7 +53201,7 @@
         <v>55</v>
       </c>
       <c r="Q721" s="9" t="s">
-        <v>3847</v>
+        <v>3845</v>
       </c>
       <c r="R721" s="9"/>
       <c r="S721" s="9"/>
@@ -53215,16 +53215,16 @@
         <v>3131</v>
       </c>
       <c r="C722" s="9" t="s">
-        <v>3848</v>
+        <v>3846</v>
       </c>
       <c r="D722" s="9" t="s">
-        <v>3849</v>
+        <v>3847</v>
       </c>
       <c r="E722" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F722" s="9" t="s">
-        <v>3850</v>
+        <v>3848</v>
       </c>
       <c r="G722" s="9"/>
       <c r="H722" s="11">
@@ -53237,16 +53237,16 @@
         <v>2</v>
       </c>
       <c r="K722" s="9" t="s">
-        <v>3826</v>
+        <v>3824</v>
       </c>
       <c r="L722" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M722" s="13">
         <v>3000</v>
       </c>
       <c r="N722" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O722" s="13">
         <v>72</v>
@@ -53255,7 +53255,7 @@
         <v>50</v>
       </c>
       <c r="Q722" s="9" t="s">
-        <v>3851</v>
+        <v>3849</v>
       </c>
       <c r="R722" s="9"/>
       <c r="S722" s="9"/>
@@ -53269,16 +53269,16 @@
         <v>2899</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>3852</v>
+        <v>3850</v>
       </c>
       <c r="D723" s="2" t="s">
-        <v>3853</v>
+        <v>3851</v>
       </c>
       <c r="E723" s="3" t="s">
         <v>964</v>
       </c>
       <c r="F723" s="2" t="s">
-        <v>3854</v>
+        <v>3852</v>
       </c>
       <c r="G723" s="2"/>
       <c r="H723" s="4">
@@ -53291,7 +53291,7 @@
         <v>1</v>
       </c>
       <c r="K723" s="2" t="s">
-        <v>3855</v>
+        <v>3853</v>
       </c>
       <c r="L723" s="2" t="s">
         <v>967</v>
@@ -53300,7 +53300,7 @@
         <v>2000</v>
       </c>
       <c r="N723" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O723" s="6">
         <v>95</v>
@@ -53309,7 +53309,7 @@
         <v>60</v>
       </c>
       <c r="Q723" s="2" t="s">
-        <v>3856</v>
+        <v>3854</v>
       </c>
       <c r="R723" s="2"/>
       <c r="S723" s="2"/>
@@ -53323,16 +53323,16 @@
         <v>2838</v>
       </c>
       <c r="C724" s="9" t="s">
-        <v>3857</v>
+        <v>3855</v>
       </c>
       <c r="D724" s="9" t="s">
-        <v>3858</v>
+        <v>3856</v>
       </c>
       <c r="E724" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F724" s="9" t="s">
-        <v>3859</v>
+        <v>3857</v>
       </c>
       <c r="G724" s="9"/>
       <c r="H724" s="11">
@@ -53345,16 +53345,16 @@
         <v>2</v>
       </c>
       <c r="K724" s="9" t="s">
-        <v>3860</v>
+        <v>3858</v>
       </c>
       <c r="L724" s="9" t="s">
-        <v>3861</v>
+        <v>3859</v>
       </c>
       <c r="M724" s="13">
         <v>2000</v>
       </c>
       <c r="N724" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O724" s="13">
         <v>82</v>
@@ -53363,7 +53363,7 @@
         <v>55</v>
       </c>
       <c r="Q724" s="9" t="s">
-        <v>3862</v>
+        <v>3860</v>
       </c>
       <c r="R724" s="9"/>
       <c r="S724" s="9"/>
@@ -53371,22 +53371,22 @@
     </row>
     <row r="725" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="2" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C725" s="2" t="s">
+        <v>3861</v>
+      </c>
+      <c r="D725" s="2" t="s">
+        <v>3862</v>
+      </c>
+      <c r="E725" s="3" t="s">
         <v>3863</v>
       </c>
-      <c r="D725" s="2" t="s">
+      <c r="F725" s="2" t="s">
         <v>3864</v>
-      </c>
-      <c r="E725" s="3" t="s">
-        <v>3865</v>
-      </c>
-      <c r="F725" s="2" t="s">
-        <v>3866</v>
       </c>
       <c r="G725" s="2"/>
       <c r="H725" s="4">
@@ -53399,16 +53399,16 @@
         <v>1</v>
       </c>
       <c r="K725" s="2" t="s">
-        <v>3867</v>
+        <v>3865</v>
       </c>
       <c r="L725" s="2" t="s">
-        <v>3868</v>
+        <v>3866</v>
       </c>
       <c r="M725" s="6">
         <v>2000</v>
       </c>
       <c r="N725" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O725" s="6">
         <v>95</v>
@@ -53417,7 +53417,7 @@
         <v>60</v>
       </c>
       <c r="Q725" s="2" t="s">
-        <v>3869</v>
+        <v>3867</v>
       </c>
       <c r="R725" s="2"/>
       <c r="S725" s="2"/>
@@ -53431,16 +53431,16 @@
         <v>495</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>3870</v>
+        <v>3868</v>
       </c>
       <c r="D726" s="2" t="s">
-        <v>3871</v>
+        <v>3869</v>
       </c>
       <c r="E726" s="3" t="s">
         <v>964</v>
       </c>
       <c r="F726" s="2" t="s">
-        <v>3872</v>
+        <v>3870</v>
       </c>
       <c r="G726" s="2"/>
       <c r="H726" s="4">
@@ -53453,7 +53453,7 @@
         <v>1</v>
       </c>
       <c r="K726" s="2" t="s">
-        <v>3873</v>
+        <v>3871</v>
       </c>
       <c r="L726" s="2" t="s">
         <v>967</v>
@@ -53462,7 +53462,7 @@
         <v>2000</v>
       </c>
       <c r="N726" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O726" s="6">
         <v>90</v>
@@ -53471,7 +53471,7 @@
         <v>55</v>
       </c>
       <c r="Q726" s="2" t="s">
-        <v>3874</v>
+        <v>3872</v>
       </c>
       <c r="R726" s="2"/>
       <c r="S726" s="2"/>
@@ -53485,16 +53485,16 @@
         <v>1837</v>
       </c>
       <c r="C727" s="9" t="s">
-        <v>3875</v>
+        <v>3873</v>
       </c>
       <c r="D727" s="9" t="s">
-        <v>3876</v>
+        <v>3874</v>
       </c>
       <c r="E727" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F727" s="9" t="s">
-        <v>3877</v>
+        <v>3875</v>
       </c>
       <c r="G727" s="9"/>
       <c r="H727" s="11">
@@ -53507,16 +53507,16 @@
         <v>2</v>
       </c>
       <c r="K727" s="9" t="s">
-        <v>3878</v>
+        <v>3876</v>
       </c>
       <c r="L727" s="9" t="s">
-        <v>3879</v>
+        <v>3877</v>
       </c>
       <c r="M727" s="13">
         <v>2500</v>
       </c>
       <c r="N727" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O727" s="13">
         <v>72</v>
@@ -53525,7 +53525,7 @@
         <v>50</v>
       </c>
       <c r="Q727" s="9" t="s">
-        <v>3880</v>
+        <v>3878</v>
       </c>
       <c r="R727" s="9"/>
       <c r="S727" s="9"/>
@@ -53539,16 +53539,16 @@
         <v>2343</v>
       </c>
       <c r="C728" s="9" t="s">
-        <v>3881</v>
+        <v>3879</v>
       </c>
       <c r="D728" s="9" t="s">
-        <v>3882</v>
+        <v>3880</v>
       </c>
       <c r="E728" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F728" s="9" t="s">
-        <v>3883</v>
+        <v>3881</v>
       </c>
       <c r="G728" s="9"/>
       <c r="H728" s="11">
@@ -53561,7 +53561,7 @@
         <v>2</v>
       </c>
       <c r="K728" s="9" t="s">
-        <v>3884</v>
+        <v>3882</v>
       </c>
       <c r="L728" s="9" t="s">
         <v>967</v>
@@ -53570,7 +53570,7 @@
         <v>1500</v>
       </c>
       <c r="N728" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O728" s="13">
         <v>78</v>
@@ -53579,7 +53579,7 @@
         <v>50</v>
       </c>
       <c r="Q728" s="9" t="s">
-        <v>3885</v>
+        <v>3883</v>
       </c>
       <c r="R728" s="9"/>
       <c r="S728" s="9"/>
@@ -53593,16 +53593,16 @@
         <v>1702</v>
       </c>
       <c r="C729" s="9" t="s">
-        <v>3886</v>
+        <v>3884</v>
       </c>
       <c r="D729" s="9" t="s">
-        <v>3887</v>
+        <v>3885</v>
       </c>
       <c r="E729" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F729" s="9" t="s">
-        <v>3888</v>
+        <v>3886</v>
       </c>
       <c r="G729" s="9"/>
       <c r="H729" s="11">
@@ -53615,16 +53615,16 @@
         <v>2</v>
       </c>
       <c r="K729" s="9" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
       <c r="L729" s="9" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
       <c r="M729" s="13">
         <v>3000</v>
       </c>
       <c r="N729" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O729" s="13">
         <v>78</v>
@@ -53633,7 +53633,7 @@
         <v>50</v>
       </c>
       <c r="Q729" s="9" t="s">
-        <v>3891</v>
+        <v>3889</v>
       </c>
       <c r="R729" s="9"/>
       <c r="S729" s="9"/>
@@ -53647,16 +53647,16 @@
         <v>2528</v>
       </c>
       <c r="C730" s="9" t="s">
-        <v>3892</v>
+        <v>3890</v>
       </c>
       <c r="D730" s="9" t="s">
-        <v>3893</v>
+        <v>3891</v>
       </c>
       <c r="E730" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F730" s="9" t="s">
-        <v>3894</v>
+        <v>3892</v>
       </c>
       <c r="G730" s="9"/>
       <c r="H730" s="11">
@@ -53669,16 +53669,16 @@
         <v>2</v>
       </c>
       <c r="K730" s="9" t="s">
-        <v>3895</v>
+        <v>3893</v>
       </c>
       <c r="L730" s="9" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
       <c r="M730" s="13">
         <v>2500</v>
       </c>
       <c r="N730" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O730" s="13">
         <v>72</v>
@@ -53687,7 +53687,7 @@
         <v>50</v>
       </c>
       <c r="Q730" s="9" t="s">
-        <v>3896</v>
+        <v>3894</v>
       </c>
       <c r="R730" s="9"/>
       <c r="S730" s="9"/>
@@ -53701,16 +53701,16 @@
         <v>570</v>
       </c>
       <c r="C731" s="9" t="s">
-        <v>3897</v>
+        <v>3895</v>
       </c>
       <c r="D731" s="9" t="s">
-        <v>3898</v>
+        <v>3896</v>
       </c>
       <c r="E731" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F731" s="9" t="s">
-        <v>3899</v>
+        <v>3897</v>
       </c>
       <c r="G731" s="9"/>
       <c r="H731" s="11">
@@ -53723,16 +53723,16 @@
         <v>2</v>
       </c>
       <c r="K731" s="9" t="s">
-        <v>3860</v>
+        <v>3858</v>
       </c>
       <c r="L731" s="9" t="s">
-        <v>3900</v>
+        <v>3898</v>
       </c>
       <c r="M731" s="13">
         <v>2000</v>
       </c>
       <c r="N731" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O731" s="13">
         <v>82</v>
@@ -53741,7 +53741,7 @@
         <v>55</v>
       </c>
       <c r="Q731" s="9" t="s">
-        <v>3901</v>
+        <v>3899</v>
       </c>
       <c r="R731" s="9"/>
       <c r="S731" s="9"/>
@@ -53755,16 +53755,16 @@
         <v>2899</v>
       </c>
       <c r="C732" s="9" t="s">
+        <v>3900</v>
+      </c>
+      <c r="D732" s="9" t="s">
+        <v>3901</v>
+      </c>
+      <c r="E732" s="10" t="s">
         <v>3902</v>
       </c>
-      <c r="D732" s="9" t="s">
+      <c r="F732" s="9" t="s">
         <v>3903</v>
-      </c>
-      <c r="E732" s="10" t="s">
-        <v>3904</v>
-      </c>
-      <c r="F732" s="9" t="s">
-        <v>3905</v>
       </c>
       <c r="G732" s="9"/>
       <c r="H732" s="11">
@@ -53777,16 +53777,16 @@
         <v>2</v>
       </c>
       <c r="K732" s="9" t="s">
-        <v>3906</v>
+        <v>3904</v>
       </c>
       <c r="L732" s="9" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
       <c r="M732" s="13">
         <v>5000</v>
       </c>
       <c r="N732" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O732" s="13">
         <v>88</v>
@@ -53795,7 +53795,7 @@
         <v>65</v>
       </c>
       <c r="Q732" s="9" t="s">
-        <v>3908</v>
+        <v>3906</v>
       </c>
       <c r="R732" s="9"/>
       <c r="S732" s="9"/>
@@ -53809,16 +53809,16 @@
         <v>2069</v>
       </c>
       <c r="C733" s="9" t="s">
+        <v>3907</v>
+      </c>
+      <c r="D733" s="9" t="s">
+        <v>3908</v>
+      </c>
+      <c r="E733" s="10" t="s">
+        <v>3902</v>
+      </c>
+      <c r="F733" s="9" t="s">
         <v>3909</v>
-      </c>
-      <c r="D733" s="9" t="s">
-        <v>3910</v>
-      </c>
-      <c r="E733" s="10" t="s">
-        <v>3904</v>
-      </c>
-      <c r="F733" s="9" t="s">
-        <v>3911</v>
       </c>
       <c r="G733" s="9"/>
       <c r="H733" s="11">
@@ -53831,16 +53831,16 @@
         <v>2</v>
       </c>
       <c r="K733" s="9" t="s">
-        <v>3906</v>
+        <v>3904</v>
       </c>
       <c r="L733" s="9" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
       <c r="M733" s="13">
         <v>4000</v>
       </c>
       <c r="N733" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O733" s="13">
         <v>82</v>
@@ -53849,7 +53849,7 @@
         <v>60</v>
       </c>
       <c r="Q733" s="9" t="s">
-        <v>3912</v>
+        <v>3910</v>
       </c>
       <c r="R733" s="9"/>
       <c r="S733" s="9"/>
@@ -53863,16 +53863,16 @@
         <v>1242</v>
       </c>
       <c r="C734" s="9" t="s">
+        <v>3911</v>
+      </c>
+      <c r="D734" s="9" t="s">
+        <v>3912</v>
+      </c>
+      <c r="E734" s="10" t="s">
+        <v>3902</v>
+      </c>
+      <c r="F734" s="9" t="s">
         <v>3913</v>
-      </c>
-      <c r="D734" s="9" t="s">
-        <v>3914</v>
-      </c>
-      <c r="E734" s="10" t="s">
-        <v>3904</v>
-      </c>
-      <c r="F734" s="9" t="s">
-        <v>3915</v>
       </c>
       <c r="G734" s="9"/>
       <c r="H734" s="11">
@@ -53885,16 +53885,16 @@
         <v>2</v>
       </c>
       <c r="K734" s="9" t="s">
-        <v>3916</v>
+        <v>3914</v>
       </c>
       <c r="L734" s="9" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
       <c r="M734" s="13">
         <v>4000</v>
       </c>
       <c r="N734" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O734" s="13">
         <v>72</v>
@@ -53903,7 +53903,7 @@
         <v>55</v>
       </c>
       <c r="Q734" s="9" t="s">
-        <v>3917</v>
+        <v>3915</v>
       </c>
       <c r="R734" s="9"/>
       <c r="S734" s="9"/>
@@ -53917,16 +53917,16 @@
         <v>2528</v>
       </c>
       <c r="C735" s="9" t="s">
+        <v>3916</v>
+      </c>
+      <c r="D735" s="9" t="s">
+        <v>3917</v>
+      </c>
+      <c r="E735" s="10" t="s">
+        <v>3902</v>
+      </c>
+      <c r="F735" s="9" t="s">
         <v>3918</v>
-      </c>
-      <c r="D735" s="9" t="s">
-        <v>3919</v>
-      </c>
-      <c r="E735" s="10" t="s">
-        <v>3904</v>
-      </c>
-      <c r="F735" s="9" t="s">
-        <v>3920</v>
       </c>
       <c r="G735" s="9"/>
       <c r="H735" s="11">
@@ -53939,16 +53939,16 @@
         <v>2</v>
       </c>
       <c r="K735" s="9" t="s">
-        <v>3921</v>
+        <v>3919</v>
       </c>
       <c r="L735" s="9" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
       <c r="M735" s="13">
         <v>5000</v>
       </c>
       <c r="N735" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O735" s="13">
         <v>85</v>
@@ -53957,7 +53957,7 @@
         <v>60</v>
       </c>
       <c r="Q735" s="9" t="s">
-        <v>3922</v>
+        <v>3920</v>
       </c>
       <c r="R735" s="9"/>
       <c r="S735" s="9"/>
@@ -53965,22 +53965,22 @@
     </row>
     <row r="736" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="9" t="s">
-        <v>3923</v>
+        <v>3921</v>
       </c>
       <c r="B736" s="9" t="s">
         <v>2764</v>
       </c>
       <c r="C736" s="9" t="s">
+        <v>3922</v>
+      </c>
+      <c r="D736" s="9" t="s">
+        <v>3923</v>
+      </c>
+      <c r="E736" s="10" t="s">
+        <v>3902</v>
+      </c>
+      <c r="F736" s="9" t="s">
         <v>3924</v>
-      </c>
-      <c r="D736" s="9" t="s">
-        <v>3925</v>
-      </c>
-      <c r="E736" s="10" t="s">
-        <v>3904</v>
-      </c>
-      <c r="F736" s="9" t="s">
-        <v>3926</v>
       </c>
       <c r="G736" s="9"/>
       <c r="H736" s="11">
@@ -53993,16 +53993,16 @@
         <v>2</v>
       </c>
       <c r="K736" s="9" t="s">
-        <v>3906</v>
+        <v>3904</v>
       </c>
       <c r="L736" s="9" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
       <c r="M736" s="13">
         <v>4000</v>
       </c>
       <c r="N736" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O736" s="13">
         <v>80</v>
@@ -54011,7 +54011,7 @@
         <v>60</v>
       </c>
       <c r="Q736" s="9" t="s">
-        <v>3927</v>
+        <v>3925</v>
       </c>
       <c r="R736" s="9"/>
       <c r="S736" s="9"/>
@@ -54025,16 +54025,16 @@
         <v>335</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>3928</v>
+        <v>3926</v>
       </c>
       <c r="D737" s="2" t="s">
-        <v>3929</v>
+        <v>3927</v>
       </c>
       <c r="E737" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F737" s="2" t="s">
-        <v>3930</v>
+        <v>3928</v>
       </c>
       <c r="G737" s="2"/>
       <c r="H737" s="4">
@@ -54047,16 +54047,16 @@
         <v>1</v>
       </c>
       <c r="K737" s="2" t="s">
-        <v>3931</v>
+        <v>3929</v>
       </c>
       <c r="L737" s="2" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="M737" s="6">
         <v>4000</v>
       </c>
       <c r="N737" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O737" s="6">
         <v>95</v>
@@ -54065,7 +54065,7 @@
         <v>65</v>
       </c>
       <c r="Q737" s="2" t="s">
-        <v>3933</v>
+        <v>3931</v>
       </c>
       <c r="R737" s="2"/>
       <c r="S737" s="2"/>
@@ -54079,16 +54079,16 @@
         <v>1927</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>3934</v>
+        <v>3932</v>
       </c>
       <c r="D738" s="2" t="s">
-        <v>3935</v>
+        <v>3933</v>
       </c>
       <c r="E738" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F738" s="2" t="s">
-        <v>3936</v>
+        <v>3934</v>
       </c>
       <c r="G738" s="2"/>
       <c r="H738" s="4">
@@ -54101,16 +54101,16 @@
         <v>1</v>
       </c>
       <c r="K738" s="2" t="s">
-        <v>3937</v>
+        <v>3935</v>
       </c>
       <c r="L738" s="2" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="M738" s="6">
         <v>3500</v>
       </c>
       <c r="N738" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O738" s="6">
         <v>92</v>
@@ -54119,7 +54119,7 @@
         <v>65</v>
       </c>
       <c r="Q738" s="2" t="s">
-        <v>3938</v>
+        <v>3936</v>
       </c>
       <c r="R738" s="2"/>
       <c r="S738" s="2"/>
@@ -54133,16 +54133,16 @@
         <v>894</v>
       </c>
       <c r="C739" s="9" t="s">
-        <v>3939</v>
+        <v>3937</v>
       </c>
       <c r="D739" s="9" t="s">
-        <v>3940</v>
+        <v>3938</v>
       </c>
       <c r="E739" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F739" s="9" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
       <c r="G739" s="9"/>
       <c r="H739" s="11">
@@ -54155,16 +54155,16 @@
         <v>2</v>
       </c>
       <c r="K739" s="9" t="s">
-        <v>3942</v>
+        <v>3940</v>
       </c>
       <c r="L739" s="9" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="M739" s="13">
         <v>5000</v>
       </c>
       <c r="N739" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O739" s="13">
         <v>82</v>
@@ -54173,7 +54173,7 @@
         <v>60</v>
       </c>
       <c r="Q739" s="9" t="s">
-        <v>3943</v>
+        <v>3941</v>
       </c>
       <c r="R739" s="9"/>
       <c r="S739" s="9"/>
@@ -54187,16 +54187,16 @@
         <v>1317</v>
       </c>
       <c r="C740" s="9" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
       <c r="D740" s="9" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
       <c r="E740" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F740" s="9" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
       <c r="G740" s="9"/>
       <c r="H740" s="11">
@@ -54209,16 +54209,16 @@
         <v>2</v>
       </c>
       <c r="K740" s="9" t="s">
-        <v>3947</v>
+        <v>3945</v>
       </c>
       <c r="L740" s="9" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="M740" s="13">
         <v>4000</v>
       </c>
       <c r="N740" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O740" s="13">
         <v>75</v>
@@ -54227,7 +54227,7 @@
         <v>55</v>
       </c>
       <c r="Q740" s="9" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
       <c r="R740" s="9"/>
       <c r="S740" s="9"/>
@@ -54241,16 +54241,16 @@
         <v>3131</v>
       </c>
       <c r="C741" s="9" t="s">
-        <v>3949</v>
+        <v>3947</v>
       </c>
       <c r="D741" s="9" t="s">
-        <v>3950</v>
+        <v>3948</v>
       </c>
       <c r="E741" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F741" s="9" t="s">
-        <v>3951</v>
+        <v>3949</v>
       </c>
       <c r="G741" s="9"/>
       <c r="H741" s="11">
@@ -54263,16 +54263,16 @@
         <v>2</v>
       </c>
       <c r="K741" s="9" t="s">
-        <v>3952</v>
+        <v>3950</v>
       </c>
       <c r="L741" s="9" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="M741" s="13">
         <v>3000</v>
       </c>
       <c r="N741" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O741" s="13">
         <v>72</v>
@@ -54281,7 +54281,7 @@
         <v>50</v>
       </c>
       <c r="Q741" s="9" t="s">
-        <v>3953</v>
+        <v>3951</v>
       </c>
       <c r="R741" s="9"/>
       <c r="S741" s="9"/>
@@ -54295,16 +54295,16 @@
         <v>335</v>
       </c>
       <c r="C742" s="9" t="s">
-        <v>3954</v>
+        <v>3952</v>
       </c>
       <c r="D742" s="9" t="s">
-        <v>3955</v>
+        <v>3953</v>
       </c>
       <c r="E742" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F742" s="9" t="s">
-        <v>3956</v>
+        <v>3954</v>
       </c>
       <c r="G742" s="9"/>
       <c r="H742" s="11">
@@ -54317,16 +54317,16 @@
         <v>2</v>
       </c>
       <c r="K742" s="9" t="s">
-        <v>3957</v>
+        <v>3955</v>
       </c>
       <c r="L742" s="9" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="M742" s="13">
         <v>3000</v>
       </c>
       <c r="N742" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O742" s="13">
         <v>72</v>
@@ -54335,7 +54335,7 @@
         <v>50</v>
       </c>
       <c r="Q742" s="9" t="s">
-        <v>3958</v>
+        <v>3956</v>
       </c>
       <c r="R742" s="9"/>
       <c r="S742" s="9"/>
@@ -54349,16 +54349,16 @@
         <v>2245</v>
       </c>
       <c r="C743" s="9" t="s">
-        <v>3959</v>
+        <v>3957</v>
       </c>
       <c r="D743" s="9" t="s">
-        <v>3960</v>
+        <v>3958</v>
       </c>
       <c r="E743" s="10" t="s">
         <v>355</v>
       </c>
       <c r="F743" s="9" t="s">
-        <v>3961</v>
+        <v>3959</v>
       </c>
       <c r="G743" s="9"/>
       <c r="H743" s="11">
@@ -54371,16 +54371,16 @@
         <v>2</v>
       </c>
       <c r="K743" s="9" t="s">
-        <v>3962</v>
+        <v>3960</v>
       </c>
       <c r="L743" s="9" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
       <c r="M743" s="13">
         <v>3000</v>
       </c>
       <c r="N743" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O743" s="13">
         <v>70</v>
@@ -54389,7 +54389,7 @@
         <v>50</v>
       </c>
       <c r="Q743" s="9" t="s">
-        <v>3963</v>
+        <v>3961</v>
       </c>
       <c r="R743" s="9"/>
       <c r="S743" s="9"/>
@@ -54403,16 +54403,16 @@
         <v>570</v>
       </c>
       <c r="C744" s="9" t="s">
+        <v>3962</v>
+      </c>
+      <c r="D744" s="9" t="s">
+        <v>3963</v>
+      </c>
+      <c r="E744" s="10" t="s">
         <v>3964</v>
       </c>
-      <c r="D744" s="9" t="s">
+      <c r="F744" s="9" t="s">
         <v>3965</v>
-      </c>
-      <c r="E744" s="10" t="s">
-        <v>3966</v>
-      </c>
-      <c r="F744" s="9" t="s">
-        <v>3967</v>
       </c>
       <c r="G744" s="9"/>
       <c r="H744" s="11">
@@ -54425,16 +54425,16 @@
         <v>2</v>
       </c>
       <c r="K744" s="9" t="s">
-        <v>3968</v>
+        <v>3966</v>
       </c>
       <c r="L744" s="9" t="s">
-        <v>3969</v>
+        <v>3967</v>
       </c>
       <c r="M744" s="13">
         <v>2000</v>
       </c>
       <c r="N744" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O744" s="13">
         <v>72</v>
@@ -54443,7 +54443,7 @@
         <v>50</v>
       </c>
       <c r="Q744" s="9" t="s">
-        <v>3970</v>
+        <v>3968</v>
       </c>
       <c r="R744" s="9"/>
       <c r="S744" s="9"/>
@@ -54457,16 +54457,16 @@
         <v>702</v>
       </c>
       <c r="C745" s="9" t="s">
-        <v>3971</v>
+        <v>3969</v>
       </c>
       <c r="D745" s="9" t="s">
-        <v>3972</v>
+        <v>3970</v>
       </c>
       <c r="E745" s="10" t="s">
         <v>964</v>
       </c>
       <c r="F745" s="9" t="s">
-        <v>3973</v>
+        <v>3971</v>
       </c>
       <c r="G745" s="9"/>
       <c r="H745" s="11">
@@ -54479,16 +54479,16 @@
         <v>2</v>
       </c>
       <c r="K745" s="9" t="s">
-        <v>3974</v>
+        <v>3972</v>
       </c>
       <c r="L745" s="9" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
       <c r="M745" s="13">
         <v>2000</v>
       </c>
       <c r="N745" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O745" s="13">
         <v>70</v>
@@ -54497,7 +54497,7 @@
         <v>50</v>
       </c>
       <c r="Q745" s="9" t="s">
-        <v>3975</v>
+        <v>3973</v>
       </c>
       <c r="R745" s="9"/>
       <c r="S745" s="9"/>
@@ -54511,16 +54511,16 @@
         <v>1521</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>3976</v>
+        <v>3974</v>
       </c>
       <c r="D746" s="2" t="s">
-        <v>3977</v>
+        <v>3975</v>
       </c>
       <c r="E746" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F746" s="2" t="s">
-        <v>3978</v>
+        <v>3976</v>
       </c>
       <c r="G746" s="2"/>
       <c r="H746" s="4">
@@ -54533,16 +54533,16 @@
         <v>1</v>
       </c>
       <c r="K746" s="2" t="s">
-        <v>3979</v>
+        <v>3977</v>
       </c>
       <c r="L746" s="2" t="s">
-        <v>3980</v>
+        <v>3978</v>
       </c>
       <c r="M746" s="6">
         <v>2000</v>
       </c>
       <c r="N746" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O746" s="6">
         <v>95</v>
@@ -54551,7 +54551,7 @@
         <v>60</v>
       </c>
       <c r="Q746" s="2" t="s">
-        <v>3981</v>
+        <v>3979</v>
       </c>
       <c r="R746" s="2"/>
       <c r="S746" s="2"/>
@@ -54565,16 +54565,16 @@
         <v>2434</v>
       </c>
       <c r="C747" s="9" t="s">
+        <v>3980</v>
+      </c>
+      <c r="D747" s="9" t="s">
+        <v>3981</v>
+      </c>
+      <c r="E747" s="10" t="s">
         <v>3982</v>
       </c>
-      <c r="D747" s="9" t="s">
+      <c r="F747" s="9" t="s">
         <v>3983</v>
-      </c>
-      <c r="E747" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F747" s="9" t="s">
-        <v>3985</v>
       </c>
       <c r="G747" s="9"/>
       <c r="H747" s="11">
@@ -54587,16 +54587,16 @@
         <v>2</v>
       </c>
       <c r="K747" s="9" t="s">
-        <v>3986</v>
+        <v>3984</v>
       </c>
       <c r="L747" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M747" s="13">
         <v>3000</v>
       </c>
       <c r="N747" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O747" s="13">
         <v>72</v>
@@ -54605,7 +54605,7 @@
         <v>50</v>
       </c>
       <c r="Q747" s="9" t="s">
-        <v>3988</v>
+        <v>3986</v>
       </c>
       <c r="R747" s="9"/>
       <c r="S747" s="9"/>
@@ -54619,16 +54619,16 @@
         <v>415</v>
       </c>
       <c r="C748" s="9" t="s">
+        <v>3987</v>
+      </c>
+      <c r="D748" s="9" t="s">
+        <v>3988</v>
+      </c>
+      <c r="E748" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F748" s="9" t="s">
         <v>3989</v>
-      </c>
-      <c r="D748" s="9" t="s">
-        <v>3990</v>
-      </c>
-      <c r="E748" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F748" s="9" t="s">
-        <v>3991</v>
       </c>
       <c r="G748" s="9"/>
       <c r="H748" s="11">
@@ -54641,16 +54641,16 @@
         <v>2</v>
       </c>
       <c r="K748" s="9" t="s">
-        <v>3992</v>
+        <v>3990</v>
       </c>
       <c r="L748" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M748" s="13">
         <v>3000</v>
       </c>
       <c r="N748" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O748" s="13">
         <v>70</v>
@@ -54659,7 +54659,7 @@
         <v>50</v>
       </c>
       <c r="Q748" s="9" t="s">
-        <v>3993</v>
+        <v>3991</v>
       </c>
       <c r="R748" s="9"/>
       <c r="S748" s="9"/>
@@ -54667,22 +54667,22 @@
     </row>
     <row r="749" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="9" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="B749" s="9" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="C749" s="9" t="s">
-        <v>3994</v>
+        <v>3992</v>
       </c>
       <c r="D749" s="9" t="s">
-        <v>3995</v>
+        <v>3993</v>
       </c>
       <c r="E749" s="10" t="s">
         <v>830</v>
       </c>
       <c r="F749" s="9" t="s">
-        <v>3996</v>
+        <v>3994</v>
       </c>
       <c r="G749" s="9"/>
       <c r="H749" s="11">
@@ -54695,16 +54695,16 @@
         <v>2</v>
       </c>
       <c r="K749" s="9" t="s">
-        <v>3997</v>
+        <v>3995</v>
       </c>
       <c r="L749" s="9" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
       <c r="M749" s="13">
         <v>4000</v>
       </c>
       <c r="N749" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O749" s="13">
         <v>80</v>
@@ -54713,7 +54713,7 @@
         <v>60</v>
       </c>
       <c r="Q749" s="9" t="s">
-        <v>3999</v>
+        <v>3997</v>
       </c>
       <c r="R749" s="9"/>
       <c r="S749" s="9"/>
@@ -54727,16 +54727,16 @@
         <v>20</v>
       </c>
       <c r="C750" s="9" t="s">
+        <v>3998</v>
+      </c>
+      <c r="D750" s="9" t="s">
+        <v>3999</v>
+      </c>
+      <c r="E750" s="10" t="s">
         <v>4000</v>
       </c>
-      <c r="D750" s="9" t="s">
+      <c r="F750" s="9" t="s">
         <v>4001</v>
-      </c>
-      <c r="E750" s="10" t="s">
-        <v>4002</v>
-      </c>
-      <c r="F750" s="9" t="s">
-        <v>4003</v>
       </c>
       <c r="G750" s="9"/>
       <c r="H750" s="11">
@@ -54749,16 +54749,16 @@
         <v>2</v>
       </c>
       <c r="K750" s="9" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="L750" s="9" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="M750" s="13">
         <v>4000</v>
       </c>
       <c r="N750" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O750" s="13">
         <v>80</v>
@@ -54767,7 +54767,7 @@
         <v>55</v>
       </c>
       <c r="Q750" s="9" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="R750" s="9"/>
       <c r="S750" s="9"/>
@@ -54775,22 +54775,22 @@
     </row>
     <row r="751" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B751" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C751" s="9" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="D751" s="9" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="E751" s="10" t="s">
         <v>2172</v>
       </c>
       <c r="F751" s="9" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="G751" s="9"/>
       <c r="H751" s="11">
@@ -54803,16 +54803,16 @@
         <v>2</v>
       </c>
       <c r="K751" s="9" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="L751" s="9" t="s">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="M751" s="13">
         <v>5000</v>
       </c>
       <c r="N751" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O751" s="13">
         <v>75</v>
@@ -54821,7 +54821,7 @@
         <v>55</v>
       </c>
       <c r="Q751" s="9" t="s">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="R751" s="9"/>
       <c r="S751" s="9"/>
@@ -54835,16 +54835,16 @@
         <v>207</v>
       </c>
       <c r="C752" s="9" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="D752" s="9" t="s">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="E752" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F752" s="9" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="G752" s="9"/>
       <c r="H752" s="11">
@@ -54857,16 +54857,16 @@
         <v>2</v>
       </c>
       <c r="K752" s="9" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="L752" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M752" s="13">
         <v>4000</v>
       </c>
       <c r="N752" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O752" s="13">
         <v>72</v>
@@ -54875,7 +54875,7 @@
         <v>55</v>
       </c>
       <c r="Q752" s="9" t="s">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="R752" s="9"/>
       <c r="S752" s="9"/>
@@ -54889,16 +54889,16 @@
         <v>894</v>
       </c>
       <c r="C753" s="9" t="s">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="D753" s="9" t="s">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="E753" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F753" s="9" t="s">
-        <v>4020</v>
+        <v>4018</v>
       </c>
       <c r="G753" s="9"/>
       <c r="H753" s="11">
@@ -54911,16 +54911,16 @@
         <v>2</v>
       </c>
       <c r="K753" s="9" t="s">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="L753" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M753" s="13">
         <v>3000</v>
       </c>
       <c r="N753" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O753" s="13">
         <v>75</v>
@@ -54929,7 +54929,7 @@
         <v>55</v>
       </c>
       <c r="Q753" s="9" t="s">
-        <v>4022</v>
+        <v>4020</v>
       </c>
       <c r="R753" s="9"/>
       <c r="S753" s="9"/>
@@ -54937,22 +54937,22 @@
     </row>
     <row r="754" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B754" s="9" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C754" s="9" t="s">
+        <v>4021</v>
+      </c>
+      <c r="D754" s="9" t="s">
+        <v>4022</v>
+      </c>
+      <c r="E754" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F754" s="9" t="s">
         <v>4023</v>
-      </c>
-      <c r="D754" s="9" t="s">
-        <v>4024</v>
-      </c>
-      <c r="E754" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F754" s="9" t="s">
-        <v>4025</v>
       </c>
       <c r="G754" s="9"/>
       <c r="H754" s="11">
@@ -54965,16 +54965,16 @@
         <v>2</v>
       </c>
       <c r="K754" s="9" t="s">
-        <v>4026</v>
+        <v>4024</v>
       </c>
       <c r="L754" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M754" s="13">
         <v>2000</v>
       </c>
       <c r="N754" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O754" s="13">
         <v>70</v>
@@ -54983,7 +54983,7 @@
         <v>50</v>
       </c>
       <c r="Q754" s="9" t="s">
-        <v>4027</v>
+        <v>4025</v>
       </c>
       <c r="R754" s="9"/>
       <c r="S754" s="9"/>
@@ -54997,16 +54997,16 @@
         <v>1070</v>
       </c>
       <c r="C755" s="9" t="s">
-        <v>4028</v>
+        <v>4026</v>
       </c>
       <c r="D755" s="9" t="s">
-        <v>4029</v>
+        <v>4027</v>
       </c>
       <c r="E755" s="10" t="s">
         <v>1120</v>
       </c>
       <c r="F755" s="9" t="s">
-        <v>4030</v>
+        <v>4028</v>
       </c>
       <c r="G755" s="9"/>
       <c r="H755" s="11">
@@ -55019,7 +55019,7 @@
         <v>2</v>
       </c>
       <c r="K755" s="9" t="s">
-        <v>4031</v>
+        <v>4029</v>
       </c>
       <c r="L755" s="9" t="s">
         <v>1122</v>
@@ -55028,7 +55028,7 @@
         <v>2000</v>
       </c>
       <c r="N755" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O755" s="13">
         <v>68</v>
@@ -55037,7 +55037,7 @@
         <v>50</v>
       </c>
       <c r="Q755" s="9" t="s">
-        <v>4032</v>
+        <v>4030</v>
       </c>
       <c r="R755" s="9"/>
       <c r="S755" s="9"/>
@@ -55051,16 +55051,16 @@
         <v>2958</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>4033</v>
+        <v>4031</v>
       </c>
       <c r="D756" s="2" t="s">
-        <v>4034</v>
+        <v>4032</v>
       </c>
       <c r="E756" s="3" t="s">
         <v>1120</v>
       </c>
       <c r="F756" s="2" t="s">
-        <v>4035</v>
+        <v>4033</v>
       </c>
       <c r="G756" s="2"/>
       <c r="H756" s="4">
@@ -55073,7 +55073,7 @@
         <v>1</v>
       </c>
       <c r="K756" s="2" t="s">
-        <v>4036</v>
+        <v>4034</v>
       </c>
       <c r="L756" s="2" t="s">
         <v>1122</v>
@@ -55082,7 +55082,7 @@
         <v>2500</v>
       </c>
       <c r="N756" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O756" s="6">
         <v>95</v>
@@ -55091,7 +55091,7 @@
         <v>60</v>
       </c>
       <c r="Q756" s="2" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
       <c r="R756" s="2"/>
       <c r="S756" s="2"/>
@@ -55105,16 +55105,16 @@
         <v>782</v>
       </c>
       <c r="C757" s="9" t="s">
-        <v>4038</v>
+        <v>4036</v>
       </c>
       <c r="D757" s="9" t="s">
-        <v>4039</v>
+        <v>4037</v>
       </c>
       <c r="E757" s="10" t="s">
         <v>1100</v>
       </c>
       <c r="F757" s="9" t="s">
-        <v>4040</v>
+        <v>4038</v>
       </c>
       <c r="G757" s="9"/>
       <c r="H757" s="11">
@@ -55127,16 +55127,16 @@
         <v>2</v>
       </c>
       <c r="K757" s="9" t="s">
-        <v>4041</v>
+        <v>4039</v>
       </c>
       <c r="L757" s="9" t="s">
-        <v>4042</v>
+        <v>4040</v>
       </c>
       <c r="M757" s="13">
         <v>3000</v>
       </c>
       <c r="N757" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O757" s="13">
         <v>78</v>
@@ -55145,7 +55145,7 @@
         <v>55</v>
       </c>
       <c r="Q757" s="9" t="s">
-        <v>4043</v>
+        <v>4041</v>
       </c>
       <c r="R757" s="9"/>
       <c r="S757" s="9"/>
@@ -55159,16 +55159,16 @@
         <v>3296</v>
       </c>
       <c r="C758" s="9" t="s">
-        <v>4044</v>
+        <v>4042</v>
       </c>
       <c r="D758" s="9" t="s">
-        <v>4045</v>
+        <v>4043</v>
       </c>
       <c r="E758" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F758" s="9" t="s">
-        <v>4046</v>
+        <v>4044</v>
       </c>
       <c r="G758" s="9"/>
       <c r="H758" s="11">
@@ -55181,16 +55181,16 @@
         <v>2</v>
       </c>
       <c r="K758" s="9" t="s">
-        <v>4047</v>
+        <v>4045</v>
       </c>
       <c r="L758" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M758" s="13">
         <v>2500</v>
       </c>
       <c r="N758" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O758" s="13">
         <v>65</v>
@@ -55199,7 +55199,7 @@
         <v>50</v>
       </c>
       <c r="Q758" s="9" t="s">
-        <v>4048</v>
+        <v>4046</v>
       </c>
       <c r="R758" s="9"/>
       <c r="S758" s="9"/>
@@ -55207,22 +55207,22 @@
     </row>
     <row r="759" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="9" t="s">
-        <v>3923</v>
+        <v>3921</v>
       </c>
       <c r="B759" s="9" t="s">
         <v>2764</v>
       </c>
       <c r="C759" s="9" t="s">
-        <v>4049</v>
+        <v>4047</v>
       </c>
       <c r="D759" s="9" t="s">
-        <v>4050</v>
+        <v>4048</v>
       </c>
       <c r="E759" s="10" t="s">
         <v>857</v>
       </c>
       <c r="F759" s="9" t="s">
-        <v>4051</v>
+        <v>4049</v>
       </c>
       <c r="G759" s="9"/>
       <c r="H759" s="11">
@@ -55235,16 +55235,16 @@
         <v>2</v>
       </c>
       <c r="K759" s="9" t="s">
-        <v>4052</v>
+        <v>4050</v>
       </c>
       <c r="L759" s="9" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="M759" s="13">
         <v>3000</v>
       </c>
       <c r="N759" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O759" s="13">
         <v>68</v>
@@ -55253,7 +55253,7 @@
         <v>50</v>
       </c>
       <c r="Q759" s="9" t="s">
-        <v>4053</v>
+        <v>4051</v>
       </c>
       <c r="R759" s="9"/>
       <c r="S759" s="9"/>
@@ -55267,16 +55267,16 @@
         <v>3365</v>
       </c>
       <c r="C760" s="2" t="s">
+        <v>4052</v>
+      </c>
+      <c r="D760" s="2" t="s">
+        <v>4053</v>
+      </c>
+      <c r="E760" s="3" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F760" s="2" t="s">
         <v>4054</v>
-      </c>
-      <c r="D760" s="2" t="s">
-        <v>4055</v>
-      </c>
-      <c r="E760" s="3" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F760" s="2" t="s">
-        <v>4056</v>
       </c>
       <c r="G760" s="2"/>
       <c r="H760" s="4">
@@ -55289,16 +55289,16 @@
         <v>1</v>
       </c>
       <c r="K760" s="2" t="s">
-        <v>4057</v>
+        <v>4055</v>
       </c>
       <c r="L760" s="2" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M760" s="6">
         <v>8000</v>
       </c>
       <c r="N760" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O760" s="6">
         <v>98</v>
@@ -55307,7 +55307,7 @@
         <v>65</v>
       </c>
       <c r="Q760" s="2" t="s">
-        <v>4058</v>
+        <v>4056</v>
       </c>
       <c r="R760" s="2"/>
       <c r="S760" s="2"/>
@@ -55321,16 +55321,16 @@
         <v>894</v>
       </c>
       <c r="C761" s="2" t="s">
+        <v>4057</v>
+      </c>
+      <c r="D761" s="2" t="s">
+        <v>4058</v>
+      </c>
+      <c r="E761" s="3" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F761" s="2" t="s">
         <v>4059</v>
-      </c>
-      <c r="D761" s="2" t="s">
-        <v>4060</v>
-      </c>
-      <c r="E761" s="3" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F761" s="2" t="s">
-        <v>4061</v>
       </c>
       <c r="G761" s="2"/>
       <c r="H761" s="4">
@@ -55343,16 +55343,16 @@
         <v>1</v>
       </c>
       <c r="K761" s="2" t="s">
-        <v>4057</v>
+        <v>4055</v>
       </c>
       <c r="L761" s="2" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M761" s="6">
         <v>8000</v>
       </c>
       <c r="N761" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O761" s="6">
         <v>97</v>
@@ -55361,7 +55361,7 @@
         <v>65</v>
       </c>
       <c r="Q761" s="2" t="s">
-        <v>4062</v>
+        <v>4060</v>
       </c>
       <c r="R761" s="2"/>
       <c r="S761" s="2"/>
@@ -55375,16 +55375,16 @@
         <v>2343</v>
       </c>
       <c r="C762" s="9" t="s">
+        <v>4061</v>
+      </c>
+      <c r="D762" s="9" t="s">
+        <v>4062</v>
+      </c>
+      <c r="E762" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F762" s="9" t="s">
         <v>4063</v>
-      </c>
-      <c r="D762" s="9" t="s">
-        <v>4064</v>
-      </c>
-      <c r="E762" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F762" s="9" t="s">
-        <v>4065</v>
       </c>
       <c r="G762" s="9"/>
       <c r="H762" s="11">
@@ -55397,16 +55397,16 @@
         <v>2</v>
       </c>
       <c r="K762" s="9" t="s">
-        <v>4066</v>
+        <v>4064</v>
       </c>
       <c r="L762" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M762" s="13">
         <v>6000</v>
       </c>
       <c r="N762" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O762" s="13">
         <v>88</v>
@@ -55415,7 +55415,7 @@
         <v>60</v>
       </c>
       <c r="Q762" s="9" t="s">
-        <v>4067</v>
+        <v>4065</v>
       </c>
       <c r="R762" s="9"/>
       <c r="S762" s="9"/>
@@ -55429,16 +55429,16 @@
         <v>415</v>
       </c>
       <c r="C763" s="9" t="s">
+        <v>4066</v>
+      </c>
+      <c r="D763" s="9" t="s">
+        <v>4067</v>
+      </c>
+      <c r="E763" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F763" s="9" t="s">
         <v>4068</v>
-      </c>
-      <c r="D763" s="9" t="s">
-        <v>4069</v>
-      </c>
-      <c r="E763" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F763" s="9" t="s">
-        <v>4070</v>
       </c>
       <c r="G763" s="9"/>
       <c r="H763" s="11">
@@ -55451,16 +55451,16 @@
         <v>2</v>
       </c>
       <c r="K763" s="9" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="L763" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M763" s="13">
         <v>5000</v>
       </c>
       <c r="N763" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O763" s="13">
         <v>80</v>
@@ -55469,7 +55469,7 @@
         <v>55</v>
       </c>
       <c r="Q763" s="9" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="R763" s="9"/>
       <c r="S763" s="9"/>
@@ -55477,22 +55477,22 @@
     </row>
     <row r="764" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B764" s="9" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C764" s="9" t="s">
+        <v>4071</v>
+      </c>
+      <c r="D764" s="9" t="s">
+        <v>4072</v>
+      </c>
+      <c r="E764" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F764" s="9" t="s">
         <v>4073</v>
-      </c>
-      <c r="D764" s="9" t="s">
-        <v>4074</v>
-      </c>
-      <c r="E764" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F764" s="9" t="s">
-        <v>4075</v>
       </c>
       <c r="G764" s="9"/>
       <c r="H764" s="11">
@@ -55505,16 +55505,16 @@
         <v>2</v>
       </c>
       <c r="K764" s="9" t="s">
-        <v>4076</v>
+        <v>4074</v>
       </c>
       <c r="L764" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M764" s="13">
         <v>4000</v>
       </c>
       <c r="N764" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O764" s="13">
         <v>75</v>
@@ -55523,7 +55523,7 @@
         <v>55</v>
       </c>
       <c r="Q764" s="9" t="s">
-        <v>4077</v>
+        <v>4075</v>
       </c>
       <c r="R764" s="9"/>
       <c r="S764" s="9"/>
@@ -55537,16 +55537,16 @@
         <v>600</v>
       </c>
       <c r="C765" s="2" t="s">
+        <v>4076</v>
+      </c>
+      <c r="D765" s="2" t="s">
+        <v>4077</v>
+      </c>
+      <c r="E765" s="3" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F765" s="2" t="s">
         <v>4078</v>
-      </c>
-      <c r="D765" s="2" t="s">
-        <v>4079</v>
-      </c>
-      <c r="E765" s="3" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F765" s="2" t="s">
-        <v>4080</v>
       </c>
       <c r="G765" s="2"/>
       <c r="H765" s="4">
@@ -55559,16 +55559,16 @@
         <v>1</v>
       </c>
       <c r="K765" s="2" t="s">
-        <v>4081</v>
+        <v>4079</v>
       </c>
       <c r="L765" s="2" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M765" s="6">
         <v>4000</v>
       </c>
       <c r="N765" s="34" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O765" s="6">
         <v>92</v>
@@ -55577,7 +55577,7 @@
         <v>60</v>
       </c>
       <c r="Q765" s="2" t="s">
-        <v>4082</v>
+        <v>4080</v>
       </c>
       <c r="R765" s="2"/>
       <c r="S765" s="2"/>
@@ -55591,16 +55591,16 @@
         <v>3365</v>
       </c>
       <c r="C766" s="9" t="s">
+        <v>4081</v>
+      </c>
+      <c r="D766" s="9" t="s">
+        <v>4082</v>
+      </c>
+      <c r="E766" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F766" s="9" t="s">
         <v>4083</v>
-      </c>
-      <c r="D766" s="9" t="s">
-        <v>4084</v>
-      </c>
-      <c r="E766" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F766" s="9" t="s">
-        <v>4085</v>
       </c>
       <c r="G766" s="9"/>
       <c r="H766" s="11">
@@ -55613,16 +55613,16 @@
         <v>2</v>
       </c>
       <c r="K766" s="9" t="s">
-        <v>4086</v>
+        <v>4084</v>
       </c>
       <c r="L766" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M766" s="13">
         <v>4000</v>
       </c>
       <c r="N766" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O766" s="13">
         <v>85</v>
@@ -55631,7 +55631,7 @@
         <v>58</v>
       </c>
       <c r="Q766" s="9" t="s">
-        <v>4087</v>
+        <v>4085</v>
       </c>
       <c r="R766" s="9"/>
       <c r="S766" s="9"/>
@@ -55645,16 +55645,16 @@
         <v>2434</v>
       </c>
       <c r="C767" s="9" t="s">
+        <v>4086</v>
+      </c>
+      <c r="D767" s="9" t="s">
+        <v>4087</v>
+      </c>
+      <c r="E767" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F767" s="9" t="s">
         <v>4088</v>
-      </c>
-      <c r="D767" s="9" t="s">
-        <v>4089</v>
-      </c>
-      <c r="E767" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F767" s="9" t="s">
-        <v>4090</v>
       </c>
       <c r="G767" s="9"/>
       <c r="H767" s="11">
@@ -55667,16 +55667,16 @@
         <v>2</v>
       </c>
       <c r="K767" s="9" t="s">
-        <v>4091</v>
+        <v>4089</v>
       </c>
       <c r="L767" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M767" s="13">
         <v>3000</v>
       </c>
       <c r="N767" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O767" s="13">
         <v>78</v>
@@ -55685,7 +55685,7 @@
         <v>55</v>
       </c>
       <c r="Q767" s="9" t="s">
-        <v>4092</v>
+        <v>4090</v>
       </c>
       <c r="R767" s="9"/>
       <c r="S767" s="9"/>
@@ -55699,16 +55699,16 @@
         <v>894</v>
       </c>
       <c r="C768" s="9" t="s">
+        <v>4091</v>
+      </c>
+      <c r="D768" s="9" t="s">
+        <v>4092</v>
+      </c>
+      <c r="E768" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F768" s="9" t="s">
         <v>4093</v>
-      </c>
-      <c r="D768" s="9" t="s">
-        <v>4094</v>
-      </c>
-      <c r="E768" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F768" s="9" t="s">
-        <v>4095</v>
       </c>
       <c r="G768" s="9"/>
       <c r="H768" s="11">
@@ -55721,16 +55721,16 @@
         <v>2</v>
       </c>
       <c r="K768" s="9" t="s">
-        <v>4096</v>
+        <v>4094</v>
       </c>
       <c r="L768" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M768" s="13">
         <v>3000</v>
       </c>
       <c r="N768" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O768" s="13">
         <v>72</v>
@@ -55739,7 +55739,7 @@
         <v>50</v>
       </c>
       <c r="Q768" s="9" t="s">
-        <v>4097</v>
+        <v>4095</v>
       </c>
       <c r="R768" s="9"/>
       <c r="S768" s="9"/>
@@ -55753,16 +55753,16 @@
         <v>2343</v>
       </c>
       <c r="C769" s="9" t="s">
+        <v>4096</v>
+      </c>
+      <c r="D769" s="9" t="s">
+        <v>4097</v>
+      </c>
+      <c r="E769" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F769" s="9" t="s">
         <v>4098</v>
-      </c>
-      <c r="D769" s="9" t="s">
-        <v>4099</v>
-      </c>
-      <c r="E769" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F769" s="9" t="s">
-        <v>4100</v>
       </c>
       <c r="G769" s="9"/>
       <c r="H769" s="11">
@@ -55775,16 +55775,16 @@
         <v>2</v>
       </c>
       <c r="K769" s="9" t="s">
-        <v>4101</v>
+        <v>4099</v>
       </c>
       <c r="L769" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M769" s="13">
         <v>2500</v>
       </c>
       <c r="N769" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O769" s="13">
         <v>68</v>
@@ -55793,7 +55793,7 @@
         <v>50</v>
       </c>
       <c r="Q769" s="9" t="s">
-        <v>4102</v>
+        <v>4100</v>
       </c>
       <c r="R769" s="9"/>
       <c r="S769" s="9"/>
@@ -55807,16 +55807,16 @@
         <v>1317</v>
       </c>
       <c r="C770" s="9" t="s">
+        <v>4101</v>
+      </c>
+      <c r="D770" s="9" t="s">
+        <v>4102</v>
+      </c>
+      <c r="E770" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F770" s="9" t="s">
         <v>4103</v>
-      </c>
-      <c r="D770" s="9" t="s">
-        <v>4104</v>
-      </c>
-      <c r="E770" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F770" s="9" t="s">
-        <v>4105</v>
       </c>
       <c r="G770" s="9"/>
       <c r="H770" s="11">
@@ -55829,16 +55829,16 @@
         <v>2</v>
       </c>
       <c r="K770" s="9" t="s">
-        <v>4106</v>
+        <v>4104</v>
       </c>
       <c r="L770" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M770" s="13">
         <v>3500</v>
       </c>
       <c r="N770" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O770" s="13">
         <v>72</v>
@@ -55847,7 +55847,7 @@
         <v>52</v>
       </c>
       <c r="Q770" s="9" t="s">
-        <v>4107</v>
+        <v>4105</v>
       </c>
       <c r="R770" s="9"/>
       <c r="S770" s="9"/>
@@ -55855,22 +55855,22 @@
     </row>
     <row r="771" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="9" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="B771" s="9" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C771" s="9" t="s">
+        <v>4106</v>
+      </c>
+      <c r="D771" s="9" t="s">
+        <v>4107</v>
+      </c>
+      <c r="E771" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F771" s="9" t="s">
         <v>4108</v>
-      </c>
-      <c r="D771" s="9" t="s">
-        <v>4109</v>
-      </c>
-      <c r="E771" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F771" s="9" t="s">
-        <v>4110</v>
       </c>
       <c r="G771" s="9"/>
       <c r="H771" s="11">
@@ -55883,16 +55883,16 @@
         <v>2</v>
       </c>
       <c r="K771" s="9" t="s">
-        <v>4111</v>
+        <v>4109</v>
       </c>
       <c r="L771" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M771" s="13">
         <v>3000</v>
       </c>
       <c r="N771" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O771" s="13">
         <v>68</v>
@@ -55901,7 +55901,7 @@
         <v>50</v>
       </c>
       <c r="Q771" s="9" t="s">
-        <v>4112</v>
+        <v>4110</v>
       </c>
       <c r="R771" s="9"/>
       <c r="S771" s="9"/>
@@ -55915,16 +55915,16 @@
         <v>1521</v>
       </c>
       <c r="C772" s="9" t="s">
+        <v>4111</v>
+      </c>
+      <c r="D772" s="9" t="s">
+        <v>4112</v>
+      </c>
+      <c r="E772" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F772" s="9" t="s">
         <v>4113</v>
-      </c>
-      <c r="D772" s="9" t="s">
-        <v>4114</v>
-      </c>
-      <c r="E772" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F772" s="9" t="s">
-        <v>4115</v>
       </c>
       <c r="G772" s="9"/>
       <c r="H772" s="11">
@@ -55937,16 +55937,16 @@
         <v>2</v>
       </c>
       <c r="K772" s="9" t="s">
-        <v>4116</v>
+        <v>4114</v>
       </c>
       <c r="L772" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M772" s="13">
         <v>3000</v>
       </c>
       <c r="N772" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O772" s="13">
         <v>70</v>
@@ -55955,7 +55955,7 @@
         <v>50</v>
       </c>
       <c r="Q772" s="9" t="s">
-        <v>4117</v>
+        <v>4115</v>
       </c>
       <c r="R772" s="9"/>
       <c r="S772" s="9"/>
@@ -55969,16 +55969,16 @@
         <v>495</v>
       </c>
       <c r="C773" s="9" t="s">
+        <v>4116</v>
+      </c>
+      <c r="D773" s="9" t="s">
+        <v>4117</v>
+      </c>
+      <c r="E773" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F773" s="9" t="s">
         <v>4118</v>
-      </c>
-      <c r="D773" s="9" t="s">
-        <v>4119</v>
-      </c>
-      <c r="E773" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F773" s="9" t="s">
-        <v>4120</v>
       </c>
       <c r="G773" s="9"/>
       <c r="H773" s="11">
@@ -55991,16 +55991,16 @@
         <v>2</v>
       </c>
       <c r="K773" s="9" t="s">
-        <v>4121</v>
+        <v>4119</v>
       </c>
       <c r="L773" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M773" s="13">
         <v>2500</v>
       </c>
       <c r="N773" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O773" s="13">
         <v>68</v>
@@ -56009,7 +56009,7 @@
         <v>50</v>
       </c>
       <c r="Q773" s="9" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="R773" s="9"/>
       <c r="S773" s="9"/>
@@ -56017,22 +56017,22 @@
     </row>
     <row r="774" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B774" s="9" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C774" s="9" t="s">
+        <v>4121</v>
+      </c>
+      <c r="D774" s="9" t="s">
+        <v>4122</v>
+      </c>
+      <c r="E774" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F774" s="9" t="s">
         <v>4123</v>
-      </c>
-      <c r="D774" s="9" t="s">
-        <v>4124</v>
-      </c>
-      <c r="E774" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F774" s="9" t="s">
-        <v>4125</v>
       </c>
       <c r="G774" s="9"/>
       <c r="H774" s="11">
@@ -56045,16 +56045,16 @@
         <v>2</v>
       </c>
       <c r="K774" s="9" t="s">
-        <v>4126</v>
+        <v>4124</v>
       </c>
       <c r="L774" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M774" s="13">
         <v>2500</v>
       </c>
       <c r="N774" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O774" s="13">
         <v>65</v>
@@ -56063,7 +56063,7 @@
         <v>48</v>
       </c>
       <c r="Q774" s="9" t="s">
-        <v>4127</v>
+        <v>4125</v>
       </c>
       <c r="R774" s="9"/>
       <c r="S774" s="9"/>
@@ -56077,16 +56077,16 @@
         <v>3212</v>
       </c>
       <c r="C775" s="9" t="s">
+        <v>4126</v>
+      </c>
+      <c r="D775" s="9" t="s">
+        <v>4127</v>
+      </c>
+      <c r="E775" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F775" s="9" t="s">
         <v>4128</v>
-      </c>
-      <c r="D775" s="9" t="s">
-        <v>4129</v>
-      </c>
-      <c r="E775" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F775" s="9" t="s">
-        <v>4130</v>
       </c>
       <c r="G775" s="9"/>
       <c r="H775" s="11">
@@ -56099,16 +56099,16 @@
         <v>2</v>
       </c>
       <c r="K775" s="9" t="s">
-        <v>4131</v>
+        <v>4129</v>
       </c>
       <c r="L775" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M775" s="13">
         <v>2500</v>
       </c>
       <c r="N775" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O775" s="13">
         <v>65</v>
@@ -56117,7 +56117,7 @@
         <v>48</v>
       </c>
       <c r="Q775" s="9" t="s">
-        <v>4132</v>
+        <v>4130</v>
       </c>
       <c r="R775" s="9"/>
       <c r="S775" s="9"/>
@@ -56131,16 +56131,16 @@
         <v>600</v>
       </c>
       <c r="C776" s="9" t="s">
+        <v>4131</v>
+      </c>
+      <c r="D776" s="9" t="s">
+        <v>4132</v>
+      </c>
+      <c r="E776" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F776" s="9" t="s">
         <v>4133</v>
-      </c>
-      <c r="D776" s="9" t="s">
-        <v>4134</v>
-      </c>
-      <c r="E776" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F776" s="9" t="s">
-        <v>4135</v>
       </c>
       <c r="G776" s="9"/>
       <c r="H776" s="11">
@@ -56153,16 +56153,16 @@
         <v>2</v>
       </c>
       <c r="K776" s="9" t="s">
-        <v>4081</v>
+        <v>4079</v>
       </c>
       <c r="L776" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M776" s="13">
         <v>3000</v>
       </c>
       <c r="N776" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O776" s="13">
         <v>68</v>
@@ -56171,7 +56171,7 @@
         <v>50</v>
       </c>
       <c r="Q776" s="9" t="s">
-        <v>4136</v>
+        <v>4134</v>
       </c>
       <c r="R776" s="9"/>
       <c r="S776" s="9"/>
@@ -56185,16 +56185,16 @@
         <v>2245</v>
       </c>
       <c r="C777" s="9" t="s">
+        <v>4135</v>
+      </c>
+      <c r="D777" s="9" t="s">
+        <v>4136</v>
+      </c>
+      <c r="E777" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F777" s="9" t="s">
         <v>4137</v>
-      </c>
-      <c r="D777" s="9" t="s">
-        <v>4138</v>
-      </c>
-      <c r="E777" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F777" s="9" t="s">
-        <v>4139</v>
       </c>
       <c r="G777" s="9"/>
       <c r="H777" s="11">
@@ -56207,16 +56207,16 @@
         <v>2</v>
       </c>
       <c r="K777" s="9" t="s">
-        <v>4140</v>
+        <v>4138</v>
       </c>
       <c r="L777" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M777" s="13">
         <v>5000</v>
       </c>
       <c r="N777" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O777" s="13">
         <v>75</v>
@@ -56225,7 +56225,7 @@
         <v>52</v>
       </c>
       <c r="Q777" s="9" t="s">
-        <v>4141</v>
+        <v>4139</v>
       </c>
       <c r="R777" s="9"/>
       <c r="S777" s="9"/>
@@ -56239,16 +56239,16 @@
         <v>2434</v>
       </c>
       <c r="C778" s="9" t="s">
+        <v>4140</v>
+      </c>
+      <c r="D778" s="9" t="s">
+        <v>4141</v>
+      </c>
+      <c r="E778" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F778" s="9" t="s">
         <v>4142</v>
-      </c>
-      <c r="D778" s="9" t="s">
-        <v>4143</v>
-      </c>
-      <c r="E778" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F778" s="9" t="s">
-        <v>4144</v>
       </c>
       <c r="G778" s="9"/>
       <c r="H778" s="11">
@@ -56261,16 +56261,16 @@
         <v>2</v>
       </c>
       <c r="K778" s="9" t="s">
-        <v>4145</v>
+        <v>4143</v>
       </c>
       <c r="L778" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M778" s="13">
         <v>3500</v>
       </c>
       <c r="N778" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O778" s="13">
         <v>75</v>
@@ -56279,7 +56279,7 @@
         <v>52</v>
       </c>
       <c r="Q778" s="9" t="s">
-        <v>4146</v>
+        <v>4144</v>
       </c>
       <c r="R778" s="9"/>
       <c r="S778" s="9"/>
@@ -56293,16 +56293,16 @@
         <v>125</v>
       </c>
       <c r="C779" s="9" t="s">
+        <v>4145</v>
+      </c>
+      <c r="D779" s="9" t="s">
+        <v>4146</v>
+      </c>
+      <c r="E779" s="10" t="s">
+        <v>3982</v>
+      </c>
+      <c r="F779" s="9" t="s">
         <v>4147</v>
-      </c>
-      <c r="D779" s="9" t="s">
-        <v>4148</v>
-      </c>
-      <c r="E779" s="10" t="s">
-        <v>3984</v>
-      </c>
-      <c r="F779" s="9" t="s">
-        <v>4149</v>
       </c>
       <c r="G779" s="9"/>
       <c r="H779" s="11">
@@ -56315,16 +56315,16 @@
         <v>2</v>
       </c>
       <c r="K779" s="9" t="s">
-        <v>4150</v>
+        <v>4148</v>
       </c>
       <c r="L779" s="9" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
       <c r="M779" s="13">
         <v>6000</v>
       </c>
       <c r="N779" s="35" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="O779" s="13">
         <v>72</v>
@@ -56333,7 +56333,7 @@
         <v>55</v>
       </c>
       <c r="Q779" s="9" t="s">
-        <v>4151</v>
+        <v>4149</v>
       </c>
       <c r="R779" s="9"/>
       <c r="S779" s="9"/>
@@ -56347,10 +56347,10 @@
         <v>287</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>4152</v>
+        <v>4150</v>
       </c>
       <c r="D780" s="2" t="s">
-        <v>4153</v>
+        <v>4151</v>
       </c>
       <c r="E780" s="3" t="s">
         <v>56</v>
@@ -56385,12 +56385,12 @@
         <v>85</v>
       </c>
       <c r="Q780" s="2" t="s">
-        <v>4154</v>
+        <v>4152</v>
       </c>
       <c r="R780" s="2"/>
       <c r="S780" s="2"/>
       <c r="T780" s="2" t="s">
-        <v>4155</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="781" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -56401,10 +56401,10 @@
         <v>287</v>
       </c>
       <c r="C781" s="9" t="s">
-        <v>4156</v>
+        <v>4154</v>
       </c>
       <c r="D781" s="9" t="s">
-        <v>4157</v>
+        <v>4155</v>
       </c>
       <c r="E781" s="10" t="s">
         <v>648</v>
@@ -56421,7 +56421,7 @@
         <v>2</v>
       </c>
       <c r="K781" s="9" t="s">
-        <v>4158</v>
+        <v>4156</v>
       </c>
       <c r="L781" s="9" t="s">
         <v>66</v>
@@ -56439,7 +56439,7 @@
         <v>75</v>
       </c>
       <c r="Q781" s="9" t="s">
-        <v>4159</v>
+        <v>4157</v>
       </c>
       <c r="R781" s="9"/>
       <c r="S781" s="9"/>
@@ -56453,10 +56453,10 @@
         <v>287</v>
       </c>
       <c r="C782" s="9" t="s">
-        <v>4160</v>
+        <v>4158</v>
       </c>
       <c r="D782" s="9" t="s">
-        <v>4161</v>
+        <v>4159</v>
       </c>
       <c r="E782" s="10" t="s">
         <v>1160</v>
@@ -56491,7 +56491,7 @@
         <v>80</v>
       </c>
       <c r="Q782" s="9" t="s">
-        <v>4162</v>
+        <v>4160</v>
       </c>
       <c r="R782" s="9"/>
       <c r="S782" s="9"/>
@@ -56505,13 +56505,13 @@
         <v>287</v>
       </c>
       <c r="C783" s="9" t="s">
+        <v>4161</v>
+      </c>
+      <c r="D783" s="9" t="s">
+        <v>4162</v>
+      </c>
+      <c r="E783" s="10" t="s">
         <v>4163</v>
-      </c>
-      <c r="D783" s="9" t="s">
-        <v>4164</v>
-      </c>
-      <c r="E783" s="10" t="s">
-        <v>4165</v>
       </c>
       <c r="F783" s="9"/>
       <c r="G783" s="9"/>
@@ -56543,7 +56543,7 @@
         <v>75</v>
       </c>
       <c r="Q783" s="9" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="R783" s="9"/>
       <c r="S783" s="9"/>
@@ -56557,10 +56557,10 @@
         <v>287</v>
       </c>
       <c r="C784" s="9" t="s">
-        <v>4167</v>
+        <v>4165</v>
       </c>
       <c r="D784" s="9" t="s">
-        <v>4168</v>
+        <v>4166</v>
       </c>
       <c r="E784" s="10" t="s">
         <v>864</v>
@@ -56595,7 +56595,7 @@
         <v>75</v>
       </c>
       <c r="Q784" s="9" t="s">
-        <v>4169</v>
+        <v>4167</v>
       </c>
       <c r="R784" s="9"/>
       <c r="S784" s="9"/>
@@ -56609,10 +56609,10 @@
         <v>287</v>
       </c>
       <c r="C785" s="9" t="s">
-        <v>4170</v>
+        <v>4168</v>
       </c>
       <c r="D785" s="9" t="s">
-        <v>4171</v>
+        <v>4169</v>
       </c>
       <c r="E785" s="10" t="s">
         <v>40</v>
@@ -56629,10 +56629,10 @@
         <v>2</v>
       </c>
       <c r="K785" s="9" t="s">
-        <v>4172</v>
+        <v>4170</v>
       </c>
       <c r="L785" s="9" t="s">
-        <v>4173</v>
+        <v>4171</v>
       </c>
       <c r="M785" s="13">
         <v>8000</v>
@@ -56647,7 +56647,7 @@
         <v>75</v>
       </c>
       <c r="Q785" s="9" t="s">
-        <v>4174</v>
+        <v>4172</v>
       </c>
       <c r="R785" s="9"/>
       <c r="S785" s="9"/>
@@ -56661,10 +56661,10 @@
         <v>287</v>
       </c>
       <c r="C786" s="17" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
       <c r="D786" s="17" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="E786" s="18" t="s">
         <v>2388</v>
@@ -56681,7 +56681,7 @@
         <v>3</v>
       </c>
       <c r="K786" s="17" t="s">
-        <v>4177</v>
+        <v>4175</v>
       </c>
       <c r="L786" s="17" t="s">
         <v>35</v>
@@ -56699,7 +56699,7 @@
         <v>60</v>
       </c>
       <c r="Q786" s="17" t="s">
-        <v>4178</v>
+        <v>4176</v>
       </c>
       <c r="R786" s="17"/>
       <c r="S786" s="17"/>
@@ -56713,13 +56713,13 @@
         <v>287</v>
       </c>
       <c r="C787" s="17" t="s">
+        <v>4177</v>
+      </c>
+      <c r="D787" s="17" t="s">
+        <v>4178</v>
+      </c>
+      <c r="E787" s="18" t="s">
         <v>4179</v>
-      </c>
-      <c r="D787" s="17" t="s">
-        <v>4180</v>
-      </c>
-      <c r="E787" s="18" t="s">
-        <v>4181</v>
       </c>
       <c r="F787" s="17"/>
       <c r="G787" s="17"/>
@@ -56733,7 +56733,7 @@
         <v>3</v>
       </c>
       <c r="K787" s="17" t="s">
-        <v>4182</v>
+        <v>4180</v>
       </c>
       <c r="L787" s="17" t="s">
         <v>112</v>
@@ -56751,7 +56751,7 @@
         <v>60</v>
       </c>
       <c r="Q787" s="17" t="s">
-        <v>4183</v>
+        <v>4181</v>
       </c>
       <c r="R787" s="17"/>
       <c r="S787" s="17"/>
@@ -56765,10 +56765,10 @@
         <v>287</v>
       </c>
       <c r="C788" s="17" t="s">
-        <v>4184</v>
+        <v>4182</v>
       </c>
       <c r="D788" s="17" t="s">
-        <v>4185</v>
+        <v>4183</v>
       </c>
       <c r="E788" s="18" t="s">
         <v>301</v>
@@ -56785,7 +56785,7 @@
         <v>3</v>
       </c>
       <c r="K788" s="17" t="s">
-        <v>4186</v>
+        <v>4184</v>
       </c>
       <c r="L788" s="17" t="s">
         <v>3369</v>
@@ -56803,7 +56803,7 @@
         <v>60</v>
       </c>
       <c r="Q788" s="17" t="s">
-        <v>4187</v>
+        <v>4185</v>
       </c>
       <c r="R788" s="17"/>
       <c r="S788" s="17"/>
@@ -56817,10 +56817,10 @@
         <v>570</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>4188</v>
+        <v>4186</v>
       </c>
       <c r="D789" s="2" t="s">
-        <v>4189</v>
+        <v>4187</v>
       </c>
       <c r="E789" s="3" t="s">
         <v>23</v>
@@ -56855,12 +56855,12 @@
         <v>85</v>
       </c>
       <c r="Q789" s="2" t="s">
-        <v>4190</v>
+        <v>4188</v>
       </c>
       <c r="R789" s="2"/>
       <c r="S789" s="2"/>
       <c r="T789" s="2" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="790" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -56871,10 +56871,10 @@
         <v>570</v>
       </c>
       <c r="C790" s="9" t="s">
-        <v>4192</v>
+        <v>4190</v>
       </c>
       <c r="D790" s="9" t="s">
-        <v>4193</v>
+        <v>4191</v>
       </c>
       <c r="E790" s="10" t="s">
         <v>1120</v>
@@ -56891,7 +56891,7 @@
         <v>2</v>
       </c>
       <c r="K790" s="9" t="s">
-        <v>4194</v>
+        <v>4192</v>
       </c>
       <c r="L790" s="9" t="s">
         <v>100</v>
@@ -56909,7 +56909,7 @@
         <v>80</v>
       </c>
       <c r="Q790" s="9" t="s">
-        <v>4195</v>
+        <v>4193</v>
       </c>
       <c r="R790" s="9"/>
       <c r="S790" s="9"/>
@@ -56923,10 +56923,10 @@
         <v>570</v>
       </c>
       <c r="C791" s="9" t="s">
-        <v>4196</v>
+        <v>4194</v>
       </c>
       <c r="D791" s="9" t="s">
-        <v>4197</v>
+        <v>4195</v>
       </c>
       <c r="E791" s="10" t="s">
         <v>63</v>
@@ -56961,7 +56961,7 @@
         <v>80</v>
       </c>
       <c r="Q791" s="9" t="s">
-        <v>4198</v>
+        <v>4196</v>
       </c>
       <c r="R791" s="9"/>
       <c r="S791" s="9"/>
@@ -56975,13 +56975,13 @@
         <v>570</v>
       </c>
       <c r="C792" s="9" t="s">
+        <v>4197</v>
+      </c>
+      <c r="D792" s="9" t="s">
+        <v>4198</v>
+      </c>
+      <c r="E792" s="10" t="s">
         <v>4199</v>
-      </c>
-      <c r="D792" s="9" t="s">
-        <v>4200</v>
-      </c>
-      <c r="E792" s="10" t="s">
-        <v>4201</v>
       </c>
       <c r="F792" s="9"/>
       <c r="G792" s="9"/>
@@ -57013,7 +57013,7 @@
         <v>75</v>
       </c>
       <c r="Q792" s="9" t="s">
-        <v>4202</v>
+        <v>4200</v>
       </c>
       <c r="R792" s="9"/>
       <c r="S792" s="9"/>
@@ -57027,13 +57027,13 @@
         <v>570</v>
       </c>
       <c r="C793" s="9" t="s">
+        <v>4201</v>
+      </c>
+      <c r="D793" s="9" t="s">
+        <v>4202</v>
+      </c>
+      <c r="E793" s="10" t="s">
         <v>4203</v>
-      </c>
-      <c r="D793" s="9" t="s">
-        <v>4204</v>
-      </c>
-      <c r="E793" s="10" t="s">
-        <v>4205</v>
       </c>
       <c r="F793" s="9"/>
       <c r="G793" s="9"/>
@@ -57065,7 +57065,7 @@
         <v>75</v>
       </c>
       <c r="Q793" s="9" t="s">
-        <v>4206</v>
+        <v>4204</v>
       </c>
       <c r="R793" s="9"/>
       <c r="S793" s="9"/>
@@ -57079,13 +57079,13 @@
         <v>570</v>
       </c>
       <c r="C794" s="9" t="s">
+        <v>4205</v>
+      </c>
+      <c r="D794" s="9" t="s">
+        <v>4206</v>
+      </c>
+      <c r="E794" s="10" t="s">
         <v>4207</v>
-      </c>
-      <c r="D794" s="9" t="s">
-        <v>4208</v>
-      </c>
-      <c r="E794" s="10" t="s">
-        <v>4209</v>
       </c>
       <c r="F794" s="9"/>
       <c r="G794" s="9"/>
@@ -57102,7 +57102,7 @@
         <v>382</v>
       </c>
       <c r="L794" s="9" t="s">
-        <v>4210</v>
+        <v>4208</v>
       </c>
       <c r="M794" s="13">
         <v>7000</v>
@@ -57117,12 +57117,12 @@
         <v>75</v>
       </c>
       <c r="Q794" s="9" t="s">
-        <v>4211</v>
+        <v>4209</v>
       </c>
       <c r="R794" s="9"/>
       <c r="S794" s="9"/>
       <c r="T794" s="9" t="s">
-        <v>4212</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="795" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -57133,10 +57133,10 @@
         <v>570</v>
       </c>
       <c r="C795" s="9" t="s">
-        <v>4213</v>
+        <v>4211</v>
       </c>
       <c r="D795" s="9" t="s">
-        <v>4214</v>
+        <v>4212</v>
       </c>
       <c r="E795" s="10" t="s">
         <v>520</v>
@@ -57156,7 +57156,7 @@
         <v>522</v>
       </c>
       <c r="L795" s="9" t="s">
-        <v>4215</v>
+        <v>4213</v>
       </c>
       <c r="M795" s="13">
         <v>8000</v>
@@ -57171,12 +57171,12 @@
         <v>75</v>
       </c>
       <c r="Q795" s="9" t="s">
-        <v>4216</v>
+        <v>4214</v>
       </c>
       <c r="R795" s="9"/>
       <c r="S795" s="9"/>
       <c r="T795" s="9" t="s">
-        <v>4217</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="796" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -57187,10 +57187,10 @@
         <v>570</v>
       </c>
       <c r="C796" s="17" t="s">
-        <v>4218</v>
+        <v>4216</v>
       </c>
       <c r="D796" s="17" t="s">
-        <v>4219</v>
+        <v>4217</v>
       </c>
       <c r="E796" s="18" t="s">
         <v>1986</v>
@@ -57225,7 +57225,7 @@
         <v>60</v>
       </c>
       <c r="Q796" s="17" t="s">
-        <v>4220</v>
+        <v>4218</v>
       </c>
       <c r="R796" s="17"/>
       <c r="S796" s="17"/>
@@ -57239,13 +57239,13 @@
         <v>570</v>
       </c>
       <c r="C797" s="17" t="s">
+        <v>4219</v>
+      </c>
+      <c r="D797" s="17" t="s">
+        <v>4220</v>
+      </c>
+      <c r="E797" s="18" t="s">
         <v>4221</v>
-      </c>
-      <c r="D797" s="17" t="s">
-        <v>4222</v>
-      </c>
-      <c r="E797" s="18" t="s">
-        <v>4223</v>
       </c>
       <c r="F797" s="17"/>
       <c r="G797" s="17"/>
@@ -57259,7 +57259,7 @@
         <v>3</v>
       </c>
       <c r="K797" s="17" t="s">
-        <v>4224</v>
+        <v>4222</v>
       </c>
       <c r="L797" s="17" t="s">
         <v>66</v>
@@ -57277,7 +57277,7 @@
         <v>60</v>
       </c>
       <c r="Q797" s="17" t="s">
-        <v>4225</v>
+        <v>4223</v>
       </c>
       <c r="R797" s="17"/>
       <c r="S797" s="17"/>
@@ -57291,10 +57291,10 @@
         <v>570</v>
       </c>
       <c r="C798" s="17" t="s">
-        <v>4226</v>
+        <v>4224</v>
       </c>
       <c r="D798" s="17" t="s">
-        <v>4227</v>
+        <v>4225</v>
       </c>
       <c r="E798" s="18" t="s">
         <v>418</v>
@@ -57329,7 +57329,7 @@
         <v>60</v>
       </c>
       <c r="Q798" s="17" t="s">
-        <v>4228</v>
+        <v>4226</v>
       </c>
       <c r="R798" s="17"/>
       <c r="S798" s="17"/>
@@ -57343,13 +57343,13 @@
         <v>1242</v>
       </c>
       <c r="C799" s="17" t="s">
+        <v>4227</v>
+      </c>
+      <c r="D799" s="17" t="s">
+        <v>4228</v>
+      </c>
+      <c r="E799" s="18" t="s">
         <v>4229</v>
-      </c>
-      <c r="D799" s="17" t="s">
-        <v>4230</v>
-      </c>
-      <c r="E799" s="18" t="s">
-        <v>4231</v>
       </c>
       <c r="F799" s="17"/>
       <c r="G799" s="17"/>
@@ -57363,10 +57363,10 @@
         <v>3</v>
       </c>
       <c r="K799" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L799" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M799" s="21">
         <v>3000</v>
@@ -57381,10 +57381,10 @@
         <v>120</v>
       </c>
       <c r="Q799" s="17" t="s">
-        <v>4234</v>
+        <v>4232</v>
       </c>
       <c r="R799" s="17" t="s">
-        <v>4235</v>
+        <v>4233</v>
       </c>
       <c r="S799" s="17"/>
       <c r="T799" s="17"/>
@@ -57397,13 +57397,13 @@
         <v>1242</v>
       </c>
       <c r="C800" s="17" t="s">
+        <v>4234</v>
+      </c>
+      <c r="D800" s="17" t="s">
+        <v>4235</v>
+      </c>
+      <c r="E800" s="18" t="s">
         <v>4236</v>
-      </c>
-      <c r="D800" s="17" t="s">
-        <v>4237</v>
-      </c>
-      <c r="E800" s="18" t="s">
-        <v>4238</v>
       </c>
       <c r="F800" s="17"/>
       <c r="G800" s="17"/>
@@ -57417,10 +57417,10 @@
         <v>3</v>
       </c>
       <c r="K800" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L800" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M800" s="21">
         <v>3000</v>
@@ -57435,10 +57435,10 @@
         <v>120</v>
       </c>
       <c r="Q800" s="17" t="s">
-        <v>4239</v>
+        <v>4237</v>
       </c>
       <c r="R800" s="17" t="s">
-        <v>4240</v>
+        <v>4238</v>
       </c>
       <c r="S800" s="17"/>
       <c r="T800" s="17"/>
@@ -57451,13 +57451,13 @@
         <v>2069</v>
       </c>
       <c r="C801" s="17" t="s">
+        <v>4239</v>
+      </c>
+      <c r="D801" s="17" t="s">
+        <v>4240</v>
+      </c>
+      <c r="E801" s="18" t="s">
         <v>4241</v>
-      </c>
-      <c r="D801" s="17" t="s">
-        <v>4242</v>
-      </c>
-      <c r="E801" s="18" t="s">
-        <v>4243</v>
       </c>
       <c r="F801" s="17"/>
       <c r="G801" s="17"/>
@@ -57471,10 +57471,10 @@
         <v>3</v>
       </c>
       <c r="K801" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L801" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M801" s="21">
         <v>3000</v>
@@ -57489,10 +57489,10 @@
         <v>120</v>
       </c>
       <c r="Q801" s="17" t="s">
-        <v>4244</v>
+        <v>4242</v>
       </c>
       <c r="R801" s="17" t="s">
-        <v>4245</v>
+        <v>4243</v>
       </c>
       <c r="S801" s="17"/>
       <c r="T801" s="17"/>
@@ -57505,13 +57505,13 @@
         <v>782</v>
       </c>
       <c r="C802" s="17" t="s">
+        <v>4244</v>
+      </c>
+      <c r="D802" s="17" t="s">
+        <v>4245</v>
+      </c>
+      <c r="E802" s="18" t="s">
         <v>4246</v>
-      </c>
-      <c r="D802" s="17" t="s">
-        <v>4247</v>
-      </c>
-      <c r="E802" s="18" t="s">
-        <v>4248</v>
       </c>
       <c r="F802" s="17"/>
       <c r="G802" s="17"/>
@@ -57525,10 +57525,10 @@
         <v>3</v>
       </c>
       <c r="K802" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L802" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M802" s="21">
         <v>3000</v>
@@ -57543,10 +57543,10 @@
         <v>120</v>
       </c>
       <c r="Q802" s="17" t="s">
-        <v>4249</v>
+        <v>4247</v>
       </c>
       <c r="R802" s="17" t="s">
-        <v>4250</v>
+        <v>4248</v>
       </c>
       <c r="S802" s="17"/>
       <c r="T802" s="17"/>
@@ -57559,13 +57559,13 @@
         <v>1996</v>
       </c>
       <c r="C803" s="17" t="s">
+        <v>4249</v>
+      </c>
+      <c r="D803" s="17" t="s">
+        <v>4250</v>
+      </c>
+      <c r="E803" s="18" t="s">
         <v>4251</v>
-      </c>
-      <c r="D803" s="17" t="s">
-        <v>4252</v>
-      </c>
-      <c r="E803" s="18" t="s">
-        <v>4253</v>
       </c>
       <c r="F803" s="17"/>
       <c r="G803" s="17"/>
@@ -57579,10 +57579,10 @@
         <v>3</v>
       </c>
       <c r="K803" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L803" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M803" s="21">
         <v>3000</v>
@@ -57597,10 +57597,10 @@
         <v>120</v>
       </c>
       <c r="Q803" s="17" t="s">
-        <v>4254</v>
+        <v>4252</v>
       </c>
       <c r="R803" s="17" t="s">
-        <v>4255</v>
+        <v>4253</v>
       </c>
       <c r="S803" s="17"/>
       <c r="T803" s="17"/>
@@ -57613,13 +57613,13 @@
         <v>2764</v>
       </c>
       <c r="C804" s="17" t="s">
+        <v>4254</v>
+      </c>
+      <c r="D804" s="17" t="s">
+        <v>4255</v>
+      </c>
+      <c r="E804" s="18" t="s">
         <v>4256</v>
-      </c>
-      <c r="D804" s="17" t="s">
-        <v>4257</v>
-      </c>
-      <c r="E804" s="18" t="s">
-        <v>4258</v>
       </c>
       <c r="F804" s="17"/>
       <c r="G804" s="17"/>
@@ -57633,10 +57633,10 @@
         <v>3</v>
       </c>
       <c r="K804" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L804" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M804" s="21">
         <v>3000</v>
@@ -57651,10 +57651,10 @@
         <v>120</v>
       </c>
       <c r="Q804" s="17" t="s">
-        <v>4259</v>
+        <v>4257</v>
       </c>
       <c r="R804" s="17" t="s">
-        <v>4260</v>
+        <v>4258</v>
       </c>
       <c r="S804" s="17"/>
       <c r="T804" s="17"/>
@@ -57667,13 +57667,13 @@
         <v>1927</v>
       </c>
       <c r="C805" s="17" t="s">
-        <v>4261</v>
+        <v>4259</v>
       </c>
       <c r="D805" s="17" t="s">
-        <v>4262</v>
+        <v>4260</v>
       </c>
       <c r="E805" s="18" t="s">
-        <v>4181</v>
+        <v>4179</v>
       </c>
       <c r="F805" s="17"/>
       <c r="G805" s="17"/>
@@ -57687,10 +57687,10 @@
         <v>3</v>
       </c>
       <c r="K805" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L805" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M805" s="21">
         <v>3000</v>
@@ -57705,10 +57705,10 @@
         <v>120</v>
       </c>
       <c r="Q805" s="17" t="s">
-        <v>4263</v>
+        <v>4261</v>
       </c>
       <c r="R805" s="17" t="s">
-        <v>4264</v>
+        <v>4262</v>
       </c>
       <c r="S805" s="17"/>
       <c r="T805" s="17"/>
@@ -57721,13 +57721,13 @@
         <v>415</v>
       </c>
       <c r="C806" s="17" t="s">
+        <v>4263</v>
+      </c>
+      <c r="D806" s="17" t="s">
+        <v>4264</v>
+      </c>
+      <c r="E806" s="18" t="s">
         <v>4265</v>
-      </c>
-      <c r="D806" s="17" t="s">
-        <v>4266</v>
-      </c>
-      <c r="E806" s="18" t="s">
-        <v>4267</v>
       </c>
       <c r="F806" s="17"/>
       <c r="G806" s="17"/>
@@ -57741,10 +57741,10 @@
         <v>3</v>
       </c>
       <c r="K806" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L806" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M806" s="21">
         <v>3000</v>
@@ -57759,10 +57759,10 @@
         <v>120</v>
       </c>
       <c r="Q806" s="17" t="s">
-        <v>4268</v>
+        <v>4266</v>
       </c>
       <c r="R806" s="17" t="s">
-        <v>4269</v>
+        <v>4267</v>
       </c>
       <c r="S806" s="17"/>
       <c r="T806" s="17"/>
@@ -57775,13 +57775,13 @@
         <v>2899</v>
       </c>
       <c r="C807" s="17" t="s">
+        <v>4268</v>
+      </c>
+      <c r="D807" s="17" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E807" s="18" t="s">
         <v>4270</v>
-      </c>
-      <c r="D807" s="17" t="s">
-        <v>4271</v>
-      </c>
-      <c r="E807" s="18" t="s">
-        <v>4272</v>
       </c>
       <c r="F807" s="17"/>
       <c r="G807" s="17"/>
@@ -57795,10 +57795,10 @@
         <v>3</v>
       </c>
       <c r="K807" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L807" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M807" s="21">
         <v>3000</v>
@@ -57813,10 +57813,10 @@
         <v>120</v>
       </c>
       <c r="Q807" s="17" t="s">
-        <v>4273</v>
+        <v>4271</v>
       </c>
       <c r="R807" s="17" t="s">
-        <v>4274</v>
+        <v>4272</v>
       </c>
       <c r="S807" s="17"/>
       <c r="T807" s="17"/>
@@ -57829,13 +57829,13 @@
         <v>2838</v>
       </c>
       <c r="C808" s="17" t="s">
-        <v>4275</v>
+        <v>4273</v>
       </c>
       <c r="D808" s="17" t="s">
-        <v>4276</v>
+        <v>4274</v>
       </c>
       <c r="E808" s="18" t="s">
-        <v>4205</v>
+        <v>4203</v>
       </c>
       <c r="F808" s="17"/>
       <c r="G808" s="17"/>
@@ -57849,10 +57849,10 @@
         <v>3</v>
       </c>
       <c r="K808" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L808" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M808" s="21">
         <v>3000</v>
@@ -57867,10 +57867,10 @@
         <v>120</v>
       </c>
       <c r="Q808" s="17" t="s">
-        <v>4277</v>
+        <v>4275</v>
       </c>
       <c r="R808" s="17" t="s">
-        <v>4278</v>
+        <v>4276</v>
       </c>
       <c r="S808" s="17"/>
       <c r="T808" s="17"/>
@@ -57883,13 +57883,13 @@
         <v>1777</v>
       </c>
       <c r="C809" s="17" t="s">
+        <v>4277</v>
+      </c>
+      <c r="D809" s="17" t="s">
+        <v>4278</v>
+      </c>
+      <c r="E809" s="18" t="s">
         <v>4279</v>
-      </c>
-      <c r="D809" s="17" t="s">
-        <v>4280</v>
-      </c>
-      <c r="E809" s="18" t="s">
-        <v>4281</v>
       </c>
       <c r="F809" s="17"/>
       <c r="G809" s="17"/>
@@ -57903,10 +57903,10 @@
         <v>3</v>
       </c>
       <c r="K809" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L809" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M809" s="21">
         <v>3000</v>
@@ -57921,10 +57921,10 @@
         <v>120</v>
       </c>
       <c r="Q809" s="17" t="s">
-        <v>4282</v>
+        <v>4280</v>
       </c>
       <c r="R809" s="17" t="s">
-        <v>4283</v>
+        <v>4281</v>
       </c>
       <c r="S809" s="17"/>
       <c r="T809" s="17"/>
@@ -57937,13 +57937,13 @@
         <v>1317</v>
       </c>
       <c r="C810" s="17" t="s">
+        <v>4282</v>
+      </c>
+      <c r="D810" s="17" t="s">
+        <v>4283</v>
+      </c>
+      <c r="E810" s="18" t="s">
         <v>4284</v>
-      </c>
-      <c r="D810" s="17" t="s">
-        <v>4285</v>
-      </c>
-      <c r="E810" s="18" t="s">
-        <v>4286</v>
       </c>
       <c r="F810" s="17"/>
       <c r="G810" s="17"/>
@@ -57957,10 +57957,10 @@
         <v>3</v>
       </c>
       <c r="K810" s="17" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
       <c r="L810" s="17" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="M810" s="21">
         <v>3000</v>
@@ -57975,10 +57975,10 @@
         <v>120</v>
       </c>
       <c r="Q810" s="17" t="s">
-        <v>4287</v>
+        <v>4285</v>
       </c>
       <c r="R810" s="17" t="s">
-        <v>4288</v>
+        <v>4286</v>
       </c>
       <c r="S810" s="17"/>
       <c r="T810" s="17"/>
@@ -57991,17 +57991,17 @@
         <v>1581</v>
       </c>
       <c r="C811" s="2" t="s">
-        <v>4289</v>
+        <v>4287</v>
       </c>
       <c r="D811" s="2" t="s">
-        <v>4290</v>
+        <v>4288</v>
       </c>
       <c r="E811" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F811" s="2"/>
       <c r="G811" s="2" t="s">
-        <v>4292</v>
+        <v>4290</v>
       </c>
       <c r="H811" s="4">
         <v>41.81</v>
@@ -58013,10 +58013,10 @@
         <v>1</v>
       </c>
       <c r="K811" s="2" t="s">
-        <v>4291</v>
+        <v>4289</v>
       </c>
       <c r="L811" s="2" t="s">
-        <v>4292</v>
+        <v>4290</v>
       </c>
       <c r="M811" s="6">
         <v>6000</v>
@@ -58031,7 +58031,7 @@
         <v>90</v>
       </c>
       <c r="Q811" s="2" t="s">
-        <v>4293</v>
+        <v>4291</v>
       </c>
       <c r="R811" s="2"/>
       <c r="S811" s="2"/>
@@ -58045,10 +58045,10 @@
         <v>1642</v>
       </c>
       <c r="C812" s="9" t="s">
-        <v>4294</v>
+        <v>4292</v>
       </c>
       <c r="D812" s="9" t="s">
-        <v>4295</v>
+        <v>4293</v>
       </c>
       <c r="E812" s="10" t="s">
         <v>418</v>
@@ -58065,7 +58065,7 @@
         <v>2</v>
       </c>
       <c r="K812" s="9" t="s">
-        <v>4291</v>
+        <v>4289</v>
       </c>
       <c r="L812" s="9" t="s">
         <v>421</v>
@@ -58083,7 +58083,7 @@
         <v>75</v>
       </c>
       <c r="Q812" s="9" t="s">
-        <v>4296</v>
+        <v>4294</v>
       </c>
       <c r="R812" s="9"/>
       <c r="S812" s="9"/>
@@ -58097,13 +58097,13 @@
         <v>1927</v>
       </c>
       <c r="C813" s="9" t="s">
+        <v>4295</v>
+      </c>
+      <c r="D813" s="9" t="s">
+        <v>4296</v>
+      </c>
+      <c r="E813" s="10" t="s">
         <v>4297</v>
-      </c>
-      <c r="D813" s="9" t="s">
-        <v>4298</v>
-      </c>
-      <c r="E813" s="10" t="s">
-        <v>4299</v>
       </c>
       <c r="F813" s="9"/>
       <c r="G813" s="9"/>
@@ -58117,7 +58117,7 @@
         <v>2</v>
       </c>
       <c r="K813" s="9" t="s">
-        <v>4291</v>
+        <v>4289</v>
       </c>
       <c r="L813" s="9" t="s">
         <v>421</v>
@@ -58135,7 +58135,7 @@
         <v>75</v>
       </c>
       <c r="Q813" s="9" t="s">
-        <v>4300</v>
+        <v>4298</v>
       </c>
       <c r="R813" s="9"/>
       <c r="S813" s="9"/>
@@ -58149,10 +58149,10 @@
         <v>2528</v>
       </c>
       <c r="C814" s="9" t="s">
-        <v>4301</v>
+        <v>4299</v>
       </c>
       <c r="D814" s="9" t="s">
-        <v>4302</v>
+        <v>4300</v>
       </c>
       <c r="E814" s="10" t="s">
         <v>3378</v>
@@ -58169,7 +58169,7 @@
         <v>2</v>
       </c>
       <c r="K814" s="9" t="s">
-        <v>4303</v>
+        <v>4301</v>
       </c>
       <c r="L814" s="9" t="s">
         <v>421</v>
@@ -58187,7 +58187,7 @@
         <v>75</v>
       </c>
       <c r="Q814" s="9" t="s">
-        <v>4304</v>
+        <v>4302</v>
       </c>
       <c r="R814" s="9"/>
       <c r="S814" s="9"/>
@@ -58201,10 +58201,10 @@
         <v>125</v>
       </c>
       <c r="C815" s="9" t="s">
-        <v>4305</v>
+        <v>4303</v>
       </c>
       <c r="D815" s="9" t="s">
-        <v>4306</v>
+        <v>4304</v>
       </c>
       <c r="E815" s="10" t="s">
         <v>418</v>
@@ -58221,7 +58221,7 @@
         <v>2</v>
       </c>
       <c r="K815" s="9" t="s">
-        <v>4307</v>
+        <v>4305</v>
       </c>
       <c r="L815" s="9" t="s">
         <v>421</v>
@@ -58239,7 +58239,7 @@
         <v>75</v>
       </c>
       <c r="Q815" s="9" t="s">
-        <v>4308</v>
+        <v>4306</v>
       </c>
       <c r="R815" s="9"/>
       <c r="S815" s="9"/>
@@ -58253,13 +58253,13 @@
         <v>2163</v>
       </c>
       <c r="C816" s="9" t="s">
+        <v>4307</v>
+      </c>
+      <c r="D816" s="9" t="s">
+        <v>4308</v>
+      </c>
+      <c r="E816" s="10" t="s">
         <v>4309</v>
-      </c>
-      <c r="D816" s="9" t="s">
-        <v>4310</v>
-      </c>
-      <c r="E816" s="10" t="s">
-        <v>4311</v>
       </c>
       <c r="F816" s="9"/>
       <c r="G816" s="9"/>
@@ -58273,7 +58273,7 @@
         <v>2</v>
       </c>
       <c r="K816" s="9" t="s">
-        <v>4291</v>
+        <v>4289</v>
       </c>
       <c r="L816" s="9" t="s">
         <v>421</v>
@@ -58291,7 +58291,7 @@
         <v>75</v>
       </c>
       <c r="Q816" s="9" t="s">
-        <v>4312</v>
+        <v>4310</v>
       </c>
       <c r="R816" s="9"/>
       <c r="S816" s="9"/>
@@ -58305,10 +58305,10 @@
         <v>2838</v>
       </c>
       <c r="C817" s="9" t="s">
-        <v>4313</v>
+        <v>4311</v>
       </c>
       <c r="D817" s="9" t="s">
-        <v>4314</v>
+        <v>4312</v>
       </c>
       <c r="E817" s="10" t="s">
         <v>63</v>
@@ -58325,7 +58325,7 @@
         <v>2</v>
       </c>
       <c r="K817" s="9" t="s">
-        <v>4315</v>
+        <v>4313</v>
       </c>
       <c r="L817" s="9" t="s">
         <v>421</v>
@@ -58343,7 +58343,7 @@
         <v>75</v>
       </c>
       <c r="Q817" s="9" t="s">
-        <v>4316</v>
+        <v>4314</v>
       </c>
       <c r="R817" s="9"/>
       <c r="S817" s="9"/>
@@ -58357,13 +58357,13 @@
         <v>495</v>
       </c>
       <c r="C818" s="9" t="s">
+        <v>4315</v>
+      </c>
+      <c r="D818" s="9" t="s">
+        <v>4316</v>
+      </c>
+      <c r="E818" s="10" t="s">
         <v>4317</v>
-      </c>
-      <c r="D818" s="9" t="s">
-        <v>4318</v>
-      </c>
-      <c r="E818" s="10" t="s">
-        <v>4319</v>
       </c>
       <c r="F818" s="9"/>
       <c r="G818" s="9"/>
@@ -58377,10 +58377,10 @@
         <v>2</v>
       </c>
       <c r="K818" s="9" t="s">
-        <v>4320</v>
+        <v>4318</v>
       </c>
       <c r="L818" s="9" t="s">
-        <v>4321</v>
+        <v>4319</v>
       </c>
       <c r="M818" s="13">
         <v>4500</v>
@@ -58395,7 +58395,7 @@
         <v>75</v>
       </c>
       <c r="Q818" s="9" t="s">
-        <v>4322</v>
+        <v>4320</v>
       </c>
       <c r="R818" s="9"/>
       <c r="S818" s="9"/>
@@ -58409,13 +58409,13 @@
         <v>600</v>
       </c>
       <c r="C819" s="17" t="s">
+        <v>4321</v>
+      </c>
+      <c r="D819" s="17" t="s">
+        <v>4322</v>
+      </c>
+      <c r="E819" s="18" t="s">
         <v>4323</v>
-      </c>
-      <c r="D819" s="17" t="s">
-        <v>4324</v>
-      </c>
-      <c r="E819" s="18" t="s">
-        <v>4325</v>
       </c>
       <c r="F819" s="17"/>
       <c r="G819" s="17"/>
@@ -58429,10 +58429,10 @@
         <v>3</v>
       </c>
       <c r="K819" s="17" t="s">
-        <v>4326</v>
+        <v>4324</v>
       </c>
       <c r="L819" s="17" t="s">
-        <v>4321</v>
+        <v>4319</v>
       </c>
       <c r="M819" s="21">
         <v>4000</v>
@@ -58447,7 +58447,7 @@
         <v>60</v>
       </c>
       <c r="Q819" s="17" t="s">
-        <v>4327</v>
+        <v>4325</v>
       </c>
       <c r="R819" s="17"/>
       <c r="S819" s="17"/>
@@ -58461,13 +58461,13 @@
         <v>1242</v>
       </c>
       <c r="C820" s="17" t="s">
+        <v>4326</v>
+      </c>
+      <c r="D820" s="17" t="s">
+        <v>4327</v>
+      </c>
+      <c r="E820" s="18" t="s">
         <v>4328</v>
-      </c>
-      <c r="D820" s="17" t="s">
-        <v>4329</v>
-      </c>
-      <c r="E820" s="18" t="s">
-        <v>4330</v>
       </c>
       <c r="F820" s="17"/>
       <c r="G820" s="17"/>
@@ -58481,10 +58481,10 @@
         <v>3</v>
       </c>
       <c r="K820" s="17" t="s">
-        <v>4331</v>
+        <v>4329</v>
       </c>
       <c r="L820" s="17" t="s">
-        <v>4321</v>
+        <v>4319</v>
       </c>
       <c r="M820" s="21">
         <v>4500</v>
@@ -58499,7 +58499,7 @@
         <v>60</v>
       </c>
       <c r="Q820" s="17" t="s">
-        <v>4332</v>
+        <v>4330</v>
       </c>
       <c r="R820" s="17"/>
       <c r="S820" s="17"/>
@@ -58513,10 +58513,10 @@
         <v>2958</v>
       </c>
       <c r="C821" s="17" t="s">
-        <v>4333</v>
+        <v>4331</v>
       </c>
       <c r="D821" s="17" t="s">
-        <v>4334</v>
+        <v>4332</v>
       </c>
       <c r="E821" s="18" t="s">
         <v>301</v>
@@ -58533,10 +58533,10 @@
         <v>3</v>
       </c>
       <c r="K821" s="17" t="s">
-        <v>4326</v>
+        <v>4324</v>
       </c>
       <c r="L821" s="17" t="s">
-        <v>4321</v>
+        <v>4319</v>
       </c>
       <c r="M821" s="21">
         <v>4500</v>
@@ -58551,7 +58551,7 @@
         <v>60</v>
       </c>
       <c r="Q821" s="17" t="s">
-        <v>4335</v>
+        <v>4333</v>
       </c>
       <c r="R821" s="17"/>
       <c r="S821" s="17"/>
@@ -58559,19 +58559,19 @@
     </row>
     <row r="822" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="17" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="B822" s="17" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="C822" s="17" t="s">
+        <v>4334</v>
+      </c>
+      <c r="D822" s="17" t="s">
+        <v>4335</v>
+      </c>
+      <c r="E822" s="18" t="s">
         <v>4336</v>
-      </c>
-      <c r="D822" s="17" t="s">
-        <v>4337</v>
-      </c>
-      <c r="E822" s="18" t="s">
-        <v>4338</v>
       </c>
       <c r="F822" s="17"/>
       <c r="G822" s="17"/>
@@ -58585,10 +58585,10 @@
         <v>3</v>
       </c>
       <c r="K822" s="17" t="s">
-        <v>4326</v>
+        <v>4324</v>
       </c>
       <c r="L822" s="17" t="s">
-        <v>4321</v>
+        <v>4319</v>
       </c>
       <c r="M822" s="21">
         <v>5000</v>
@@ -58603,7 +58603,7 @@
         <v>60</v>
       </c>
       <c r="Q822" s="17" t="s">
-        <v>4339</v>
+        <v>4337</v>
       </c>
       <c r="R822" s="17"/>
       <c r="S822" s="17"/>
@@ -58617,10 +58617,10 @@
         <v>2899</v>
       </c>
       <c r="C823" s="17" t="s">
-        <v>4340</v>
+        <v>4338</v>
       </c>
       <c r="D823" s="17" t="s">
-        <v>4341</v>
+        <v>4339</v>
       </c>
       <c r="E823" s="18" t="s">
         <v>2388</v>
@@ -58637,10 +58637,10 @@
         <v>3</v>
       </c>
       <c r="K823" s="17" t="s">
-        <v>4326</v>
+        <v>4324</v>
       </c>
       <c r="L823" s="17" t="s">
-        <v>4321</v>
+        <v>4319</v>
       </c>
       <c r="M823" s="21">
         <v>4500</v>
@@ -58655,7 +58655,7 @@
         <v>60</v>
       </c>
       <c r="Q823" s="17" t="s">
-        <v>4342</v>
+        <v>4340</v>
       </c>
       <c r="R823" s="17"/>
       <c r="S823" s="17"/>
@@ -58669,10 +58669,10 @@
         <v>2690</v>
       </c>
       <c r="C824" s="17" t="s">
-        <v>4343</v>
+        <v>4341</v>
       </c>
       <c r="D824" s="17" t="s">
-        <v>4344</v>
+        <v>4342</v>
       </c>
       <c r="E824" s="18" t="s">
         <v>830</v>
@@ -58689,10 +58689,10 @@
         <v>3</v>
       </c>
       <c r="K824" s="17" t="s">
-        <v>4326</v>
+        <v>4324</v>
       </c>
       <c r="L824" s="17" t="s">
-        <v>4321</v>
+        <v>4319</v>
       </c>
       <c r="M824" s="21">
         <v>3500</v>
@@ -58707,7 +58707,7 @@
         <v>60</v>
       </c>
       <c r="Q824" s="17" t="s">
-        <v>4345</v>
+        <v>4343</v>
       </c>
       <c r="R824" s="17"/>
       <c r="S824" s="17"/>
@@ -58730,41 +58730,41 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="37" t="s">
-        <v>4346</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
-        <v>4347</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
-        <v>4348</v>
+        <v>4346</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>4349</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
-        <v>4350</v>
+        <v>4348</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>4351</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="42" t="s">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>4353</v>
+        <v>4351</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>4354</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -58772,7 +58772,7 @@
         <v>101</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -58780,23 +58780,23 @@
         <v>36</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="45" t="s">
-        <v>4356</v>
+        <v>4354</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="46" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -58804,15 +58804,15 @@
         <v>1884</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="48" t="s">
-        <v>4357</v>
+        <v>4355</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -58820,7 +58820,7 @@
         <v>992</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -58828,12 +58828,12 @@
         <v>2648</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>4355</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="38" t="s">
-        <v>4358</v>
+        <v>4356</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -58841,7 +58841,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>4359</v>
+        <v>4357</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -58849,7 +58849,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>4360</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -58857,15 +58857,15 @@
         <v>4</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>4361</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="51" t="s">
-        <v>4362</v>
+        <v>4360</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>4363</v>
+        <v>4361</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -58873,7 +58873,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>4364</v>
+        <v>4362</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -58881,7 +58881,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>4365</v>
+        <v>4363</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -58889,7 +58889,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>4366</v>
+        <v>4364</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -58897,7 +58897,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>4367</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -58905,7 +58905,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>4368</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -58913,7 +58913,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>4369</v>
+        <v>4367</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -58921,7 +58921,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>4370</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -58929,7 +58929,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>4371</v>
+        <v>4369</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -58937,30 +58937,30 @@
         <v>18</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>4372</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
-        <v>4373</v>
+        <v>4371</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>4374</v>
+        <v>4372</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="52" t="s">
-        <v>4375</v>
+        <v>4373</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.2">
       <c r="B35" s="53" t="s">
-        <v>4376</v>
+        <v>4374</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B36" s="53" t="s">
-        <v>4377</v>
+        <v>4375</v>
       </c>
     </row>
   </sheetData>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304EBEFA-B427-0849-80A9-7E7F705AA0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46C34B6-08B5-0548-8B22-BA13CE44CCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13907,7 +13907,7 @@
     <col min="4" max="4" width="50" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="30" bestFit="1" customWidth="1"/>
@@ -29311,10 +29311,10 @@
       <c r="F283" s="9"/>
       <c r="G283" s="9"/>
       <c r="H283" s="11">
-        <v>41.2592268</v>
+        <v>4.1259408633897001</v>
       </c>
       <c r="I283" s="11">
-        <v>-3.7534036</v>
+        <v>-3.59157939542433</v>
       </c>
       <c r="J283" s="12">
         <v>2</v>
@@ -29326,7 +29326,7 @@
         <v>4384</v>
       </c>
       <c r="M283" s="13">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N283" s="16" t="s">
         <v>312</v>

--- a/pois.xlsx
+++ b/pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos/Projects/raidio-backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46C34B6-08B5-0548-8B22-BA13CE44CCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE198FA7-6E1C-D54D-AD94-8E982FE22033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29311,7 +29311,7 @@
       <c r="F283" s="9"/>
       <c r="G283" s="9"/>
       <c r="H283" s="11">
-        <v>4.1259408633897001</v>
+        <v>41.259408633897003</v>
       </c>
       <c r="I283" s="11">
         <v>-3.59157939542433</v>
